--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,15 +966,95 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>grid.overlay_radius</t>
+          <t>world.view_radius_chunks</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>建造模式叠加层以核心为中心的半径(格)</t>
+          <t>镜头周围生成与显示的区块半径(区块,切比雪夫),FGR-GEN-050</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>world.pregen_margin_chunks</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>已探索范围外的预生成边距(区块),FGR-GEN-050 初值 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>world.stream.max_inflight</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>同时在工作线程生成的区块上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>world.stream.integrate_budget_ms</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>主线程每帧接入区块的时间预算(毫秒),FG17 第7节单块&lt;=0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>world.stream.max_resident_chunks</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>常驻内存的区块上限;超出时回收离镜头最远的纯地形未修改区块</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>world.coord_limit</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>实际可达范围:离原点最多多少格(FGR-GEN-051 初值 ±1,000,000)</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1058,246 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>clock.sim_step_hz</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>60</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>世界模拟固定步长频率(次/游戏秒);与渲染帧率无关,倍速只改变每帧跑几步,结果与1x一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>clock.max_steps_per_frame</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>单帧最多补跑的模拟步数(防卡顿雪崩);超出部分丢弃=世界短暂变慢,不跳步</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>clock.max_frame_seconds</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>单帧计入的真实时间上限(秒);断点/加载后的超长帧不会一次补跑几十秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>clock.day_seconds</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1个游戏日在1x下的真实秒数(FGR-ENV-001:20分钟;1游戏小时=50秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>clock.start_hour</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>新战役开始时是当天几点(0~23),第1日从这个时刻起算</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>clock.objective_recompute_seconds</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>目标兜底重算间隔(游戏秒,跟随世界模拟步进,观察与否一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sim.activity_refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>活跃区块集合(己方实体/行进中的队伍/被观察)重算间隔(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>camera.fly_seconds</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>镜头飞跃过渡时长(真实秒),FG17 初值 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>camera.explored_margin_cells</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>24</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>星球镜头可平移范围=已探索区域外再放宽多少格</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>camera.precision_safe_cells</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16384</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>不启用浮动原点时镜头可达范围上限(格);超出前必须接浮动原点(DEBT-FG0ARCH01-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>camera.zoom_min_ortho</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>战略视角最近缩放(正交半高,格);Demo 初值 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>camera.zoom_max_ortho</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>46</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>战略视角最远缩放(正交半高,格);整个已探索世界的战略地图缩放由 FG17 FGR-GEN-080 承接卡放宽(DEBT-FG0ARCH01-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>camera.zoom_step</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>鼠标滚轮每格的缩放量(正交半高,格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>transit.raid_speed_cells_per_second</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>突袭队伍在星球上的行进速度(格/游戏秒);FG6-DEF-04 起按编成里最慢的单位取</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>transit.arrival_radius_cells</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>12</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>队伍离目标多少格以内算到达</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,6 +1298,166 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>logistics.step_hz</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>20</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>传送带内核固定步长频率(次/游戏秒),FGR-ARC-004 初值 20;在 60Hz 世界步里按游戏时间累计推进</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>logistics.slots_per_cell</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>每格传送带最多几个物品(1~4),FG03 第10章初值 4;物品最小间距=1/该值 格</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>logistics.items_per_minute_t1</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>60</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>T1 传送带满载吞吐(件/分钟),FG03 第10章初值</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>logistics.items_per_minute_t2</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>120</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>T2 传送带满载吞吐(件/分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>logistics.items_per_minute_t3</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>240</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>T3 传送带满载吞吐(件/分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>logistics.stats_bucket_steps</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>300</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>吞吐统计快照间隔(内核步);窗口=4个快照(20Hz 下 60 游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>logistics.render.flow_ortho_enter</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>38</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>镜头正交半高 &gt;= 此值切到远景流动贴图(不再逐物品绘制);须大于家园默认缩放 30、小于最远 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>logistics.render.flow_ortho_exit</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>34</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>远景下正交半高 &lt;= 此值切回近景(回差,避免在阈值附近来回闪)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>logistics.render.item_size</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>带上物品的边长(格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>logistics.render.height</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>传送带面的高度(世界单位,在地貌之上、建筑之下)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,6 +1458,518 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>combat.grid_cell_m</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>combat.events.gameplay_per_step</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>64</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>combat.events.cues_per_step</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>24</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>combat.projectile_capacity</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>combat.compact_ratio</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>combat.render.unit_height</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>combat.bench.raider_hp</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>120</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>突袭者原型耐久</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>combat.bench.raider_speed</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>combat.bench.raider_radius</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>突袭者原型半径(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>combat.bench.raider_sense</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>60</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>combat.bench.raider_range</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>突袭者原型射程(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>combat.bench.raider_damage</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>突袭者原型每发伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>combat.bench.raider_cooldown</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>突袭者原型开火间隔(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>combat.bench.raider_projectile_speed</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>18</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>突袭者原型弹速(米/游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>combat.bench.raider_projectile_radius</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>突袭者原型弹体半径(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>combat.bench.turret_hp</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>400</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>炮塔原型耐久</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>combat.bench.turret_radius</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>combat.bench.turret_range</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>26</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>炮塔原型射程(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>combat.bench.turret_damage</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>14</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>炮塔原型每发伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>combat.bench.turret_cooldown</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>炮塔原型开火间隔(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>combat.bench.turret_projectile_speed</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>24</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>炮塔原型弹速(米/游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>combat.bench.turret_projectile_radius</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>炮塔原型弹体半径(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>combat.perf.enemies</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>200</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>性能场景:同时存在的敌人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>combat.perf.turrets</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>80</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>性能场景:炮塔数</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>combat.perf.min_projectiles</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>combat.perf.step_budget_ms</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>6</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>combat.perf.hp_scale</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>25</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>combat.perf.turret_cooldown</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>combat.perf.raider_cooldown</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>combat.perf.projectile_speed</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>8</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>combat.perf.turret_range</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>30</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>性能场景:炮塔射程(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>combat.perf.raider_range</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>20</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>性能场景:突袭者射程(米)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1970,6 +1970,374 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>nav.latency_steps</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>6</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>nav.batch_max_requests</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>64</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>每批最多处理的寻路请求数</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>nav.batch_distance_budget</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>nav.search_margin_chunks</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>nav.max_expansions</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>nav.goal_search_radius</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>6</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>nav.start_search_radius</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>6</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>nav.smooth_lookahead</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>48</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>路线拉直时一个锚点最多向前看几格</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>nav.separation_factor</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>nav.preview_margin_cells</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>16</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>nav.perf.route_cells</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>性能验收:长距离路线的最短长度(格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>nav.perf.budget_ms</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>20</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>nav.perf.mass_requests</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>200</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>负向:同一步同时请求长路线的单位数</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>outpost.dormant_distance_cells</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>300</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>outpost.wake_hysteresis_cells</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>32</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>outpost.wakes_per_step</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>4</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>outpost.wake_budget_ms</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>outpost.reinforce_interval_days</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>outpost.garrison_cap</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>12</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>原型据点驻军上限(台)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>outpost.garrison_start</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>6</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>原型据点初始驻军(台)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>outpost.patrol_radius_cells</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>24</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>outpost.patrol_speed_cells_per_second</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>outpost.patrol_units</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>3</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>原型巡逻队人数(台)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2338,6 +2338,86 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>signal.core.initial_slots</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>signal.core.max_slots</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>5</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>signal.core.max_presets</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>8</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>signal.core.preset_name_max_chars</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>16</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>signal.firmware_chip.print_scrap</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2418,6 +2418,22 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>signal.uplink.quota</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2434,6 +2434,22 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>signal.uplink.transition_seconds</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2450,6 +2450,150 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>signal.coverage.core_radius</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>150</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>signal.coverage.tower_radius</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>300</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 500 待信号塔升级落地)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>signal.coverage.edge_warn_cells</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>15</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>signal.coverage.refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>signal.link.grace_seconds</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>signal.link.warn_repeat_seconds</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>signal.safe_mode.exit_seconds</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>signal.safe_mode.check_seconds</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2594,6 +2594,230 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>signal.raw.exposure_per_fire</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>signal.raw.heat_multiplier</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>signal.raw.charge_interval_seconds</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>8</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>exposure.max</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>100</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>exposure.core_fire</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>exposure.high_power.threshold</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>100</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>exposure.high_power.full_at</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>200</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>exposure.high_power.cap_per_hour</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>exposure.high_power.settle_seconds</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>50</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>exposure.alien_tech_per_expedition</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>exposure.node_destroyed</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>3</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>exposure.node_link_cut_drop</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>15</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>exposure.tower_off_drop_per_10s</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>exposure.history_max</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>64</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 500 待信号塔升级落地)</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.5</v>
+        <v>80</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>50</v>
+        <v>1.5</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -2806,13 +2806,125 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
+          <t>exposure.high_power.full_at</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>200</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>exposure.high_power.cap_per_hour</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>3</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>exposure.high_power.settle_seconds</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>50</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>exposure.alien_tech_per_expedition</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>exposure.node_destroyed</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>3</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>exposure.node_link_cut_drop</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>15</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>exposure.tower_off_drop_per_10s</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>exposure.history_max</t>
         </is>
       </c>
-      <c r="C149" t="n">
+      <c r="C156" t="n">
         <v>64</v>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2930,6 +2930,22 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>morph.transition_seconds</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.5</v>
+        <v>34</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -2934,13 +2934,61 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
+          <t>exposure.node_link_cut_drop</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>15</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>exposure.tower_off_drop_per_10s</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>exposure.history_max</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>64</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
           <t>morph.transition_seconds</t>
         </is>
       </c>
-      <c r="C157" t="n">
+      <c r="C160" t="n">
         <v>0.3</v>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2994,6 +2994,262 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>reading.status_seconds</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>3</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>reading.escort.seconds</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>8</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>reading.escort.ratio</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>reading.escort.cooldown</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>reading.escort.leash</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>10</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>reading.drone.speed</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>9</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>无人机移动速度(米/游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>reading.drone.reach</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>无人机触及距离(米,另加目标半径)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>reading.tick.status</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>reading.tick.zone</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>reading.capacity.zones</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>512</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>reading.capacity.echoes</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>每个地点待结算的回波上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>reading.capacity.drones</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>512</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>每个地点同时存在的无人机上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>reading.weave.dps_ratio</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>reading.weave.margin</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>reading.zone.status_seconds</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>combat.machine.attack_interval</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3250,6 +3250,22 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>status.stack_cap</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>3</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3266,6 +3266,86 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>firmware.storage.base_slots</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>8</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>firmware.storage.per_warehouse</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>16</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>firmware.library.disassemble_scrap</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>5</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>firmware.library.refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>firmware.library.route_cache_seconds</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1542,15 +1542,15 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -1558,15 +1558,15 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>120</v>
+        <v>0.6</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -1574,15 +1574,15 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3.5</v>
+        <v>120</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -1590,15 +1590,15 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1606,15 +1606,15 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>60</v>
+        <v>0.6</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -1622,15 +1622,15 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -1638,15 +1638,15 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -1654,15 +1654,15 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -1670,15 +1670,15 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>18</v>
+        <v>1.2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1686,15 +1686,15 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.15</v>
+        <v>18</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1702,15 +1702,15 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>400</v>
+        <v>0.15</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -1718,15 +1718,15 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -1734,15 +1734,15 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -1750,15 +1750,15 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -1766,15 +1766,15 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -1782,15 +1782,15 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>24</v>
+        <v>0.5</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1798,15 +1798,15 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.2</v>
+        <v>24</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1814,15 +1814,15 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>200</v>
+        <v>0.2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -1830,15 +1830,15 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -1846,15 +1846,15 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1500</v>
+        <v>80</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -1862,15 +1862,15 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>1500</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -1878,15 +1878,15 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -1894,15 +1894,15 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -1910,15 +1910,15 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1926,15 +1926,15 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1942,15 +1942,15 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -1958,15 +1958,15 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -1974,15 +1974,15 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -1990,15 +1990,15 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2006,15 +2006,15 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6000</v>
+        <v>64</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -2022,15 +2022,15 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>6000</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -2038,15 +2038,15 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>40000</v>
+        <v>4</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -2054,15 +2054,15 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>40000</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -2086,15 +2086,15 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.5</v>
+        <v>48</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2118,15 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>16</v>
+        <v>0.5</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -2134,15 +2134,15 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2000</v>
+        <v>16</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -2150,15 +2150,15 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -2166,15 +2166,15 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -2182,15 +2182,15 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -2198,15 +2198,15 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>32</v>
+        <v>300</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -2214,15 +2214,15 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -2230,15 +2230,15 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -2246,15 +2246,15 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -2262,15 +2262,15 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -2278,15 +2278,15 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -2294,15 +2294,15 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -2310,15 +2310,15 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1.5</v>
+        <v>24</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2326,15 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2342,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -2358,15 +2358,15 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -2438,15 +2438,15 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.35</v>
+        <v>2</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>150</v>
+        <v>0.35</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1.5</v>
+        <v>500</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>60</v>
+        <v>1.5</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0.3</v>
+        <v>64</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.4</v>
+        <v>8</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3142,15 +3142,15 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>512</v>
+        <v>0.5</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>0.15</v>
+        <v>512</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,79 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
+          <t>firmware.library.refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
           <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
-      <c r="C182" t="n">
+      <c r="C183" t="n">
         <v>1</v>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>firmware.restore.cost_common</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>4</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>firmware.restore.cost_rare</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>8</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>firmware.restore.cost_epic</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>12</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D186"/>
+  <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,15 +1062,15 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>clock.sim_step_hz</t>
+          <t>world.relief.cliff_height</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>世界模拟固定步长频率(次/游戏秒);与渲染帧率无关,倍速只改变每帧跑几步,结果与1x一致</t>
+          <t>悬崖区块内部的基础隆起高度(米)</t>
         </is>
       </c>
     </row>
@@ -1078,15 +1078,15 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>clock.max_steps_per_frame</t>
+          <t>world.relief.cliff_noise</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>单帧最多补跑的模拟步数(防卡顿雪崩);超出部分丢弃=世界短暂变慢,不跳步</t>
+          <t>悬崖隆起的噪声起伏幅度(米)</t>
         </is>
       </c>
     </row>
@@ -1094,15 +1094,15 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>clock.max_frame_seconds</t>
+          <t>world.relief.water_depth</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>单帧计入的真实时间上限(秒);断点/加载后的超长帧不会一次补跑几十秒</t>
+          <t>水面下陷深度(米)</t>
         </is>
       </c>
     </row>
@@ -1110,15 +1110,15 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>clock.day_seconds</t>
+          <t>world.relief.noise_scale</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1200</v>
+        <v>9</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1个游戏日在1x下的真实秒数(FGR-ENV-001:20分钟;1游戏小时=50秒)</t>
+          <t>起伏噪声格距(格)</t>
         </is>
       </c>
     </row>
@@ -1126,15 +1126,15 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>clock.start_hour</t>
+          <t>map.open_zoom_steps</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>新战役开始时是当天几点(0~23),第1日从这个时刻起算</t>
+          <t>战略视角已缩到最远后,再拉远几次滚轮切到战略地图</t>
         </is>
       </c>
     </row>
@@ -1142,15 +1142,15 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>clock.objective_recompute_seconds</t>
+          <t>map.cells_per_pixel_min</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>目标兜底重算间隔(游戏秒,跟随世界模拟步进,观察与否一致)</t>
+          <t>兜底:没有镜头时(编辑模式自检)战略地图最近时每像素多少格;正常游戏里地图最近=镜头最远缩放时的比例(连续缩放,FGR-GEN-080)</t>
         </is>
       </c>
     </row>
@@ -1158,15 +1158,15 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>sim.activity_refresh_seconds</t>
+          <t>map.open_view_scale</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>活跃区块集合(己方实体/行进中的队伍/被观察)重算间隔(游戏秒)</t>
+          <t>战略地图打开时的比例=镜头最远缩放时的比例×该值(约多拉远一格滚轮;在地图里拉近一格就回到镜头)</t>
         </is>
       </c>
     </row>
@@ -1174,15 +1174,15 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>camera.fly_seconds</t>
+          <t>map.zoom_gesture_gap_seconds</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>镜头飞跃过渡时长(真实秒),FG17 初值 0.5</t>
+          <t>两次滚轮间隔达到这么多真实秒算新的一次缩放手势(镜头最远时,新手势再拉远才切到战略地图)</t>
         </is>
       </c>
     </row>
@@ -1190,15 +1190,15 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>camera.explored_margin_cells</t>
+          <t>map.own_cluster_cells</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>星球镜头可平移范围=已探索区域外再放宽多少格</t>
+          <t>战略地图己方建筑群的聚合格边长(格);相邻(八邻接)的聚合格连成一群</t>
         </is>
       </c>
     </row>
@@ -1206,15 +1206,15 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>camera.precision_safe_cells</t>
+          <t>map.own_outpost_distance</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16384</v>
+        <v>300</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>不启用浮动原点时镜头可达范围上限(格);超出前必须接浮动原点(DEBT-FG0ARCH01-02)</t>
+          <t>离核心多少格以外的己方建筑群在地图上标为前哨站(FG08 FGR-EXP-017 初值 300)</t>
         </is>
       </c>
     </row>
@@ -1222,15 +1222,15 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>camera.zoom_min_ortho</t>
+          <t>map.cells_per_pixel_max</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>战略视角最近缩放(正交半高,格);Demo 初值 8</t>
+          <t>战略地图最远时每像素多少格</t>
         </is>
       </c>
     </row>
@@ -1238,15 +1238,15 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>camera.zoom_max_ortho</t>
+          <t>map.zoom_factor</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>46</v>
+        <v>1.35</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>战略视角最远缩放(正交半高,格);整个已探索世界的战略地图缩放由 FG17 FGR-GEN-080 承接卡放宽(DEBT-FG0ARCH01-08)</t>
+          <t>战略地图每次滚轮缩放的倍率</t>
         </is>
       </c>
     </row>
@@ -1254,15 +1254,15 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>camera.zoom_step</t>
+          <t>map.texture_size</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3.5</v>
+        <v>256</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>鼠标滚轮每格的缩放量(正交半高,格)</t>
+          <t>战略地图底图边长(像素;显示时拉伸)</t>
         </is>
       </c>
     </row>
@@ -1270,15 +1270,15 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>transit.raid_speed_cells_per_second</t>
+          <t>map.repaint_min_seconds</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>突袭队伍在星球上的行进速度(格/游戏秒);FG6-DEF-04 起按编成里最慢的单位取</t>
+          <t>底图两次重画的最短间隔(秒,真实时间)</t>
         </is>
       </c>
     </row>
@@ -1286,15 +1286,15 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>transit.arrival_radius_cells</t>
+          <t>minimap.radius_cells</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>队伍离目标多少格以内算到达</t>
+          <t>小地图显示镜头周围多少格(半边长)</t>
         </is>
       </c>
     </row>
@@ -1302,15 +1302,15 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>logistics.step_hz</t>
+          <t>minimap.texture_size</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>传送带内核固定步长频率(次/游戏秒),FGR-ARC-004 初值 20;在 60Hz 世界步里按游戏时间累计推进</t>
+          <t>小地图底图边长(像素)</t>
         </is>
       </c>
     </row>
@@ -1318,15 +1318,15 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>logistics.slots_per_cell</t>
+          <t>map.max_icons</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>256</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>每格传送带最多几个物品(1~4),FG03 第10章初值 4;物品最小间距=1/该值 格</t>
+          <t>战略地图同时显示的图标上限(超出按距离取近的)</t>
         </is>
       </c>
     </row>
@@ -1334,15 +1334,15 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>logistics.items_per_minute_t1</t>
+          <t>map.marker_max</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>T1 传送带满载吞吐(件/分钟),FG03 第10章初值</t>
+          <t>玩家标记数量上限</t>
         </is>
       </c>
     </row>
@@ -1350,15 +1350,15 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>logistics.items_per_minute_t2</t>
+          <t>outpost.nest_garrison_per_tier</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>T2 传送带满载吞吐(件/分钟)</t>
+          <t>侦察巢每级驻军(台);离核心越远等级越高(FGR-GEN-032)</t>
         </is>
       </c>
     </row>
@@ -1366,15 +1366,15 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>logistics.items_per_minute_t3</t>
+          <t>clock.sim_step_hz</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>T3 传送带满载吞吐(件/分钟)</t>
+          <t>世界模拟固定步长频率(次/游戏秒);与渲染帧率无关,倍速只改变每帧跑几步,结果与1x一致</t>
         </is>
       </c>
     </row>
@@ -1382,15 +1382,15 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>logistics.stats_bucket_steps</t>
+          <t>clock.max_steps_per_frame</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>300</v>
+        <v>12</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>吞吐统计快照间隔(内核步);窗口=4个快照(20Hz 下 60 游戏秒)</t>
+          <t>单帧最多补跑的模拟步数(防卡顿雪崩);超出部分丢弃=世界短暂变慢,不跳步</t>
         </is>
       </c>
     </row>
@@ -1398,15 +1398,15 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>logistics.render.flow_ortho_enter</t>
+          <t>clock.max_frame_seconds</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>38</v>
+        <v>0.25</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>镜头正交半高 &gt;= 此值切到远景流动贴图(不再逐物品绘制);须大于家园默认缩放 30、小于最远 46</t>
+          <t>单帧计入的真实时间上限(秒);断点/加载后的超长帧不会一次补跑几十秒</t>
         </is>
       </c>
     </row>
@@ -1414,15 +1414,15 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>logistics.render.flow_ortho_exit</t>
+          <t>clock.day_seconds</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>34</v>
+        <v>1200</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>远景下正交半高 &lt;= 此值切回近景(回差,避免在阈值附近来回闪)</t>
+          <t>1个游戏日在1x下的真实秒数(FGR-ENV-001:20分钟;1游戏小时=50秒)</t>
         </is>
       </c>
     </row>
@@ -1430,15 +1430,15 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>logistics.render.item_size</t>
+          <t>clock.start_hour</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.22</v>
+        <v>6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>带上物品的边长(格)</t>
+          <t>新战役开始时是当天几点(0~23),第1日从这个时刻起算</t>
         </is>
       </c>
     </row>
@@ -1446,15 +1446,15 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>logistics.render.height</t>
+          <t>clock.objective_recompute_seconds</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.04</v>
+        <v>0.5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>传送带面的高度(世界单位,在地貌之上、建筑之下)</t>
+          <t>目标兜底重算间隔(游戏秒,跟随世界模拟步进,观察与否一致)</t>
         </is>
       </c>
     </row>
@@ -1462,15 +1462,15 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>combat.grid_cell_m</t>
+          <t>sim.activity_refresh_seconds</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+          <t>活跃区块集合(己方实体/行进中的队伍/被观察)重算间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1478,15 +1478,15 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>combat.events.gameplay_per_step</t>
+          <t>camera.fly_seconds</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>64</v>
+        <v>0.5</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+          <t>镜头飞跃过渡时长(真实秒),FG17 初值 0.5</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>combat.events.cues_per_step</t>
+          <t>camera.explored_margin_cells</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+          <t>星球镜头可平移范围=已探索区域外再放宽多少格</t>
         </is>
       </c>
     </row>
@@ -1510,15 +1510,15 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>combat.projectile_capacity</t>
+          <t>camera.precision_safe_cells</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4096</v>
+        <v>16384</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+          <t>不启用浮动原点时镜头可达范围上限(格);超出前必须接浮动原点(DEBT-FG0ARCH01-02)</t>
         </is>
       </c>
     </row>
@@ -1526,15 +1526,15 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>combat.compact_ratio</t>
+          <t>camera.zoom_min_ortho</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+          <t>战略视角最近缩放(正交半高,格);Demo 初值 8</t>
         </is>
       </c>
     </row>
@@ -1542,15 +1542,15 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>combat.fuse_trace_seconds</t>
+          <t>camera.zoom_max_ortho</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.15</v>
+        <v>46</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
+          <t>战略视角最远缩放(正交半高,格);整个已探索世界的战略地图缩放由 FG17 FGR-GEN-080 承接卡放宽(DEBT-FG0ARCH01-08)</t>
         </is>
       </c>
     </row>
@@ -1558,15 +1558,15 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>camera.zoom_step</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>鼠标滚轮每格的缩放量(正交半高,格)</t>
         </is>
       </c>
     </row>
@@ -1574,15 +1574,15 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>transit.raid_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>120</v>
+        <v>1.5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>突袭队伍在星球上的行进速度(格/游戏秒);FG6-DEF-04 起按编成里最慢的单位取</t>
         </is>
       </c>
     </row>
@@ -1590,15 +1590,15 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>transit.arrival_radius_cells</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>队伍离目标多少格以内算到达</t>
         </is>
       </c>
     </row>
@@ -1606,15 +1606,15 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>logistics.step_hz</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.6</v>
+        <v>20</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>传送带内核固定步长频率(次/游戏秒),FGR-ARC-004 初值 20;在 60Hz 世界步里按游戏时间累计推进</t>
         </is>
       </c>
     </row>
@@ -1622,15 +1622,15 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>logistics.slots_per_cell</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>每格传送带最多几个物品(1~4),FG03 第10章初值 4;物品最小间距=1/该值 格</t>
         </is>
       </c>
     </row>
@@ -1638,15 +1638,15 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>logistics.items_per_minute_t1</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>T1 传送带满载吞吐(件/分钟),FG03 第10章初值</t>
         </is>
       </c>
     </row>
@@ -1654,15 +1654,15 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>logistics.items_per_minute_t2</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>T2 传送带满载吞吐(件/分钟)</t>
         </is>
       </c>
     </row>
@@ -1670,15 +1670,15 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>logistics.items_per_minute_t3</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.2</v>
+        <v>240</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>T3 传送带满载吞吐(件/分钟)</t>
         </is>
       </c>
     </row>
@@ -1686,15 +1686,15 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>logistics.stats_bucket_steps</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>吞吐统计快照间隔(内核步);窗口=4个快照(20Hz 下 60 游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1702,15 +1702,15 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>logistics.render.flow_ortho_enter</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.15</v>
+        <v>38</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>镜头正交半高 &gt;= 此值切到远景流动贴图(不再逐物品绘制);须大于家园默认缩放 30、小于最远 46</t>
         </is>
       </c>
     </row>
@@ -1718,15 +1718,15 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>logistics.render.flow_ortho_exit</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>400</v>
+        <v>34</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>远景下正交半高 &lt;= 此值切回近景(回差,避免在阈值附近来回闪)</t>
         </is>
       </c>
     </row>
@@ -1734,15 +1734,15 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>logistics.render.item_size</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0.22</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>带上物品的边长(格)</t>
         </is>
       </c>
     </row>
@@ -1750,15 +1750,15 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>logistics.render.height</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>26</v>
+        <v>0.04</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>传送带面的高度(世界单位,在地貌之上、建筑之下)</t>
         </is>
       </c>
     </row>
@@ -1766,15 +1766,15 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.grid_cell_m</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
         </is>
       </c>
     </row>
@@ -1782,15 +1782,15 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.events.gameplay_per_step</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.5</v>
+        <v>64</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.events.cues_per_step</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
         </is>
       </c>
     </row>
@@ -1814,15 +1814,15 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.projectile_capacity</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.2</v>
+        <v>4096</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
         </is>
       </c>
     </row>
@@ -1830,15 +1830,15 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.compact_ratio</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
         </is>
       </c>
     </row>
@@ -1846,15 +1846,15 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>80</v>
+        <v>0.15</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -1862,15 +1862,15 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1500</v>
+        <v>0.6</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -1878,15 +1878,15 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -1894,15 +1894,15 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>3.5</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1910,15 +1910,15 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -1926,15 +1926,15 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -1942,15 +1942,15 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -1958,15 +1958,15 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -1974,15 +1974,15 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -1990,15 +1990,15 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2006,15 +2006,15 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>64</v>
+        <v>0.15</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2022,15 +2022,15 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6000</v>
+        <v>400</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -2038,15 +2038,15 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -2054,15 +2054,15 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>40000</v>
+        <v>26</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2070,15 +2070,15 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2086,15 +2086,15 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2118,15 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2134,15 +2134,15 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -2150,15 +2150,15 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2000</v>
+        <v>80</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -2166,15 +2166,15 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>20</v>
+        <v>1500</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -2182,15 +2182,15 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -2198,15 +2198,15 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -2214,15 +2214,15 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>32</v>
+        <v>0.25</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2230,15 +2230,15 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2246,15 +2246,15 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -2262,15 +2262,15 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -2278,15 +2278,15 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2310,15 +2310,15 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2326,15 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1.5</v>
+        <v>6000</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2342,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -2358,15 +2358,15 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>40000</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -2438,15 +2438,15 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.35</v>
+        <v>2000</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>60</v>
+        <v>0.35</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>34</v>
+        <v>300</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.5</v>
+        <v>80</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.8</v>
+        <v>60</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>512</v>
+        <v>100</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1024</v>
+        <v>200</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>512</v>
+        <v>3</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>0.15</v>
+        <v>50</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1.2</v>
+        <v>15</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>16</v>
+        <v>0.3</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -3398,13 +3398,317 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
+          <t>reading.drone.speed</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>9</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>无人机移动速度(米/游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>reading.drone.reach</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>无人机触及距离(米,另加目标半径)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>reading.tick.status</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>reading.tick.zone</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>reading.capacity.zones</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>512</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>reading.capacity.echoes</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>每个地点待结算的回波上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>reading.capacity.drones</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>512</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>每个地点同时存在的无人机上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>reading.weave.dps_ratio</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>reading.weave.margin</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>reading.zone.status_seconds</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>combat.machine.attack_interval</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>status.stack_cap</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>firmware.storage.base_slots</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>8</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>firmware.storage.per_warehouse</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>16</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>firmware.library.disassemble_scrap</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>5</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>firmware.library.refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>firmware.library.route_cache_seconds</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>firmware.restore.cost_common</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>4</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>firmware.restore.cost_rare</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>8</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
           <t>firmware.restore.cost_epic</t>
         </is>
       </c>
-      <c r="C186" t="n">
+      <c r="C205" t="n">
         <v>12</v>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D205"/>
+  <dimension ref="A1:D212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3714,6 +3714,118 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>grid.relocate_seconds</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>20</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>grid.batch_demolish_confirm</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>20</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>grid.pollution_warn_level</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>grid.drag_max_cells</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>256</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>grid.explore_machine_radius</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>12</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>grid.explore_lattice</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>4</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>grid.explore_machines_per_step</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D212"/>
+  <dimension ref="A1:D214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3826,6 +3826,38 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>40</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>build.belt_seconds_per_cell</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D214"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1766,15 +1766,15 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>combat.grid_cell_m</t>
+          <t>logistics.item.scrap_id</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+          <t>废料在传送带上的物品编号(FG4-ECO-01 物品表之前的临时映射;内核只认编号)</t>
         </is>
       </c>
     </row>
@@ -1782,15 +1782,15 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>combat.events.gameplay_per_step</t>
+          <t>logistics.port.sink_buffer</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+          <t>建筑输入端口的缓存(件):满了就不收,传送带停下(原因写下游建筑名);仓库输入口每个内核步把缓存存进仓库</t>
         </is>
       </c>
     </row>
@@ -1798,15 +1798,15 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>combat.events.cues_per_step</t>
+          <t>logistics.port.source_buffer</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+          <t>仓库输出端口一次从库存取出、等着推上传送带的件数(在途量上限;过滤改变或建筑停用时退回仓库)</t>
         </is>
       </c>
     </row>
@@ -1814,15 +1814,15 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>combat.projectile_capacity</t>
+          <t>logistics.port.source_interval_steps</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+          <t>输出端口推一件的最短间隔(内核步);1 = 传送带入口一有空位就推(三档都能跑满)</t>
         </is>
       </c>
     </row>
@@ -1830,15 +1830,15 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>combat.compact_ratio</t>
+          <t>logistics.port.sync_seconds</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+          <t>建筑端口与建筑状态对账的间隔(游戏秒):建筑建成 / 修好 / 转向 / 搬迁 / 拆除后最迟这么久端口跟上;按世界步序号取整,与观察无关</t>
         </is>
       </c>
     </row>
@@ -1846,15 +1846,15 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>combat.fuse_trace_seconds</t>
+          <t>logistics.belt.hp_t1</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.15</v>
+        <v>60</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
+          <t>T1 传送带每格耐久(初值;被突袭 / 天气打到 0 时摧毁,物品落地,原位置留虚影)</t>
         </is>
       </c>
     </row>
@@ -1862,15 +1862,15 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>logistics.belt.hp_t2</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.6</v>
+        <v>90</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>T2 传送带每格耐久(初值)</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>logistics.belt.hp_t3</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>T3 传送带每格耐久(初值)</t>
         </is>
       </c>
     </row>
@@ -1894,15 +1894,15 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>logistics.weather.sandstorm_slow_pct</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3.5</v>
+        <v>25</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>沙暴期间露天传送带减速(百分比,FG03 第10章初值 -25%);顶棚下不受影响</t>
         </is>
       </c>
     </row>
@@ -1910,15 +1910,15 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>combat.grid_cell_m</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
         </is>
       </c>
     </row>
@@ -1926,15 +1926,15 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>combat.events.gameplay_per_step</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
         </is>
       </c>
     </row>
@@ -1942,15 +1942,15 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>combat.events.cues_per_step</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
         </is>
       </c>
     </row>
@@ -1958,15 +1958,15 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>combat.projectile_capacity</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>4096</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
         </is>
       </c>
     </row>
@@ -1974,15 +1974,15 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>combat.compact_ratio</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
         </is>
       </c>
     </row>
@@ -1990,15 +1990,15 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>18</v>
+        <v>0.15</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -2006,15 +2006,15 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -2022,15 +2022,15 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -2038,15 +2038,15 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2054,15 +2054,15 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>26</v>
+        <v>0.6</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -2070,15 +2070,15 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -2086,15 +2086,15 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2118,15 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2134,15 +2134,15 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2150,15 +2150,15 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>80</v>
+        <v>0.15</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2166,15 +2166,15 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -2182,15 +2182,15 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -2198,15 +2198,15 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2214,15 +2214,15 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.25</v>
+        <v>14</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2246,15 +2246,15 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2262,15 +2262,15 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>30</v>
+        <v>0.2</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2278,15 +2278,15 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -2294,15 +2294,15 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -2310,15 +2310,15 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>64</v>
+        <v>1500</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2326,15 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6000</v>
+        <v>6</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2342,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -2358,15 +2358,15 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>40000</v>
+        <v>0.25</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -2438,15 +2438,15 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2000</v>
+        <v>64</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>20</v>
+        <v>6000</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>300</v>
+        <v>40000</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1.5</v>
+        <v>200</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.35</v>
+        <v>24</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>10</v>
+        <v>0.35</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>34</v>
+        <v>0.5</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -3142,15 +3142,15 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>64</v>
+        <v>0.5</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.3</v>
+        <v>100</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.4</v>
+        <v>50</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3398,15 +3398,15 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3414,15 +3414,15 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3430,15 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0.5</v>
+        <v>64</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3446,15 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3462,15 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>512</v>
+        <v>3</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1024</v>
+        <v>8</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -3494,15 +3494,15 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>512</v>
+        <v>0.4</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -3510,15 +3510,15 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.15</v>
+        <v>0.8</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3526,15 +3526,15 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -3542,15 +3542,15 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -3574,15 +3574,15 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3590,15 +3590,15 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -3606,15 +3606,15 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>16</v>
+        <v>512</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -3622,15 +3622,15 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>5</v>
+        <v>1024</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -3638,15 +3638,15 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.5</v>
+        <v>512</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -3654,15 +3654,15 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -3670,15 +3670,15 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -3686,15 +3686,15 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3702,15 +3702,15 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_epic</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>12</v>
+        <v>1.2</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -3718,15 +3718,15 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>grid.relocate_seconds</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -3734,15 +3734,15 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>grid.batch_demolish_confirm</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -3750,15 +3750,15 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>grid.pollution_warn_level</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -3766,15 +3766,15 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>grid.drag_max_cells</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>256</v>
+        <v>5</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -3782,15 +3782,15 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>grid.explore_machine_radius</t>
+          <t>firmware.library.refresh_seconds</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>grid.explore_lattice</t>
+          <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
         </is>
       </c>
     </row>
@@ -3814,15 +3814,15 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>grid.explore_machines_per_step</t>
+          <t>firmware.restore.cost_common</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
         </is>
       </c>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>build.carry_per_trip</t>
+          <t>firmware.restore.cost_rare</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -3846,13 +3846,157 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
+          <t>firmware.restore.cost_epic</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>12</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>grid.relocate_seconds</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>20</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>grid.batch_demolish_confirm</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>20</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>grid.pollution_warn_level</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>grid.drag_max_cells</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>256</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>grid.explore_machine_radius</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>12</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>grid.explore_lattice</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>4</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>grid.explore_machines_per_step</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>40</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
           <t>build.belt_seconds_per_cell</t>
         </is>
       </c>
-      <c r="C214" t="n">
+      <c r="C223" t="n">
         <v>1</v>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,15 +1910,15 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>combat.grid_cell_m</t>
+          <t>logistics.underground.span_t1</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+          <t>T1 地下传送带最大跨度(入口与出口之间隔着的格数,FG03 第10章初值 4)</t>
         </is>
       </c>
     </row>
@@ -1926,15 +1926,15 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>combat.events.gameplay_per_step</t>
+          <t>logistics.underground.span_t2</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+          <t>T2 地下传送带最大跨度(FG03 第10章初值 6)</t>
         </is>
       </c>
     </row>
@@ -1942,15 +1942,15 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>combat.events.cues_per_step</t>
+          <t>logistics.underground.span_t3</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+          <t>T3 地下传送带最大跨度(FG03 第10章初值 8)</t>
         </is>
       </c>
     </row>
@@ -1958,15 +1958,15 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>combat.projectile_capacity</t>
+          <t>logistics.splitter.custom_presets_max</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4096</v>
+        <v>8</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+          <t>每局最多保存几个自定义分流器预设(过滤器预设,跟着存档)</t>
         </is>
       </c>
     </row>
@@ -1974,15 +1974,15 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>combat.compact_ratio</t>
+          <t>combat.grid_cell_m</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
         </is>
       </c>
     </row>
@@ -1990,15 +1990,15 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>combat.fuse_trace_seconds</t>
+          <t>combat.events.gameplay_per_step</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.15</v>
+        <v>64</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
         </is>
       </c>
     </row>
@@ -2006,15 +2006,15 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>combat.events.cues_per_step</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>0.6</v>
+        <v>24</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
         </is>
       </c>
     </row>
@@ -2022,15 +2022,15 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>combat.projectile_capacity</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>120</v>
+        <v>4096</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
         </is>
       </c>
     </row>
@@ -2038,15 +2038,15 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>combat.compact_ratio</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
         </is>
       </c>
     </row>
@@ -2054,15 +2054,15 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -2070,15 +2070,15 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>60</v>
+        <v>0.6</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -2086,15 +2086,15 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2118,15 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -2134,15 +2134,15 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -2150,15 +2150,15 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.15</v>
+        <v>16</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2166,15 +2166,15 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>400</v>
+        <v>6</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2182,15 +2182,15 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2198,15 +2198,15 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2214,15 +2214,15 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>14</v>
+        <v>0.15</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2230,15 +2230,15 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.5</v>
+        <v>400</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -2246,15 +2246,15 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -2262,15 +2262,15 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0.2</v>
+        <v>26</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2278,15 +2278,15 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2294,15 +2294,15 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>80</v>
+        <v>0.5</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2310,15 +2310,15 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1500</v>
+        <v>24</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2326,15 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>0.2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2342,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -2358,15 +2358,15 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.25</v>
+        <v>80</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.5</v>
+        <v>1500</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>20</v>
+        <v>0.25</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2438,15 +2438,15 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>6000</v>
+        <v>30</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>40000</v>
+        <v>6</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>6000</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.5</v>
+        <v>40000</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2000</v>
+        <v>6</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>32</v>
+        <v>2000</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.35</v>
+        <v>8</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>200</v>
+        <v>0.35</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1.5</v>
+        <v>200</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -3142,15 +3142,15 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>67</v>
+        <v>0.5</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.5</v>
+        <v>67</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3398,15 +3398,15 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3414,15 +3414,15 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3430,15 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3446,15 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3462,15 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3494,15 +3494,15 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.4</v>
+        <v>64</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -3510,15 +3510,15 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -3526,15 +3526,15 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -3542,15 +3542,15 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -3558,15 +3558,15 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -3574,15 +3574,15 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3590,15 +3590,15 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -3606,15 +3606,15 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>512</v>
+        <v>9</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3622,15 +3622,15 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1024</v>
+        <v>1.2</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -3638,15 +3638,15 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>512</v>
+        <v>0.5</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3654,15 +3654,15 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -3670,15 +3670,15 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>0.6</v>
+        <v>512</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -3686,15 +3686,15 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>2</v>
+        <v>1024</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -3702,15 +3702,15 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1.2</v>
+        <v>512</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -3718,15 +3718,15 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>3</v>
+        <v>0.15</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -3734,15 +3734,15 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -3750,15 +3750,15 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3766,15 +3766,15 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -3782,15 +3782,15 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -3814,15 +3814,15 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -3846,15 +3846,15 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_epic</t>
+          <t>firmware.library.refresh_seconds</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
         </is>
       </c>
     </row>
@@ -3862,15 +3862,15 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>grid.relocate_seconds</t>
+          <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
         </is>
       </c>
     </row>
@@ -3878,15 +3878,15 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>grid.batch_demolish_confirm</t>
+          <t>firmware.restore.cost_common</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
         </is>
       </c>
     </row>
@@ -3894,15 +3894,15 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>grid.pollution_warn_level</t>
+          <t>firmware.restore.cost_rare</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -3910,15 +3910,15 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>grid.drag_max_cells</t>
+          <t>firmware.restore.cost_epic</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>256</v>
+        <v>12</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -3926,15 +3926,15 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>grid.explore_machine_radius</t>
+          <t>grid.relocate_seconds</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
         </is>
       </c>
     </row>
@@ -3942,15 +3942,15 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>grid.explore_lattice</t>
+          <t>grid.batch_demolish_confirm</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>grid.explore_machines_per_step</t>
+          <t>grid.pollution_warn_level</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
         </is>
       </c>
     </row>
@@ -3974,15 +3974,15 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>build.carry_per_trip</t>
+          <t>grid.drag_max_cells</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>40</v>
+        <v>256</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
         </is>
       </c>
     </row>
@@ -3990,13 +3990,77 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
+          <t>grid.explore_machine_radius</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>12</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>grid.explore_lattice</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>4</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>grid.explore_machines_per_step</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>40</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
           <t>build.belt_seconds_per_cell</t>
         </is>
       </c>
-      <c r="C223" t="n">
+      <c r="C227" t="n">
         <v>1</v>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D227"/>
+  <dimension ref="A1:D236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1974,15 +1974,15 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>combat.grid_cell_m</t>
+          <t>logistics.pipe.lpm_t1</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>600</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+          <t>T1 管线吞吐(升/分钟),FG03 第10章初值;网络吞吐上限=网络里最低等级管线的吞吐(FGR-LOG-042)</t>
         </is>
       </c>
     </row>
@@ -1990,15 +1990,15 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>combat.events.gameplay_per_step</t>
+          <t>logistics.pipe.lpm_t2</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>64</v>
+        <v>1200</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+          <t>T2 管线吞吐(升/分钟),FG03 第10章初值</t>
         </is>
       </c>
     </row>
@@ -2006,15 +2006,15 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>combat.events.cues_per_step</t>
+          <t>logistics.pipe.pump_lpm</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+          <t>泵的固定抽取速率(升/分钟),FG03 第10章初值(FGR-LOG-041)</t>
         </is>
       </c>
     </row>
@@ -2022,15 +2022,15 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>combat.projectile_capacity</t>
+          <t>logistics.pipe.tank_liters</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4096</v>
+        <v>5000</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+          <t>储罐容量(升),FG03 第10章初值(FGR-LOG-043)</t>
         </is>
       </c>
     </row>
@@ -2038,15 +2038,15 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>combat.compact_ratio</t>
+          <t>logistics.pipe.tank_lpm</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0.5</v>
+        <v>1200</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+          <t>储罐进出速率上限(升/分钟),初值=T2 管线吞吐(FG16 调参)</t>
         </is>
       </c>
     </row>
@@ -2054,15 +2054,15 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>combat.fuse_trace_seconds</t>
+          <t>logistics.pipe.valve_lpm</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.15</v>
+        <v>1200</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
+          <t>阀门输送速率上限(升/分钟),初值=T2 管线吞吐(FG16 调参)</t>
         </is>
       </c>
     </row>
@@ -2070,15 +2070,15 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>logistics.pipe.freeze_idle_hours</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>结冰条件:流量为0超过这么多游戏小时(FGR-LOG-045;本 Story 只预留计时接口,结冰由 FG7-ENV-03 寒潮接入)</t>
         </is>
       </c>
     </row>
@@ -2086,15 +2086,15 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>logistics.pipe.icon_every</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>管线每隔几格画一个流体图标(泵/储罐/阀门每件都画;B15 颜色之外的形状区分)</t>
         </is>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>logistics.pipe.render.height</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3.5</v>
+        <v>0.05</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>管线面的高度(世界单位,传送带面之上、建筑之下)</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2118,15 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>combat.grid_cell_m</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
         </is>
       </c>
     </row>
@@ -2134,15 +2134,15 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>combat.events.gameplay_per_step</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
         </is>
       </c>
     </row>
@@ -2150,15 +2150,15 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>combat.events.cues_per_step</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
         </is>
       </c>
     </row>
@@ -2166,15 +2166,15 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>combat.projectile_capacity</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>4096</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
         </is>
       </c>
     </row>
@@ -2182,15 +2182,15 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>combat.compact_ratio</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
         </is>
       </c>
     </row>
@@ -2198,15 +2198,15 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>18</v>
+        <v>0.15</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -2214,15 +2214,15 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -2230,15 +2230,15 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -2246,15 +2246,15 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2262,15 +2262,15 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>26</v>
+        <v>0.6</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -2278,15 +2278,15 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -2294,15 +2294,15 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2310,15 +2310,15 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2326,15 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2342,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2358,15 +2358,15 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>80</v>
+        <v>0.15</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.25</v>
+        <v>14</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>30</v>
+        <v>0.2</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>64</v>
+        <v>1500</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6000</v>
+        <v>6</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>40000</v>
+        <v>0.25</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2000</v>
+        <v>64</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>20</v>
+        <v>6000</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>300</v>
+        <v>40000</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1.5</v>
+        <v>200</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.35</v>
+        <v>24</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>150</v>
+        <v>1.5</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>10</v>
+        <v>0.35</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -3142,15 +3142,15 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>34</v>
+        <v>0.5</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3398,15 +3398,15 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3414,15 +3414,15 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3430,15 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3446,15 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3462,15 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3494,15 +3494,15 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>64</v>
+        <v>0.5</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3510,15 +3510,15 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.3</v>
+        <v>100</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3526,15 +3526,15 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3542,15 +3542,15 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3558,15 +3558,15 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0.4</v>
+        <v>50</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3574,15 +3574,15 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3590,15 +3590,15 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3606,15 +3606,15 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3622,15 +3622,15 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3638,15 +3638,15 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.5</v>
+        <v>64</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -3654,15 +3654,15 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -3670,15 +3670,15 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>512</v>
+        <v>3</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -3686,15 +3686,15 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1024</v>
+        <v>8</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -3702,15 +3702,15 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>512</v>
+        <v>0.4</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -3718,15 +3718,15 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.15</v>
+        <v>0.8</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3734,15 +3734,15 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -3750,15 +3750,15 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -3782,15 +3782,15 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -3814,15 +3814,15 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>16</v>
+        <v>512</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>5</v>
+        <v>1024</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -3846,15 +3846,15 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.5</v>
+        <v>512</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -3862,15 +3862,15 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -3878,15 +3878,15 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -3894,15 +3894,15 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3910,15 +3910,15 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_epic</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>12</v>
+        <v>1.2</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -3926,15 +3926,15 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>grid.relocate_seconds</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -3942,15 +3942,15 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>grid.batch_demolish_confirm</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -3958,15 +3958,15 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>grid.pollution_warn_level</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -3974,15 +3974,15 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>grid.drag_max_cells</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>256</v>
+        <v>5</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -3990,15 +3990,15 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>grid.explore_machine_radius</t>
+          <t>firmware.library.refresh_seconds</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
         </is>
       </c>
     </row>
@@ -4006,15 +4006,15 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>grid.explore_lattice</t>
+          <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
         </is>
       </c>
     </row>
@@ -4022,15 +4022,15 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>grid.explore_machines_per_step</t>
+          <t>firmware.restore.cost_common</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
         </is>
       </c>
     </row>
@@ -4038,15 +4038,15 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>build.carry_per_trip</t>
+          <t>firmware.restore.cost_rare</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4054,13 +4054,157 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
+          <t>firmware.restore.cost_epic</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>12</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>grid.relocate_seconds</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>20</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>grid.batch_demolish_confirm</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>20</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>grid.pollution_warn_level</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>grid.drag_max_cells</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>256</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>grid.explore_machine_radius</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>12</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>grid.explore_lattice</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>4</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>grid.explore_machines_per_step</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>40</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
           <t>build.belt_seconds_per_cell</t>
         </is>
       </c>
-      <c r="C227" t="n">
+      <c r="C236" t="n">
         <v>1</v>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D236"/>
+  <dimension ref="A1:D239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2118,15 +2118,15 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>combat.grid_cell_m</t>
+          <t>power.sample_seconds</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+          <t>电网曲线每隔多少游戏秒记一个点(FGR-LOG-061;按游戏时钟,暂停不记、倍速同比)</t>
         </is>
       </c>
     </row>
@@ -2134,15 +2134,15 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>combat.events.gameplay_per_step</t>
+          <t>power.curve_samples</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+          <t>每个电网曲线最多保留多少个点(90 × 10 秒 = 最近 15 游戏分钟),进存档</t>
         </is>
       </c>
     </row>
@@ -2150,15 +2150,15 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>combat.events.cues_per_step</t>
+          <t>power.preview_max_nodes</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+          <t>放置预览最多检查附近多少个电力节点(防止极端布局下预览卡顿;超出只少报连到的电网,不影响结算)</t>
         </is>
       </c>
     </row>
@@ -2166,15 +2166,15 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>combat.projectile_capacity</t>
+          <t>combat.grid_cell_m</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4096</v>
+        <v>8</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
         </is>
       </c>
     </row>
@@ -2182,15 +2182,15 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>combat.compact_ratio</t>
+          <t>combat.events.gameplay_per_step</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.5</v>
+        <v>64</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
         </is>
       </c>
     </row>
@@ -2198,15 +2198,15 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>combat.fuse_trace_seconds</t>
+          <t>combat.events.cues_per_step</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.15</v>
+        <v>24</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
         </is>
       </c>
     </row>
@@ -2214,15 +2214,15 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>combat.projectile_capacity</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.6</v>
+        <v>4096</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
         </is>
       </c>
     </row>
@@ -2230,15 +2230,15 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>combat.compact_ratio</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>120</v>
+        <v>0.5</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
         </is>
       </c>
     </row>
@@ -2246,15 +2246,15 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3.5</v>
+        <v>0.15</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -2278,15 +2278,15 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -2294,15 +2294,15 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>16</v>
+        <v>3.5</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2310,15 +2310,15 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2326,15 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1.2</v>
+        <v>60</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2342,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2358,15 +2358,15 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.15</v>
+        <v>6</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>400</v>
+        <v>1.2</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>26</v>
+        <v>0.15</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>14</v>
+        <v>400</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -2438,15 +2438,15 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.2</v>
+        <v>14</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1500</v>
+        <v>0.2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.25</v>
+        <v>1500</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>30</v>
+        <v>0.25</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>6000</v>
+        <v>20</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>40000</v>
+        <v>64</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>6000</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>48</v>
+        <v>40000</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2000</v>
+        <v>48</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.35</v>
+        <v>16</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -3142,15 +3142,15 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>500</v>
+        <v>0.35</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1.5</v>
+        <v>80</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -3398,15 +3398,15 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3414,15 +3414,15 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>60</v>
+        <v>0.5</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3430,15 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3446,15 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>34</v>
+        <v>1.5</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3462,15 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3494,15 +3494,15 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.5</v>
+        <v>34</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3510,15 +3510,15 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3526,15 +3526,15 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3542,15 +3542,15 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3558,15 +3558,15 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3574,15 +3574,15 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3606,15 +3606,15 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3638,15 +3638,15 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3654,15 +3654,15 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.3</v>
+        <v>15</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3670,15 +3670,15 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3686,15 +3686,15 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -3702,15 +3702,15 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -3718,15 +3718,15 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -3734,15 +3734,15 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -3750,15 +3750,15 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>9</v>
+        <v>0.4</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -3766,15 +3766,15 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3782,15 +3782,15 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3814,15 +3814,15 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>512</v>
+        <v>1.2</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1024</v>
+        <v>0.5</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3846,15 +3846,15 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>512</v>
+        <v>0.5</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -3862,15 +3862,15 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>0.15</v>
+        <v>512</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -3878,15 +3878,15 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>0.6</v>
+        <v>1024</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -3894,15 +3894,15 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>512</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -3910,15 +3910,15 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1.2</v>
+        <v>0.15</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -3926,15 +3926,15 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -3942,15 +3942,15 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3958,15 +3958,15 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>16</v>
+        <v>1.2</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -3974,15 +3974,15 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -3990,15 +3990,15 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -4006,15 +4006,15 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -4022,15 +4022,15 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -4038,15 +4038,15 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>firmware.library.refresh_seconds</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
         </is>
       </c>
     </row>
@@ -4054,15 +4054,15 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_epic</t>
+          <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
         </is>
       </c>
     </row>
@@ -4070,15 +4070,15 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>grid.relocate_seconds</t>
+          <t>firmware.restore.cost_common</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
         </is>
       </c>
     </row>
@@ -4086,15 +4086,15 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>grid.batch_demolish_confirm</t>
+          <t>firmware.restore.cost_rare</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4102,15 +4102,15 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>grid.pollution_warn_level</t>
+          <t>firmware.restore.cost_epic</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4118,15 +4118,15 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>grid.drag_max_cells</t>
+          <t>grid.relocate_seconds</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>256</v>
+        <v>20</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
         </is>
       </c>
     </row>
@@ -4134,15 +4134,15 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>grid.explore_machine_radius</t>
+          <t>grid.batch_demolish_confirm</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
         </is>
       </c>
     </row>
@@ -4150,15 +4150,15 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>grid.explore_lattice</t>
+          <t>grid.pollution_warn_level</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
         </is>
       </c>
     </row>
@@ -4166,15 +4166,15 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>grid.explore_machines_per_step</t>
+          <t>grid.drag_max_cells</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
         </is>
       </c>
     </row>
@@ -4182,15 +4182,15 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>build.carry_per_trip</t>
+          <t>grid.explore_machine_radius</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
         </is>
       </c>
     </row>
@@ -4198,13 +4198,61 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
+          <t>grid.explore_lattice</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>4</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>grid.explore_machines_per_step</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>40</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
           <t>build.belt_seconds_per_cell</t>
         </is>
       </c>
-      <c r="C236" t="n">
+      <c r="C239" t="n">
         <v>1</v>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D239"/>
+  <dimension ref="A1:D244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2166,15 +2166,15 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>combat.grid_cell_m</t>
+          <t>plan.undo_depth</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+          <t>撤销栈保留这么多步(FGR-LOG-009 初值 50,更早的丢掉);一步 = 一次玩家操作(粘贴、框选拆除算一步);单步件数上限 = plan.layout_max_entries,存档体积有上界</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>combat.events.gameplay_per_step</t>
+          <t>plan.layout_max</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+          <t>布局库最多保存几个布局(跨存档共享,存在玩家配置目录)</t>
         </is>
       </c>
     </row>
@@ -2198,15 +2198,15 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>combat.events.cues_per_step</t>
+          <t>plan.layout_max_entries</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>24</v>
+        <v>1024</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+          <t>一次复制 / 一个布局最多几件(超出给原因,不静默截断)</t>
         </is>
       </c>
     </row>
@@ -2214,15 +2214,15 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>combat.projectile_capacity</t>
+          <t>plan.preview_max_tiles</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4096</v>
+        <v>1024</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+          <t>粘贴预览最多画几格虚影(超出的件照常校验与放置,只是不画;状态行写明)</t>
         </is>
       </c>
     </row>
@@ -2230,15 +2230,15 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>combat.compact_ratio</t>
+          <t>plan.thumbnail_px</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.5</v>
+        <v>64</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+          <t>布局缩略图边长(像素)</t>
         </is>
       </c>
     </row>
@@ -2246,15 +2246,15 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>combat.fuse_trace_seconds</t>
+          <t>combat.grid_cell_m</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.15</v>
+        <v>8</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
         </is>
       </c>
     </row>
@@ -2262,15 +2262,15 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>combat.events.gameplay_per_step</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0.6</v>
+        <v>64</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
         </is>
       </c>
     </row>
@@ -2278,15 +2278,15 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>combat.events.cues_per_step</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
         </is>
       </c>
     </row>
@@ -2294,15 +2294,15 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>combat.projectile_capacity</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3.5</v>
+        <v>4096</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
         </is>
       </c>
     </row>
@@ -2310,15 +2310,15 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>combat.compact_ratio</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2326,15 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>60</v>
+        <v>0.15</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2342,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>16</v>
+        <v>0.6</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -2358,15 +2358,15 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.15</v>
+        <v>60</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>400</v>
+        <v>16</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2438,15 +2438,15 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>26</v>
+        <v>1.2</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>24</v>
+        <v>400</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1500</v>
+        <v>0.5</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>25</v>
+        <v>0.2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.25</v>
+        <v>200</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.5</v>
+        <v>80</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>8</v>
+        <v>1500</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>0.25</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>64</v>
+        <v>0.5</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6000</v>
+        <v>8</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>40000</v>
+        <v>20</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>48</v>
+        <v>6000</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>16</v>
+        <v>40000</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2000</v>
+        <v>6</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>300</v>
+        <v>0.5</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>16</v>
+        <v>1.5</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>0.35</v>
+        <v>5</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>80</v>
+        <v>0.35</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1.5</v>
+        <v>500</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -3398,15 +3398,15 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -3414,15 +3414,15 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3430,15 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3446,15 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3462,15 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3494,15 +3494,15 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>34</v>
+        <v>0.5</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3510,15 +3510,15 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3526,15 +3526,15 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>100</v>
+        <v>1.5</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3542,15 +3542,15 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3558,15 +3558,15 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3574,15 +3574,15 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3590,15 +3590,15 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3606,15 +3606,15 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3622,15 +3622,15 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3638,15 +3638,15 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3654,15 +3654,15 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3670,15 +3670,15 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3686,15 +3686,15 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3702,15 +3702,15 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3734,15 +3734,15 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3750,15 +3750,15 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3766,15 +3766,15 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>0.8</v>
+        <v>64</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -3782,15 +3782,15 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -3814,15 +3814,15 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -3846,15 +3846,15 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3862,15 +3862,15 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>512</v>
+        <v>10</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -3878,15 +3878,15 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1024</v>
+        <v>9</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3894,15 +3894,15 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>512</v>
+        <v>1.2</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -3910,15 +3910,15 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3926,15 +3926,15 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -3942,15 +3942,15 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2</v>
+        <v>512</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -3958,15 +3958,15 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1.2</v>
+        <v>1024</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -3974,15 +3974,15 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3</v>
+        <v>512</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -3990,15 +3990,15 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -4006,15 +4006,15 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>16</v>
+        <v>0.6</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -4022,15 +4022,15 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4038,15 +4038,15 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -4054,15 +4054,15 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -4070,15 +4070,15 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -4086,15 +4086,15 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -4102,15 +4102,15 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_epic</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -4118,15 +4118,15 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>grid.relocate_seconds</t>
+          <t>firmware.library.refresh_seconds</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
         </is>
       </c>
     </row>
@@ -4134,15 +4134,15 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>grid.batch_demolish_confirm</t>
+          <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
         </is>
       </c>
     </row>
@@ -4150,15 +4150,15 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>grid.pollution_warn_level</t>
+          <t>firmware.restore.cost_common</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
         </is>
       </c>
     </row>
@@ -4166,15 +4166,15 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>grid.drag_max_cells</t>
+          <t>firmware.restore.cost_rare</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>256</v>
+        <v>8</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>grid.explore_machine_radius</t>
+          <t>firmware.restore.cost_epic</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4198,15 +4198,15 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>grid.explore_lattice</t>
+          <t>grid.relocate_seconds</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
         </is>
       </c>
     </row>
@@ -4214,15 +4214,15 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>grid.explore_machines_per_step</t>
+          <t>grid.batch_demolish_confirm</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
         </is>
       </c>
     </row>
@@ -4230,15 +4230,15 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>build.carry_per_trip</t>
+          <t>grid.pollution_warn_level</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
         </is>
       </c>
     </row>
@@ -4246,13 +4246,93 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
+          <t>grid.drag_max_cells</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>256</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>grid.explore_machine_radius</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>12</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>grid.explore_lattice</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>4</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>grid.explore_machines_per_step</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>40</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
           <t>build.belt_seconds_per_cell</t>
         </is>
       </c>
-      <c r="C239" t="n">
+      <c r="C244" t="n">
         <v>1</v>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D244"/>
+  <dimension ref="A1:D252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2246,15 +2246,15 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>combat.grid_cell_m</t>
+          <t>diag.refresh_seconds</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+          <t>“为什么不工作”面板 / 堵塞叠加层开着时诊断的刷新间隔(真实秒;暂停中也刷新;只读派生,不影响模拟)</t>
         </is>
       </c>
     </row>
@@ -2262,15 +2262,15 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>combat.events.gameplay_per_step</t>
+          <t>diag.max_reports</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+          <t>诊断清单最多列多少个停工对象(超出的写“还有 N 处”,先解决上面的)</t>
         </is>
       </c>
     </row>
@@ -2278,15 +2278,15 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>combat.events.cues_per_step</t>
+          <t>diag.max_belt_roots</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+          <t>每次诊断最多追溯多少个传送带堵塞源头(逐格扫描在 AOT 内核)</t>
         </is>
       </c>
     </row>
@@ -2294,15 +2294,15 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>combat.projectile_capacity</t>
+          <t>diag.slice_buildings</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4096</v>
+        <v>32</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+          <t>分帧诊断:每帧最多诊断几座建筑(施工 / 传送带网络 / 流体网络各占一帧;整轮做完才更新清单;保证任何一帧的开销与建筑总数无关)</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>combat.compact_ratio</t>
+          <t>overlay.refresh_seconds</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+          <t>叠加层线条 / 标记 / 标签的重建间隔(真实秒;数据变化时立即重建)</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2326,15 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>combat.fuse_trace_seconds</t>
+          <t>overlay.max_labels</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.15</v>
+        <v>48</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
+          <t>叠加层世界标签最多同时显示几条(离镜头焦点近的优先;每帧只投影这么多条)</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2342,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>overlay.max_markers</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.6</v>
+        <v>256</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>叠加层线条 / 施工方框 / 停工标记的上限(超出的不画,清单里照样有)</t>
         </is>
       </c>
     </row>
@@ -2358,15 +2358,15 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>overlay.raid_outpost_radius</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>突袭路径叠加层:离归还核心多少格以内的敌方据点画“可能来路”(格)</t>
         </is>
       </c>
     </row>
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>combat.grid_cell_m</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>combat.events.gameplay_per_step</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.6</v>
+        <v>64</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>combat.events.cues_per_step</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>combat.projectile_capacity</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>16</v>
+        <v>4096</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
         </is>
       </c>
     </row>
@@ -2438,15 +2438,15 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>combat.compact_ratio</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1.2</v>
+        <v>0.15</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.15</v>
+        <v>120</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>400</v>
+        <v>3.5</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>24</v>
+        <v>1.2</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.2</v>
+        <v>18</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>200</v>
+        <v>0.15</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.5</v>
+        <v>24</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>8</v>
+        <v>0.2</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>1500</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>6000</v>
+        <v>25</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>40000</v>
+        <v>0.5</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>200</v>
+        <v>40000</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1.5</v>
+        <v>300</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -3142,15 +3142,15 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0.35</v>
+        <v>1.5</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>500</v>
+        <v>5</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1.5</v>
+        <v>0.35</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -3398,15 +3398,15 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -3414,15 +3414,15 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3430,15 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0.5</v>
+        <v>200</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3446,15 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3462,15 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -3494,15 +3494,15 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -3510,15 +3510,15 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -3526,15 +3526,15 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -3542,15 +3542,15 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -3558,15 +3558,15 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>67</v>
+        <v>0.5</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -3574,15 +3574,15 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -3590,15 +3590,15 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -3606,15 +3606,15 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3638,15 +3638,15 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3654,15 +3654,15 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>200</v>
+        <v>1.5</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3670,15 +3670,15 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3686,15 +3686,15 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3702,15 +3702,15 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3718,15 +3718,15 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3734,15 +3734,15 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3750,15 +3750,15 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3766,15 +3766,15 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3782,15 +3782,15 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.3</v>
+        <v>200</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3814,15 +3814,15 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3846,15 +3846,15 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3862,15 +3862,15 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3878,15 +3878,15 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3894,15 +3894,15 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1.2</v>
+        <v>64</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -3910,15 +3910,15 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -3926,15 +3926,15 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -3942,15 +3942,15 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>512</v>
+        <v>8</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -3958,15 +3958,15 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1024</v>
+        <v>0.4</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -3974,15 +3974,15 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>512</v>
+        <v>0.8</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3990,15 +3990,15 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.15</v>
+        <v>10</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -4006,15 +4006,15 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>0.6</v>
+        <v>9</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4022,15 +4022,15 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -4038,15 +4038,15 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4054,15 +4054,15 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -4070,15 +4070,15 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>8</v>
+        <v>512</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -4086,15 +4086,15 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>16</v>
+        <v>1024</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -4102,15 +4102,15 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>5</v>
+        <v>512</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -4118,15 +4118,15 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -4134,15 +4134,15 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -4150,15 +4150,15 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4166,15 +4166,15 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -4182,15 +4182,15 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_epic</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -4198,15 +4198,15 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>grid.relocate_seconds</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -4214,15 +4214,15 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>grid.batch_demolish_confirm</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -4230,15 +4230,15 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>grid.pollution_warn_level</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -4246,15 +4246,15 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>grid.drag_max_cells</t>
+          <t>firmware.library.refresh_seconds</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>256</v>
+        <v>0.5</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
         </is>
       </c>
     </row>
@@ -4262,15 +4262,15 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>grid.explore_machine_radius</t>
+          <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>grid.explore_lattice</t>
+          <t>firmware.restore.cost_common</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
         </is>
       </c>
     </row>
@@ -4294,15 +4294,15 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>grid.explore_machines_per_step</t>
+          <t>firmware.restore.cost_rare</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4310,15 +4310,15 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>build.carry_per_trip</t>
+          <t>firmware.restore.cost_epic</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4326,13 +4326,141 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
+          <t>grid.relocate_seconds</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>20</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>grid.batch_demolish_confirm</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>20</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>grid.pollution_warn_level</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>1</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>grid.drag_max_cells</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>256</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>grid.explore_machine_radius</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>12</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>grid.explore_lattice</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>4</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>grid.explore_machines_per_step</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>40</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
           <t>build.belt_seconds_per_cell</t>
         </is>
       </c>
-      <c r="C244" t="n">
+      <c r="C252" t="n">
         <v>1</v>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D252"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>combat.grid_cell_m</t>
+          <t>home.visual_slice_buildings</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+          <t>家园画面对账(DEBT-FG0ARCH04-09):镜头在家园时每帧最多轮询几座建筑的外观(颜色/朝向/状态标记);建筑增删、电网/施工变化时立即整份对账一次,其余变化最迟 建筑数÷本值 帧内画出来;保证每帧开销与建筑总数无关</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>combat.events.gameplay_per_step</t>
+          <t>combat.grid_cell_m</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>combat.events.cues_per_step</t>
+          <t>combat.events.gameplay_per_step</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>combat.projectile_capacity</t>
+          <t>combat.events.cues_per_step</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4096</v>
+        <v>24</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
         </is>
       </c>
     </row>
@@ -2438,15 +2438,15 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>combat.compact_ratio</t>
+          <t>combat.projectile_capacity</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.5</v>
+        <v>4096</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>combat.fuse_trace_seconds</t>
+          <t>combat.compact_ratio</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>120</v>
+        <v>0.6</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3.5</v>
+        <v>120</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>60</v>
+        <v>0.6</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>18</v>
+        <v>1.2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.15</v>
+        <v>18</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>400</v>
+        <v>0.15</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>24</v>
+        <v>0.5</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.2</v>
+        <v>24</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>200</v>
+        <v>0.2</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1500</v>
+        <v>80</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>6</v>
+        <v>1500</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.25</v>
+        <v>25</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>6000</v>
+        <v>64</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4</v>
+        <v>6000</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>40000</v>
+        <v>4</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>6</v>
+        <v>40000</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.5</v>
+        <v>48</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>16</v>
+        <v>0.5</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2000</v>
+        <v>16</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>32</v>
+        <v>300</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -3142,15 +3142,15 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1.5</v>
+        <v>24</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>0.35</v>
+        <v>2</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>150</v>
+        <v>0.35</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -3398,15 +3398,15 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -3414,15 +3414,15 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3430,15 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3446,15 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3462,15 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -3494,15 +3494,15 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1.5</v>
+        <v>500</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -3510,15 +3510,15 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -3526,15 +3526,15 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -3542,15 +3542,15 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -3558,15 +3558,15 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -3574,15 +3574,15 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -3590,15 +3590,15 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -3606,15 +3606,15 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -3622,15 +3622,15 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3638,15 +3638,15 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3654,15 +3654,15 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3670,15 +3670,15 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>60</v>
+        <v>1.5</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3686,15 +3686,15 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3702,15 +3702,15 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3718,15 +3718,15 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3734,15 +3734,15 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3750,15 +3750,15 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3766,15 +3766,15 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3782,15 +3782,15 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3814,15 +3814,15 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3846,15 +3846,15 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3862,15 +3862,15 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3878,15 +3878,15 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3894,15 +3894,15 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3910,15 +3910,15 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>0.3</v>
+        <v>64</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -3926,15 +3926,15 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -3942,15 +3942,15 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -3958,15 +3958,15 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0.4</v>
+        <v>8</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -3974,15 +3974,15 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -3990,15 +3990,15 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4006,15 +4006,15 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -4022,15 +4022,15 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>1.2</v>
+        <v>9</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4038,15 +4038,15 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4070,15 +4070,15 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>512</v>
+        <v>0.5</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -4086,15 +4086,15 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -4102,15 +4102,15 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -4118,15 +4118,15 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0.15</v>
+        <v>512</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -4134,15 +4134,15 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -4150,15 +4150,15 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -4166,15 +4166,15 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4182,15 +4182,15 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -4198,15 +4198,15 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -4214,15 +4214,15 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -4230,15 +4230,15 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -4246,15 +4246,15 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -4262,15 +4262,15 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>firmware.library.refresh_seconds</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
         </is>
       </c>
     </row>
@@ -4278,15 +4278,15 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
         </is>
       </c>
     </row>
@@ -4294,15 +4294,15 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>firmware.restore.cost_common</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
         </is>
       </c>
     </row>
@@ -4310,15 +4310,15 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_epic</t>
+          <t>firmware.restore.cost_rare</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4326,15 +4326,15 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>grid.relocate_seconds</t>
+          <t>firmware.restore.cost_epic</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>grid.batch_demolish_confirm</t>
+          <t>grid.relocate_seconds</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
         </is>
       </c>
     </row>
@@ -4358,15 +4358,15 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>grid.pollution_warn_level</t>
+          <t>grid.batch_demolish_confirm</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
         </is>
       </c>
     </row>
@@ -4374,15 +4374,15 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>grid.drag_max_cells</t>
+          <t>grid.pollution_warn_level</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>256</v>
+        <v>1</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
         </is>
       </c>
     </row>
@@ -4390,15 +4390,15 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>grid.explore_machine_radius</t>
+          <t>grid.drag_max_cells</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
         </is>
       </c>
     </row>
@@ -4406,15 +4406,15 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>grid.explore_lattice</t>
+          <t>grid.explore_machine_radius</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
         </is>
       </c>
     </row>
@@ -4422,15 +4422,15 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>grid.explore_machines_per_step</t>
+          <t>grid.explore_lattice</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
         </is>
       </c>
     </row>
@@ -4438,15 +4438,15 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>build.carry_per_trip</t>
+          <t>grid.explore_machines_per_step</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
         </is>
       </c>
     </row>
@@ -4454,13 +4454,29 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
+          <t>build.carry_per_trip</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>40</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
           <t>build.belt_seconds_per_cell</t>
         </is>
       </c>
-      <c r="C252" t="n">
+      <c r="C253" t="n">
         <v>1</v>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D253"/>
+  <dimension ref="A1:D257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>eco.flow.sample_seconds</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>物品库存采样间隔(游戏秒;净速率=窗口首尾库存差,按世界步采样,与观察无关;FG04 第7节统计按时间窗口聚合)</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>eco.flow.window_samples</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>净速率窗口的采样段数(初值 6 段 × 10 游戏秒 = 1 游戏分钟;FG4-ECO-08 扩四个时间窗口)</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>eco.hover.refresh_seconds</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>6000</v>
+        <v>0.5</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>物品悬停 / 物资面板“总库存 / 分布”的定时重读间隔(真实秒;库存变化不提前失效,端口每个内核步都在改库存;只在开面板 / 读档 / 换表 / 端口绑定变化时提前重建;不每帧计算)</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>eco.vault.capacity</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>999</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>核心保管库每种物品的容量(关键材料由任务固定给出,数量很少;只防异常数据)</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>40000</v>
+        <v>6</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>6</v>
+        <v>6000</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.5</v>
+        <v>40000</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2000</v>
+        <v>6</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -3142,15 +3142,15 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>32</v>
+        <v>2000</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0.35</v>
+        <v>8</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -3398,15 +3398,15 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -3414,15 +3414,15 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3430,15 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3446,15 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>200</v>
+        <v>0.35</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3462,15 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -3510,15 +3510,15 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1.5</v>
+        <v>200</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -3526,15 +3526,15 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -3542,15 +3542,15 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -3558,15 +3558,15 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -3574,15 +3574,15 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -3590,15 +3590,15 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -3606,15 +3606,15 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -3622,15 +3622,15 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -3670,15 +3670,15 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -3686,15 +3686,15 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3702,15 +3702,15 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>67</v>
+        <v>0.5</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3718,15 +3718,15 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3734,15 +3734,15 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3750,15 +3750,15 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3766,15 +3766,15 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>0.5</v>
+        <v>67</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3782,15 +3782,15 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3814,15 +3814,15 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3846,15 +3846,15 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3862,15 +3862,15 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3878,15 +3878,15 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3894,15 +3894,15 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3910,15 +3910,15 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3926,15 +3926,15 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3942,15 +3942,15 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3958,15 +3958,15 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3974,15 +3974,15 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0.4</v>
+        <v>64</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -3990,15 +3990,15 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -4006,15 +4006,15 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -4022,15 +4022,15 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -4038,15 +4038,15 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -4054,15 +4054,15 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4070,15 +4070,15 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -4086,15 +4086,15 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>512</v>
+        <v>9</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4102,15 +4102,15 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1024</v>
+        <v>1.2</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -4118,15 +4118,15 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>512</v>
+        <v>0.5</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4134,15 +4134,15 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -4150,15 +4150,15 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>0.6</v>
+        <v>512</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -4166,15 +4166,15 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>2</v>
+        <v>1024</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -4182,15 +4182,15 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1.2</v>
+        <v>512</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -4198,15 +4198,15 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3</v>
+        <v>0.15</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -4214,15 +4214,15 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -4230,15 +4230,15 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4246,15 +4246,15 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -4262,15 +4262,15 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -4278,15 +4278,15 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -4294,15 +4294,15 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -4310,15 +4310,15 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -4326,15 +4326,15 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_epic</t>
+          <t>firmware.library.refresh_seconds</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
         </is>
       </c>
     </row>
@@ -4342,15 +4342,15 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>grid.relocate_seconds</t>
+          <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
         </is>
       </c>
     </row>
@@ -4358,15 +4358,15 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>grid.batch_demolish_confirm</t>
+          <t>firmware.restore.cost_common</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
         </is>
       </c>
     </row>
@@ -4374,15 +4374,15 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>grid.pollution_warn_level</t>
+          <t>firmware.restore.cost_rare</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4390,15 +4390,15 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>grid.drag_max_cells</t>
+          <t>firmware.restore.cost_epic</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>256</v>
+        <v>12</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4406,15 +4406,15 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>grid.explore_machine_radius</t>
+          <t>grid.relocate_seconds</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
         </is>
       </c>
     </row>
@@ -4422,15 +4422,15 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>grid.explore_lattice</t>
+          <t>grid.batch_demolish_confirm</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>grid.explore_machines_per_step</t>
+          <t>grid.pollution_warn_level</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
         </is>
       </c>
     </row>
@@ -4454,15 +4454,15 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>build.carry_per_trip</t>
+          <t>grid.drag_max_cells</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>40</v>
+        <v>256</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
         </is>
       </c>
     </row>
@@ -4470,13 +4470,77 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
+          <t>grid.explore_machine_radius</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>12</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>grid.explore_lattice</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>4</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>grid.explore_machines_per_step</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>40</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
           <t>build.belt_seconds_per_cell</t>
         </is>
       </c>
-      <c r="C253" t="n">
+      <c r="C257" t="n">
         <v>1</v>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D257"/>
+  <dimension ref="A1:D265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4546,6 +4546,134 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>eco.prod.step_ticks</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>3</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>生产建筑每隔几个世界步推进一次(世界 60 Hz,3 = 20 Hz,与传送带同一节拍);进度按游戏时钟步数累计,与观察 / 倍速无关</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>eco.prod.sync_seconds</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>生产建筑与管线(流体口)、建筑状态对账的间隔(游戏秒):建成 / 修好 / 转向 / 搬迁 / 拆除后最迟这么久流体口跟上</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>eco.prod.fluid_intake_factor</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>配方建筑流体输入口的抽取速率 = 配方额定用量 × 这个倍数(升/分钟):缓存满了就不再要,不会多抽</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>eco.ruin.scrap_per_cell</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>80</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>每格废墟的废料储量(回收站逐格拆;一格拆完变成可建空地)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>eco.ruin.act1_two_hour_scrap</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>第一幕前两小时的废料需求估算(ADR-ECO-002 第 4 节:修复 / 第一批建筑 / 传送带 / 电塔 / 中继 / 早期废料炼合金);起始区保证的废墟群储量必须不少于它(DEBT-FG3GEN01-03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>eco.vibration.max</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>100</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>家园震动值上限(FG10 FGR-EVT-010:0~100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>eco.vibration.decay_per_minute</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>2</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>家园震动值每游戏分钟自然衰减(FG10 初值 -2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>eco.prod.sources_shown</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>3</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>提取钻悬停 / 面板里列出的主要震动来源数</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D265"/>
+  <dimension ref="A1:D267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4674,6 +4674,38 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>eco.assembly.buffer_per_item</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>20</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>装配站材料缓存每种物品最多放几件(输入口送来的机器材料先进这里;放满了带停下)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>eco.assembly.scrap_substitute_default</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>1</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>装配站“缺材料时用废料代付”的默认值(1 开 / 0 关;玩家在装配站面板改,跟存档走)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D267"/>
+  <dimension ref="A1:D272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2118,15 +2118,15 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>power.sample_seconds</t>
+          <t>logistics.pipe.underground_span_t1</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>电网曲线每隔多少游戏秒记一个点(FGR-LOG-061;按游戏时钟,暂停不记、倍速同比)</t>
+          <t>地下管线 T1 最多跨几格(两口之间的格数);吞吐同 T1 管线</t>
         </is>
       </c>
     </row>
@@ -2134,15 +2134,15 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>power.curve_samples</t>
+          <t>logistics.pipe.underground_span_t2</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>每个电网曲线最多保留多少个点(90 × 10 秒 = 最近 15 游戏分钟),进存档</t>
+          <t>地下管线 T2 最多跨几格(两口之间的格数);吞吐同 T2 管线</t>
         </is>
       </c>
     </row>
@@ -2150,15 +2150,15 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>power.preview_max_nodes</t>
+          <t>power.sample_seconds</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>放置预览最多检查附近多少个电力节点(防止极端布局下预览卡顿;超出只少报连到的电网,不影响结算)</t>
+          <t>电网曲线每隔多少游戏秒记一个点(FGR-LOG-061;按游戏时钟,暂停不记、倍速同比)</t>
         </is>
       </c>
     </row>
@@ -2166,15 +2166,15 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>plan.undo_depth</t>
+          <t>power.curve_samples</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>撤销栈保留这么多步(FGR-LOG-009 初值 50,更早的丢掉);一步 = 一次玩家操作(粘贴、框选拆除算一步);单步件数上限 = plan.layout_max_entries,存档体积有上界</t>
+          <t>每个电网曲线最多保留多少个点(90 × 10 秒 = 最近 15 游戏分钟),进存档</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>plan.layout_max</t>
+          <t>power.preview_max_nodes</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>布局库最多保存几个布局(跨存档共享,存在玩家配置目录)</t>
+          <t>放置预览最多检查附近多少个电力节点(防止极端布局下预览卡顿;超出只少报连到的电网,不影响结算)</t>
         </is>
       </c>
     </row>
@@ -2198,15 +2198,15 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>plan.layout_max_entries</t>
+          <t>plan.undo_depth</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1024</v>
+        <v>50</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>一次复制 / 一个布局最多几件(超出给原因,不静默截断)</t>
+          <t>撤销栈保留这么多步(FGR-LOG-009 初值 50,更早的丢掉);一步 = 一次玩家操作(粘贴、框选拆除算一步);单步件数上限 = plan.layout_max_entries,存档体积有上界</t>
         </is>
       </c>
     </row>
@@ -2214,15 +2214,15 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>plan.preview_max_tiles</t>
+          <t>plan.layout_max</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1024</v>
+        <v>64</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>粘贴预览最多画几格虚影(超出的件照常校验与放置,只是不画;状态行写明)</t>
+          <t>布局库最多保存几个布局(跨存档共享,存在玩家配置目录)</t>
         </is>
       </c>
     </row>
@@ -2230,15 +2230,15 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>plan.thumbnail_px</t>
+          <t>plan.layout_max_entries</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>64</v>
+        <v>1024</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>布局缩略图边长(像素)</t>
+          <t>一次复制 / 一个布局最多几件(超出给原因,不静默截断)</t>
         </is>
       </c>
     </row>
@@ -2246,15 +2246,15 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>diag.refresh_seconds</t>
+          <t>plan.preview_max_tiles</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.5</v>
+        <v>1024</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>“为什么不工作”面板 / 堵塞叠加层开着时诊断的刷新间隔(真实秒;暂停中也刷新;只读派生,不影响模拟)</t>
+          <t>粘贴预览最多画几格虚影(超出的件照常校验与放置,只是不画;状态行写明)</t>
         </is>
       </c>
     </row>
@@ -2262,15 +2262,15 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>diag.max_reports</t>
+          <t>plan.thumbnail_px</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>诊断清单最多列多少个停工对象(超出的写“还有 N 处”,先解决上面的)</t>
+          <t>布局缩略图边长(像素)</t>
         </is>
       </c>
     </row>
@@ -2278,15 +2278,15 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>diag.max_belt_roots</t>
+          <t>diag.refresh_seconds</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>64</v>
+        <v>0.5</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>每次诊断最多追溯多少个传送带堵塞源头(逐格扫描在 AOT 内核)</t>
+          <t>“为什么不工作”面板 / 堵塞叠加层开着时诊断的刷新间隔(真实秒;暂停中也刷新;只读派生,不影响模拟)</t>
         </is>
       </c>
     </row>
@@ -2294,15 +2294,15 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>diag.slice_buildings</t>
+          <t>diag.max_reports</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>分帧诊断:每帧最多诊断几座建筑(施工 / 传送带网络 / 流体网络各占一帧;整轮做完才更新清单;保证任何一帧的开销与建筑总数无关)</t>
+          <t>诊断清单最多列多少个停工对象(超出的写“还有 N 处”,先解决上面的)</t>
         </is>
       </c>
     </row>
@@ -2310,15 +2310,15 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>overlay.refresh_seconds</t>
+          <t>diag.max_belt_roots</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.5</v>
+        <v>64</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>叠加层线条 / 标记 / 标签的重建间隔(真实秒;数据变化时立即重建)</t>
+          <t>每次诊断最多追溯多少个传送带堵塞源头(逐格扫描在 AOT 内核)</t>
         </is>
       </c>
     </row>
@@ -2326,15 +2326,15 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>overlay.max_labels</t>
+          <t>diag.slice_buildings</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>叠加层世界标签最多同时显示几条(离镜头焦点近的优先;每帧只投影这么多条)</t>
+          <t>分帧诊断:每帧最多诊断几座建筑(施工 / 传送带网络 / 流体网络各占一帧;整轮做完才更新清单;保证任何一帧的开销与建筑总数无关)</t>
         </is>
       </c>
     </row>
@@ -2342,15 +2342,15 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>overlay.max_markers</t>
+          <t>overlay.refresh_seconds</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>256</v>
+        <v>0.5</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>叠加层线条 / 施工方框 / 停工标记的上限(超出的不画,清单里照样有)</t>
+          <t>叠加层线条 / 标记 / 标签的重建间隔(真实秒;数据变化时立即重建)</t>
         </is>
       </c>
     </row>
@@ -2358,15 +2358,15 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>overlay.raid_outpost_radius</t>
+          <t>overlay.max_labels</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>400</v>
+        <v>48</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>突袭路径叠加层:离归还核心多少格以内的敌方据点画“可能来路”(格)</t>
+          <t>叠加层世界标签最多同时显示几条(离镜头焦点近的优先;每帧只投影这么多条)</t>
         </is>
       </c>
     </row>
@@ -2374,15 +2374,15 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>home.visual_slice_buildings</t>
+          <t>overlay.max_markers</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>48</v>
+        <v>256</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>家园画面对账(DEBT-FG0ARCH04-09):镜头在家园时每帧最多轮询几座建筑的外观(颜色/朝向/状态标记);建筑增删、电网/施工变化时立即整份对账一次,其余变化最迟 建筑数÷本值 帧内画出来;保证每帧开销与建筑总数无关</t>
+          <t>叠加层线条 / 施工方框 / 停工标记的上限(超出的不画,清单里照样有)</t>
         </is>
       </c>
     </row>
@@ -2390,15 +2390,15 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>combat.grid_cell_m</t>
+          <t>overlay.raid_outpost_radius</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
+          <t>突袭路径叠加层:离归还核心多少格以内的敌方据点画“可能来路”(格)</t>
         </is>
       </c>
     </row>
@@ -2406,15 +2406,15 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>combat.events.gameplay_per_step</t>
+          <t>home.visual_slice_buildings</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
+          <t>家园画面对账(DEBT-FG0ARCH04-09):镜头在家园时每帧最多轮询几座建筑的外观(颜色/朝向/状态标记);建筑增删、电网/施工变化时立即整份对账一次,其余变化最迟 建筑数÷本值 帧内画出来;保证每帧开销与建筑总数无关</t>
         </is>
       </c>
     </row>
@@ -2422,15 +2422,15 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>combat.events.cues_per_step</t>
+          <t>combat.grid_cell_m</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
+          <t>战斗内核空间网格格边长(米);目标选择与弹体碰撞按格查询,结果只由比较规则决定(确定性)</t>
         </is>
       </c>
     </row>
@@ -2438,15 +2438,15 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>combat.projectile_capacity</t>
+          <t>combat.events.gameplay_per_step</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>4096</v>
+        <v>64</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
+          <t>每个地点每步最多交给热更层处理的玩法事件数(阵亡/伤害请求/命令结束等);超出的留到下一步,永不丢弃,进存档</t>
         </is>
       </c>
     </row>
@@ -2454,15 +2454,15 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>combat.compact_ratio</t>
+          <t>combat.events.cues_per_step</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.5</v>
+        <v>24</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
+          <t>每个地点每步最多保留的提示事件数(开火音/护甲命中等);超出的丢弃并计数(B17 同类音效有数量上限)</t>
         </is>
       </c>
     </row>
@@ -2470,15 +2470,15 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>combat.fuse_trace_seconds</t>
+          <t>combat.projectile_capacity</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.15</v>
+        <v>4096</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
+          <t>每个地点同时存在的弹体上限;超出的开火不生成弹体并计数(FGR-SYS-041 目标 1500)</t>
         </is>
       </c>
     </row>
@@ -2486,15 +2486,15 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>combat.render.unit_height</t>
+          <t>combat.compact_ratio</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
+          <t>阵亡即移除的单位占槽位比例超过此值时在步首压实(保持相对顺序)</t>
         </is>
       </c>
     </row>
@@ -2502,15 +2502,15 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>combat.bench.raider_hp</t>
+          <t>combat.fuse_trace_seconds</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>120</v>
+        <v>0.15</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>突袭者原型耐久</t>
+          <t>装了引信类固件的武器每次开火留下的弹迹与炮口装定闪光停留的游戏秒(按游戏时间淡出,暂停静止;表现数据不进快照)</t>
         </is>
       </c>
     </row>
@@ -2518,15 +2518,15 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>combat.bench.raider_speed</t>
+          <t>combat.render.unit_height</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>突袭者原型移动速度(米/游戏秒)</t>
+          <t>实例化单位(突袭者/炮塔原型)圆片的画面高度(世界单位)</t>
         </is>
       </c>
     </row>
@@ -2534,15 +2534,15 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>combat.bench.raider_radius</t>
+          <t>combat.bench.raider_hp</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.6</v>
+        <v>120</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>突袭者原型半径(米)</t>
+          <t>突袭者原型耐久</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2550,15 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>combat.bench.raider_sense</t>
+          <t>combat.bench.raider_speed</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>60</v>
+        <v>3.5</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
+          <t>突袭者原型移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2566,15 +2566,15 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>combat.bench.raider_range</t>
+          <t>combat.bench.raider_radius</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>16</v>
+        <v>0.6</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>突袭者原型射程(米)</t>
+          <t>突袭者原型半径(米)</t>
         </is>
       </c>
     </row>
@@ -2582,15 +2582,15 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>combat.bench.raider_damage</t>
+          <t>combat.bench.raider_sense</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>突袭者原型每发伤害</t>
+          <t>突袭者原型感知距离(米):范围内有己方目标就扑过去,否则朝目标点前进</t>
         </is>
       </c>
     </row>
@@ -2598,15 +2598,15 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>combat.bench.raider_cooldown</t>
+          <t>combat.bench.raider_range</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1.2</v>
+        <v>16</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>突袭者原型开火间隔(游戏秒)</t>
+          <t>突袭者原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2614,15 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_speed</t>
+          <t>combat.bench.raider_damage</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>突袭者原型弹速(米/游戏秒)</t>
+          <t>突袭者原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2630,15 +2630,15 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>combat.bench.raider_projectile_radius</t>
+          <t>combat.bench.raider_cooldown</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.15</v>
+        <v>1.2</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>突袭者原型弹体半径(米)</t>
+          <t>突袭者原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>combat.bench.turret_hp</t>
+          <t>combat.bench.raider_projectile_speed</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>炮塔原型耐久</t>
+          <t>突袭者原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2662,15 +2662,15 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>combat.bench.turret_radius</t>
+          <t>combat.bench.raider_projectile_radius</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
+          <t>突袭者原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2678,15 +2678,15 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>combat.bench.turret_range</t>
+          <t>combat.bench.turret_hp</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>26</v>
+        <v>400</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>炮塔原型射程(米)</t>
+          <t>炮塔原型耐久</t>
         </is>
       </c>
     </row>
@@ -2694,15 +2694,15 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>combat.bench.turret_damage</t>
+          <t>combat.bench.turret_radius</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>炮塔原型每发伤害</t>
+          <t>炮塔原型半径(米,轻型 2x2 占地的内切圆)</t>
         </is>
       </c>
     </row>
@@ -2710,15 +2710,15 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>combat.bench.turret_cooldown</t>
+          <t>combat.bench.turret_range</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.5</v>
+        <v>26</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>炮塔原型开火间隔(游戏秒)</t>
+          <t>炮塔原型射程(米)</t>
         </is>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_speed</t>
+          <t>combat.bench.turret_damage</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>炮塔原型弹速(米/游戏秒)</t>
+          <t>炮塔原型每发伤害</t>
         </is>
       </c>
     </row>
@@ -2742,15 +2742,15 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>combat.bench.turret_projectile_radius</t>
+          <t>combat.bench.turret_cooldown</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>炮塔原型弹体半径(米)</t>
+          <t>炮塔原型开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2758,15 +2758,15 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>combat.perf.enemies</t>
+          <t>combat.bench.turret_projectile_speed</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>性能场景:同时存在的敌人数</t>
+          <t>炮塔原型弹速(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2774,15 +2774,15 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>combat.perf.turrets</t>
+          <t>combat.bench.turret_projectile_radius</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>80</v>
+        <v>0.2</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>性能场景:炮塔数</t>
+          <t>炮塔原型弹体半径(米)</t>
         </is>
       </c>
     </row>
@@ -2790,15 +2790,15 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>combat.perf.min_projectiles</t>
+          <t>combat.perf.enemies</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
+          <t>性能场景:同时存在的敌人数</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>combat.perf.step_budget_ms</t>
+          <t>combat.perf.turrets</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
+          <t>性能场景:炮塔数</t>
         </is>
       </c>
     </row>
@@ -2822,15 +2822,15 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>combat.perf.hp_scale</t>
+          <t>combat.perf.min_projectiles</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>25</v>
+        <v>1500</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
+          <t>性能场景:测量窗口内同时存在的弹体数下限</t>
         </is>
       </c>
     </row>
@@ -2838,15 +2838,15 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>combat.perf.turret_cooldown</t>
+          <t>combat.perf.step_budget_ms</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>性能场景:炮塔开火间隔(游戏秒)</t>
+          <t>战斗内核单步预算(毫秒,推荐配置;FGR-SYS-042 内核(物流+战斗)&lt;=6ms)</t>
         </is>
       </c>
     </row>
@@ -2854,15 +2854,15 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>combat.perf.raider_cooldown</t>
+          <t>combat.perf.hp_scale</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.5</v>
+        <v>25</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>性能场景:突袭者开火间隔(游戏秒)</t>
+          <t>性能场景:突袭者与炮塔耐久倍率(让测量窗口内双方数量保持在规模目标附近)</t>
         </is>
       </c>
     </row>
@@ -2870,15 +2870,15 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>combat.perf.projectile_speed</t>
+          <t>combat.perf.turret_cooldown</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>8</v>
+        <v>0.25</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
+          <t>性能场景:炮塔开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2886,15 +2886,15 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>combat.perf.turret_range</t>
+          <t>combat.perf.raider_cooldown</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>性能场景:炮塔射程(米)</t>
+          <t>性能场景:突袭者开火间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -2902,15 +2902,15 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>combat.perf.raider_range</t>
+          <t>combat.perf.projectile_speed</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>性能场景:突袭者射程(米)</t>
+          <t>性能场景:弹速(米/游戏秒;较慢,让弹体在空中停留更久,达到同时存在的弹体数目标)</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>eco.flow.sample_seconds</t>
+          <t>combat.perf.turret_range</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>物品库存采样间隔(游戏秒;净速率=窗口首尾库存差,按世界步采样,与观察无关;FG04 第7节统计按时间窗口聚合)</t>
+          <t>性能场景:炮塔射程(米)</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>eco.flow.window_samples</t>
+          <t>combat.perf.raider_range</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>净速率窗口的采样段数(初值 6 段 × 10 游戏秒 = 1 游戏分钟;FG4-ECO-08 扩四个时间窗口)</t>
+          <t>性能场景:突袭者射程(米)</t>
         </is>
       </c>
     </row>
@@ -2950,15 +2950,15 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>eco.hover.refresh_seconds</t>
+          <t>eco.flow.sample_seconds</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>物品悬停 / 物资面板“总库存 / 分布”的定时重读间隔(真实秒;库存变化不提前失效,端口每个内核步都在改库存;只在开面板 / 读档 / 换表 / 端口绑定变化时提前重建;不每帧计算)</t>
+          <t>物品库存采样间隔(游戏秒;净速率=窗口首尾库存差,按世界步采样,与观察无关;FG04 第7节统计按时间窗口聚合)</t>
         </is>
       </c>
     </row>
@@ -2966,15 +2966,15 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>eco.vault.capacity</t>
+          <t>eco.flow.window_samples</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>999</v>
+        <v>6</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>核心保管库每种物品的容量(关键材料由任务固定给出,数量很少;只防异常数据)</t>
+          <t>净速率窗口的采样段数(初值 6 段 × 10 游戏秒 = 1 游戏分钟;FG4-ECO-08 扩四个时间窗口)</t>
         </is>
       </c>
     </row>
@@ -2982,15 +2982,15 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>nav.latency_steps</t>
+          <t>eco.hover.refresh_seconds</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
+          <t>物品悬停 / 物资面板“总库存 / 分布”的定时重读间隔(真实秒;库存变化不提前失效,端口每个内核步都在改库存;只在开面板 / 读档 / 换表 / 端口绑定变化时提前重建;不每帧计算)</t>
         </is>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>nav.batch_max_requests</t>
+          <t>eco.vault.capacity</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>64</v>
+        <v>999</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>每批最多处理的寻路请求数</t>
+          <t>核心保管库每种物品的容量(关键材料由任务固定给出,数量很少;只防异常数据)</t>
         </is>
       </c>
     </row>
@@ -3014,15 +3014,15 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>nav.batch_distance_budget</t>
+          <t>nav.latency_steps</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>6000</v>
+        <v>6</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
+          <t>寻路结果在请求批次调度后第几个模拟步采纳(固定延迟;60Hz 下 0.1 游戏秒);与工作线程快慢/帧率/倍速无关,保证确定性</t>
         </is>
       </c>
     </row>
@@ -3030,15 +3030,15 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>nav.search_margin_chunks</t>
+          <t>nav.batch_max_requests</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
+          <t>每批最多处理的寻路请求数</t>
         </is>
       </c>
     </row>
@@ -3046,15 +3046,15 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>nav.max_expansions</t>
+          <t>nav.batch_distance_budget</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>40000</v>
+        <v>6000</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
+          <t>每批请求的估算工作量上限(起终点八向距离之和,格);第一条总会处理;超出的留到下一批</t>
         </is>
       </c>
     </row>
@@ -3062,15 +3062,15 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>nav.goal_search_radius</t>
+          <t>nav.search_margin_chunks</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
+          <t>抽象搜索范围:起终点区块外接矩形向外放宽的区块数</t>
         </is>
       </c>
     </row>
@@ -3078,15 +3078,15 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>nav.start_search_radius</t>
+          <t>nav.max_expansions</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>6</v>
+        <v>40000</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
+          <t>单条请求最多展开的抽象节点数(超出按“超出寻路范围”失败)</t>
         </is>
       </c>
     </row>
@@ -3094,15 +3094,15 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>nav.smooth_lookahead</t>
+          <t>nav.goal_search_radius</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>路线拉直时一个锚点最多向前看几格</t>
+          <t>目标格走不了(压在建筑/悬崖/水上)时找就近可走格的半径(格);最大建筑 5x5,中心到外沿 3 格</t>
         </is>
       </c>
     </row>
@@ -3110,15 +3110,15 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>nav.separation_factor</t>
+          <t>nav.start_search_radius</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
+          <t>起点格走不了(机器站在建筑占地里)时找就近可走格的半径(格)</t>
         </is>
       </c>
     </row>
@@ -3126,15 +3126,15 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>nav.preview_margin_cells</t>
+          <t>nav.smooth_lookahead</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
+          <t>路线拉直时一个锚点最多向前看几格</t>
         </is>
       </c>
     </row>
@@ -3142,15 +3142,15 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>nav.perf.route_cells</t>
+          <t>nav.separation_factor</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2000</v>
+        <v>0.5</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>性能验收:长距离路线的最短长度(格)</t>
+          <t>分离:同阵营移动单位重叠时每步最大推开量占移动速度的比例(DEBT-FG0ARCH03-03);0=关</t>
         </is>
       </c>
     </row>
@@ -3158,15 +3158,15 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>nav.perf.budget_ms</t>
+          <t>nav.preview_margin_cells</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
+          <t>放置预览的可达性检查区域:全部家园建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -3174,15 +3174,15 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>nav.perf.mass_requests</t>
+          <t>nav.perf.route_cells</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>负向:同一步同时请求长路线的单位数</t>
+          <t>性能验收:长距离路线的最短长度(格)</t>
         </is>
       </c>
     </row>
@@ -3190,15 +3190,15 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>outpost.dormant_distance_cells</t>
+          <t>nav.perf.budget_ms</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
+          <t>性能验收:一条长距离路线在工作线程上的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -3206,15 +3206,15 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>outpost.wake_hysteresis_cells</t>
+          <t>nav.perf.mass_requests</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
+          <t>负向:同一步同时请求长路线的单位数</t>
         </is>
       </c>
     </row>
@@ -3222,15 +3222,15 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>outpost.wakes_per_step</t>
+          <t>outpost.dormant_distance_cells</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
+          <t>敌方据点与巡逻离所有己方实体都超过此距离(格)时休眠(FGR-GEN-052 初值 300)</t>
         </is>
       </c>
     </row>
@@ -3238,15 +3238,15 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>outpost.wake_budget_ms</t>
+          <t>outpost.wake_hysteresis_cells</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
+          <t>滞回:已唤醒的据点要离己方实体超过 休眠距离+此值 才重新休眠,避免边缘来回切换</t>
         </is>
       </c>
     </row>
@@ -3254,15 +3254,15 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>outpost.reinforce_interval_days</t>
+          <t>outpost.wakes_per_step</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
+          <t>每个模拟步最多唤醒几个据点(分帧进行,FG17 休眠唤醒行)</t>
         </is>
       </c>
     </row>
@@ -3270,15 +3270,15 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>outpost.garrison_cap</t>
+          <t>outpost.wake_budget_ms</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>原型据点驻军上限(台)</t>
+          <t>性能验收:单个据点唤醒耗时上限(毫秒,FG17 表)</t>
         </is>
       </c>
     </row>
@@ -3286,15 +3286,15 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>outpost.garrison_start</t>
+          <t>outpost.reinforce_interval_days</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>原型据点初始驻军(台)</t>
+          <t>增援间隔(游戏日;FG08“每 3 个游戏日增援一次”初值;正式规则 FG8-EXP-03)</t>
         </is>
       </c>
     </row>
@@ -3302,15 +3302,15 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>outpost.patrol_radius_cells</t>
+          <t>outpost.garrison_cap</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>原型巡逻:折返点离据点的距离(格)</t>
+          <t>原型据点驻军上限(台)</t>
         </is>
       </c>
     </row>
@@ -3318,15 +3318,15 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>outpost.patrol_speed_cells_per_second</t>
+          <t>outpost.garrison_start</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>原型巡逻行进速度(格/游戏秒)</t>
+          <t>原型据点初始驻军(台)</t>
         </is>
       </c>
     </row>
@@ -3334,15 +3334,15 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>outpost.patrol_units</t>
+          <t>outpost.patrol_radius_cells</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>原型巡逻队人数(台)</t>
+          <t>原型巡逻:折返点离据点的距离(格)</t>
         </is>
       </c>
     </row>
@@ -3350,15 +3350,15 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>signal.core.initial_slots</t>
+          <t>outpost.patrol_speed_cells_per_second</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
+          <t>原型巡逻行进速度(格/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -3366,15 +3366,15 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>signal.core.max_slots</t>
+          <t>outpost.patrol_units</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
+          <t>原型巡逻队人数(台)</t>
         </is>
       </c>
     </row>
@@ -3382,15 +3382,15 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>signal.core.max_presets</t>
+          <t>signal.core.initial_slots</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
+          <t>信号核初始槽位数(FGR-SIG-010 初值 2)</t>
         </is>
       </c>
     </row>
@@ -3398,15 +3398,15 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>signal.core.preset_name_max_chars</t>
+          <t>signal.core.max_slots</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>预设名称最多几个字(中英文都按字符数算)</t>
+          <t>信号核最多槽位数(FGR-SIG-010 初值 5);第 3～5 槽由超控阵列 T1～T3 解锁(FG4-ECO-11)</t>
         </is>
       </c>
     </row>
@@ -3414,15 +3414,15 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>signal.firmware_chip.print_scrap</t>
+          <t>signal.core.max_presets</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
+          <t>信号核预设最多保存几个(补全项:防止列表无限增长,FG00 B12)</t>
         </is>
       </c>
     </row>
@@ -3430,15 +3430,15 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>signal.uplink.quota</t>
+          <t>signal.core.preset_name_max_chars</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
+          <t>预设名称最多几个字(中英文都按字符数算)</t>
         </is>
       </c>
     </row>
@@ -3446,15 +3446,15 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>signal.uplink.transition_seconds</t>
+          <t>signal.firmware_chip.print_scrap</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>0.35</v>
+        <v>10</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
+          <t>装配站刻印一枚固件芯片的废料(过渡:固件刻录台落地前由装配站承担,DEBT-FG1SIG01-02)</t>
         </is>
       </c>
     </row>
@@ -3462,15 +3462,15 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>signal.coverage.core_radius</t>
+          <t>signal.uplink.quota</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
+          <t>接入口负载配额:信号核按槽位顺序最多插入几个固件(FGR-SIG-023 初值 2);不占电路原有负载上限</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3478,15 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_radius</t>
+          <t>signal.uplink.transition_seconds</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>300</v>
+        <v>0.35</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
+          <t>接入过渡秒数(FGR-SIG-031 沿用 0.35 秒;按真实时间计,战略暂停中不走,恢复运行后完成);过渡期间冻结冲突输入,结束才插入固件</t>
         </is>
       </c>
     </row>
@@ -3494,15 +3494,15 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>signal.coverage.tower_t2_radius</t>
+          <t>signal.coverage.core_radius</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
+          <t>归还核心的信号覆盖半径(格,FGR-SIG-050 初值 150)</t>
         </is>
       </c>
     </row>
@@ -3510,15 +3510,15 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_tower_radius</t>
+          <t>signal.coverage.tower_radius</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
+          <t>信号塔(运转且有电)的信号覆盖半径(格,FGR-SIG-050 T1 初值 300;T2 见 tower_t2_radius)</t>
         </is>
       </c>
     </row>
@@ -3526,15 +3526,15 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>signal.coverage.relay_module_radius</t>
+          <t>signal.coverage.tower_t2_radius</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
+          <t>T2 信号塔的覆盖半径(格,FGR-SIG-050 初值 500);信号塔原地升级在 FG4-ECO-05,之前全部按 T1</t>
         </is>
       </c>
     </row>
@@ -3542,15 +3542,15 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>signal.coverage.expedition_uplink_radius</t>
+          <t>signal.coverage.relay_tower_radius</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
+          <t>信号中继塔(建成即提供,不用电)的覆盖半径(格,FGR-SIG-050 / FG04 初值 200)</t>
         </is>
       </c>
     </row>
@@ -3558,15 +3558,15 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>signal.jump.far_distance_cells</t>
+          <t>signal.coverage.relay_module_radius</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
+          <t>信号中继模块(机器结构槽装“信号中继”,存活且不在装配站里)的移动覆盖半径(格,FGR-SIG-050 初值 80)</t>
         </is>
       </c>
     </row>
@@ -3574,15 +3574,15 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>signal.jump.far_transition_seconds</t>
+          <t>signal.coverage.expedition_uplink_radius</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1.5</v>
+        <v>150</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
+          <t>远征地点接入点的覆盖半径(格):远征地点仍是独立表面(DEBT-FG0ARCH01-01),派遣建立的链路以接入点为根;迁入星球领地后(FG8-GEN-02)由真实中继链取代</t>
         </is>
       </c>
     </row>
@@ -3590,15 +3590,15 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>signal.jump.far_cooldown_seconds</t>
+          <t>signal.jump.far_distance_cells</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
+          <t>远距离跳转的距离门槛(格,FGR-SIG-051 / 052 初值 500);跨地点的跳转一律算远距离</t>
         </is>
       </c>
     </row>
@@ -3606,15 +3606,15 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_cells</t>
+          <t>signal.jump.far_transition_seconds</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
+          <t>远距离跳转的过渡(真实秒,FGR-SIG-051 初值 1.5;战略暂停中不走,过渡期间整个世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -3622,15 +3622,15 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>signal.coverage.edge_warn_hysteresis_cells</t>
+          <t>signal.jump.far_cooldown_seconds</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
+          <t>远距离跳转的冷却(游戏秒,FGR-SIG-052 初值 10;暂停不走、倍速按游戏时间;记在信号上并进存档)</t>
         </is>
       </c>
     </row>
@@ -3638,15 +3638,15 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>signal.coverage.refresh_seconds</t>
+          <t>signal.coverage.edge_warn_cells</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.5</v>
+        <v>15</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
+          <t>被接入的机器离覆盖边缘不到几格时预警(HUD + 预警音 + 地图上画出覆盖圈);退回 edge_warn_hysteresis_cells 格以上才解除</t>
         </is>
       </c>
     </row>
@@ -3654,15 +3654,15 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>signal.link.grace_seconds</t>
+          <t>signal.coverage.edge_warn_hysteresis_cells</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
+          <t>边缘预警的回差(格):进入预警在 edge_warn_cells 以内,解除要退回到 edge_warn_cells + 本值以外(边缘来回走时预警不闪)</t>
         </is>
       </c>
     </row>
@@ -3670,15 +3670,15 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>signal.link.warn_repeat_seconds</t>
+          <t>signal.coverage.refresh_seconds</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
+          <t>覆盖源(核心 / 信号塔)列表按游戏时间多久重建一次(游戏秒);建筑数量变化立即重建</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>signal.safe_mode.exit_seconds</t>
+          <t>signal.link.grace_seconds</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
+          <t>走出信号覆盖后的宽限(游戏秒):宽限内回到覆盖即恢复,耗尽才断链(干扰场沿用地点自己的 2 秒宽限)</t>
         </is>
       </c>
     </row>
@@ -3702,15 +3702,15 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>signal.safe_mode.check_seconds</t>
+          <t>signal.link.warn_repeat_seconds</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
+          <t>同一台机器同一种链路预警音的最短间隔(真实秒):边缘反复进出不刷屏</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>signal.raw.exposure_per_fire</t>
+          <t>signal.safe_mode.exit_seconds</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
+          <t>断链条件(干扰 / 覆盖外 / 静默夜)消失并持续多久后退出安全模式(游戏秒):边缘反复进出时图标不闪</t>
         </is>
       </c>
     </row>
@@ -3734,15 +3734,15 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>signal.raw.heat_multiplier</t>
+          <t>signal.safe_mode.check_seconds</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
+          <t>安全模式退出判定的间隔(游戏秒,与是否被观察无关)</t>
         </is>
       </c>
     </row>
@@ -3750,15 +3750,15 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>signal.link.strength_full_cells</t>
+          <t>signal.raw.exposure_per_fire</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
+          <t>裸跑敌方固件每次发动增加的信号暴露(FGR-SIG-061 初值 +2;每件未破解固件各计一次)</t>
         </is>
       </c>
     </row>
@@ -3766,15 +3766,15 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>signal.link.strength_strong_percent</t>
+          <t>signal.raw.heat_multiplier</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>67</v>
+        <v>1.5</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“强”</t>
+          <t>裸跑时经过接入口那条武器的积热倍率(FGR-SIG-061:同类已破解固件的 1.5 倍,初值)</t>
         </is>
       </c>
     </row>
@@ -3782,15 +3782,15 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>signal.link.strength_medium_percent</t>
+          <t>signal.link.strength_full_cells</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
+          <t>接入 HUD 链路强度满格所需的离覆盖边缘格数(补全项:FG01 只写“越近越弱”;60 = 预警距离 15 的 4 倍)</t>
         </is>
       </c>
     </row>
@@ -3798,15 +3798,15 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>signal.raw.charge_interval_seconds</t>
+          <t>signal.link.strength_strong_percent</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
+          <t>链路强度不低于这个百分比显示“强”</t>
         </is>
       </c>
     </row>
@@ -3814,15 +3814,15 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>exposure.max</t>
+          <t>signal.link.strength_medium_percent</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>信号暴露上限(沿用 Demo 0～100)</t>
+          <t>链路强度不低于这个百分比显示“中”,再低显示“弱”;进入边缘预警时显示“边缘”</t>
         </is>
       </c>
     </row>
@@ -3830,15 +3830,15 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>exposure.core_fire</t>
+          <t>signal.raw.charge_interval_seconds</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
+          <t>常规裸跑固件的“发动”计次间隔(游戏秒):武器开火即发动一次并计暴露,之后这么久内的开火不再计(与核心固件冷却同初值;记在信号上,换机器不重置,进存档)</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>exposure.high_power.threshold</t>
+          <t>exposure.max</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
+          <t>信号暴露上限(沿用 Demo 0～100)</t>
         </is>
       </c>
     </row>
@@ -3862,15 +3862,15 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>exposure.high_power.full_at</t>
+          <t>exposure.core_fire</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
+          <t>核心固件每次发动增加的暴露(FG16 初值 +0.5;“发动”= 具名反应真正打出的那一发,FG1-SIG-03)</t>
         </is>
       </c>
     </row>
@@ -3878,15 +3878,15 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>exposure.high_power.cap_per_hour</t>
+          <t>exposure.high_power.threshold</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
+          <t>高功率生产:家园总用电需求超过这个值的部分才计暴露(补全项:FG16 只写“按总功率换算”,阈值 = Demo 开局满配供电 20+80)</t>
         </is>
       </c>
     </row>
@@ -3894,15 +3894,15 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>exposure.high_power.settle_seconds</t>
+          <t>exposure.high_power.full_at</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
+          <t>高功率生产:总用电需求达到这个值时按每游戏小时上限计;阈值到这里之间线性</t>
         </is>
       </c>
     </row>
@@ -3910,15 +3910,15 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>exposure.alien_tech_per_expedition</t>
+          <t>exposure.high_power.cap_per_hour</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
+          <t>高功率生产每游戏小时最多增加的暴露(FG16 初值 +3;按游戏时间累计,家园不被观察时照常)</t>
         </is>
       </c>
     </row>
@@ -3926,15 +3926,15 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>exposure.node_destroyed</t>
+          <t>exposure.high_power.settle_seconds</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
+          <t>高功率生产的结算间隔(游戏秒;50 = 1 游戏小时,每小时记一笔来源,不逐帧刷明细)</t>
         </is>
       </c>
     </row>
@@ -3942,15 +3942,15 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>exposure.node_link_cut_drop</t>
+          <t>exposure.alien_tech_per_expedition</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
+          <t>使用异派技术:出发的远征队里有机器装着跨阵营蓝图时,每次远征 +2(FG16 初值;取代 Demo“首次使用异派固件 +10”)</t>
         </is>
       </c>
     </row>
@@ -3958,15 +3958,15 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>exposure.tower_off_drop_per_10s</t>
+          <t>exposure.node_destroyed</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
+          <t>摧毁敌方节点每个 +3(FG16 初值;取代 Demo 战斗 +8)</t>
         </is>
       </c>
     </row>
@@ -3974,15 +3974,15 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>exposure.history_max</t>
+          <t>exposure.node_link_cut_drop</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
+          <t>摧毁监听节点切断监听链,暴露降低这么多(沿用 Demo 的降暴露手段 -15;调参表只收正数,代码里取负)</t>
         </is>
       </c>
     </row>
@@ -3990,15 +3990,15 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>morph.transition_seconds</t>
+          <t>exposure.tower_off_drop_per_10s</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
+          <t>关闭信号塔主动广播,每 10 游戏秒暴露降低这么多(沿用 Demo 的降暴露手段 -2;代码里取负)</t>
         </is>
       </c>
     </row>
@@ -4006,15 +4006,15 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>reading.status_seconds</t>
+          <t>exposure.history_max</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
+          <t>暴露来源明细最多保留几条(最近的;各来源与各阵营的累计另有汇总,不随明细截断丢失)</t>
         </is>
       </c>
     </row>
@@ -4022,15 +4022,15 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>reading.escort.seconds</t>
+          <t>morph.transition_seconds</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
+          <t>机身形变过渡秒数(FGR-FW-021 初值 0.3;接入与离开都播放、完全可逆;按真实时间计,不随倍速,战略暂停中不走,与接入过渡同一口径)</t>
         </is>
       </c>
     </row>
@@ -4038,15 +4038,15 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>reading.escort.ratio</t>
+          <t>reading.status_seconds</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
+          <t>固件状态标签的持续秒数(FG2-FW-02;同类效果取大、到期取晚,不叠层,叠层与反应在 FG2-FW-03)</t>
         </is>
       </c>
     </row>
@@ -4054,15 +4054,15 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>reading.escort.cooldown</t>
+          <t>reading.escort.seconds</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
+          <t>集群协议伴飞无人机的存活秒数(母机开火时刷新)</t>
         </is>
       </c>
     </row>
@@ -4070,15 +4070,15 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>reading.escort.leash</t>
+          <t>reading.escort.ratio</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>10</v>
+        <v>0.4</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>集群协议伴飞无人机离母机最远(米)</t>
+          <t>集群协议伴飞无人机每次命中 = 武器伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -4086,15 +4086,15 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>reading.drone.speed</t>
+          <t>reading.escort.cooldown</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>无人机移动速度(米/游戏秒)</t>
+          <t>集群协议伴飞无人机出手间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4102,15 +4102,15 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>reading.drone.reach</t>
+          <t>reading.escort.leash</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>无人机触及距离(米,另加目标半径)</t>
+          <t>集群协议伴飞无人机离母机最远(米)</t>
         </is>
       </c>
     </row>
@@ -4118,15 +4118,15 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>reading.tick.status</t>
+          <t>reading.drone.speed</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>状态持续伤害的结算节拍(游戏秒)</t>
+          <t>无人机移动速度(米/游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4134,15 +4134,15 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>reading.tick.zone</t>
+          <t>reading.drone.reach</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
+          <t>无人机触及距离(米,另加目标半径)</t>
         </is>
       </c>
     </row>
@@ -4150,15 +4150,15 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>reading.capacity.zones</t>
+          <t>reading.tick.status</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>512</v>
+        <v>0.5</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
+          <t>状态持续伤害的结算节拍(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4166,15 +4166,15 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>reading.capacity.echoes</t>
+          <t>reading.tick.zone</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1024</v>
+        <v>0.5</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>每个地点待结算的回波上限</t>
+          <t>区域伤害 / 挂状态的结算节拍(游戏秒,乱流读法按倍率加密)</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>reading.capacity.drones</t>
+          <t>reading.capacity.zones</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>每个地点同时存在的无人机上限</t>
+          <t>每个地点同时存在的读法区域上限(超出的不生成并计数)</t>
         </is>
       </c>
     </row>
@@ -4198,15 +4198,15 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>reading.weave.dps_ratio</t>
+          <t>reading.capacity.echoes</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>0.15</v>
+        <v>1024</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
+          <t>每个地点待结算的回波上限</t>
         </is>
       </c>
     </row>
@@ -4214,15 +4214,15 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>reading.weave.margin</t>
+          <t>reading.capacity.drones</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>0.6</v>
+        <v>512</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>连网减速网比两端之间的半距再宽多少米</t>
+          <t>每个地点同时存在的无人机上限</t>
         </is>
       </c>
     </row>
@@ -4230,15 +4230,15 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>reading.zone.status_seconds</t>
+          <t>reading.weave.dps_ratio</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>2</v>
+        <v>0.15</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
+          <t>连网减速网的每秒伤害 = 命中伤害 × 本值(读法里没有别的区域伤害时;持续秒数与减速比例在 fg.TbCarrierReading weave 行 b / c)</t>
         </is>
       </c>
     </row>
@@ -4246,15 +4246,15 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>combat.machine.attack_interval</t>
+          <t>reading.weave.margin</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
+          <t>连网减速网比两端之间的半距再宽多少米</t>
         </is>
       </c>
     </row>
@@ -4262,15 +4262,15 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>status.stack_cap</t>
+          <t>reading.zone.status_seconds</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
+          <t>区域给站在里面的单位挂状态(减速等)时,读法没带状态时长(没有状态标签固件)用的时长(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -4278,15 +4278,15 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>firmware.storage.base_slots</t>
+          <t>combat.machine.attack_interval</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
+          <t>机器的基础出手间隔(游戏秒):编队攻击命令的攻击间隔,即时命中武器(连射器 / 切割束 / 新作战组件)的武器冷却;驻守开火的炮塔与直控蓄力门槛按它 × 出手间隔倍率</t>
         </is>
       </c>
     </row>
@@ -4294,15 +4294,15 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>firmware.storage.per_warehouse</t>
+          <t>status.stack_cap</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
+          <t>同一状态标签在一个单位上最多叠几层(FG2-FW-03;再挂只刷新时长;持续伤害按层数成倍,减速 / 易伤不随层数增强)</t>
         </is>
       </c>
     </row>
@@ -4310,15 +4310,15 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>firmware.library.disassemble_scrap</t>
+          <t>firmware.storage.base_slots</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
+          <t>芯片存放的基础格数(没有运转中的仓库时;沿用 Demo 基元仓 8 格,FGR-FW-060)</t>
         </is>
       </c>
     </row>
@@ -4326,15 +4326,15 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>firmware.library.refresh_seconds</t>
+          <t>firmware.storage.per_warehouse</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
+          <t>每座运转中的仓库追加的芯片存放格数(FGR-FW-060“改为受仓库容量约束”;初值)</t>
         </is>
       </c>
     </row>
@@ -4342,15 +4342,15 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>firmware.library.route_cache_seconds</t>
+          <t>firmware.library.disassemble_scrap</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
+          <t>分解一枚固件芯片返还的废料(刻印 10 的一半,防止刻印-分解刷废料;初值)</t>
         </is>
       </c>
     </row>
@@ -4358,15 +4358,15 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_common</t>
+          <t>firmware.library.refresh_seconds</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
+          <t>固件库面板打开时按这个真实秒间隔重读芯片(每帧不遍历芯片;操作后立即刷新)</t>
         </is>
       </c>
     </row>
@@ -4374,15 +4374,15 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_rare</t>
+          <t>firmware.library.route_cache_seconds</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>数据复原一条精良固件的技术数据(初值)</t>
+          <t>“仓储 → 装配站”路线检查结果缓存的真实秒数(只在详情页显示时检查)</t>
         </is>
       </c>
     </row>
@@ -4390,15 +4390,15 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>firmware.restore.cost_epic</t>
+          <t>firmware.restore.cost_common</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
+          <t>数据复原一条普通固件的技术数据(初值;Demo 全部解析约 50 技术数据)</t>
         </is>
       </c>
     </row>
@@ -4406,15 +4406,15 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>grid.relocate_seconds</t>
+          <t>firmware.restore.cost_rare</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
+          <t>数据复原一条精良固件的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4422,15 +4422,15 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>grid.batch_demolish_confirm</t>
+          <t>firmware.restore.cost_epic</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
+          <t>数据复原一条稀有固件(含阵营首领的核心固件)的技术数据(初值)</t>
         </is>
       </c>
     </row>
@@ -4438,15 +4438,15 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>grid.pollution_warn_level</t>
+          <t>grid.relocate_seconds</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
+          <t>搬迁施工耗时(游戏秒):机器到新位置施工这么久后,原建筑拆走、新位置完工(FGR-LOG-008,初值)</t>
         </is>
       </c>
     </row>
@@ -4454,15 +4454,15 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>grid.drag_max_cells</t>
+          <t>grid.batch_demolish_confirm</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>256</v>
+        <v>20</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
+          <t>一次拆除超过这么多座建筑时先弹确认(FGR-LOG-007 初值 20)</t>
         </is>
       </c>
     </row>
@@ -4470,15 +4470,15 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>grid.explore_machine_radius</t>
+          <t>grid.pollution_warn_level</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
+          <t>污染达到此级(且低于不可建等级)时放置只警告:建筑受天气损伤加倍(FGR-LOG-012)</t>
         </is>
       </c>
     </row>
@@ -4486,15 +4486,15 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>grid.explore_lattice</t>
+          <t>grid.drag_max_cells</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>4</v>
+        <v>256</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
+          <t>一次拖拽铺设最多几格(超出给原因,避免一笔拖出上千格)</t>
         </is>
       </c>
     </row>
@@ -4502,15 +4502,15 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>grid.explore_machines_per_step</t>
+          <t>grid.explore_machine_radius</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
+          <t>机器走到哪里就把周围这么多格记为已探索(FGR-LOG-013 初值)</t>
         </is>
       </c>
     </row>
@@ -4518,15 +4518,15 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>build.carry_per_trip</t>
+          <t>grid.explore_lattice</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
+          <t>机器探索圆心吸附到的格距(格):同一小片区域只记一个圆,已探索圆的数量有上界</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>build.belt_seconds_per_cell</t>
+          <t>grid.explore_machines_per_step</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
+          <t>每个世界模拟步检查几台家园机器的位置(轮流检查,热更层每步 O(1),与机器数无关)</t>
         </is>
       </c>
     </row>
@@ -4550,15 +4550,15 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>eco.prod.step_ticks</t>
+          <t>build.carry_per_trip</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>生产建筑每隔几个世界步推进一次(世界 60 Hz,3 = 20 Hz,与传送带同一节拍);进度按游戏时钟步数累计,与观察 / 倍速无关</t>
+          <t>机器每趟从仓库取多少施工材料(废料):不够就回去再取;与货位单位 home.scrap_units_per_cargo_slot 同量级(FGR-LOG-006 机器取料施工,初值)</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>eco.prod.sync_seconds</t>
+          <t>build.belt_seconds_per_cell</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>生产建筑与管线(流体口)、建筑状态对账的间隔(游戏秒):建成 / 修好 / 转向 / 搬迁 / 拆除后最迟这么久流体口跟上</t>
+          <t>传送带虚影每格施工耗时(游戏秒):机器按路径顺序一格一格建成(FGR-LOG-006,初值)</t>
         </is>
       </c>
     </row>
@@ -4582,15 +4582,15 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>eco.prod.fluid_intake_factor</t>
+          <t>eco.prod.step_ticks</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>配方建筑流体输入口的抽取速率 = 配方额定用量 × 这个倍数(升/分钟):缓存满了就不再要,不会多抽</t>
+          <t>生产建筑每隔几个世界步推进一次(世界 60 Hz,3 = 20 Hz,与传送带同一节拍);进度按游戏时钟步数累计,与观察 / 倍速无关</t>
         </is>
       </c>
     </row>
@@ -4598,15 +4598,15 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>eco.ruin.scrap_per_cell</t>
+          <t>eco.prod.sync_seconds</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>每格废墟的废料储量(回收站逐格拆;一格拆完变成可建空地)</t>
+          <t>生产建筑与管线(流体口)、建筑状态对账的间隔(游戏秒):建成 / 修好 / 转向 / 搬迁 / 拆除后最迟这么久流体口跟上</t>
         </is>
       </c>
     </row>
@@ -4614,15 +4614,15 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>eco.ruin.act1_two_hour_scrap</t>
+          <t>eco.prod.fluid_intake_factor</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1200</v>
+        <v>2</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>第一幕前两小时的废料需求估算(ADR-ECO-002 第 4 节:修复 / 第一批建筑 / 传送带 / 电塔 / 中继 / 早期废料炼合金);起始区保证的废墟群储量必须不少于它(DEBT-FG3GEN01-03)</t>
+          <t>配方建筑流体输入口的抽取速率 = 配方额定用量 × 这个倍数(升/分钟):缓存满了就不再要,不会多抽</t>
         </is>
       </c>
     </row>
@@ -4630,15 +4630,15 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>eco.vibration.max</t>
+          <t>eco.ruin.scrap_per_cell</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>家园震动值上限(FG10 FGR-EVT-010:0~100)</t>
+          <t>每格废墟的废料储量(回收站逐格拆;一格拆完变成可建空地)</t>
         </is>
       </c>
     </row>
@@ -4646,15 +4646,15 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>eco.vibration.decay_per_minute</t>
+          <t>eco.ruin.act1_two_hour_scrap</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>2</v>
+        <v>1200</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>家园震动值每游戏分钟自然衰减(FG10 初值 -2)</t>
+          <t>第一幕前两小时的废料需求估算(ADR-ECO-002 第 4 节:修复 / 第一批建筑 / 传送带 / 电塔 / 中继 / 早期废料炼合金);起始区保证的废墟群储量必须不少于它(DEBT-FG3GEN01-03)</t>
         </is>
       </c>
     </row>
@@ -4662,15 +4662,15 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>eco.prod.sources_shown</t>
+          <t>eco.vibration.max</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>提取钻悬停 / 面板里列出的主要震动来源数</t>
+          <t>家园震动值上限(FG10 FGR-EVT-010:0~100)</t>
         </is>
       </c>
     </row>
@@ -4678,15 +4678,15 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>eco.assembly.buffer_per_item</t>
+          <t>eco.vibration.decay_per_minute</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>装配站材料缓存每种物品最多放几件(输入口送来的机器材料先进这里;放满了带停下)</t>
+          <t>家园震动值每游戏分钟自然衰减(FG10 初值 -2)</t>
         </is>
       </c>
     </row>
@@ -4694,15 +4694,95 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
+          <t>eco.prod.sources_shown</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>3</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>提取钻悬停 / 面板里列出的主要震动来源数</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>eco.assembly.buffer_per_item</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>20</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>装配站材料缓存每种物品最多放几件(输入口送来的机器材料先进这里;放满了带停下)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
           <t>eco.assembly.scrap_substitute_default</t>
         </is>
       </c>
-      <c r="C267" t="n">
+      <c r="C269" t="n">
         <v>1</v>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>装配站“缺材料时用废料代付”的默认值(1 开 / 0 关;玩家在装配站面板改,跟存档走)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>power.solar.sandstorm_factor</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>太阳能沙暴时的发电系数(FG04 / FG07:沙暴 -60%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>power.fuel.restart_seconds</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>5</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>燃油发电机烧空停机后,机内攒够多少秒满负荷的燃油才重新发电(防止来一滴烧一滴的反复启停)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>power.storage.reserve_levels</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>3</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>储能站放电对象最多能留给前几档优先级(1~3;界面列出“只给优先级 1~N”)</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4786,6 +4786,214 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>building.name.max_chars</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>24</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>building.repair.min_seconds</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>2</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>一次维修工期的下限(秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>building.jump.max_links</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>4</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>building.stats.window_minutes</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>10</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>building.stats.bucket_seconds</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>60</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>building.batch.confirm</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>1</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ui.build.result_seconds</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>4</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>logistics.port.keep.1</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>10</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>logistics.port.keep.2</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>25</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>预设 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>logistics.port.keep.3</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>50</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>预设 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr"/>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>logistics.port.keep.4</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>100</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>预设 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>logistics.port.keep.5</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>200</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>预设 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>logistics.port.keep.6</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>500</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>预设 6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D285"/>
+  <dimension ref="A1:D294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4994,6 +4994,150 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>rules.check_seconds</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>60</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>rules.log_max</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>100</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>rules.max_count</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>60</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>rules.supply.batch_default</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>10</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>阈值补给每次送几件的默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>rules.supply.batch_max</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>100</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>阈值补给每次最多送几件</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>rules.supply.unload_seconds</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>rules.repair_bay.slots</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>2</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>一座维修台同时修几台机器</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>rules.war.repair_priority</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>2</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D294"/>
+  <dimension ref="A1:D303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5138,6 +5138,150 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>roster.name_max_length</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>16</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>roster.labor_refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>1</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>roster.batch_max</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>64</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>work.history_keep</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>200</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ledger.history_keep</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>600</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip.erc_001</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>40</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip.erc_002</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>40</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ERC-002 每趟取料上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip.erc_003</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>40</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>ERC-003 战斗履带每趟取料上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>build.carry_per_trip.chassis_hover</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>40</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>维修悬浮每趟取料上限</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D303"/>
+  <dimension ref="A1:D321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5282,6 +5282,294 @@
         </is>
       </c>
     </row>
+    <row r="304">
+      <c r="A304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>eco.stats.buckets</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>30</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>eco.stats.tier0.bucket_seconds</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>eco.stats.tier1.bucket_seconds</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>20</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>eco.stats.tier2.bucket_seconds</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>120</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>eco.stats.tier3.bucket_seconds</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>eco.stats.deficit_minutes</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>10</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>eco.stats.deficit_probe_seconds</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>120</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>eco.stats.deficit_check_seconds</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>20</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>eco.stats.panel_refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>1</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>eco.stats.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>8</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>瓶颈页最多列几种物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>eco.topbar.max_pins</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>8</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>eco.topbar.refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>eco.topbar.rate_window</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>1</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>eco.topbar.max_subnets</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>3</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>eco.topbar.target_tolerance</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>eco.planner.max_depth</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>12</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>eco.planner.default_rate</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>10</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>eco.planner.max_rate</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5570,6 +5570,150 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>away.reports_keep</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>3</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>away.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>3</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>away.items_max</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>12</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>away.entries_max</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>60</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>40</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>20</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>64</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>60</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D330"/>
+  <dimension ref="A1:D338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5714,6 +5714,134 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>1</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>2</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>100</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>1</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>5</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>120</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>10</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>eco.softlock.unreachable_seconds</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>20</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4790,15 +4790,15 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>research.lab.tech_per_minute</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>每台实验室每分钟消耗的技术数据(FGR-RND-001 初值 2;按每件一个周期取)</t>
         </is>
       </c>
     </row>
@@ -4806,15 +4806,15 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>research.lab.points_per_minute</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>T1 实验室(转换效率 1.0)每分钟产出的研究点(FGR-RND-001 初值 1;T2/T3 乘等级效果值)</t>
         </is>
       </c>
     </row>
@@ -4822,15 +4822,15 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>research.queue.max</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>研究队列最多几项(FGR-RND-013 初值 5)</t>
         </is>
       </c>
     </row>
@@ -4838,15 +4838,15 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>research.efficiency_cap</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>效率类节点单项累计上限(FGR-RND-011:+30%)</t>
         </is>
       </c>
     </row>
@@ -4854,15 +4854,15 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>research.tree.zoom_min</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>60</v>
+        <v>0.5</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>研发树最小缩放</t>
         </is>
       </c>
     </row>
@@ -4870,15 +4870,15 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>research.tree.zoom_max</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>研发树最大缩放</t>
         </is>
       </c>
     </row>
@@ -4886,15 +4886,15 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>research.tree.zoom_step</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>滚轮 / 按钮每一下缩放多少</t>
         </is>
       </c>
     </row>
@@ -4902,15 +4902,15 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>research.tree.col_width</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>10</v>
+        <v>230</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>研发树一列的宽(像素,缩放 1.0 时;节点位置 = 列 × 列宽)</t>
         </is>
       </c>
     </row>
@@ -4918,15 +4918,15 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>research.tree.row_height</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>研发树一行的高(像素)</t>
         </is>
       </c>
     </row>
@@ -4934,15 +4934,15 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>research.tree.lane_gap</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>分支之间的间隔(像素,分支标题占这一段)</t>
         </is>
       </c>
     </row>
@@ -4950,15 +4950,15 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -4966,15 +4966,15 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -4982,15 +4982,15 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -4998,15 +4998,15 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -5014,15 +5014,15 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -5030,15 +5030,15 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -5046,15 +5046,15 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -5062,15 +5062,15 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -5078,15 +5078,15 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -5094,15 +5094,15 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -5110,15 +5110,15 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>0.02</v>
+        <v>100</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -5126,15 +5126,15 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -5142,15 +5142,15 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -5158,15 +5158,15 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -5174,15 +5174,15 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -5190,15 +5190,15 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -5206,15 +5206,15 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -5222,15 +5222,15 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -5238,15 +5238,15 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5254,15 +5254,15 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -5270,15 +5270,15 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>40</v>
+        <v>0.02</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -5286,15 +5286,15 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -5302,15 +5302,15 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5318,15 +5318,15 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -5334,15 +5334,15 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -5350,15 +5350,15 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5366,15 +5366,15 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5382,15 +5382,15 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -5398,15 +5398,15 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5414,15 +5414,15 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5430,15 +5430,15 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5446,15 +5446,15 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -5462,15 +5462,15 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -5494,15 +5494,15 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -5510,15 +5510,15 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>0.05</v>
+        <v>1200</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -5526,15 +5526,15 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -5542,15 +5542,15 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -5558,15 +5558,15 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>100000</v>
+        <v>20</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -5574,15 +5574,15 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -5590,15 +5590,15 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -5606,15 +5606,15 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5622,15 +5622,15 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>60</v>
+        <v>0.5</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -5638,15 +5638,15 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -5654,15 +5654,15 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -5670,15 +5670,15 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>64</v>
+        <v>0.05</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -5686,15 +5686,15 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -5702,15 +5702,15 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>0.3</v>
+        <v>10</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5734,15 +5734,15 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -5750,15 +5750,15 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -5766,15 +5766,15 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -5782,15 +5782,15 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -5798,15 +5798,15 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -5814,15 +5814,15 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -5830,13 +5830,173 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>64</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>60</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>1</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr"/>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>2</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>100</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr"/>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>1</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>5</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>120</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>10</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C338" t="n">
+      <c r="C348" t="n">
         <v>20</v>
       </c>
-      <c r="D338" t="inlineStr">
+      <c r="D348" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D348"/>
+  <dimension ref="A1:D351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4950,15 +4950,15 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>analysis.queue.capacity</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>解析队列最多几项(FGR-RND-020 初值 8;只数排队/解析中/断电暂停)</t>
         </is>
       </c>
     </row>
@@ -4966,15 +4966,15 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>analysis.wreck.buffer</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>解析台的残骸缓存最多几件(传送带 / 面板送进来,队列空闲时逐件处理)</t>
         </is>
       </c>
     </row>
@@ -4982,15 +4982,15 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>analysis.history.keep</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>队列里保留几条最近结束的记录给面板看(更早的清掉;Demo 区域任务物的完成记录不清,目标判定要用)</t>
         </is>
       </c>
     </row>
@@ -4998,15 +4998,15 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -5014,15 +5014,15 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -5030,15 +5030,15 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -5046,15 +5046,15 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -5062,15 +5062,15 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -5078,15 +5078,15 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -5094,15 +5094,15 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -5110,15 +5110,15 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -5126,15 +5126,15 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -5142,15 +5142,15 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -5158,15 +5158,15 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -5174,15 +5174,15 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -5190,15 +5190,15 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -5206,15 +5206,15 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -5238,15 +5238,15 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -5254,15 +5254,15 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -5270,15 +5270,15 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>0.02</v>
+        <v>100</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5302,15 +5302,15 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -5318,15 +5318,15 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -5334,15 +5334,15 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -5350,15 +5350,15 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5366,15 +5366,15 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -5382,15 +5382,15 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -5398,15 +5398,15 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5414,15 +5414,15 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -5446,15 +5446,15 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5462,15 +5462,15 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5494,15 +5494,15 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -5510,15 +5510,15 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1200</v>
+        <v>2</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -5526,15 +5526,15 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -5558,15 +5558,15 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -5574,15 +5574,15 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -5590,15 +5590,15 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -5606,15 +5606,15 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -5622,15 +5622,15 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -5638,15 +5638,15 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -5654,15 +5654,15 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5670,15 +5670,15 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -5686,15 +5686,15 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -5702,15 +5702,15 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>100000</v>
+        <v>0.05</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -5734,15 +5734,15 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -5750,15 +5750,15 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -5766,15 +5766,15 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>12</v>
+        <v>100000</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5782,15 +5782,15 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -5798,15 +5798,15 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -5814,15 +5814,15 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -5830,15 +5830,15 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -5846,15 +5846,15 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -5862,15 +5862,15 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>0.3</v>
+        <v>20</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -5878,15 +5878,15 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>away.machines_max</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -5894,15 +5894,15 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>alarm.jam_seconds</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
         </is>
       </c>
     </row>
@@ -5910,15 +5910,15 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>alarm.machine_wounded_fraction</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.softlock.check_seconds</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
         </is>
       </c>
     </row>
@@ -5942,15 +5942,15 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.softlock.print_min_machines</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
         </is>
       </c>
     </row>
@@ -5958,15 +5958,15 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.softlock.print_health</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
         </is>
       </c>
     </row>
@@ -5974,15 +5974,15 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.softlock.core_scrap_per_minute</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
         </is>
       </c>
     </row>
@@ -5990,13 +5990,61 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>5</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>120</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>10</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C348" t="n">
+      <c r="C351" t="n">
         <v>20</v>
       </c>
-      <c r="D348" t="inlineStr">
+      <c r="D351" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D351"/>
+  <dimension ref="A1:D363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4998,15 +4998,15 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>range.projection.max</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>同时存在的仿真投影上限(全部靶场合计;FG05 第 7 节初值 6)</t>
         </is>
       </c>
     </row>
@@ -5014,15 +5014,15 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>range.target.slots</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>每座靶场的靶位数(远端 2 排 × 4 列)</t>
         </is>
       </c>
     </row>
@@ -5030,15 +5030,15 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>range.test.max_seconds</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>一次测试最长游戏秒,到点自动结束并记下读数</t>
         </is>
       </c>
     </row>
@@ -5046,15 +5046,15 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>range.sample_seconds</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>读数采样间隔(游戏秒;标签覆盖率与热量曲线按它采样)</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>range.curve.points</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>测试记录里热量曲线最多保留几个点(超出时等距抽样)</t>
         </is>
       </c>
     </row>
@@ -5078,15 +5078,15 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>range.history.keep</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>测试记录最多保留几条(新的在后)</t>
         </is>
       </c>
     </row>
@@ -5094,15 +5094,15 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>range.presets.max</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>靶子布置预设最多几个</t>
         </is>
       </c>
     </row>
@@ -5110,15 +5110,15 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>range.target.respawn_seconds</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>投影靶被打空后原地复位的游戏秒</t>
         </is>
       </c>
     </row>
@@ -5126,15 +5126,15 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>range.attack_range</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>投影的攻击命令射程(与远征编队攻击同一个数)</t>
         </is>
       </c>
     </row>
@@ -5142,15 +5142,15 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>range.retarget_seconds</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>投影没有目标时多久重新找一次最近的投影靶</t>
         </is>
       </c>
     </row>
@@ -5158,15 +5158,15 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>range.swarm.spread</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>100</v>
+        <v>0.9</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>集群靶在靶位里的散开半径</t>
         </is>
       </c>
     </row>
@@ -5174,15 +5174,15 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>range.edge_margin</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>200</v>
+        <v>0.6</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>单位离靶场边缘至少留多远(高速靶的摆动不出靶场)</t>
         </is>
       </c>
     </row>
@@ -5190,15 +5190,15 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -5206,15 +5206,15 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -5222,15 +5222,15 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -5238,15 +5238,15 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -5254,15 +5254,15 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -5270,15 +5270,15 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -5286,15 +5286,15 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -5302,15 +5302,15 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -5318,15 +5318,15 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>0.02</v>
+        <v>25</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -5334,15 +5334,15 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -5350,15 +5350,15 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -5366,15 +5366,15 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -5382,15 +5382,15 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>64</v>
+        <v>500</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -5398,15 +5398,15 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -5414,15 +5414,15 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -5430,15 +5430,15 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -5446,15 +5446,15 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -5462,15 +5462,15 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5494,15 +5494,15 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -5510,15 +5510,15 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -5526,15 +5526,15 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -5542,15 +5542,15 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5558,15 +5558,15 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -5574,15 +5574,15 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -5590,15 +5590,15 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5606,15 +5606,15 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5622,15 +5622,15 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -5638,15 +5638,15 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5654,15 +5654,15 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5670,15 +5670,15 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5686,15 +5686,15 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -5702,15 +5702,15 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>0.05</v>
+        <v>20</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -5734,15 +5734,15 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -5750,15 +5750,15 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -5766,15 +5766,15 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>100000</v>
+        <v>10</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -5782,15 +5782,15 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -5798,15 +5798,15 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -5814,15 +5814,15 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -5830,15 +5830,15 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -5846,15 +5846,15 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5862,15 +5862,15 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -5878,15 +5878,15 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -5894,15 +5894,15 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -5910,15 +5910,15 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -5926,15 +5926,15 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -5942,15 +5942,15 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -5958,15 +5958,15 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5974,15 +5974,15 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -5990,15 +5990,15 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -6006,15 +6006,15 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -6022,15 +6022,15 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6038,13 +6038,205 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>40</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>20</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>64</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>60</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>1</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>2</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>100</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>5</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>120</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>10</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C351" t="n">
+      <c r="C363" t="n">
         <v>20</v>
       </c>
-      <c r="D351" t="inlineStr">
+      <c r="D363" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D363"/>
+  <dimension ref="A1:D376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5190,15 +5190,15 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>fusion.sim_tech</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>模拟熔合花的技术数据(FGR-RND-040 初值 5;没有配方也照收,父固件一条都不消耗)</t>
         </is>
       </c>
     </row>
@@ -5206,15 +5206,15 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>fusion.formal_tech</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>正式熔合花的技术数据(FGR-RND-041 初值 30;入队时预留,取消 / 合成台被毁退回)</t>
         </is>
       </c>
     </row>
@@ -5222,15 +5222,15 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>fusion.formal_substrate</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>正式熔合花的芯片基板(FGR-RND-041 初值 2)</t>
         </is>
       </c>
     </row>
@@ -5238,15 +5238,15 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>fusion.formal_seconds</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>正式熔合用时(游戏秒;合成台缺电 / 禁用时暂停、进度保留)</t>
         </is>
       </c>
     </row>
@@ -5254,15 +5254,15 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>fusion.burn_substrate</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>固件刻录台量产一枚混合固件的芯片基板(FGR-RND-042 初值 3,常规固件是 1)</t>
         </is>
       </c>
     </row>
@@ -5270,15 +5270,15 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>fusion.queue_max</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>每座电路合成台的正式熔合队列上限(含正在做的那一项)</t>
         </is>
       </c>
     </row>
@@ -5286,15 +5286,15 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>fusion.load_bonus</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>混合固件的负载 = 两条父固件中较大值 + 本值(FGR-FW-050 初值 1;生成数据时用,自检核对)</t>
         </is>
       </c>
     </row>
@@ -5302,15 +5302,15 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>fusion.clue_partial_min</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>一场里某条反应触发达到这么多次 → 部分线索(只知道一条父固件)</t>
         </is>
       </c>
     </row>
@@ -5318,15 +5318,15 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>fusion.clue_full_min</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>一场里某条反应触发达到这么多次 → 完整线索(两条父固件都知道)</t>
         </is>
       </c>
     </row>
@@ -5334,15 +5334,15 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>fusion.clue_per_session</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>一场战斗最多生成几条线索(按触发次数从多到少)</t>
         </is>
       </c>
     </row>
@@ -5350,15 +5350,15 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>fusion.clue_keep</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>配方书里最多保留几条线索(超出时去掉最旧的、已经没用的线索)</t>
         </is>
       </c>
     </row>
@@ -5366,15 +5366,15 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>fusion.pending_keep</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>没有仿真实验室时最多先存几场战斗记录</t>
         </is>
       </c>
     </row>
@@ -5382,15 +5382,15 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>fusion.sim_log_keep</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>模拟熔合记录最多保留几条(“这一对模拟过:无反应”的提示用)</t>
         </is>
       </c>
     </row>
@@ -5398,15 +5398,15 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -5414,15 +5414,15 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -5430,15 +5430,15 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -5462,15 +5462,15 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -5494,15 +5494,15 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -5510,15 +5510,15 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>0.02</v>
+        <v>10</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -5526,15 +5526,15 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -5542,15 +5542,15 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -5558,15 +5558,15 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -5574,15 +5574,15 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -5590,15 +5590,15 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -5606,15 +5606,15 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -5622,15 +5622,15 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -5638,15 +5638,15 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -5654,15 +5654,15 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -5670,15 +5670,15 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -5686,15 +5686,15 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>20</v>
+        <v>0.02</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -5734,15 +5734,15 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -5750,15 +5750,15 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>1200</v>
+        <v>16</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5766,15 +5766,15 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -5782,15 +5782,15 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -5798,15 +5798,15 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5814,15 +5814,15 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5830,15 +5830,15 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -5846,15 +5846,15 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5862,15 +5862,15 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5878,15 +5878,15 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5894,15 +5894,15 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -5910,15 +5910,15 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -5926,15 +5926,15 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -5942,15 +5942,15 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -5958,15 +5958,15 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>100000</v>
+        <v>1200</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -5974,15 +5974,15 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -5990,15 +5990,15 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -6006,15 +6006,15 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -6022,15 +6022,15 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -6038,15 +6038,15 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -6054,15 +6054,15 @@
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6070,15 +6070,15 @@
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>64</v>
+        <v>0.5</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -6086,15 +6086,15 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -6102,15 +6102,15 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -6118,15 +6118,15 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -6134,15 +6134,15 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -6150,15 +6150,15 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -6166,15 +6166,15 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6182,15 +6182,15 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -6198,15 +6198,15 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -6214,15 +6214,15 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -6230,13 +6230,221 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
+          <t>away.entries_max</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>60</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>40</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>20</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>64</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>60</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr"/>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>1</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr"/>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>2</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>100</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>1</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>5</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>120</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr"/>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>10</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C363" t="n">
+      <c r="C376" t="n">
         <v>20</v>
       </c>
-      <c r="D363" t="inlineStr">
+      <c r="D376" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D376"/>
+  <dimension ref="A1:D380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5398,15 +5398,15 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>intel.raid_window_frac</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>24</v>
+        <v>0.15</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>突袭预报的抵达窗口 = 预计抵达时间 ×(1 ± 本值)(FGR-RND-050 时间窗口)</t>
         </is>
       </c>
     </row>
@@ -5414,15 +5414,15 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>intel.raid_window_min_seconds</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>突袭预报抵达窗口的最小半宽(游戏秒;快到的部队窗口不至于只有一瞬)</t>
         </is>
       </c>
     </row>
@@ -5430,15 +5430,15 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>intel.keep_per_kind</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>每类情报最多保留几条“已过时”的旧情报(有效的情报不受限;超出时去掉最旧的已过时情报)</t>
         </is>
       </c>
     </row>
@@ -5446,15 +5446,15 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>intel.map_arrow_cells</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>地图上突袭预报箭头的长度(格;箭头从来袭方向指向归还核心)</t>
         </is>
       </c>
     </row>
@@ -5462,15 +5462,15 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -5526,15 +5526,15 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -5542,15 +5542,15 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -5558,15 +5558,15 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -5574,15 +5574,15 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -5590,15 +5590,15 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -5606,15 +5606,15 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -5638,15 +5638,15 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -5654,15 +5654,15 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -5670,15 +5670,15 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -5686,15 +5686,15 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -5702,15 +5702,15 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>0.02</v>
+        <v>10</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -5734,15 +5734,15 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -5750,15 +5750,15 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5766,15 +5766,15 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -5782,15 +5782,15 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>64</v>
+        <v>0.02</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -5798,15 +5798,15 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -5814,15 +5814,15 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>600</v>
+        <v>16</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5830,15 +5830,15 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -5846,15 +5846,15 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -5862,15 +5862,15 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5878,15 +5878,15 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5894,15 +5894,15 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -5910,15 +5910,15 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5926,15 +5926,15 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5942,15 +5942,15 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5958,15 +5958,15 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>1200</v>
+        <v>30</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -5974,15 +5974,15 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -5990,15 +5990,15 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -6006,15 +6006,15 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -6022,15 +6022,15 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -6038,15 +6038,15 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -6054,15 +6054,15 @@
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -6070,15 +6070,15 @@
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -6102,15 +6102,15 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -6118,15 +6118,15 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>0.05</v>
+        <v>8</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6134,15 +6134,15 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -6150,15 +6150,15 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -6166,15 +6166,15 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>100000</v>
+        <v>3</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -6182,15 +6182,15 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>3</v>
+        <v>0.05</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -6198,15 +6198,15 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -6214,15 +6214,15 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -6230,15 +6230,15 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6246,15 +6246,15 @@
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -6262,15 +6262,15 @@
       <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -6278,15 +6278,15 @@
       <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6310,15 +6310,15 @@
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>0.3</v>
+        <v>40</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -6326,15 +6326,15 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6342,15 +6342,15 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>away.machines_max</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6358,15 +6358,15 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>alarm.jam_seconds</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
         </is>
       </c>
     </row>
@@ -6374,15 +6374,15 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>alarm.machine_wounded_fraction</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
         </is>
       </c>
     </row>
@@ -6390,15 +6390,15 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.softlock.check_seconds</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
         </is>
       </c>
     </row>
@@ -6406,15 +6406,15 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.softlock.print_min_machines</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
         </is>
       </c>
     </row>
@@ -6422,15 +6422,15 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.softlock.print_health</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
         </is>
       </c>
     </row>
@@ -6438,13 +6438,77 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>1</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr"/>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>5</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr"/>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>120</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr"/>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>10</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr"/>
+      <c r="B380" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C376" t="n">
+      <c r="C380" t="n">
         <v>20</v>
       </c>
-      <c r="D376" t="inlineStr">
+      <c r="D380" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D380"/>
+  <dimension ref="A1:D383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5462,15 +5462,15 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>blackbox.points_per_box</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>每个黑匣子共产出多少技术数据(FGR-RND-060 初值 20;按分析进度逐点入账)</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>blackbox.days_per_box</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>一座陈列馆分析完一个黑匣子要几个游戏日(FGR-RND-060 初值 1;1 游戏日 = clock.day_seconds 游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5494,15 +5494,15 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>blackbox.boxes_per_gallery</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>每座工作中的陈列馆同时分析几个黑匣子(其余按回收先后排队;多座各自独立、不递减)</t>
         </is>
       </c>
     </row>
@@ -5510,15 +5510,15 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -5526,15 +5526,15 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -5542,15 +5542,15 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -5558,15 +5558,15 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -5574,15 +5574,15 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -5590,15 +5590,15 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -5606,15 +5606,15 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -5622,15 +5622,15 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -5638,15 +5638,15 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -5654,15 +5654,15 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -5670,15 +5670,15 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -5686,15 +5686,15 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -5702,15 +5702,15 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -5750,15 +5750,15 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -5766,15 +5766,15 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -5782,15 +5782,15 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>0.02</v>
+        <v>100</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5814,15 +5814,15 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -5830,15 +5830,15 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -5846,15 +5846,15 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -5862,15 +5862,15 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5878,15 +5878,15 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -5894,15 +5894,15 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -5910,15 +5910,15 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5926,15 +5926,15 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -5958,15 +5958,15 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5974,15 +5974,15 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5990,15 +5990,15 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6006,15 +6006,15 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -6022,15 +6022,15 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>1200</v>
+        <v>2</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -6038,15 +6038,15 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -6070,15 +6070,15 @@
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -6086,15 +6086,15 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -6102,15 +6102,15 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -6118,15 +6118,15 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -6134,15 +6134,15 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -6150,15 +6150,15 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -6166,15 +6166,15 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6182,15 +6182,15 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -6198,15 +6198,15 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -6214,15 +6214,15 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -6230,15 +6230,15 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>100000</v>
+        <v>0.05</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -6246,15 +6246,15 @@
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -6262,15 +6262,15 @@
       <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -6278,15 +6278,15 @@
       <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>12</v>
+        <v>100000</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6294,15 +6294,15 @@
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -6310,15 +6310,15 @@
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -6326,15 +6326,15 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -6342,15 +6342,15 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6358,15 +6358,15 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -6374,15 +6374,15 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0.3</v>
+        <v>20</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6390,15 +6390,15 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>away.machines_max</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6406,15 +6406,15 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>alarm.jam_seconds</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
         </is>
       </c>
     </row>
@@ -6422,15 +6422,15 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>alarm.machine_wounded_fraction</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.softlock.check_seconds</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
         </is>
       </c>
     </row>
@@ -6454,15 +6454,15 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.softlock.print_min_machines</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
         </is>
       </c>
     </row>
@@ -6470,15 +6470,15 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.softlock.print_health</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
         </is>
       </c>
     </row>
@@ -6486,15 +6486,15 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.softlock.core_scrap_per_minute</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
         </is>
       </c>
     </row>
@@ -6502,13 +6502,61 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>5</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr"/>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>120</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr"/>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>10</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr"/>
+      <c r="B383" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C380" t="n">
+      <c r="C383" t="n">
         <v>20</v>
       </c>
-      <c r="D380" t="inlineStr">
+      <c r="D383" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D383"/>
+  <dimension ref="A1:D384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4950,15 +4950,15 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>analysis.queue.capacity</t>
+          <t>research.start_tech_data</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>8</v>
+        <v>370</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>解析队列最多几项(FGR-RND-020 初值 8;只数排队/解析中/断电暂停)</t>
+          <t>新战役开局带来的技术数据(过渡初值:&gt;= 研发树开放前开局可造内容的研究成本换算;FG15-BAL-01 复核)</t>
         </is>
       </c>
     </row>
@@ -4966,15 +4966,15 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>analysis.wreck.buffer</t>
+          <t>analysis.queue.capacity</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>解析台的残骸缓存最多几件(传送带 / 面板送进来,队列空闲时逐件处理)</t>
+          <t>解析队列最多几项(FGR-RND-020 初值 8;只数排队/解析中/断电暂停)</t>
         </is>
       </c>
     </row>
@@ -4982,15 +4982,15 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>analysis.history.keep</t>
+          <t>analysis.wreck.buffer</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>队列里保留几条最近结束的记录给面板看(更早的清掉;Demo 区域任务物的完成记录不清,目标判定要用)</t>
+          <t>解析台的残骸缓存最多几件(传送带 / 面板送进来,队列空闲时逐件处理)</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>range.projection.max</t>
+          <t>analysis.history.keep</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>同时存在的仿真投影上限(全部靶场合计;FG05 第 7 节初值 6)</t>
+          <t>队列里保留几条最近结束的记录给面板看(更早的清掉;Demo 区域任务物的完成记录不清,目标判定要用)</t>
         </is>
       </c>
     </row>
@@ -5014,15 +5014,15 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>range.target.slots</t>
+          <t>range.projection.max</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>每座靶场的靶位数(远端 2 排 × 4 列)</t>
+          <t>同时存在的仿真投影上限(全部靶场合计;FG05 第 7 节初值 6)</t>
         </is>
       </c>
     </row>
@@ -5030,15 +5030,15 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>range.test.max_seconds</t>
+          <t>range.target.slots</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>一次测试最长游戏秒,到点自动结束并记下读数</t>
+          <t>每座靶场的靶位数(远端 2 排 × 4 列)</t>
         </is>
       </c>
     </row>
@@ -5046,15 +5046,15 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>range.sample_seconds</t>
+          <t>range.test.max_seconds</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>0.5</v>
+        <v>180</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>读数采样间隔(游戏秒;标签覆盖率与热量曲线按它采样)</t>
+          <t>一次测试最长游戏秒,到点自动结束并记下读数</t>
         </is>
       </c>
     </row>
@@ -5062,15 +5062,15 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>range.curve.points</t>
+          <t>range.sample_seconds</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>60</v>
+        <v>0.5</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>测试记录里热量曲线最多保留几个点(超出时等距抽样)</t>
+          <t>读数采样间隔(游戏秒;标签覆盖率与热量曲线按它采样)</t>
         </is>
       </c>
     </row>
@@ -5078,15 +5078,15 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>range.history.keep</t>
+          <t>range.curve.points</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>测试记录最多保留几条(新的在后)</t>
+          <t>测试记录里热量曲线最多保留几个点(超出时等距抽样)</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>range.presets.max</t>
+          <t>range.history.keep</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>靶子布置预设最多几个</t>
+          <t>测试记录最多保留几条(新的在后)</t>
         </is>
       </c>
     </row>
@@ -5110,15 +5110,15 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>range.target.respawn_seconds</t>
+          <t>range.presets.max</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>投影靶被打空后原地复位的游戏秒</t>
+          <t>靶子布置预设最多几个</t>
         </is>
       </c>
     </row>
@@ -5126,15 +5126,15 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>range.attack_range</t>
+          <t>range.target.respawn_seconds</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>投影的攻击命令射程(与远征编队攻击同一个数)</t>
+          <t>投影靶被打空后原地复位的游戏秒</t>
         </is>
       </c>
     </row>
@@ -5142,15 +5142,15 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>range.retarget_seconds</t>
+          <t>range.attack_range</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>投影没有目标时多久重新找一次最近的投影靶</t>
+          <t>投影的攻击命令射程(与远征编队攻击同一个数)</t>
         </is>
       </c>
     </row>
@@ -5158,15 +5158,15 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>range.swarm.spread</t>
+          <t>range.retarget_seconds</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>集群靶在靶位里的散开半径</t>
+          <t>投影没有目标时多久重新找一次最近的投影靶</t>
         </is>
       </c>
     </row>
@@ -5174,15 +5174,15 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>range.edge_margin</t>
+          <t>range.swarm.spread</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>单位离靶场边缘至少留多远(高速靶的摆动不出靶场)</t>
+          <t>集群靶在靶位里的散开半径</t>
         </is>
       </c>
     </row>
@@ -5190,15 +5190,15 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>fusion.sim_tech</t>
+          <t>range.edge_margin</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>模拟熔合花的技术数据(FGR-RND-040 初值 5;没有配方也照收,父固件一条都不消耗)</t>
+          <t>单位离靶场边缘至少留多远(高速靶的摆动不出靶场)</t>
         </is>
       </c>
     </row>
@@ -5206,15 +5206,15 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>fusion.formal_tech</t>
+          <t>fusion.sim_tech</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>正式熔合花的技术数据(FGR-RND-041 初值 30;入队时预留,取消 / 合成台被毁退回)</t>
+          <t>模拟熔合花的技术数据(FGR-RND-040 初值 5;没有配方也照收,父固件一条都不消耗)</t>
         </is>
       </c>
     </row>
@@ -5222,15 +5222,15 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>fusion.formal_substrate</t>
+          <t>fusion.formal_tech</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>正式熔合花的芯片基板(FGR-RND-041 初值 2)</t>
+          <t>正式熔合花的技术数据(FGR-RND-041 初值 30;入队时预留,取消 / 合成台被毁退回)</t>
         </is>
       </c>
     </row>
@@ -5238,15 +5238,15 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>fusion.formal_seconds</t>
+          <t>fusion.formal_substrate</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>正式熔合用时(游戏秒;合成台缺电 / 禁用时暂停、进度保留)</t>
+          <t>正式熔合花的芯片基板(FGR-RND-041 初值 2)</t>
         </is>
       </c>
     </row>
@@ -5254,15 +5254,15 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>fusion.burn_substrate</t>
+          <t>fusion.formal_seconds</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>固件刻录台量产一枚混合固件的芯片基板(FGR-RND-042 初值 3,常规固件是 1)</t>
+          <t>正式熔合用时(游戏秒;合成台缺电 / 禁用时暂停、进度保留)</t>
         </is>
       </c>
     </row>
@@ -5270,15 +5270,15 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>fusion.queue_max</t>
+          <t>fusion.burn_substrate</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>每座电路合成台的正式熔合队列上限(含正在做的那一项)</t>
+          <t>固件刻录台量产一枚混合固件的芯片基板(FGR-RND-042 初值 3,常规固件是 1)</t>
         </is>
       </c>
     </row>
@@ -5286,15 +5286,15 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>fusion.load_bonus</t>
+          <t>fusion.queue_max</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>混合固件的负载 = 两条父固件中较大值 + 本值(FGR-FW-050 初值 1;生成数据时用,自检核对)</t>
+          <t>每座电路合成台的正式熔合队列上限(含正在做的那一项)</t>
         </is>
       </c>
     </row>
@@ -5302,15 +5302,15 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>fusion.clue_partial_min</t>
+          <t>fusion.load_bonus</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>一场里某条反应触发达到这么多次 → 部分线索(只知道一条父固件)</t>
+          <t>混合固件的负载 = 两条父固件中较大值 + 本值(FGR-FW-050 初值 1;生成数据时用,自检核对)</t>
         </is>
       </c>
     </row>
@@ -5318,15 +5318,15 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>fusion.clue_full_min</t>
+          <t>fusion.clue_partial_min</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>一场里某条反应触发达到这么多次 → 完整线索(两条父固件都知道)</t>
+          <t>一场里某条反应触发达到这么多次 → 部分线索(只知道一条父固件)</t>
         </is>
       </c>
     </row>
@@ -5334,15 +5334,15 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>fusion.clue_per_session</t>
+          <t>fusion.clue_full_min</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>一场战斗最多生成几条线索(按触发次数从多到少)</t>
+          <t>一场里某条反应触发达到这么多次 → 完整线索(两条父固件都知道)</t>
         </is>
       </c>
     </row>
@@ -5350,15 +5350,15 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>fusion.clue_keep</t>
+          <t>fusion.clue_per_session</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>配方书里最多保留几条线索(超出时去掉最旧的、已经没用的线索)</t>
+          <t>一场战斗最多生成几条线索(按触发次数从多到少)</t>
         </is>
       </c>
     </row>
@@ -5366,15 +5366,15 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>fusion.pending_keep</t>
+          <t>fusion.clue_keep</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>没有仿真实验室时最多先存几场战斗记录</t>
+          <t>配方书里最多保留几条线索(超出时去掉最旧的、已经没用的线索)</t>
         </is>
       </c>
     </row>
@@ -5382,15 +5382,15 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>fusion.sim_log_keep</t>
+          <t>fusion.pending_keep</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>模拟熔合记录最多保留几条(“这一对模拟过:无反应”的提示用)</t>
+          <t>没有仿真实验室时最多先存几场战斗记录</t>
         </is>
       </c>
     </row>
@@ -5398,15 +5398,15 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>intel.raid_window_frac</t>
+          <t>fusion.sim_log_keep</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>0.15</v>
+        <v>40</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>突袭预报的抵达窗口 = 预计抵达时间 ×(1 ± 本值)(FGR-RND-050 时间窗口)</t>
+          <t>模拟熔合记录最多保留几条(“这一对模拟过:无反应”的提示用)</t>
         </is>
       </c>
     </row>
@@ -5414,15 +5414,15 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>intel.raid_window_min_seconds</t>
+          <t>intel.raid_window_frac</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>20</v>
+        <v>0.15</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>突袭预报抵达窗口的最小半宽(游戏秒;快到的部队窗口不至于只有一瞬)</t>
+          <t>突袭预报的抵达窗口 = 预计抵达时间 ×(1 ± 本值)(FGR-RND-050 时间窗口)</t>
         </is>
       </c>
     </row>
@@ -5430,15 +5430,15 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>intel.keep_per_kind</t>
+          <t>intel.raid_window_min_seconds</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>每类情报最多保留几条“已过时”的旧情报(有效的情报不受限;超出时去掉最旧的已过时情报)</t>
+          <t>突袭预报抵达窗口的最小半宽(游戏秒;快到的部队窗口不至于只有一瞬)</t>
         </is>
       </c>
     </row>
@@ -5446,15 +5446,15 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>intel.map_arrow_cells</t>
+          <t>intel.keep_per_kind</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>地图上突袭预报箭头的长度(格;箭头从来袭方向指向归还核心)</t>
+          <t>每类情报最多保留几条“已过时”的旧情报(有效的情报不受限;超出时去掉最旧的已过时情报)</t>
         </is>
       </c>
     </row>
@@ -5462,15 +5462,15 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>blackbox.points_per_box</t>
+          <t>intel.map_arrow_cells</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>每个黑匣子共产出多少技术数据(FGR-RND-060 初值 20;按分析进度逐点入账)</t>
+          <t>地图上突袭预报箭头的长度(格;箭头从来袭方向指向归还核心)</t>
         </is>
       </c>
     </row>
@@ -5478,15 +5478,15 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>blackbox.days_per_box</t>
+          <t>blackbox.points_per_box</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>一座陈列馆分析完一个黑匣子要几个游戏日(FGR-RND-060 初值 1;1 游戏日 = clock.day_seconds 游戏秒)</t>
+          <t>每个黑匣子共产出多少技术数据(FGR-RND-060 初值 20;按分析进度逐点入账)</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>blackbox.boxes_per_gallery</t>
+          <t>blackbox.days_per_box</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>每座工作中的陈列馆同时分析几个黑匣子(其余按回收先后排队;多座各自独立、不递减)</t>
+          <t>一座陈列馆分析完一个黑匣子要几个游戏日(FGR-RND-060 初值 1;1 游戏日 = clock.day_seconds 游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5510,15 +5510,15 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>blackbox.boxes_per_gallery</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>每座工作中的陈列馆同时分析几个黑匣子(其余按回收先后排队;多座各自独立、不递减)</t>
         </is>
       </c>
     </row>
@@ -5526,15 +5526,15 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -5542,15 +5542,15 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -5558,15 +5558,15 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -5574,15 +5574,15 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -5590,15 +5590,15 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -5606,15 +5606,15 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -5622,15 +5622,15 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -5638,15 +5638,15 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -5654,15 +5654,15 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -5670,15 +5670,15 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -5686,15 +5686,15 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -5702,15 +5702,15 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -5734,15 +5734,15 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -5750,15 +5750,15 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -5766,15 +5766,15 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -5782,15 +5782,15 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -5798,15 +5798,15 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5830,15 +5830,15 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -5846,15 +5846,15 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -5862,15 +5862,15 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -5878,15 +5878,15 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -5894,15 +5894,15 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -5910,15 +5910,15 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -5926,15 +5926,15 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5942,15 +5942,15 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6006,15 +6006,15 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6022,15 +6022,15 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -6038,15 +6038,15 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -6054,15 +6054,15 @@
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -6070,15 +6070,15 @@
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -6086,15 +6086,15 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -6102,15 +6102,15 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -6118,15 +6118,15 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -6134,15 +6134,15 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -6150,15 +6150,15 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -6182,15 +6182,15 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6198,15 +6198,15 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -6214,15 +6214,15 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -6230,15 +6230,15 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -6246,15 +6246,15 @@
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>12</v>
+        <v>0.05</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -6262,15 +6262,15 @@
       <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -6278,15 +6278,15 @@
       <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>100000</v>
+        <v>10</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -6294,15 +6294,15 @@
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>3</v>
+        <v>100000</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -6326,15 +6326,15 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -6342,15 +6342,15 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -6358,15 +6358,15 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6374,15 +6374,15 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -6390,15 +6390,15 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6406,15 +6406,15 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>away.machines_max</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6422,15 +6422,15 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>alarm.jam_seconds</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>0.3</v>
+        <v>60</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
         </is>
       </c>
     </row>
@@ -6438,15 +6438,15 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>alarm.machine_wounded_fraction</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
         </is>
       </c>
     </row>
@@ -6454,15 +6454,15 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.softlock.check_seconds</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
         </is>
       </c>
     </row>
@@ -6470,15 +6470,15 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.softlock.print_min_machines</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
         </is>
       </c>
     </row>
@@ -6486,15 +6486,15 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.softlock.print_health</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
         </is>
       </c>
     </row>
@@ -6502,15 +6502,15 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.softlock.core_scrap_per_minute</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
         </is>
       </c>
     </row>
@@ -6518,15 +6518,15 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.softlock.loop_check_seconds</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
         </is>
       </c>
     </row>
@@ -6534,15 +6534,15 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.softlock.loop_stall_seconds</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
         </is>
       </c>
     </row>
@@ -6550,13 +6550,29 @@
       <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>10</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr"/>
+      <c r="B384" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C383" t="n">
+      <c r="C384" t="n">
         <v>20</v>
       </c>
-      <c r="D383" t="inlineStr">
+      <c r="D384" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D384"/>
+  <dimension ref="A1:D395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5526,15 +5526,15 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>turret.aim_tolerance_deg</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>有转速的炮塔:炮口与目标方向夹角在这个度数以内才开火(FGR-DEF-002)</t>
         </is>
       </c>
     </row>
@@ -5542,15 +5542,15 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>turret.sync_seconds</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>炮塔对账间隔(游戏秒):建成 / 摧毁 / 禁用 / 断电 / 换蓝图 / 管线补给装填,按步序号定时做,与观察无关</t>
         </is>
       </c>
     </row>
@@ -5558,15 +5558,15 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>turret.supply.magazine_shots</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>每次装进内核的补给上限(发):补给一发一扣在内核里,热更层按对账间隔从管线缓存装填</t>
         </is>
       </c>
     </row>
@@ -5574,15 +5574,15 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>turret.supply.buffer_shots</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>炮塔自己存得下多少发的流体(升 = 发数 × 每发升数;拆除 / 摧毁时留在炮塔里,读档照旧)</t>
         </is>
       </c>
     </row>
@@ -5590,15 +5590,15 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>turret.supply.lpm</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>炮塔从管线进流体的速率上限(升/分钟)</t>
         </is>
       </c>
     </row>
@@ -5606,15 +5606,15 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>turret.supply.pipe_priority</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>炮塔作为管线消费者的优先级(1~4,4 最高;初值与生产建筑同档,不抢发电)</t>
         </is>
       </c>
     </row>
@@ -5622,15 +5622,15 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>turret.supply.low_shots</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>补给低于这么多发时状态行写“补给快用完”(只提示,不改行为)</t>
         </is>
       </c>
     </row>
@@ -5638,15 +5638,15 @@
       <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>turret.tier.armor.t2</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>T2 炮塔座受到的伤害减少比例(全方位)</t>
         </is>
       </c>
     </row>
@@ -5654,15 +5654,15 @@
       <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>turret.tier.armor.t3</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>25</v>
+        <v>0.35</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>T3 炮塔座受到的伤害减少比例(全方位)</t>
         </is>
       </c>
     </row>
@@ -5670,15 +5670,15 @@
       <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>turret.notify.cooldown_seconds</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>同一座炮塔“缺补给停火”通知的最短间隔(游戏秒;同类通知另按聚合窗口合并)</t>
         </is>
       </c>
     </row>
@@ -5686,15 +5686,15 @@
       <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>turret.ring.segments</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>射程圈的折线段数(放置预览 / 选中炮塔时画在地面上)</t>
         </is>
       </c>
     </row>
@@ -5702,15 +5702,15 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -5734,15 +5734,15 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -5750,15 +5750,15 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -5782,15 +5782,15 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -5798,15 +5798,15 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -5814,15 +5814,15 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -5830,15 +5830,15 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -5846,15 +5846,15 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>0.02</v>
+        <v>50</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -5862,15 +5862,15 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -5878,15 +5878,15 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -5894,15 +5894,15 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -5910,15 +5910,15 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -5926,15 +5926,15 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -5942,15 +5942,15 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -5958,15 +5958,15 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -5974,15 +5974,15 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -5990,15 +5990,15 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -6006,15 +6006,15 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -6022,15 +6022,15 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>30</v>
+        <v>0.02</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -6054,15 +6054,15 @@
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6070,15 +6070,15 @@
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -6086,15 +6086,15 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>1200</v>
+        <v>64</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -6102,15 +6102,15 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -6118,15 +6118,15 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -6134,15 +6134,15 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -6150,15 +6150,15 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6166,15 +6166,15 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6182,15 +6182,15 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6198,15 +6198,15 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>0.5</v>
+        <v>30</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -6214,15 +6214,15 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -6230,15 +6230,15 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -6246,15 +6246,15 @@
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>0.05</v>
+        <v>120</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -6262,15 +6262,15 @@
       <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -6294,15 +6294,15 @@
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>100000</v>
+        <v>120</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -6310,15 +6310,15 @@
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -6326,15 +6326,15 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -6342,15 +6342,15 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -6358,15 +6358,15 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6374,15 +6374,15 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>40</v>
+        <v>0.5</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -6390,15 +6390,15 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -6406,15 +6406,15 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -6422,15 +6422,15 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>60</v>
+        <v>0.05</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -6438,15 +6438,15 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>0.3</v>
+        <v>12</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -6454,15 +6454,15 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -6470,15 +6470,15 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>2</v>
+        <v>100000</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6486,15 +6486,15 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -6502,15 +6502,15 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -6518,15 +6518,15 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -6534,15 +6534,15 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -6550,15 +6550,15 @@
       <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -6566,13 +6566,189 @@
       <c r="A384" t="inlineStr"/>
       <c r="B384" t="inlineStr">
         <is>
-          <t>eco.softlock.unreachable_seconds</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C384" t="n">
         <v>20</v>
       </c>
       <c r="D384" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr"/>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>64</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr"/>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>60</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr"/>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr"/>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>1</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr"/>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>2</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr"/>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>100</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr"/>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>1</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr"/>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>5</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr"/>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>120</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr"/>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>10</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr"/>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>eco.softlock.unreachable_seconds</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>20</v>
+      </c>
+      <c r="D395" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D395"/>
+  <dimension ref="A1:D419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5702,15 +5702,15 @@
       <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>defense.sync_seconds</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>24</v>
+        <v>0.5</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>防御建筑对账间隔(游戏秒):建成 / 摧毁 / 禁用 / 断电 / 维修 → 战斗内核里的结构单位、护盾、陷阱;按步序号定时做,与观察无关</t>
         </is>
       </c>
     </row>
@@ -5718,15 +5718,15 @@
       <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>defense.preview.margin_cells</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>放置屏障时预览敌方路线的搜索范围:家园建筑外接矩形向外放宽的格数(敌人从这个框的边上进来)</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>defense.preview.max_routes</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>放置屏障时最多预览几条敌方来路(按敌方据点方向取;没有已知据点时取东南西北)</t>
         </is>
       </c>
     </row>
@@ -5750,15 +5750,15 @@
       <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>shield.radius</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>护盾半径(米;以护盾发生器为圆心,进入圆内的敌方弹体被吸收)</t>
         </is>
       </c>
     </row>
@@ -5766,15 +5766,15 @@
       <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>shield.capacity</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>护盾值上限(吸收的伤害;耗尽 = 过载)</t>
         </is>
       </c>
     </row>
@@ -5782,15 +5782,15 @@
       <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>shield.power_per_dps</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>护盾每承受 1 点每秒伤害多耗多少电(FGR-DEF-012“耗电随承受的伤害上升”)</t>
         </is>
       </c>
     </row>
@@ -5798,15 +5798,15 @@
       <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>shield.power_band</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>护盾额外耗电按这个档位向上取整(只在档位变化时重新结算电网,避免每步重算)</t>
         </is>
       </c>
     </row>
@@ -5814,15 +5814,15 @@
       <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>shield.power_extra_cap</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>护盾额外耗电上限</t>
         </is>
       </c>
     </row>
@@ -5830,15 +5830,15 @@
       <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>shield.load_window_seconds</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>“最近承受的伤害(每秒)”的统计窗口(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -5846,15 +5846,15 @@
       <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>shield.notify.cooldown_seconds</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>同一座护盾“过载”通知的最短间隔(游戏秒;同类通知另按聚合窗口合并)</t>
         </is>
       </c>
     </row>
@@ -5862,15 +5862,15 @@
       <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>shield.ring.segments</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>护盾圈的折线段数(地面上画出护盾范围)</t>
         </is>
       </c>
     </row>
@@ -5878,15 +5878,15 @@
       <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>trap.line_length</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>陷阱发射器“一条线”模式:沿朝向铺多长(米)</t>
         </is>
       </c>
     </row>
@@ -5894,15 +5894,15 @@
       <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>trap.area_radius</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>陷阱发射器“一片区域”模式:以发射器为圆心铺多大(米)</t>
         </is>
       </c>
     </row>
@@ -5910,15 +5910,15 @@
       <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>trap.zone_radius</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>铺出的每一块场地的半径(米;线 = 一串、区域 = 一圈圈)</t>
         </is>
       </c>
     </row>
@@ -5926,15 +5926,15 @@
       <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>trap.lay_seconds</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>每隔多少游戏秒铺一轮(每轮消耗表里的每轮流体)</t>
         </is>
       </c>
     </row>
@@ -5942,15 +5942,15 @@
       <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>trap.zone_seconds</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>60</v>
+        <v>1.6</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>每一块场地持续多少游戏秒(比铺设间隔略长,接得上;停供后很快消失)</t>
         </is>
       </c>
     </row>
@@ -5958,15 +5958,15 @@
       <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>trap.buffer_lays</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>陷阱发射器自己存得下多少轮的流体(拆除 / 摧毁时留在发射器里,读档照旧)</t>
         </is>
       </c>
     </row>
@@ -5974,15 +5974,15 @@
       <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>trap.supply_lpm</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>陷阱发射器从管线进流体的速率上限(升/分钟)</t>
         </is>
       </c>
     </row>
@@ -5990,15 +5990,15 @@
       <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>trap.pipe_priority</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>陷阱发射器作为管线消费者的优先级(1~4,4 最高;与炮塔同档)</t>
         </is>
       </c>
     </row>
@@ -6006,15 +6006,15 @@
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>trap.notify.cooldown_seconds</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>同一座陷阱发射器“缺流体”通知的最短间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -6022,15 +6022,15 @@
       <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>trap.capacity.fields</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>0.02</v>
+        <v>512</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>家园同时存在的陷阱场地上限(与读法区域 reading.capacity.zones 分开计数,铺满不挤掉炮塔 / 机器的读法区域;超出的这一轮不铺并在状态行写明)</t>
         </is>
       </c>
     </row>
@@ -6038,15 +6038,15 @@
       <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>trap.area_spacing</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>“一片区域”模式:相邻两圈场地的间距 = 场地半径 × 本值</t>
         </is>
       </c>
     </row>
@@ -6054,15 +6054,15 @@
       <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>trap.line_spacing</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>16</v>
+        <v>1.2</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>“一条线”模式:相邻两块场地的间距 = 场地半径 × 本值</t>
         </is>
       </c>
     </row>
@@ -6070,15 +6070,15 @@
       <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>trap.line_offset</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>“一条线”模式:第一块场地离发射器中心多远(米,另加半个间距)</t>
         </is>
       </c>
     </row>
@@ -6086,15 +6086,15 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -6102,15 +6102,15 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -6118,15 +6118,15 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>600</v>
+        <v>4</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -6134,15 +6134,15 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -6150,15 +6150,15 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -6166,15 +6166,15 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -6182,15 +6182,15 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -6198,15 +6198,15 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -6214,15 +6214,15 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -6230,15 +6230,15 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -6246,15 +6246,15 @@
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -6262,15 +6262,15 @@
       <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -6278,15 +6278,15 @@
       <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -6294,15 +6294,15 @@
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -6310,15 +6310,15 @@
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -6326,15 +6326,15 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -6342,15 +6342,15 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -6358,15 +6358,15 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -6374,15 +6374,15 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -6390,15 +6390,15 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -6406,15 +6406,15 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>3</v>
+        <v>0.02</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -6422,15 +6422,15 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -6438,15 +6438,15 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6454,15 +6454,15 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -6470,15 +6470,15 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>100000</v>
+        <v>64</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -6486,15 +6486,15 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -6502,15 +6502,15 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>3</v>
+        <v>600</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -6518,15 +6518,15 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -6534,15 +6534,15 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6566,15 +6566,15 @@
       <c r="A384" t="inlineStr"/>
       <c r="B384" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6582,15 +6582,15 @@
       <c r="A385" t="inlineStr"/>
       <c r="B385" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -6598,15 +6598,15 @@
       <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -6614,15 +6614,15 @@
       <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>0.3</v>
+        <v>20</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -6630,15 +6630,15 @@
       <c r="A388" t="inlineStr"/>
       <c r="B388" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -6646,15 +6646,15 @@
       <c r="A389" t="inlineStr"/>
       <c r="B389" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>2</v>
+        <v>1200</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -6662,15 +6662,15 @@
       <c r="A390" t="inlineStr"/>
       <c r="B390" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -6678,15 +6678,15 @@
       <c r="A391" t="inlineStr"/>
       <c r="B391" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -6694,15 +6694,15 @@
       <c r="A392" t="inlineStr"/>
       <c r="B392" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -6710,15 +6710,15 @@
       <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -6726,15 +6726,15 @@
       <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -6742,13 +6742,397 @@
       <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
+          <t>eco.topbar.max_pins</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>8</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr"/>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>eco.topbar.refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr"/>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>eco.topbar.rate_window</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>1</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>eco.topbar.max_subnets</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>3</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>eco.topbar.target_tolerance</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>eco.planner.max_depth</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>12</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>eco.planner.default_rate</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>10</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>eco.planner.max_rate</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>away.reports_keep</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>3</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>away.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>3</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>away.items_max</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>12</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr"/>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>away.entries_max</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>60</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>40</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>20</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr"/>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>64</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr"/>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>60</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr"/>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>1</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr"/>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>2</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr"/>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>100</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>1</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr"/>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>5</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>120</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr"/>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>10</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr"/>
+      <c r="B419" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C395" t="n">
+      <c r="C419" t="n">
         <v>20</v>
       </c>
-      <c r="D395" t="inlineStr">
+      <c r="D419" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D419"/>
+  <dimension ref="A1:D434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6086,15 +6086,15 @@
       <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>drone.count</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>每座维修无人机站常备几架无人机(FGR-DEF-014)</t>
         </is>
       </c>
     </row>
@@ -6102,15 +6102,15 @@
       <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>drone.range</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>维修无人机站的覆盖范围(米,以站中心为圆心;目标中心在圈内才修)</t>
         </is>
       </c>
     </row>
@@ -6118,15 +6118,15 @@
       <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>drone.speed</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>维修无人机飞行速度(米/游戏秒;直线飞,不受地形与建筑阻挡)</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>drone.repair_per_second</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>每架无人机每游戏秒修好的耐久</t>
         </is>
       </c>
     </row>
@@ -6150,15 +6150,15 @@
       <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>drone.hp</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>维修无人机的耐久(在战斗内核里,敌人的弹体能打中它)</t>
         </is>
       </c>
     </row>
@@ -6166,15 +6166,15 @@
       <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>drone.radius</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>维修无人机在战斗内核里的半径(米)</t>
         </is>
       </c>
     </row>
@@ -6182,15 +6182,15 @@
       <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>drone.reach</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>无人机离目标边缘多近开始修理(米)</t>
         </is>
       </c>
     </row>
@@ -6198,15 +6198,15 @@
       <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>drone.respawn_seconds</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>站点补充一架被击落的无人机要多少游戏秒(只在站点运转且有电时计时)</t>
         </is>
       </c>
     </row>
@@ -6214,15 +6214,15 @@
       <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>drone.respawn_scrap</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>站点补充一架无人机花多少废料(开始补充时扣;不够就等,写明原因)</t>
         </is>
       </c>
     </row>
@@ -6230,15 +6230,15 @@
       <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>drone.scan_seconds</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>无人机找目标 / 检查目标的间隔(游戏秒;按步序号定时做,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -6246,15 +6246,15 @@
       <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>drone.attacked_window_seconds</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>突袭中“正在受攻击”的判定:最近这么多游戏秒内耐久下降过的目标优先修理(FGR-DEF-014)</t>
         </is>
       </c>
     </row>
@@ -6262,15 +6262,15 @@
       <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>drone.belt_repair_kits</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>200</v>
+        <v>0.25</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>修满一格传送带要几件维修件(按修好的比例记账,零头累计;传送带没有建筑通用行)</t>
         </is>
       </c>
     </row>
@@ -6278,15 +6278,15 @@
       <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>drone.notify.cooldown_seconds</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>同一座维修无人机站“缺维修件 / 无人机被击落”通知的最短间隔(游戏秒;同类通知另按聚合窗口合并)</t>
         </is>
       </c>
     </row>
@@ -6294,15 +6294,15 @@
       <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>rules.zone.max</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>每条自动重建规则最多圈几个重建区域</t>
         </is>
       </c>
     </row>
@@ -6310,15 +6310,15 @@
       <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>rules.zone.min_cells</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>重建区域至少多少格(拖框;2×2 = 4)</t>
         </is>
       </c>
     </row>
@@ -6326,15 +6326,15 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -6342,15 +6342,15 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -6358,15 +6358,15 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -6374,15 +6374,15 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -6390,15 +6390,15 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -6406,15 +6406,15 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -6422,15 +6422,15 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -6438,15 +6438,15 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -6454,15 +6454,15 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -6470,15 +6470,15 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -6486,15 +6486,15 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -6502,15 +6502,15 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -6518,15 +6518,15 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -6534,15 +6534,15 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -6550,15 +6550,15 @@
       <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -6566,15 +6566,15 @@
       <c r="A384" t="inlineStr"/>
       <c r="B384" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -6582,15 +6582,15 @@
       <c r="A385" t="inlineStr"/>
       <c r="B385" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -6598,15 +6598,15 @@
       <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -6614,15 +6614,15 @@
       <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -6630,15 +6630,15 @@
       <c r="A388" t="inlineStr"/>
       <c r="B388" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -6646,15 +6646,15 @@
       <c r="A389" t="inlineStr"/>
       <c r="B389" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1200</v>
+        <v>0.02</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -6662,15 +6662,15 @@
       <c r="A390" t="inlineStr"/>
       <c r="B390" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -6678,15 +6678,15 @@
       <c r="A391" t="inlineStr"/>
       <c r="B391" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6694,15 +6694,15 @@
       <c r="A392" t="inlineStr"/>
       <c r="B392" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -6710,15 +6710,15 @@
       <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -6726,15 +6726,15 @@
       <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -6742,15 +6742,15 @@
       <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>8</v>
+        <v>600</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -6758,15 +6758,15 @@
       <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -6774,15 +6774,15 @@
       <c r="A397" t="inlineStr"/>
       <c r="B397" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6790,15 +6790,15 @@
       <c r="A398" t="inlineStr"/>
       <c r="B398" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6806,15 +6806,15 @@
       <c r="A399" t="inlineStr"/>
       <c r="B399" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>0.05</v>
+        <v>40</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -6822,15 +6822,15 @@
       <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -6838,15 +6838,15 @@
       <c r="A401" t="inlineStr"/>
       <c r="B401" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -6854,15 +6854,15 @@
       <c r="A402" t="inlineStr"/>
       <c r="B402" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>100000</v>
+        <v>20</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -6870,15 +6870,15 @@
       <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -6886,15 +6886,15 @@
       <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>3</v>
+        <v>1200</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -6902,15 +6902,15 @@
       <c r="A405" t="inlineStr"/>
       <c r="B405" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -6918,15 +6918,15 @@
       <c r="A406" t="inlineStr"/>
       <c r="B406" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -6934,15 +6934,15 @@
       <c r="A407" t="inlineStr"/>
       <c r="B407" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -6950,15 +6950,15 @@
       <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -6966,15 +6966,15 @@
       <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -6982,15 +6982,15 @@
       <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -6998,15 +6998,15 @@
       <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -7030,15 +7030,15 @@
       <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -7046,15 +7046,15 @@
       <c r="A414" t="inlineStr"/>
       <c r="B414" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>100</v>
+        <v>0.05</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -7062,15 +7062,15 @@
       <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -7078,15 +7078,15 @@
       <c r="A416" t="inlineStr"/>
       <c r="B416" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -7094,15 +7094,15 @@
       <c r="A417" t="inlineStr"/>
       <c r="B417" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>120</v>
+        <v>100000</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -7110,15 +7110,15 @@
       <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -7126,13 +7126,253 @@
       <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
+          <t>away.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>3</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr"/>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>away.items_max</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>12</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr"/>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>away.entries_max</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>60</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr"/>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>40</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr"/>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>20</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr"/>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>64</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr"/>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>60</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr"/>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr"/>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>1</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr"/>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>2</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr"/>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>100</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr"/>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr"/>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>5</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr"/>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>120</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr"/>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>10</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr"/>
+      <c r="B434" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C419" t="n">
+      <c r="C434" t="n">
         <v>20</v>
       </c>
-      <c r="D419" t="inlineStr">
+      <c r="D434" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D434"/>
+  <dimension ref="A1:D463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6326,15 +6326,15 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>raid.min_interval_days</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>两次普通突袭(按抵达时刻)之间至少间隔几个游戏日(FGR-DEF-020;剧情 / 静默夜 / 巨构阶段除外;难度频率倍率除它)</t>
         </is>
       </c>
     </row>
@@ -6342,15 +6342,15 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>raid.min_warning_hours</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>最短预警(游戏小时,FGR-DEF-024;路程不够时推迟出发,部队在出发地集结;乘难度预警倍率)</t>
         </is>
       </c>
     </row>
@@ -6358,15 +6358,15 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>raid.intel_lead_days</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>有监听站时最早提前几个游戏日预报计划中的突袭(FGR-DEF-024)</t>
         </is>
       </c>
     </row>
@@ -6374,15 +6374,15 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>raid.plan_lead_days</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>普通触发到部队出发(发预警)之间的筹备时间(游戏日;监听站在这段时间里可以破译出发前预报)</t>
         </is>
       </c>
     </row>
@@ -6390,15 +6390,15 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>raid.story_plan_lead_days</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>60</v>
+        <v>0.25</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>剧情 / 静默夜 / 巨构触发到部队出发的筹备时间(游戏日)</t>
         </is>
       </c>
     </row>
@@ -6406,15 +6406,15 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>raid.route_latency_seconds</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>排定突袭的长路线走后台寻路通道,固定这么多游戏秒后采纳(DEBT-FG0ARCH06-09:冷的长路线要几百毫秒,不让采纳步硬等;延迟固定 → 结果确定)</t>
         </is>
       </c>
     </row>
@@ -6422,15 +6422,15 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>raid.first_raid_min_days</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>开局宽限:第几个游戏日之前不会有暴露 / 骚扰触发的突袭抵达(FG16 节奏 2:00 第一次突袭;剧情突袭不受限)</t>
         </is>
       </c>
     </row>
@@ -6438,15 +6438,15 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>raid.first_raid_scale</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>10</v>
+        <v>0.6</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>第一次突袭固定 1 级,预算再乘这个系数(FG06 第 4 节“规模很小”)</t>
         </is>
       </c>
     </row>
@@ -6454,15 +6454,15 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>raid.act1_coef</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>幕系数:第一幕(FG16 第 5 节)</t>
         </is>
       </c>
     </row>
@@ -6470,15 +6470,15 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>raid.act2_coef</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>50</v>
+        <v>1.6</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>幕系数:第二幕</t>
         </is>
       </c>
     </row>
@@ -6486,15 +6486,15 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>raid.act3_coef</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>幕系数:第三幕</t>
         </is>
       </c>
     </row>
@@ -6502,15 +6502,15 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>raid.interval_bonus_per_day</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>200</v>
+        <v>0.1</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>间隔系数:距上次突袭超过最短间隔后,每多 1 个游戏日预算 + 本值</t>
         </is>
       </c>
     </row>
@@ -6518,15 +6518,15 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>raid.interval_bonus_max</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>间隔系数的加成上限</t>
         </is>
       </c>
     </row>
@@ -6534,15 +6534,15 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>raid.level4_period_days</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>暴露超过 90 后每隔几个游戏日发生一次 4 级突袭</t>
         </is>
       </c>
     </row>
@@ -6550,15 +6550,15 @@
       <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>raid.threshold_rearm</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>暴露降到阈值以下多少之后,再次越过这个阈值才会再次触发</t>
         </is>
       </c>
     </row>
@@ -6566,15 +6566,15 @@
       <c r="A384" t="inlineStr"/>
       <c r="B384" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>raid.harass_min_interval_days</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>低强度骚扰的频率上限:两次骚扰至少间隔几个游戏日</t>
         </is>
       </c>
     </row>
@@ -6582,15 +6582,15 @@
       <c r="A385" t="inlineStr"/>
       <c r="B385" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>raid.harass_quiet_days</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>距上一次任何突袭抵达至少几个游戏日才会来骚扰</t>
         </is>
       </c>
     </row>
@@ -6598,15 +6598,15 @@
       <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>raid.max_units</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>一波突袭的单位数上限(FG15 同时存在的敌人 200;超出的预算换成精英)</t>
         </is>
       </c>
     </row>
@@ -6614,15 +6614,15 @@
       <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>raid.postgame_base</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>2</v>
+        <v>1200</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>后日谈第 n 次清洗的预算基数(FG16 第 5 节)</t>
         </is>
       </c>
     </row>
@@ -6630,15 +6630,15 @@
       <c r="A388" t="inlineStr"/>
       <c r="B388" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>raid.postgame_growth</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>后日谈每次清洗的预算增长倍率</t>
         </is>
       </c>
     </row>
@@ -6646,15 +6646,15 @@
       <c r="A389" t="inlineStr"/>
       <c r="B389" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>raid.merge_window_seconds</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>0.02</v>
+        <v>1200</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>剧情 / 静默夜 / 巨构突袭与普通突袭抵达时间相差不超过这么多游戏秒视为重叠,合并为一波</t>
         </is>
       </c>
     </row>
@@ -6662,15 +6662,15 @@
       <c r="A390" t="inlineStr"/>
       <c r="B390" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>raid.destroyed_outpost_interval_bonus</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>某个方向(8 方位)每摧毁一个据点,从那个方向出发的突袭最短间隔 ×(1 + 本值)</t>
         </is>
       </c>
     </row>
@@ -6678,15 +6678,15 @@
       <c r="A391" t="inlineStr"/>
       <c r="B391" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>raid.origin_max_distance</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>16</v>
+        <v>1600</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>据点离目标超过这么多格就不算合适的出发地(改从迷雾外来袭)</t>
         </is>
       </c>
     </row>
@@ -6694,15 +6694,15 @@
       <c r="A392" t="inlineStr"/>
       <c r="B392" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>raid.target_home_weight</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>选突袭目标时家园的权重(前哨站权重 = 座数 / 10 × 领地临近系数)</t>
         </is>
       </c>
     </row>
@@ -6710,15 +6710,15 @@
       <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>raid.target_outpost_min_buildings</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>前哨站至少几座建筑才会被当成突袭目标</t>
         </is>
       </c>
     </row>
@@ -6726,15 +6726,15 @@
       <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>raid.target_proximity_cells</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>前哨站领地临近系数 = 1 + 本值 / (本值 + 到阵营领地边缘的距离)</t>
         </is>
       </c>
     </row>
@@ -6742,15 +6742,15 @@
       <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>raid.time_limit_hours</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>到达后的时间上限(游戏小时,FGR-DEF-032);攻城行为(FG6-DEF-05)之前部队在外围停留这么久后沿原路撤回出发地</t>
         </is>
       </c>
     </row>
@@ -6758,15 +6758,15 @@
       <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>raid.history_max</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>突袭历史最多保留几条</t>
         </is>
       </c>
     </row>
@@ -6774,15 +6774,15 @@
       <c r="A397" t="inlineStr"/>
       <c r="B397" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>raid.warning_rows_max</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>预警条最多列几波(更多的写“还有 n 波”)</t>
         </is>
       </c>
     </row>
@@ -6790,15 +6790,15 @@
       <c r="A398" t="inlineStr"/>
       <c r="B398" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -6806,15 +6806,15 @@
       <c r="A399" t="inlineStr"/>
       <c r="B399" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -6822,15 +6822,15 @@
       <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -6838,15 +6838,15 @@
       <c r="A401" t="inlineStr"/>
       <c r="B401" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -6854,15 +6854,15 @@
       <c r="A402" t="inlineStr"/>
       <c r="B402" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -6870,15 +6870,15 @@
       <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -6886,15 +6886,15 @@
       <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>1200</v>
+        <v>4</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       <c r="A405" t="inlineStr"/>
       <c r="B405" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -6918,15 +6918,15 @@
       <c r="A406" t="inlineStr"/>
       <c r="B406" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -6934,15 +6934,15 @@
       <c r="A407" t="inlineStr"/>
       <c r="B407" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -6950,15 +6950,15 @@
       <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -6966,15 +6966,15 @@
       <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -6982,15 +6982,15 @@
       <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -6998,15 +6998,15 @@
       <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -7014,15 +7014,15 @@
       <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -7030,15 +7030,15 @@
       <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -7046,15 +7046,15 @@
       <c r="A414" t="inlineStr"/>
       <c r="B414" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>0.05</v>
+        <v>10</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -7062,15 +7062,15 @@
       <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -7078,15 +7078,15 @@
       <c r="A416" t="inlineStr"/>
       <c r="B416" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -7094,15 +7094,15 @@
       <c r="A417" t="inlineStr"/>
       <c r="B417" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>100000</v>
+        <v>2</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -7110,15 +7110,15 @@
       <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>3</v>
+        <v>0.02</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -7126,15 +7126,15 @@
       <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -7142,15 +7142,15 @@
       <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -7158,15 +7158,15 @@
       <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -7174,15 +7174,15 @@
       <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -7190,15 +7190,15 @@
       <c r="A423" t="inlineStr"/>
       <c r="B423" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -7206,15 +7206,15 @@
       <c r="A424" t="inlineStr"/>
       <c r="B424" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>64</v>
+        <v>600</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -7222,15 +7222,15 @@
       <c r="A425" t="inlineStr"/>
       <c r="B425" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -7238,15 +7238,15 @@
       <c r="A426" t="inlineStr"/>
       <c r="B426" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>0.3</v>
+        <v>40</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -7254,15 +7254,15 @@
       <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -7270,15 +7270,15 @@
       <c r="A428" t="inlineStr"/>
       <c r="B428" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -7286,15 +7286,15 @@
       <c r="A429" t="inlineStr"/>
       <c r="B429" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -7302,15 +7302,15 @@
       <c r="A430" t="inlineStr"/>
       <c r="B430" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -7318,15 +7318,15 @@
       <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       <c r="A432" t="inlineStr"/>
       <c r="B432" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -7350,15 +7350,15 @@
       <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -7366,13 +7366,477 @@
       <c r="A434" t="inlineStr"/>
       <c r="B434" t="inlineStr">
         <is>
+          <t>eco.stats.deficit_minutes</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>10</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr"/>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>eco.stats.deficit_probe_seconds</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>120</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr"/>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>eco.stats.deficit_check_seconds</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>20</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr"/>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>eco.stats.panel_refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>1</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr"/>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>eco.stats.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>8</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>瓶颈页最多列几种物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr"/>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>eco.topbar.max_pins</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>8</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr"/>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>eco.topbar.refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr"/>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>eco.topbar.rate_window</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>1</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr"/>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>eco.topbar.max_subnets</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>3</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr"/>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>eco.topbar.target_tolerance</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr"/>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>eco.planner.max_depth</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>12</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr"/>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>eco.planner.default_rate</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>10</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr"/>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>eco.planner.max_rate</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr"/>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>away.reports_keep</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>3</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr"/>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>away.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>3</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr"/>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>away.items_max</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>12</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr"/>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>away.entries_max</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>60</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr"/>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>40</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr"/>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>20</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr"/>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>64</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr"/>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>60</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr"/>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr"/>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>1</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr"/>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>2</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr"/>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>100</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr"/>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>1</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr"/>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>5</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr"/>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>120</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr"/>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>10</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr"/>
+      <c r="B463" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C434" t="n">
+      <c r="C463" t="n">
         <v>20</v>
       </c>
-      <c r="D434" t="inlineStr">
+      <c r="D463" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D463"/>
+  <dimension ref="A1:D496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6790,15 +6790,15 @@
       <c r="A398" t="inlineStr"/>
       <c r="B398" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>siege.theater_radius_cells</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>攻城剧场:突袭目标点周围这么远(格)内的己方建筑算进流场范围</t>
         </is>
       </c>
     </row>
@@ -6806,15 +6806,15 @@
       <c r="A399" t="inlineStr"/>
       <c r="B399" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>siege.theater_margin_cells</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>攻城剧场:建筑外接矩形(含集结点)向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -6822,15 +6822,15 @@
       <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>siege.theater_max_cells</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>4</v>
+        <v>288</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>攻城剧场:流场矩形的最大边长(格);超出时以目标点为中心截取(流场内存与全量计算耗时的上限)</t>
         </is>
       </c>
     </row>
@@ -6838,15 +6838,15 @@
       <c r="A401" t="inlineStr"/>
       <c r="B401" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>siege.retarget_seconds</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>突袭单位重新选目标 / 重新看破墙目标的间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -6854,7 +6854,7 @@
       <c r="A402" t="inlineStr"/>
       <c r="B402" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>siege.breach_base_cost</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>破墙流场:穿过一格建筑的基础代价(10 = 走 1 米);越大越倾向绕路而不是破墙</t>
         </is>
       </c>
     </row>
@@ -6870,15 +6870,15 @@
       <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>siege.breach_hp_band</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>破墙流场:耐久每多这么多算一档(耐久掉档时流场增量更新)</t>
         </is>
       </c>
     </row>
@@ -6886,15 +6886,15 @@
       <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>siege.breach_cost_per_band</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>破墙流场:每档耐久加的代价(10 = 走 1 米);越大越倾向挑最薄弱的那段</t>
         </is>
       </c>
     </row>
@@ -6902,15 +6902,15 @@
       <c r="A405" t="inlineStr"/>
       <c r="B405" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>siege.loss_retreat_ratio</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>FGR-DEF-032:损失超过这个比例全队撤退(初值 70%)</t>
         </is>
       </c>
     </row>
@@ -6918,15 +6918,15 @@
       <c r="A406" t="inlineStr"/>
       <c r="B406" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>siege.exit_radius_cells</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>撤退:走到集结点这么近(格)就离开家园、并回行进队伍</t>
         </is>
       </c>
     </row>
@@ -6934,15 +6934,15 @@
       <c r="A407" t="inlineStr"/>
       <c r="B407" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>siege.retreat_max_seconds</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>撤退兜底(B11):下撤退令后这么久(游戏秒)还走不回集结点的(路被堵死时会先拆墙;连墙都拆不出去,例如被地形困住)就地离场,队伍照常原路返回</t>
         </is>
       </c>
     </row>
@@ -6950,15 +6950,15 @@
       <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>siege.hp_scale</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>突袭单位耐久 = fg.TbMechEnemy.maxHp × 本值</t>
         </is>
       </c>
     </row>
@@ -6966,15 +6966,15 @@
       <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>siege.elite_hp_scale</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>精英突袭单位的耐久倍率</t>
         </is>
       </c>
     </row>
@@ -6982,15 +6982,15 @@
       <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>siege.elite_damage_scale</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>500</v>
+        <v>1.5</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>精英突袭单位的伤害倍率</t>
         </is>
       </c>
     </row>
@@ -6998,15 +6998,15 @@
       <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>siege.spawn_spacing</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>60</v>
+        <v>1.6</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>到达展开:单位之间的间距(米;按确定性的螺旋排布)</t>
         </is>
       </c>
     </row>
@@ -7014,15 +7014,15 @@
       <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>siege.collateral_ratio</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>溅射:敌人每打中一次建筑,周围传送带 / 管线 / 施工虚影受到这一发伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -7030,15 +7030,15 @@
       <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>siege.collateral_radius_cells</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>60</v>
+        <v>1.5</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>溅射:命中点周围多远(格)内的传送带 / 管线 / 施工虚影受波及</t>
         </is>
       </c>
     </row>
@@ -7046,15 +7046,15 @@
       <c r="A414" t="inlineStr"/>
       <c r="B414" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>siege.collateral_drain_per_step</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>溅射:热更层每步最多结算几个命中格(其余留到下一步,不丢、进存档)</t>
         </is>
       </c>
     </row>
@@ -7062,15 +7062,15 @@
       <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>siege.site_hp_fraction</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>100</v>
+        <v>0.35</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>施工中的虚影被溅射打掉的耐久 = 建筑最大耐久 × 本值(打满即“施工中被摧毁”)</t>
         </is>
       </c>
     </row>
@@ -7078,15 +7078,15 @@
       <c r="A416" t="inlineStr"/>
       <c r="B416" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>siege.sync_seconds</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>攻城对账间隔(游戏秒):建筑结构单位的耐久双向对账、撤退条件、溅射以外的检查</t>
         </is>
       </c>
     </row>
@@ -7094,15 +7094,15 @@
       <c r="A417" t="inlineStr"/>
       <c r="B417" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>siege.breach_notify_seconds</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>“敌人正在拆某段墙”通知的冷却(游戏秒;同一座只报一次,换目标才再报)</t>
         </is>
       </c>
     </row>
@@ -7110,15 +7110,15 @@
       <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>siege.guard_radius_cells</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>0.02</v>
+        <v>18</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>驻防机器的守点交战半径(格):敌人进入驻防点这么近就去打,打完回驻防点</t>
         </is>
       </c>
     </row>
@@ -7126,15 +7126,15 @@
       <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>siege.intercept_radius_cells</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>拦截:己方机器离行进中的突袭部队这么近(格)时,部队就地展开成战斗单位</t>
         </is>
       </c>
     </row>
@@ -7142,15 +7142,15 @@
       <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>siege.regroup_seconds</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>拦截:附近没有己方机器满这么久(游戏秒)后,幸存者重新收拢成行进队伍继续走</t>
         </is>
       </c>
     </row>
@@ -7158,15 +7158,15 @@
       <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>siege.intercept_min_target_cells</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>拦截:离目标(家园核心 / 前哨站)不到这么远(格)的行进队伍不拦截,照常到达展开攻城(同一场仗用流场打)</t>
         </is>
       </c>
     </row>
@@ -7174,15 +7174,15 @@
       <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>siege.intercept_max_seconds</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>拦截:就地交战最多这么久(游戏秒),互相够不着的僵持到点后幸存者收拢继续走</t>
         </is>
       </c>
     </row>
@@ -7190,15 +7190,15 @@
       <c r="A423" t="inlineStr"/>
       <c r="B423" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>siege.overlay_refresh_seconds</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>200</v>
+        <v>0.5</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>突袭路径叠加层重画间隔(真实秒;纯表现)</t>
         </is>
       </c>
     </row>
@@ -7206,15 +7206,15 @@
       <c r="A424" t="inlineStr"/>
       <c r="B424" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>siege.perf.units</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>性能验收:同时攻城的突袭单位数(FG06 第 7 节 200)</t>
         </is>
       </c>
     </row>
@@ -7222,15 +7222,15 @@
       <c r="A425" t="inlineStr"/>
       <c r="B425" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>siege.perf.field_update_ms</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>性能验收:屏障变化时流场增量更新单次耗时上限(毫秒,FG06 第 7 节)</t>
         </is>
       </c>
     </row>
@@ -7238,15 +7238,15 @@
       <c r="A426" t="inlineStr"/>
       <c r="B426" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>siege.perf.step_ms</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>性能验收:200 单位攻城时内核单步平均耗时上限(毫秒;120 帧预算 8.33 ms 的四分之一)</t>
         </is>
       </c>
     </row>
@@ -7254,15 +7254,15 @@
       <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>logistics.pipe.hp_t1</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>管线 T1 一格的最大耐久(管线 / 泵 / 阀门 / 地下管线口按等级)</t>
         </is>
       </c>
     </row>
@@ -7270,15 +7270,15 @@
       <c r="A428" t="inlineStr"/>
       <c r="B428" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>logistics.pipe.hp_t2</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>管线 T2 一格的最大耐久</t>
         </is>
       </c>
     </row>
@@ -7286,15 +7286,15 @@
       <c r="A429" t="inlineStr"/>
       <c r="B429" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>logistics.pipe.hp_tank</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>储罐一格的最大耐久</t>
         </is>
       </c>
     </row>
@@ -7302,15 +7302,15 @@
       <c r="A430" t="inlineStr"/>
       <c r="B430" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>logistics.pipe.repair_kits</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>维修无人机修满一格管线要的维修件(与传送带同口径)</t>
         </is>
       </c>
     </row>
@@ -7318,15 +7318,15 @@
       <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -7334,15 +7334,15 @@
       <c r="A432" t="inlineStr"/>
       <c r="B432" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -7350,15 +7350,15 @@
       <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>1200</v>
+        <v>4</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       <c r="A434" t="inlineStr"/>
       <c r="B434" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -7382,15 +7382,15 @@
       <c r="A435" t="inlineStr"/>
       <c r="B435" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -7398,15 +7398,15 @@
       <c r="A436" t="inlineStr"/>
       <c r="B436" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -7414,15 +7414,15 @@
       <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -7430,15 +7430,15 @@
       <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -7446,15 +7446,15 @@
       <c r="A439" t="inlineStr"/>
       <c r="B439" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -7462,15 +7462,15 @@
       <c r="A440" t="inlineStr"/>
       <c r="B440" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -7478,15 +7478,15 @@
       <c r="A441" t="inlineStr"/>
       <c r="B441" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -7494,15 +7494,15 @@
       <c r="A442" t="inlineStr"/>
       <c r="B442" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -7510,15 +7510,15 @@
       <c r="A443" t="inlineStr"/>
       <c r="B443" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -7526,15 +7526,15 @@
       <c r="A444" t="inlineStr"/>
       <c r="B444" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -7542,15 +7542,15 @@
       <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -7558,15 +7558,15 @@
       <c r="A446" t="inlineStr"/>
       <c r="B446" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>100000</v>
+        <v>60</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -7574,15 +7574,15 @@
       <c r="A447" t="inlineStr"/>
       <c r="B447" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -7590,15 +7590,15 @@
       <c r="A448" t="inlineStr"/>
       <c r="B448" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -7606,15 +7606,15 @@
       <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -7622,15 +7622,15 @@
       <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -7638,15 +7638,15 @@
       <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>40</v>
+        <v>0.02</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -7654,15 +7654,15 @@
       <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -7670,15 +7670,15 @@
       <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -7686,15 +7686,15 @@
       <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -7702,15 +7702,15 @@
       <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>0.3</v>
+        <v>64</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -7718,15 +7718,15 @@
       <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -7734,15 +7734,15 @@
       <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -7750,15 +7750,15 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -7766,15 +7766,15 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -7782,15 +7782,15 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -7798,15 +7798,15 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -7814,15 +7814,15 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -7830,13 +7830,541 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
+          <t>eco.stats.tier0.bucket_seconds</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>2</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr"/>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>eco.stats.tier1.bucket_seconds</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>20</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr"/>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>eco.stats.tier2.bucket_seconds</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>120</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr"/>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>eco.stats.tier3.bucket_seconds</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr"/>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>eco.stats.deficit_minutes</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>10</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr"/>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>eco.stats.deficit_probe_seconds</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>120</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr"/>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>eco.stats.deficit_check_seconds</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>20</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr"/>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>eco.stats.panel_refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>1</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr"/>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>eco.stats.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>8</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>瓶颈页最多列几种物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr"/>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>eco.topbar.max_pins</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>8</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr"/>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>eco.topbar.refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr"/>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>eco.topbar.rate_window</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>1</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr"/>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>eco.topbar.max_subnets</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>3</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr"/>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>eco.topbar.target_tolerance</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr"/>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>eco.planner.max_depth</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>12</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr"/>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>eco.planner.default_rate</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>10</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr"/>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>eco.planner.max_rate</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr"/>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>away.reports_keep</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>3</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr"/>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>away.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>3</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr"/>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>away.items_max</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>12</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr"/>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>away.entries_max</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>60</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr"/>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>40</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr"/>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>20</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr"/>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>64</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr"/>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>60</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr"/>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr"/>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>1</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr"/>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>2</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr"/>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>100</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr"/>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>1</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr"/>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>5</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr"/>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>120</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr"/>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>10</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr"/>
+      <c r="B496" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C463" t="n">
+      <c r="C496" t="n">
         <v>20</v>
       </c>
-      <c r="D463" t="inlineStr">
+      <c r="D496" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D496"/>
+  <dimension ref="A1:D516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7318,15 +7318,15 @@
       <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>raid.auto_pause_first_raids</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>FGR-DEF-042:突袭到达时自动暂停的默认值只对本存档前几次突袭(波)开启;玩家在通知设置里改过的按玩家的</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       <c r="A432" t="inlineStr"/>
       <c r="B432" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>raid.spectate.default_speed</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>观战:点“观战”时切到的速度(2 或 3;复用统一时钟的倍速档)</t>
         </is>
       </c>
     </row>
@@ -7350,15 +7350,15 @@
       <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>raid.spectate.follow_seconds</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>观战:镜头每隔这么久(真实秒)重新看一次战斗重心</t>
         </is>
       </c>
     </row>
@@ -7366,15 +7366,15 @@
       <c r="A434" t="inlineStr"/>
       <c r="B434" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>raid.spectate.follow_min_cells</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>观战:战斗重心离镜头焦点超过这么远(格)才飞过去(免得镜头一直抖)</t>
         </is>
       </c>
     </row>
@@ -7382,15 +7382,15 @@
       <c r="A435" t="inlineStr"/>
       <c r="B435" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>raid.spectate.manual_cells</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>观战:玩家自己把镜头移开超过这么远(格)就暂停跟随(点“跟随战斗”恢复)</t>
         </is>
       </c>
     </row>
@@ -7398,15 +7398,15 @@
       <c r="A436" t="inlineStr"/>
       <c r="B436" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>raid.music.volume</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>预警 / 突袭音乐的音量(乘在音乐音量设置上;占位音乐,美术批次替换)</t>
         </is>
       </c>
     </row>
@@ -7414,15 +7414,15 @@
       <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>raid.hud.refresh_seconds</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>突袭 HUD 刷新间隔(真实秒;键没变不重建)</t>
         </is>
       </c>
     </row>
@@ -7430,15 +7430,15 @@
       <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>raid.hud.perf_ms</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>性能验收:突袭 HUD 一次数据刷新(各波剩余敌人 / 文字)的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -7446,15 +7446,15 @@
       <c r="A439" t="inlineStr"/>
       <c r="B439" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>defov.margin_cells</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>防御总览:热力图范围 = 家园己方建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -7462,15 +7462,15 @@
       <c r="A440" t="inlineStr"/>
       <c r="B440" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>defov.max_cells</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>50</v>
+        <v>256</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>防御总览:热力图最大边长(格;超出时以归还核心为中心截取)</t>
         </is>
       </c>
     </row>
@@ -7478,15 +7478,15 @@
       <c r="A441" t="inlineStr"/>
       <c r="B441" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>defov.weak_min_cells</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>防御总览:连续这么多格(沿路线 / 外围)没有火力覆盖才算一处薄弱点</t>
         </is>
       </c>
     </row>
@@ -7494,15 +7494,15 @@
       <c r="A442" t="inlineStr"/>
       <c r="B442" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>defov.weak_max</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>200</v>
+        <v>12</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>防御总览:最多列出几处薄弱点(按离核心由近到远)</t>
         </is>
       </c>
     </row>
@@ -7510,15 +7510,15 @@
       <c r="A443" t="inlineStr"/>
       <c r="B443" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>defov.ring_extra_cells</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>防御总览:没有预测路线时,外围检查圈 = 建筑外接矩形半对角线 + 这么多格</t>
         </is>
       </c>
     </row>
@@ -7526,15 +7526,15 @@
       <c r="A444" t="inlineStr"/>
       <c r="B444" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>defov.ring_samples</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>防御总览:外围检查圈的采样点数</t>
         </is>
       </c>
     </row>
@@ -7542,15 +7542,15 @@
       <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>defov.refresh_seconds</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>防御总览:面板开着时每隔这么久(真实秒)检查一次要不要重算覆盖(炮塔 / 建筑 / 突袭计划变了才重算)</t>
         </is>
       </c>
     </row>
@@ -7558,15 +7558,15 @@
       <c r="A446" t="inlineStr"/>
       <c r="B446" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>defov.perf_ms</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>性能验收:100 座炮塔时重算一次覆盖 + 薄弱点的耗时上限(毫秒;只在面板打开 / 防线变化时)</t>
         </is>
       </c>
     </row>
@@ -7574,15 +7574,15 @@
       <c r="A447" t="inlineStr"/>
       <c r="B447" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>roster.patrol_max_points</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>驻防巡逻(FGR-DEF-043):一台机器的巡逻路线最多几个巡逻点(不含驻防点)</t>
         </is>
       </c>
     </row>
@@ -7590,15 +7590,15 @@
       <c r="A448" t="inlineStr"/>
       <c r="B448" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>roster.patrol_arrive_cells</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>驻防巡逻:走到巡逻点这么近(格)就去下一个点</t>
         </is>
       </c>
     </row>
@@ -7606,15 +7606,15 @@
       <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>roster.patrol_arrive_slack</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>驻防巡逻:判定“站稳在这一点”时在 roster.patrol_arrive_cells 之外再放宽的格数(机器与别的单位互相推挤时也能换点)</t>
         </is>
       </c>
     </row>
@@ -7622,15 +7622,15 @@
       <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>roster.patrol_retry_seconds</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>驻防巡逻:到不了的巡逻点先跳过,过这么久(游戏秒)再试一次(墙拆了 / 路通了能自动恢复;通知只发一次,直到走到过它)</t>
         </is>
       </c>
     </row>
@@ -7638,15 +7638,15 @@
       <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>0.02</v>
+        <v>24</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -7670,15 +7670,15 @@
       <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -7686,15 +7686,15 @@
       <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -7702,15 +7702,15 @@
       <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -7718,15 +7718,15 @@
       <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -7734,15 +7734,15 @@
       <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>600</v>
+        <v>4</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -7750,15 +7750,15 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -7766,15 +7766,15 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -7782,15 +7782,15 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -7798,15 +7798,15 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -7814,15 +7814,15 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -7830,15 +7830,15 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -7846,15 +7846,15 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -7862,15 +7862,15 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -7878,15 +7878,15 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -7910,15 +7910,15 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -7926,15 +7926,15 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -7942,15 +7942,15 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -7958,15 +7958,15 @@
       <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>8</v>
+        <v>0.02</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -7974,15 +7974,15 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -7990,15 +7990,15 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -8022,15 +8022,15 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -8038,15 +8038,15 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>0.05</v>
+        <v>200</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8054,15 +8054,15 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>12</v>
+        <v>600</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8070,15 +8070,15 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -8086,15 +8086,15 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>100000</v>
+        <v>40</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8102,15 +8102,15 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8118,15 +8118,15 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8134,15 +8134,15 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -8150,15 +8150,15 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -8166,15 +8166,15 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -8182,15 +8182,15 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -8198,15 +8198,15 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>64</v>
+        <v>1200</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -8214,15 +8214,15 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -8230,15 +8230,15 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>0.3</v>
+        <v>120</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -8246,15 +8246,15 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -8262,15 +8262,15 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -8278,15 +8278,15 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -8294,15 +8294,15 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8310,15 +8310,15 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -8326,15 +8326,15 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -8342,15 +8342,15 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -8358,13 +8358,333 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
+          <t>eco.topbar.target_tolerance</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr"/>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>eco.planner.max_depth</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>12</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr"/>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>eco.planner.default_rate</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>10</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr"/>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>eco.planner.max_rate</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr"/>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>away.reports_keep</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>3</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr"/>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>away.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>3</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr"/>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>away.items_max</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>12</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr"/>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>away.entries_max</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>60</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr"/>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>40</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr"/>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>20</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr"/>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>64</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr"/>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>60</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr"/>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr"/>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>1</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr"/>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>2</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr"/>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>100</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr"/>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>1</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr"/>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>5</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr"/>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>120</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr"/>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>10</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr"/>
+      <c r="B516" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C496" t="n">
+      <c r="C516" t="n">
         <v>20</v>
       </c>
-      <c r="D496" t="inlineStr">
+      <c r="D516" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D516"/>
+  <dimension ref="A1:D523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7638,15 +7638,15 @@
       <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>raid.away.refresh_seconds</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>24</v>
+        <v>0.25</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>远征中家园遇袭:远征 HUD 弹窗 / 倒计时的刷新间隔(真实秒;文字没变不重写)</t>
         </is>
       </c>
     </row>
@@ -7654,15 +7654,15 @@
       <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>raid.away.home_refresh_seconds</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>远征中家园遇袭:家园状态小窗(核心耐久 / 关键建筑 / 剩余敌人)重新汇总的间隔(真实秒;只在小窗显示时汇总)</t>
         </is>
       </c>
     </row>
@@ -7670,15 +7670,15 @@
       <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>raid.away.perf_ms</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>性能验收:家园状态小窗汇总一次(全部建筑的类别与耐久 + 剩余敌人)的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -7686,15 +7686,15 @@
       <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>raid.away.decision_keep</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>远征中家园遇袭:存档里保留最近几波的选择(跳回家园 / 留在远征队;读档后同一波不再弹出)</t>
         </is>
       </c>
     </row>
@@ -7702,15 +7702,15 @@
       <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>raid.away.status_seconds</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>远征中家园遇袭:小窗里选择 / 被拒提示的显示时长(真实秒)</t>
         </is>
       </c>
     </row>
@@ -7718,15 +7718,15 @@
       <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>raid.away.core_low_ratio</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>远征中家园遇袭:归还核心耐久条变红的耐久比例</t>
         </is>
       </c>
     </row>
@@ -7734,15 +7734,15 @@
       <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>raid.away.intact_ratio</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>4</v>
+        <v>0.999</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>远征中家园遇袭:关键建筑算“完好”的耐久比例(浮点误差内的满耐久)</t>
         </is>
       </c>
     </row>
@@ -7750,15 +7750,15 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -7766,15 +7766,15 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -7782,15 +7782,15 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -7798,15 +7798,15 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -7814,15 +7814,15 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -7830,15 +7830,15 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -7846,15 +7846,15 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -7862,15 +7862,15 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -7878,15 +7878,15 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -7894,15 +7894,15 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -7926,15 +7926,15 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -7942,15 +7942,15 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -7958,15 +7958,15 @@
       <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>0.02</v>
+        <v>60</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -7974,15 +7974,15 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -7990,15 +7990,15 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -8006,15 +8006,15 @@
       <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -8022,15 +8022,15 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -8038,15 +8038,15 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -8054,15 +8054,15 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -8070,15 +8070,15 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>40</v>
+        <v>0.02</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -8086,15 +8086,15 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -8102,15 +8102,15 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8118,15 +8118,15 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -8134,15 +8134,15 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -8150,15 +8150,15 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8166,15 +8166,15 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8182,15 +8182,15 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -8198,15 +8198,15 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>1200</v>
+        <v>40</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8214,15 +8214,15 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8230,15 +8230,15 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8246,15 +8246,15 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -8262,15 +8262,15 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -8278,15 +8278,15 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -8294,15 +8294,15 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -8310,15 +8310,15 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>0.5</v>
+        <v>1200</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -8326,15 +8326,15 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -8342,15 +8342,15 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -8358,15 +8358,15 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>0.05</v>
+        <v>20</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -8374,15 +8374,15 @@
       <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -8390,15 +8390,15 @@
       <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -8406,15 +8406,15 @@
       <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>100000</v>
+        <v>8</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8422,15 +8422,15 @@
       <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -8438,15 +8438,15 @@
       <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -8454,15 +8454,15 @@
       <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -8470,15 +8470,15 @@
       <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>60</v>
+        <v>0.05</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -8486,15 +8486,15 @@
       <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -8502,15 +8502,15 @@
       <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -8518,15 +8518,15 @@
       <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>64</v>
+        <v>100000</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8534,15 +8534,15 @@
       <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -8550,15 +8550,15 @@
       <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -8566,15 +8566,15 @@
       <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -8582,15 +8582,15 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -8598,15 +8598,15 @@
       <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -8614,15 +8614,15 @@
       <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -8630,15 +8630,15 @@
       <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>away.machines_max</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -8646,15 +8646,15 @@
       <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>alarm.jam_seconds</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
         </is>
       </c>
     </row>
@@ -8662,15 +8662,15 @@
       <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>alarm.machine_wounded_fraction</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
         </is>
       </c>
     </row>
@@ -8678,13 +8678,125 @@
       <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>1</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr"/>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>2</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr"/>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>100</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr"/>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>1</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr"/>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>5</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr"/>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>120</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr"/>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>10</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr"/>
+      <c r="B523" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C516" t="n">
+      <c r="C523" t="n">
         <v>20</v>
       </c>
-      <c r="D516" t="inlineStr">
+      <c r="D523" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D523"/>
+  <dimension ref="A1:D540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7750,15 +7750,15 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>raid.result.wreck_per_unit</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>突袭结算:每击毁一台普通攻城敌人留下几份敌方残骸(FGR-DEF-051)</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>raid.result.wreck_per_elite</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>突袭结算:每击毁一台精英留下几份敌方残骸</t>
         </is>
       </c>
     </row>
@@ -7782,15 +7782,15 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>raid.result.wreck_merge_cells</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>突袭结算:离同一波已有残骸堆多少格以内的新残骸并进那一堆(少生成地面物与搬运单)</t>
         </is>
       </c>
     </row>
@@ -7798,15 +7798,15 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>raid.result.wreck_pile_max</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>突袭结算:一堆残骸至多几份(一台机器一趟搬完)</t>
         </is>
       </c>
     </row>
@@ -7814,15 +7814,15 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>raid.result.piles_max</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>突袭结算:一次突袭至多记住几堆残骸(超出的照样落地,只是不再合并)</t>
         </is>
       </c>
     </row>
@@ -7830,15 +7830,15 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>raid.result.drop_module_chance</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>突袭结算:每击毁一台敌人掉落未解析模块的概率(FGR-DEF-051“少数情况”;低于远征,远征掉落表在 FG8-LOOT-01)</t>
         </is>
       </c>
     </row>
@@ -7846,15 +7846,15 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>raid.result.drop_firmware_chance</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>4</v>
+        <v>0.015</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>突袭结算:每击毁一台敌人掉落敌方加密固件的概率(同上)</t>
         </is>
       </c>
     </row>
@@ -7862,15 +7862,15 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>raid.result.drop_elite_mult</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>突袭结算:精英的掉落概率倍率</t>
         </is>
       </c>
     </row>
@@ -7878,15 +7878,15 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>raid.result.timeline_max</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>突袭结算:过程时间线每次至多几条(超出的计数)</t>
         </is>
       </c>
     </row>
@@ -7894,15 +7894,15 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>raid.result.losses_max</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>突袭结算:损失明细每次至多几条(合计照常累加)</t>
         </is>
       </c>
     </row>
@@ -7910,15 +7910,15 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>raid.result.contrib_max</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>突袭结算:贡献记录每次至多几个击毁者(更多的并进“其它”)</t>
         </is>
       </c>
     </row>
@@ -7926,15 +7926,15 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>raid.result.contrib_top</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>突袭结算 / 离家报告:贡献排行显示前几名</t>
         </is>
       </c>
     </row>
@@ -7942,15 +7942,15 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>raid.result.route_seconds</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>残骸去向:每隔几游戏秒检查一次仓库里的残骸要不要送去解析台 / 回收站</t>
         </is>
       </c>
     </row>
@@ -7958,15 +7958,15 @@
       <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>raid.result.route_batch</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>残骸去向:一张送货单至多几份残骸</t>
         </is>
       </c>
     </row>
@@ -7974,15 +7974,15 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>raid.result.autosave_on_warning</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>突袭预警发出时自动存档(1=开;同一波只存一次;核心被摧毁后不再存)</t>
         </is>
       </c>
     </row>
@@ -7990,15 +7990,15 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>raid.result.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>突袭历史面板:进行中的突袭每隔几真实秒重读一次</t>
         </is>
       </c>
     </row>
@@ -8006,15 +8006,15 @@
       <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>raid.result.perf_ms</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>10</v>
+        <v>0.05</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>性能验收:热更层处理一次击毁事件(残骸 / 掉落 / 贡献 / 结算记账)的平均耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -8022,15 +8022,15 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -8054,15 +8054,15 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -8070,15 +8070,15 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>0.02</v>
+        <v>10</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -8086,15 +8086,15 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -8102,15 +8102,15 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -8118,15 +8118,15 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -8134,15 +8134,15 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -8150,15 +8150,15 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -8166,15 +8166,15 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -8182,15 +8182,15 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -8198,15 +8198,15 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -8214,15 +8214,15 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -8230,15 +8230,15 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -8246,15 +8246,15 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -8262,15 +8262,15 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -8278,15 +8278,15 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -8294,15 +8294,15 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -8310,15 +8310,15 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>1200</v>
+        <v>2</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -8326,15 +8326,15 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -8342,15 +8342,15 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>120</v>
+        <v>0.02</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -8358,15 +8358,15 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -8374,15 +8374,15 @@
       <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8390,15 +8390,15 @@
       <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -8406,15 +8406,15 @@
       <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -8422,15 +8422,15 @@
       <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>0.5</v>
+        <v>200</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8438,15 +8438,15 @@
       <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8454,15 +8454,15 @@
       <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -8470,15 +8470,15 @@
       <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>0.05</v>
+        <v>40</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8486,15 +8486,15 @@
       <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8502,15 +8502,15 @@
       <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8518,15 +8518,15 @@
       <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>100000</v>
+        <v>30</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -8534,15 +8534,15 @@
       <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -8550,15 +8550,15 @@
       <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -8566,15 +8566,15 @@
       <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -8582,15 +8582,15 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>60</v>
+        <v>1200</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -8598,15 +8598,15 @@
       <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -8614,15 +8614,15 @@
       <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -8630,15 +8630,15 @@
       <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -8646,15 +8646,15 @@
       <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -8662,15 +8662,15 @@
       <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -8678,15 +8678,15 @@
       <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8694,15 +8694,15 @@
       <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -8710,15 +8710,15 @@
       <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -8726,15 +8726,15 @@
       <c r="A519" t="inlineStr"/>
       <c r="B519" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -8742,15 +8742,15 @@
       <c r="A520" t="inlineStr"/>
       <c r="B520" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -8758,15 +8758,15 @@
       <c r="A521" t="inlineStr"/>
       <c r="B521" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       <c r="A522" t="inlineStr"/>
       <c r="B522" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -8790,13 +8790,285 @@
       <c r="A523" t="inlineStr"/>
       <c r="B523" t="inlineStr">
         <is>
+          <t>eco.planner.max_rate</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr"/>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>away.reports_keep</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>3</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr"/>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>away.bottleneck_top</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>3</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr"/>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>away.items_max</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>12</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr"/>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>away.entries_max</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>60</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr"/>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>40</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr"/>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>20</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr"/>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>64</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr"/>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>60</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr"/>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr"/>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>1</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr"/>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>2</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr"/>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>100</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr"/>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>1</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr"/>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>5</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr"/>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>120</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr"/>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>10</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr"/>
+      <c r="B540" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C523" t="n">
+      <c r="C540" t="n">
         <v>20</v>
       </c>
-      <c r="D523" t="inlineStr">
+      <c r="D540" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D540"/>
+  <dimension ref="A1:D544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8022,15 +8022,15 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>difficulty.custom_min</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>24</v>
+        <v>0.5</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>自定义难度:三个滑条(突袭频率 / 规模 / 预警时间倍率)的下限</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>difficulty.custom_max</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>自定义难度:三个滑条的上限</t>
         </is>
       </c>
     </row>
@@ -8054,15 +8054,15 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>difficulty.custom_step</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>自定义难度:滑条步长(存档里的值按它取整,同一设置同一字节)</t>
         </is>
       </c>
     </row>
@@ -8070,15 +8070,15 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>difficulty.history_max</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>难度修改记录最多保留几条(更早的只留计数;开局难度与“是否离开过开局难度”永久保留)</t>
         </is>
       </c>
     </row>
@@ -8086,15 +8086,15 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -8102,15 +8102,15 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -8150,15 +8150,15 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -8166,15 +8166,15 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -8182,15 +8182,15 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -8198,15 +8198,15 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -8214,15 +8214,15 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -8230,15 +8230,15 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -8262,15 +8262,15 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -8278,15 +8278,15 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -8294,15 +8294,15 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -8310,15 +8310,15 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -8326,15 +8326,15 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -8342,15 +8342,15 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>0.02</v>
+        <v>10</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -8358,15 +8358,15 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -8374,15 +8374,15 @@
       <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -8390,15 +8390,15 @@
       <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -8406,15 +8406,15 @@
       <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>64</v>
+        <v>0.02</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -8422,15 +8422,15 @@
       <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -8438,15 +8438,15 @@
       <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>600</v>
+        <v>16</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8454,15 +8454,15 @@
       <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -8470,15 +8470,15 @@
       <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -8486,15 +8486,15 @@
       <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8502,15 +8502,15 @@
       <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8518,15 +8518,15 @@
       <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -8534,15 +8534,15 @@
       <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8550,15 +8550,15 @@
       <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8566,15 +8566,15 @@
       <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8582,15 +8582,15 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>1200</v>
+        <v>30</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -8598,15 +8598,15 @@
       <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -8614,15 +8614,15 @@
       <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -8630,15 +8630,15 @@
       <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -8646,15 +8646,15 @@
       <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -8662,15 +8662,15 @@
       <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -8678,15 +8678,15 @@
       <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -8694,15 +8694,15 @@
       <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -8726,15 +8726,15 @@
       <c r="A519" t="inlineStr"/>
       <c r="B519" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -8742,15 +8742,15 @@
       <c r="A520" t="inlineStr"/>
       <c r="B520" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>0.05</v>
+        <v>8</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8758,15 +8758,15 @@
       <c r="A521" t="inlineStr"/>
       <c r="B521" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -8774,15 +8774,15 @@
       <c r="A522" t="inlineStr"/>
       <c r="B522" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -8790,15 +8790,15 @@
       <c r="A523" t="inlineStr"/>
       <c r="B523" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>100000</v>
+        <v>3</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -8806,15 +8806,15 @@
       <c r="A524" t="inlineStr"/>
       <c r="B524" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>3</v>
+        <v>0.05</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -8822,15 +8822,15 @@
       <c r="A525" t="inlineStr"/>
       <c r="B525" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -8838,15 +8838,15 @@
       <c r="A526" t="inlineStr"/>
       <c r="B526" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -8854,15 +8854,15 @@
       <c r="A527" t="inlineStr"/>
       <c r="B527" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>60</v>
+        <v>100000</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8870,15 +8870,15 @@
       <c r="A528" t="inlineStr"/>
       <c r="B528" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -8886,15 +8886,15 @@
       <c r="A529" t="inlineStr"/>
       <c r="B529" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -8902,15 +8902,15 @@
       <c r="A530" t="inlineStr"/>
       <c r="B530" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
       <c r="A531" t="inlineStr"/>
       <c r="B531" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -8934,15 +8934,15 @@
       <c r="A532" t="inlineStr"/>
       <c r="B532" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>0.3</v>
+        <v>40</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -8950,15 +8950,15 @@
       <c r="A533" t="inlineStr"/>
       <c r="B533" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -8966,15 +8966,15 @@
       <c r="A534" t="inlineStr"/>
       <c r="B534" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>away.machines_max</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -8982,15 +8982,15 @@
       <c r="A535" t="inlineStr"/>
       <c r="B535" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>alarm.jam_seconds</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
         </is>
       </c>
     </row>
@@ -8998,15 +8998,15 @@
       <c r="A536" t="inlineStr"/>
       <c r="B536" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>alarm.machine_wounded_fraction</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
         </is>
       </c>
     </row>
@@ -9014,15 +9014,15 @@
       <c r="A537" t="inlineStr"/>
       <c r="B537" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.softlock.check_seconds</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
         </is>
       </c>
     </row>
@@ -9030,15 +9030,15 @@
       <c r="A538" t="inlineStr"/>
       <c r="B538" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.softlock.print_min_machines</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
         </is>
       </c>
     </row>
@@ -9046,15 +9046,15 @@
       <c r="A539" t="inlineStr"/>
       <c r="B539" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.softlock.print_health</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
         </is>
       </c>
     </row>
@@ -9062,13 +9062,77 @@
       <c r="A540" t="inlineStr"/>
       <c r="B540" t="inlineStr">
         <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>1</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr"/>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>5</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr"/>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>120</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr"/>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>10</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr"/>
+      <c r="B544" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C540" t="n">
+      <c r="C544" t="n">
         <v>20</v>
       </c>
-      <c r="D540" t="inlineStr">
+      <c r="D544" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D544"/>
+  <dimension ref="A1:D557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7750,15 +7750,15 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>raid.result.wreck_per_unit</t>
+          <t>logistics.leak.breach_hp_ratio</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台普通攻城敌人留下几份敌方残骸(FGR-DEF-051)</t>
+          <t>击穿:管线件耐久掉到最大耐久 × 本值及以下(或被摧毁)就开始泄漏;维修回到本值以上算修好</t>
         </is>
       </c>
     </row>
@@ -7766,15 +7766,15 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>raid.result.wreck_per_elite</t>
+          <t>logistics.leak.base_radius</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台精英留下几份敌方残骸</t>
+          <t>液洼刚出现时的半径(米,× fg.TbFluidLeak.radiusScale)</t>
         </is>
       </c>
     </row>
@@ -7782,15 +7782,15 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>raid.result.wreck_merge_cells</t>
+          <t>logistics.leak.max_radius</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>突袭结算:离同一波已有残骸堆多少格以内的新残骸并进那一堆(少生成地面物与搬运单)</t>
+          <t>液洼一直漏下去最大能扩到的半径(米,× radiusScale)</t>
         </is>
       </c>
     </row>
@@ -7798,15 +7798,15 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>raid.result.wreck_pile_max</t>
+          <t>logistics.leak.grow_seconds</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>突袭结算:一堆残骸至多几份(一台机器一趟搬完)</t>
+          <t>液洼从刚出现扩到最大半径要的游戏秒(一直在漏时)</t>
         </is>
       </c>
     </row>
@@ -7814,15 +7814,15 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>raid.result.piles_max</t>
+          <t>logistics.leak.fade_seconds</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>突袭结算:一次突袭至多记住几堆残骸(超出的照样落地,只是不再合并)</t>
+          <t>修好管线(或冲洗 / 拆掉 / 破口两侧没有同种流体)后,液洼从当前半径缩小到消失要的游戏秒</t>
         </is>
       </c>
     </row>
@@ -7830,15 +7830,15 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>raid.result.drop_module_chance</t>
+          <t>logistics.leak.react_seconds</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>0.03</v>
+        <v>12</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台敌人掉落未解析模块的概率(FGR-DEF-051“少数情况”;低于远征,远征掉落表在 FG8-LOOT-01)</t>
+          <t>液洼整片反应成残留区域(燃油遇火 = 燃烧区)后至少持续的游戏秒(与反应自己的残留时长取大)</t>
         </is>
       </c>
     </row>
@@ -7846,15 +7846,15 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>raid.result.drop_firmware_chance</t>
+          <t>logistics.leak.fire_dps</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>0.015</v>
+        <v>6</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台敌人掉落敌方加密固件的概率(同上)</t>
+          <t>反应成的残留区域带持续伤害(燃烧)时,每游戏秒烧掉范围里管线 / 传送带 / 建筑的耐久(连锁烧毁产线)</t>
         </is>
       </c>
     </row>
@@ -7862,15 +7862,15 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>raid.result.drop_elite_mult</t>
+          <t>logistics.leak.fire_tick_seconds</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>突袭结算:精英的掉落概率倍率</t>
+          <t>火烧设施的结算间隔(游戏秒;每摊燃烧区按编号错开,每次扣 fire_dps × 本值;摊得开、每次对账只处理一部分燃烧区)</t>
         </is>
       </c>
     </row>
@@ -7878,15 +7878,15 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>raid.result.timeline_max</t>
+          <t>logistics.leak.sync_seconds</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>24</v>
+        <v>0.5</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>突袭结算:过程时间线每次至多几条(超出的计数)</t>
+          <t>液洼对账间隔(游戏秒):击穿是否还在、半径扩散 / 消退、火烧坏范围里的设施;只看步序号,与观察无关</t>
         </is>
       </c>
     </row>
@@ -7894,15 +7894,15 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>raid.result.losses_max</t>
+          <t>logistics.leak.max_puddles</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>突袭结算:损失明细每次至多几条(合计照常累加)</t>
+          <t>家园同时存在的液洼上限(超出的破口不再新增液洼并计数;一格管线最多一摊)</t>
         </is>
       </c>
     </row>
@@ -7910,15 +7910,15 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>raid.result.contrib_max</t>
+          <t>logistics.leak.warn_margin_cells</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>突袭结算:贡献记录每次至多几个击毁者(更多的并进“其它”)</t>
+          <t>泄漏起火告警:燃烧区半径外再放宽这么多格内有己方管线 / 传送带 / 建筑就发告警</t>
         </is>
       </c>
     </row>
@@ -7926,15 +7926,15 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
-          <t>raid.result.contrib_top</t>
+          <t>logistics.leak.perf.puddles</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>突袭结算 / 离家报告:贡献排行显示前几名</t>
+          <t>性能验收:同时存在的液洼数(= 上限)</t>
         </is>
       </c>
     </row>
@@ -7942,15 +7942,15 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>raid.result.route_seconds</t>
+          <t>logistics.leak.perf.sync_ms</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>残骸去向:每隔几游戏秒检查一次仓库里的残骸要不要送去解析台 / 回收站</t>
+          <t>性能验收:48 摊液洼(含一半在燃烧)时热更层一次对账的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -7958,15 +7958,15 @@
       <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
-          <t>raid.result.route_batch</t>
+          <t>raid.result.wreck_per_unit</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>残骸去向:一张送货单至多几份残骸</t>
+          <t>突袭结算:每击毁一台普通攻城敌人留下几份敌方残骸(FGR-DEF-051)</t>
         </is>
       </c>
     </row>
@@ -7974,15 +7974,15 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>raid.result.autosave_on_warning</t>
+          <t>raid.result.wreck_per_elite</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>突袭预警发出时自动存档(1=开;同一波只存一次;核心被摧毁后不再存)</t>
+          <t>突袭结算:每击毁一台精英留下几份敌方残骸</t>
         </is>
       </c>
     </row>
@@ -7990,15 +7990,15 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>raid.result.panel_refresh_seconds</t>
+          <t>raid.result.wreck_merge_cells</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>突袭历史面板:进行中的突袭每隔几真实秒重读一次</t>
+          <t>突袭结算:离同一波已有残骸堆多少格以内的新残骸并进那一堆(少生成地面物与搬运单)</t>
         </is>
       </c>
     </row>
@@ -8006,15 +8006,15 @@
       <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
-          <t>raid.result.perf_ms</t>
+          <t>raid.result.wreck_pile_max</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>0.05</v>
+        <v>5</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>性能验收:热更层处理一次击毁事件(残骸 / 掉落 / 贡献 / 结算记账)的平均耗时上限(毫秒)</t>
+          <t>突袭结算:一堆残骸至多几份(一台机器一趟搬完)</t>
         </is>
       </c>
     </row>
@@ -8022,15 +8022,15 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>difficulty.custom_min</t>
+          <t>raid.result.piles_max</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>0.5</v>
+        <v>48</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>自定义难度:三个滑条(突袭频率 / 规模 / 预警时间倍率)的下限</t>
+          <t>突袭结算:一次突袭至多记住几堆残骸(超出的照样落地,只是不再合并)</t>
         </is>
       </c>
     </row>
@@ -8038,15 +8038,15 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>difficulty.custom_max</t>
+          <t>raid.result.drop_module_chance</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>自定义难度:三个滑条的上限</t>
+          <t>突袭结算:每击毁一台敌人掉落未解析模块的概率(FGR-DEF-051“少数情况”;低于远征,远征掉落表在 FG8-LOOT-01)</t>
         </is>
       </c>
     </row>
@@ -8054,15 +8054,15 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>difficulty.custom_step</t>
+          <t>raid.result.drop_firmware_chance</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>0.1</v>
+        <v>0.015</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>自定义难度:滑条步长(存档里的值按它取整,同一设置同一字节)</t>
+          <t>突袭结算:每击毁一台敌人掉落敌方加密固件的概率(同上)</t>
         </is>
       </c>
     </row>
@@ -8070,15 +8070,15 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>difficulty.history_max</t>
+          <t>raid.result.drop_elite_mult</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>难度修改记录最多保留几条(更早的只留计数;开局难度与“是否离开过开局难度”永久保留)</t>
+          <t>突袭结算:精英的掉落概率倍率</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>raid.result.timeline_max</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>突袭结算:过程时间线每次至多几条(超出的计数)</t>
         </is>
       </c>
     </row>
@@ -8102,15 +8102,15 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>raid.result.losses_max</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>突袭结算:损失明细每次至多几条(合计照常累加)</t>
         </is>
       </c>
     </row>
@@ -8118,15 +8118,15 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>raid.result.contrib_max</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>突袭结算:贡献记录每次至多几个击毁者(更多的并进“其它”)</t>
         </is>
       </c>
     </row>
@@ -8134,15 +8134,15 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>raid.result.contrib_top</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>突袭结算 / 离家报告:贡献排行显示前几名</t>
         </is>
       </c>
     </row>
@@ -8150,15 +8150,15 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>raid.result.route_seconds</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>残骸去向:每隔几游戏秒检查一次仓库里的残骸要不要送去解析台 / 回收站</t>
         </is>
       </c>
     </row>
@@ -8166,15 +8166,15 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>raid.result.route_batch</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>残骸去向:一张送货单至多几份残骸</t>
         </is>
       </c>
     </row>
@@ -8182,15 +8182,15 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>raid.result.autosave_on_warning</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>突袭预警发出时自动存档(1=开;同一波只存一次;核心被摧毁后不再存)</t>
         </is>
       </c>
     </row>
@@ -8198,15 +8198,15 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>raid.result.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>突袭历史面板:进行中的突袭每隔几真实秒重读一次</t>
         </is>
       </c>
     </row>
@@ -8214,15 +8214,15 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>raid.result.perf_ms</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>25</v>
+        <v>0.05</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>性能验收:热更层处理一次击毁事件(残骸 / 掉落 / 贡献 / 结算记账)的平均耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -8230,15 +8230,15 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>difficulty.custom_min</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>自定义难度:三个滑条(突袭频率 / 规模 / 预警时间倍率)的下限</t>
         </is>
       </c>
     </row>
@@ -8246,15 +8246,15 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>difficulty.custom_max</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>自定义难度:三个滑条的上限</t>
         </is>
       </c>
     </row>
@@ -8262,15 +8262,15 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>difficulty.custom_step</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>200</v>
+        <v>0.1</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>自定义难度:滑条步长(存档里的值按它取整,同一设置同一字节)</t>
         </is>
       </c>
     </row>
@@ -8278,15 +8278,15 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>difficulty.history_max</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>难度修改记录最多保留几条(更早的只留计数;开局难度与“是否离开过开局难度”永久保留)</t>
         </is>
       </c>
     </row>
@@ -8294,15 +8294,15 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -8310,15 +8310,15 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -8326,15 +8326,15 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -8358,15 +8358,15 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -8374,15 +8374,15 @@
       <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -8390,15 +8390,15 @@
       <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -8406,15 +8406,15 @@
       <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>0.02</v>
+        <v>10</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -8422,15 +8422,15 @@
       <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -8438,15 +8438,15 @@
       <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -8454,15 +8454,15 @@
       <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -8470,15 +8470,15 @@
       <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -8486,15 +8486,15 @@
       <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -8502,15 +8502,15 @@
       <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -8518,15 +8518,15 @@
       <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -8534,15 +8534,15 @@
       <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -8550,15 +8550,15 @@
       <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -8566,15 +8566,15 @@
       <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -8582,15 +8582,15 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -8614,15 +8614,15 @@
       <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>20</v>
+        <v>0.02</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -8630,15 +8630,15 @@
       <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -8646,15 +8646,15 @@
       <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>1200</v>
+        <v>16</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8662,15 +8662,15 @@
       <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -8678,15 +8678,15 @@
       <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -8694,15 +8694,15 @@
       <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8710,15 +8710,15 @@
       <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8726,15 +8726,15 @@
       <c r="A519" t="inlineStr"/>
       <c r="B519" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -8742,15 +8742,15 @@
       <c r="A520" t="inlineStr"/>
       <c r="B520" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8758,15 +8758,15 @@
       <c r="A521" t="inlineStr"/>
       <c r="B521" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8774,15 +8774,15 @@
       <c r="A522" t="inlineStr"/>
       <c r="B522" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8790,15 +8790,15 @@
       <c r="A523" t="inlineStr"/>
       <c r="B523" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -8806,15 +8806,15 @@
       <c r="A524" t="inlineStr"/>
       <c r="B524" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -8822,15 +8822,15 @@
       <c r="A525" t="inlineStr"/>
       <c r="B525" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -8838,15 +8838,15 @@
       <c r="A526" t="inlineStr"/>
       <c r="B526" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -8854,15 +8854,15 @@
       <c r="A527" t="inlineStr"/>
       <c r="B527" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>100000</v>
+        <v>1200</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -8870,15 +8870,15 @@
       <c r="A528" t="inlineStr"/>
       <c r="B528" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -8886,15 +8886,15 @@
       <c r="A529" t="inlineStr"/>
       <c r="B529" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -8902,15 +8902,15 @@
       <c r="A530" t="inlineStr"/>
       <c r="B530" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -8918,15 +8918,15 @@
       <c r="A531" t="inlineStr"/>
       <c r="B531" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -8934,15 +8934,15 @@
       <c r="A532" t="inlineStr"/>
       <c r="B532" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -8950,15 +8950,15 @@
       <c r="A533" t="inlineStr"/>
       <c r="B533" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8966,15 +8966,15 @@
       <c r="A534" t="inlineStr"/>
       <c r="B534" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>64</v>
+        <v>0.5</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -8982,15 +8982,15 @@
       <c r="A535" t="inlineStr"/>
       <c r="B535" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -8998,15 +8998,15 @@
       <c r="A536" t="inlineStr"/>
       <c r="B536" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -9014,15 +9014,15 @@
       <c r="A537" t="inlineStr"/>
       <c r="B537" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -9030,15 +9030,15 @@
       <c r="A538" t="inlineStr"/>
       <c r="B538" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -9046,15 +9046,15 @@
       <c r="A539" t="inlineStr"/>
       <c r="B539" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -9062,15 +9062,15 @@
       <c r="A540" t="inlineStr"/>
       <c r="B540" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -9078,15 +9078,15 @@
       <c r="A541" t="inlineStr"/>
       <c r="B541" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -9094,15 +9094,15 @@
       <c r="A542" t="inlineStr"/>
       <c r="B542" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -9110,15 +9110,15 @@
       <c r="A543" t="inlineStr"/>
       <c r="B543" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -9126,13 +9126,221 @@
       <c r="A544" t="inlineStr"/>
       <c r="B544" t="inlineStr">
         <is>
+          <t>away.entries_max</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>60</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr"/>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>away.rules_max</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>40</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr"/>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>away.outages_max</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>20</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr"/>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>away.machines_max</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>64</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr"/>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>alarm.jam_seconds</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>60</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr"/>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>alarm.machine_wounded_fraction</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr"/>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>eco.softlock.check_seconds</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>1</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr"/>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_min_machines</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>2</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr"/>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>eco.softlock.print_health</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>100</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr"/>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>eco.softlock.core_scrap_per_minute</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>1</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr"/>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_check_seconds</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>5</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr"/>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>eco.softlock.loop_stall_seconds</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>120</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr"/>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>eco.softlock.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>10</v>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr"/>
+      <c r="B557" t="inlineStr">
+        <is>
           <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
-      <c r="C544" t="n">
+      <c r="C557" t="n">
         <v>20</v>
       </c>
-      <c r="D544" t="inlineStr">
+      <c r="D557" t="inlineStr">
         <is>
           <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D557"/>
+  <dimension ref="A1:D565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9346,6 +9346,134 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" t="inlineStr"/>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>env.daynight.night_start_hour</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>入夜时刻(游戏小时,0~24);初值20:24,夜晚以午夜为中心</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr"/>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>env.daynight.night_hours</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>夜晚持续多少游戏小时;7.2=1x下6分钟(FG07 第10节:白天14分钟,夜晚6分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr"/>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>env.daynight.twilight_hours</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>1</v>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>黄昏/黎明过渡多少游戏小时(入夜前光照从1降到0、天亮后从0升到1;夜晚本身光照恒为0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr"/>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>env.calendar.days</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>5</v>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>日历面板显示今天起几个游戏日(1~14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr"/>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>env.light.night_tint_r</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>夜里主方向光的颜色(乘在场景原光色上)红分量</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr"/>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>env.light.night_tint_g</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>夜里主方向光颜色绿分量</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr"/>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>env.light.night_tint_b</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>1</v>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>夜里主方向光颜色蓝分量</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr"/>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>env.light.apply_epsilon</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>画面亮度变化小于这个数时不写光照(每帧O(1),避免黄昏时每帧改灯)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D565"/>
+  <dimension ref="A1:D575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9474,6 +9474,166 @@
         </is>
       </c>
     </row>
+    <row r="566">
+      <c r="A566" t="inlineStr"/>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>env.silent.start_offset_hours</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>静默夜从入夜后第几个游戏小时开始(1.6 = 22:00;开始 + 持续必须落在夜里)</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr"/>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>env.silent.duration_hours</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>4</v>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>静默夜持续多少游戏小时(FG07 第10节:4 小时 = 1x 下约 3.3 分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr"/>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>env.silent.warning_hours</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>开始前多少游戏小时预警(FG07 第10节:1.2 小时 = 1x 下约 60 秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr"/>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>env.silent.dim_ramp_hours</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>静默夜画面压暗的淡入 / 淡出游戏小时(纯表现)</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr"/>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>env.silent.expedition_estimate_hours</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>12</v>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>远征准备时按多少游戏小时估计远征时长(跨过静默夜就提示;12 小时 = 1x 下 10 分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr"/>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>env.silent.debris_min</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>2</v>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>静默夜结束后家园出现几处风暴残骸(最少)</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr"/>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>env.silent.debris_max</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>4</v>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>风暴残骸最多几处</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr"/>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>env.silent.debris_rare_chance</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>每次静默夜额外出现一处稀有残骸的概率(0~1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr"/>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>env.silent.debris_ring_min</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>10</v>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>风暴残骸离归还核心至少几格</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr"/>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>env.silent.debris_ring_max</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>36</v>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>风暴残骸离归还核心至多几格(按种子地形找空地,找不到就少放)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D575"/>
+  <dimension ref="A1:D591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9634,6 +9634,262 @@
         </is>
       </c>
     </row>
+    <row r="576">
+      <c r="A576" t="inlineStr"/>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>env.weather.duration_min_days</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>一段恶劣天气最短持续几个游戏日(FG07 第10节:0.5~1.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr"/>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>env.weather.duration_max_days</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>一段恶劣天气最长持续几个游戏日</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr"/>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>env.weather.first_day</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>3</v>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>第一段恶劣天气最早在第几个游戏日开始(开局先让玩家站稳;FG16 节奏表另见 FG-GAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr"/>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>env.weather.warning_days</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>没有天气预报情报时,恶劣天气开始前多少游戏日预警(FGR-ENV-021:0.5 日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr"/>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>env.weather.forecast_days</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>3</v>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>有监听站 T2 的有效天气预报情报时,看得到未来几个游戏日的天气(FGR-ENV-021:3 日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr"/>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>env.weather.schedule_days</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>4</v>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>天气提前排定几个游戏日(必须 &gt; 预报天数,预报看得到的都已排定、写进存档)</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr"/>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>env.weather.acid_pct_per_hour</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>1</v>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>酸雨:露天建筑 / 传送带 / 炮塔每游戏小时损失最大耐久的百分之几(FG07 第10节:1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr"/>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>env.weather.damage_notify_hours</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>1</v>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>酸雨损伤的汇总通知最多每几个游戏小时一条(同一段酸雨内;摧毁另有通知)</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr"/>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>env.weather.sand_detect_factor</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>沙暴:露天炮塔探测(开火)距离乘这个数(FG07 第10节:-20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr"/>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>env.weather.cold_dissipation_mult</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>寒潮:家园里武器散热乘这个数(FG07 第10节:散热 +30%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr"/>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>env.weather.sand_fog_density</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>沙暴画面:指数雾浓度(纯表现;乘玩家的天气视觉效果强度)</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr"/>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>env.weather.fx_ramp_hours</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>天气画面淡入 / 淡出的游戏小时(纯表现)</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr"/>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>env.weather.particles_max</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>600</v>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>雨 / 沙 / 雪粒子最多同时几颗(满强度;ART-PERF-BUDGET 占位,乘视觉效果强度)</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr"/>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>env.roof.block_cells</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>4</v>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>顶棚一块的边长(格;FGR-ENV-030:4×4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr"/>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>env.roof.max_blocks_per_drag</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>64</v>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>一次拖拽最多铺几块顶棚(超出给原因,不静默截断)</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr"/>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>env.roof.build_seconds_per_block</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>3</v>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>机器施工一块顶棚要几游戏秒</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D591"/>
+  <dimension ref="A1:D598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9890,6 +9890,118 @@
         </is>
       </c>
     </row>
+    <row r="592">
+      <c r="A592" t="inlineStr"/>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>purify.hours_per_level</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>2</v>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>净化速度:每格每 N 个游戏小时降 1 级(FG07 第 10 节初值 N = 2;按持续有电有冷却液的游戏时间累计,暂停 / 倍速同比例)</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr"/>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>purify.coolant_mult_t2</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>净化塔 T2 的冷却液用量 = T1(fg.TbProducer.fluidLpm)× 本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr"/>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>purify.coolant_mult_t3</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>2</v>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>净化塔 T3 的冷却液用量 = T1 × 本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr"/>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>purify.rich_ore.radius</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>12</v>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>归还 20,000 格的奖励“稀土富矿”:揭示(探索)的圆半径,也是富矿的范围(格;范围内压在稀土矿脉上的提取钻产出加倍)</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr"/>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>purify.rich_ore.yield_mult</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>2</v>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>稀土富矿范围内的提取钻每份产出 × 本值(整数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr"/>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>purify.rich_ore.search_radius</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>400</v>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>找稀土富矿的最远距离(格,从归还核心算;先按世界规划层的稀土矿带找,找不到再按种子粗采样)</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr"/>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>purify.rich_ore.search_step</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>6</v>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>粗采样的步长(格;只在规划层没有稀土矿带时用)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D598"/>
+  <dimension ref="A1:D602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10002,6 +10002,70 @@
         </is>
       </c>
     </row>
+    <row r="599">
+      <c r="A599" t="inlineStr"/>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>explore.trail_gap_max</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>64</v>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>机器两次被检查之间走过的距离超过这么多格就当作“瞬移”(出厂 / 读档 / 跳转),不沿路补探索(格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr"/>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>explore.trail_step</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>6</v>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>沿机器走过的路补探索的采样间距(格;不大于机器探索半径的一半,保证路上不留缝)</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr"/>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>relic.pick_radius</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>右键 / 悬停离遗迹点多近算点中它(格,欧氏距离)</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr"/>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>relic.notify_max</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>6</v>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>一次揭开的一大片里最多逐个发几条“发现遗迹点”通知(其余合成一条“又发现 N 个”)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D602"/>
+  <dimension ref="A1:D606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10066,6 +10066,70 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="inlineStr"/>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>exp.check.severe_health_pct</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>机器生命低于最大值的这个比例=重伤提醒(可以派,后果写明;0~1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr"/>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>exp.check.warn_health_pct</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>机器生命低于最大值的这个比例=伤势偏重提醒(0~1,应不低于重伤线)</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr"/>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>exp.team.color_count</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>8</v>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>远征队可选颜色种数(颜色表见界面,1~8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr"/>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>squad.group_double_tap_seconds</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>连按两次同一编组键的最长间隔(真实秒;镜头飞到编组,FG13 第5节)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D606"/>
+  <dimension ref="A1:D621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7734,15 +7734,15 @@
       <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
-          <t>raid.away.intact_ratio</t>
+          <t>raid.away.march_focus_cells</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>0.999</v>
+        <v>150</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:关键建筑算“完好”的耐久比例(浮点误差内的满耐久)</t>
+          <t>FG8-EXP-02:远征队在星球上行军(还没进地点)时,镜头焦点离归还核心超过这么远(格)也算玩家在远征(远征决策条照常弹出;初值=归还核心覆盖半径)</t>
         </is>
       </c>
     </row>
@@ -7750,15 +7750,15 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>logistics.leak.breach_hp_ratio</t>
+          <t>raid.away.intact_ratio</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>0.5</v>
+        <v>0.999</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>击穿:管线件耐久掉到最大耐久 × 本值及以下(或被摧毁)就开始泄漏;维修回到本值以上算修好</t>
+          <t>远征中家园遇袭:关键建筑算“完好”的耐久比例(浮点误差内的满耐久)</t>
         </is>
       </c>
     </row>
@@ -7766,15 +7766,15 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>logistics.leak.base_radius</t>
+          <t>logistics.leak.breach_hp_ratio</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>液洼刚出现时的半径(米,× fg.TbFluidLeak.radiusScale)</t>
+          <t>击穿:管线件耐久掉到最大耐久 × 本值及以下(或被摧毁)就开始泄漏;维修回到本值以上算修好</t>
         </is>
       </c>
     </row>
@@ -7782,15 +7782,15 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>logistics.leak.max_radius</t>
+          <t>logistics.leak.base_radius</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>液洼一直漏下去最大能扩到的半径(米,× radiusScale)</t>
+          <t>液洼刚出现时的半径(米,× fg.TbFluidLeak.radiusScale)</t>
         </is>
       </c>
     </row>
@@ -7798,15 +7798,15 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>logistics.leak.grow_seconds</t>
+          <t>logistics.leak.max_radius</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>20</v>
+        <v>2.6</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>液洼从刚出现扩到最大半径要的游戏秒(一直在漏时)</t>
+          <t>液洼一直漏下去最大能扩到的半径(米,× radiusScale)</t>
         </is>
       </c>
     </row>
@@ -7814,15 +7814,15 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>logistics.leak.fade_seconds</t>
+          <t>logistics.leak.grow_seconds</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>修好管线(或冲洗 / 拆掉 / 破口两侧没有同种流体)后,液洼从当前半径缩小到消失要的游戏秒</t>
+          <t>液洼从刚出现扩到最大半径要的游戏秒(一直在漏时)</t>
         </is>
       </c>
     </row>
@@ -7830,15 +7830,15 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>logistics.leak.react_seconds</t>
+          <t>logistics.leak.fade_seconds</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>液洼整片反应成残留区域(燃油遇火 = 燃烧区)后至少持续的游戏秒(与反应自己的残留时长取大)</t>
+          <t>修好管线(或冲洗 / 拆掉 / 破口两侧没有同种流体)后,液洼从当前半径缩小到消失要的游戏秒</t>
         </is>
       </c>
     </row>
@@ -7846,15 +7846,15 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>logistics.leak.fire_dps</t>
+          <t>logistics.leak.react_seconds</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>反应成的残留区域带持续伤害(燃烧)时,每游戏秒烧掉范围里管线 / 传送带 / 建筑的耐久(连锁烧毁产线)</t>
+          <t>液洼整片反应成残留区域(燃油遇火 = 燃烧区)后至少持续的游戏秒(与反应自己的残留时长取大)</t>
         </is>
       </c>
     </row>
@@ -7862,15 +7862,15 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>logistics.leak.fire_tick_seconds</t>
+          <t>logistics.leak.fire_dps</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>火烧设施的结算间隔(游戏秒;每摊燃烧区按编号错开,每次扣 fire_dps × 本值;摊得开、每次对账只处理一部分燃烧区)</t>
+          <t>反应成的残留区域带持续伤害(燃烧)时,每游戏秒烧掉范围里管线 / 传送带 / 建筑的耐久(连锁烧毁产线)</t>
         </is>
       </c>
     </row>
@@ -7878,15 +7878,15 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>logistics.leak.sync_seconds</t>
+          <t>logistics.leak.fire_tick_seconds</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>液洼对账间隔(游戏秒):击穿是否还在、半径扩散 / 消退、火烧坏范围里的设施;只看步序号,与观察无关</t>
+          <t>火烧设施的结算间隔(游戏秒;每摊燃烧区按编号错开,每次扣 fire_dps × 本值;摊得开、每次对账只处理一部分燃烧区)</t>
         </is>
       </c>
     </row>
@@ -7894,15 +7894,15 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>logistics.leak.max_puddles</t>
+          <t>logistics.leak.sync_seconds</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>48</v>
+        <v>0.5</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>家园同时存在的液洼上限(超出的破口不再新增液洼并计数;一格管线最多一摊)</t>
+          <t>液洼对账间隔(游戏秒):击穿是否还在、半径扩散 / 消退、火烧坏范围里的设施;只看步序号,与观察无关</t>
         </is>
       </c>
     </row>
@@ -7910,15 +7910,15 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>logistics.leak.warn_margin_cells</t>
+          <t>logistics.leak.max_puddles</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>泄漏起火告警:燃烧区半径外再放宽这么多格内有己方管线 / 传送带 / 建筑就发告警</t>
+          <t>家园同时存在的液洼上限(超出的破口不再新增液洼并计数;一格管线最多一摊)</t>
         </is>
       </c>
     </row>
@@ -7926,15 +7926,15 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
-          <t>logistics.leak.perf.puddles</t>
+          <t>logistics.leak.warn_margin_cells</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>性能验收:同时存在的液洼数(= 上限)</t>
+          <t>泄漏起火告警:燃烧区半径外再放宽这么多格内有己方管线 / 传送带 / 建筑就发告警</t>
         </is>
       </c>
     </row>
@@ -7942,15 +7942,15 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>logistics.leak.perf.sync_ms</t>
+          <t>logistics.leak.perf.puddles</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>0.5</v>
+        <v>48</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>性能验收:48 摊液洼(含一半在燃烧)时热更层一次对账的耗时上限(毫秒)</t>
+          <t>性能验收:同时存在的液洼数(= 上限)</t>
         </is>
       </c>
     </row>
@@ -7958,15 +7958,15 @@
       <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
-          <t>raid.result.wreck_per_unit</t>
+          <t>logistics.leak.perf.sync_ms</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台普通攻城敌人留下几份敌方残骸(FGR-DEF-051)</t>
+          <t>性能验收:48 摊液洼(含一半在燃烧)时热更层一次对账的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -7974,15 +7974,15 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>raid.result.wreck_per_elite</t>
+          <t>raid.result.wreck_per_unit</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台精英留下几份敌方残骸</t>
+          <t>突袭结算:每击毁一台普通攻城敌人留下几份敌方残骸(FGR-DEF-051)</t>
         </is>
       </c>
     </row>
@@ -7990,15 +7990,15 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>raid.result.wreck_merge_cells</t>
+          <t>raid.result.wreck_per_elite</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>突袭结算:离同一波已有残骸堆多少格以内的新残骸并进那一堆(少生成地面物与搬运单)</t>
+          <t>突袭结算:每击毁一台精英留下几份敌方残骸</t>
         </is>
       </c>
     </row>
@@ -8006,15 +8006,15 @@
       <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
-          <t>raid.result.wreck_pile_max</t>
+          <t>raid.result.wreck_merge_cells</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>突袭结算:一堆残骸至多几份(一台机器一趟搬完)</t>
+          <t>突袭结算:离同一波已有残骸堆多少格以内的新残骸并进那一堆(少生成地面物与搬运单)</t>
         </is>
       </c>
     </row>
@@ -8022,15 +8022,15 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>raid.result.piles_max</t>
+          <t>raid.result.wreck_pile_max</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>突袭结算:一次突袭至多记住几堆残骸(超出的照样落地,只是不再合并)</t>
+          <t>突袭结算:一堆残骸至多几份(一台机器一趟搬完)</t>
         </is>
       </c>
     </row>
@@ -8038,15 +8038,15 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>raid.result.drop_module_chance</t>
+          <t>raid.result.piles_max</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>0.03</v>
+        <v>48</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台敌人掉落未解析模块的概率(FGR-DEF-051“少数情况”;低于远征,远征掉落表在 FG8-LOOT-01)</t>
+          <t>突袭结算:一次突袭至多记住几堆残骸(超出的照样落地,只是不再合并)</t>
         </is>
       </c>
     </row>
@@ -8054,15 +8054,15 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>raid.result.drop_firmware_chance</t>
+          <t>raid.result.drop_module_chance</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台敌人掉落敌方加密固件的概率(同上)</t>
+          <t>突袭结算:每击毁一台敌人掉落未解析模块的概率(FGR-DEF-051“少数情况”;低于远征,远征掉落表在 FG8-LOOT-01)</t>
         </is>
       </c>
     </row>
@@ -8070,15 +8070,15 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>raid.result.drop_elite_mult</t>
+          <t>raid.result.drop_firmware_chance</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>2</v>
+        <v>0.015</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>突袭结算:精英的掉落概率倍率</t>
+          <t>突袭结算:每击毁一台敌人掉落敌方加密固件的概率(同上)</t>
         </is>
       </c>
     </row>
@@ -8086,15 +8086,15 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>raid.result.timeline_max</t>
+          <t>raid.result.drop_elite_mult</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>突袭结算:过程时间线每次至多几条(超出的计数)</t>
+          <t>突袭结算:精英的掉落概率倍率</t>
         </is>
       </c>
     </row>
@@ -8102,15 +8102,15 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>raid.result.losses_max</t>
+          <t>raid.result.timeline_max</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>突袭结算:损失明细每次至多几条(合计照常累加)</t>
+          <t>突袭结算:过程时间线每次至多几条(超出的计数)</t>
         </is>
       </c>
     </row>
@@ -8118,15 +8118,15 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>raid.result.contrib_max</t>
+          <t>raid.result.losses_max</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>突袭结算:贡献记录每次至多几个击毁者(更多的并进“其它”)</t>
+          <t>突袭结算:损失明细每次至多几条(合计照常累加)</t>
         </is>
       </c>
     </row>
@@ -8134,15 +8134,15 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>raid.result.contrib_top</t>
+          <t>raid.result.contrib_max</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>突袭结算 / 离家报告:贡献排行显示前几名</t>
+          <t>突袭结算:贡献记录每次至多几个击毁者(更多的并进“其它”)</t>
         </is>
       </c>
     </row>
@@ -8150,15 +8150,15 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>raid.result.route_seconds</t>
+          <t>raid.result.contrib_top</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>残骸去向:每隔几游戏秒检查一次仓库里的残骸要不要送去解析台 / 回收站</t>
+          <t>突袭结算 / 离家报告:贡献排行显示前几名</t>
         </is>
       </c>
     </row>
@@ -8166,15 +8166,15 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>raid.result.route_batch</t>
+          <t>raid.result.route_seconds</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>残骸去向:一张送货单至多几份残骸</t>
+          <t>残骸去向:每隔几游戏秒检查一次仓库里的残骸要不要送去解析台 / 回收站</t>
         </is>
       </c>
     </row>
@@ -8182,15 +8182,15 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>raid.result.autosave_on_warning</t>
+          <t>raid.result.route_batch</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>突袭预警发出时自动存档(1=开;同一波只存一次;核心被摧毁后不再存)</t>
+          <t>残骸去向:一张送货单至多几份残骸</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>raid.result.panel_refresh_seconds</t>
+          <t>raid.result.autosave_on_warning</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>突袭历史面板:进行中的突袭每隔几真实秒重读一次</t>
+          <t>突袭预警发出时自动存档(1=开;同一波只存一次;核心被摧毁后不再存)</t>
         </is>
       </c>
     </row>
@@ -8214,15 +8214,15 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>raid.result.perf_ms</t>
+          <t>raid.result.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>性能验收:热更层处理一次击毁事件(残骸 / 掉落 / 贡献 / 结算记账)的平均耗时上限(毫秒)</t>
+          <t>突袭历史面板:进行中的突袭每隔几真实秒重读一次</t>
         </is>
       </c>
     </row>
@@ -8230,15 +8230,15 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>difficulty.custom_min</t>
+          <t>raid.result.perf_ms</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>自定义难度:三个滑条(突袭频率 / 规模 / 预警时间倍率)的下限</t>
+          <t>性能验收:热更层处理一次击毁事件(残骸 / 掉落 / 贡献 / 结算记账)的平均耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -8246,15 +8246,15 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>difficulty.custom_max</t>
+          <t>difficulty.custom_min</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>自定义难度:三个滑条的上限</t>
+          <t>自定义难度:三个滑条(突袭频率 / 规模 / 预警时间倍率)的下限</t>
         </is>
       </c>
     </row>
@@ -8262,15 +8262,15 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>difficulty.custom_step</t>
+          <t>difficulty.custom_max</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>自定义难度:滑条步长(存档里的值按它取整,同一设置同一字节)</t>
+          <t>自定义难度:三个滑条的上限</t>
         </is>
       </c>
     </row>
@@ -8278,15 +8278,15 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>difficulty.history_max</t>
+          <t>difficulty.custom_step</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>32</v>
+        <v>0.1</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>难度修改记录最多保留几条(更早的只留计数;开局难度与“是否离开过开局难度”永久保留)</t>
+          <t>自定义难度:滑条步长(存档里的值按它取整,同一设置同一字节)</t>
         </is>
       </c>
     </row>
@@ -8294,15 +8294,15 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>difficulty.history_max</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>难度修改记录最多保留几条(更早的只留计数;开局难度与“是否离开过开局难度”永久保留)</t>
         </is>
       </c>
     </row>
@@ -8310,15 +8310,15 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -8326,15 +8326,15 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -8342,15 +8342,15 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -8358,15 +8358,15 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -8374,15 +8374,15 @@
       <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -8390,15 +8390,15 @@
       <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -8406,15 +8406,15 @@
       <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -8422,15 +8422,15 @@
       <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -8438,15 +8438,15 @@
       <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -8454,15 +8454,15 @@
       <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -8470,15 +8470,15 @@
       <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -8486,15 +8486,15 @@
       <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -8502,15 +8502,15 @@
       <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -8518,15 +8518,15 @@
       <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -8534,15 +8534,15 @@
       <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -8550,15 +8550,15 @@
       <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -8566,15 +8566,15 @@
       <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -8582,15 +8582,15 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -8614,15 +8614,15 @@
       <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -8630,15 +8630,15 @@
       <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -8646,15 +8646,15 @@
       <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -8662,15 +8662,15 @@
       <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8678,15 +8678,15 @@
       <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -8694,15 +8694,15 @@
       <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -8710,15 +8710,15 @@
       <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8726,15 +8726,15 @@
       <c r="A519" t="inlineStr"/>
       <c r="B519" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       <c r="A520" t="inlineStr"/>
       <c r="B520" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
       <c r="A521" t="inlineStr"/>
       <c r="B521" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       <c r="A522" t="inlineStr"/>
       <c r="B522" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8790,15 +8790,15 @@
       <c r="A523" t="inlineStr"/>
       <c r="B523" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -8806,15 +8806,15 @@
       <c r="A524" t="inlineStr"/>
       <c r="B524" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -8822,15 +8822,15 @@
       <c r="A525" t="inlineStr"/>
       <c r="B525" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -8838,15 +8838,15 @@
       <c r="A526" t="inlineStr"/>
       <c r="B526" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -8854,15 +8854,15 @@
       <c r="A527" t="inlineStr"/>
       <c r="B527" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -8870,15 +8870,15 @@
       <c r="A528" t="inlineStr"/>
       <c r="B528" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -8886,15 +8886,15 @@
       <c r="A529" t="inlineStr"/>
       <c r="B529" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -8902,15 +8902,15 @@
       <c r="A530" t="inlineStr"/>
       <c r="B530" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -8918,15 +8918,15 @@
       <c r="A531" t="inlineStr"/>
       <c r="B531" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -8934,15 +8934,15 @@
       <c r="A532" t="inlineStr"/>
       <c r="B532" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       <c r="A533" t="inlineStr"/>
       <c r="B533" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -8966,15 +8966,15 @@
       <c r="A534" t="inlineStr"/>
       <c r="B534" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8982,15 +8982,15 @@
       <c r="A535" t="inlineStr"/>
       <c r="B535" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -8998,15 +8998,15 @@
       <c r="A536" t="inlineStr"/>
       <c r="B536" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -9014,15 +9014,15 @@
       <c r="A537" t="inlineStr"/>
       <c r="B537" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -9030,15 +9030,15 @@
       <c r="A538" t="inlineStr"/>
       <c r="B538" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>12</v>
+        <v>0.05</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -9046,15 +9046,15 @@
       <c r="A539" t="inlineStr"/>
       <c r="B539" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -9062,15 +9062,15 @@
       <c r="A540" t="inlineStr"/>
       <c r="B540" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>100000</v>
+        <v>10</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -9078,15 +9078,15 @@
       <c r="A541" t="inlineStr"/>
       <c r="B541" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>3</v>
+        <v>100000</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       <c r="A542" t="inlineStr"/>
       <c r="B542" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -9110,15 +9110,15 @@
       <c r="A543" t="inlineStr"/>
       <c r="B543" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -9126,15 +9126,15 @@
       <c r="A544" t="inlineStr"/>
       <c r="B544" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -9142,15 +9142,15 @@
       <c r="A545" t="inlineStr"/>
       <c r="B545" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -9158,15 +9158,15 @@
       <c r="A546" t="inlineStr"/>
       <c r="B546" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -9174,15 +9174,15 @@
       <c r="A547" t="inlineStr"/>
       <c r="B547" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -9190,15 +9190,15 @@
       <c r="A548" t="inlineStr"/>
       <c r="B548" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>away.machines_max</t>
         </is>
       </c>
       <c r="C548" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -9206,15 +9206,15 @@
       <c r="A549" t="inlineStr"/>
       <c r="B549" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>alarm.jam_seconds</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>0.3</v>
+        <v>60</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
         </is>
       </c>
     </row>
@@ -9222,15 +9222,15 @@
       <c r="A550" t="inlineStr"/>
       <c r="B550" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>alarm.machine_wounded_fraction</t>
         </is>
       </c>
       <c r="C550" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
         </is>
       </c>
     </row>
@@ -9238,15 +9238,15 @@
       <c r="A551" t="inlineStr"/>
       <c r="B551" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.softlock.check_seconds</t>
         </is>
       </c>
       <c r="C551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
         </is>
       </c>
     </row>
@@ -9254,15 +9254,15 @@
       <c r="A552" t="inlineStr"/>
       <c r="B552" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.softlock.print_min_machines</t>
         </is>
       </c>
       <c r="C552" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
         </is>
       </c>
     </row>
@@ -9270,15 +9270,15 @@
       <c r="A553" t="inlineStr"/>
       <c r="B553" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.softlock.print_health</t>
         </is>
       </c>
       <c r="C553" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
         </is>
       </c>
     </row>
@@ -9286,15 +9286,15 @@
       <c r="A554" t="inlineStr"/>
       <c r="B554" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.softlock.core_scrap_per_minute</t>
         </is>
       </c>
       <c r="C554" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
         </is>
       </c>
     </row>
@@ -9302,15 +9302,15 @@
       <c r="A555" t="inlineStr"/>
       <c r="B555" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.softlock.loop_check_seconds</t>
         </is>
       </c>
       <c r="C555" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
         </is>
       </c>
     </row>
@@ -9318,15 +9318,15 @@
       <c r="A556" t="inlineStr"/>
       <c r="B556" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.softlock.loop_stall_seconds</t>
         </is>
       </c>
       <c r="C556" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
         </is>
       </c>
     </row>
@@ -9334,15 +9334,15 @@
       <c r="A557" t="inlineStr"/>
       <c r="B557" t="inlineStr">
         <is>
-          <t>eco.softlock.unreachable_seconds</t>
+          <t>eco.softlock.reach_check_seconds</t>
         </is>
       </c>
       <c r="C557" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
         </is>
       </c>
     </row>
@@ -9350,15 +9350,15 @@
       <c r="A558" t="inlineStr"/>
       <c r="B558" t="inlineStr">
         <is>
-          <t>env.daynight.night_start_hour</t>
+          <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
       <c r="C558" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>入夜时刻(游戏小时,0~24);初值20:24,夜晚以午夜为中心</t>
+          <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>
       </c>
     </row>
@@ -9366,15 +9366,15 @@
       <c r="A559" t="inlineStr"/>
       <c r="B559" t="inlineStr">
         <is>
-          <t>env.daynight.night_hours</t>
+          <t>env.daynight.night_start_hour</t>
         </is>
       </c>
       <c r="C559" t="n">
-        <v>7.2</v>
+        <v>20.4</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>夜晚持续多少游戏小时;7.2=1x下6分钟(FG07 第10节:白天14分钟,夜晚6分钟)</t>
+          <t>入夜时刻(游戏小时,0~24);初值20:24,夜晚以午夜为中心</t>
         </is>
       </c>
     </row>
@@ -9382,15 +9382,15 @@
       <c r="A560" t="inlineStr"/>
       <c r="B560" t="inlineStr">
         <is>
-          <t>env.daynight.twilight_hours</t>
+          <t>env.daynight.night_hours</t>
         </is>
       </c>
       <c r="C560" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>黄昏/黎明过渡多少游戏小时(入夜前光照从1降到0、天亮后从0升到1;夜晚本身光照恒为0)</t>
+          <t>夜晚持续多少游戏小时;7.2=1x下6分钟(FG07 第10节:白天14分钟,夜晚6分钟)</t>
         </is>
       </c>
     </row>
@@ -9398,15 +9398,15 @@
       <c r="A561" t="inlineStr"/>
       <c r="B561" t="inlineStr">
         <is>
-          <t>env.calendar.days</t>
+          <t>env.daynight.twilight_hours</t>
         </is>
       </c>
       <c r="C561" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>日历面板显示今天起几个游戏日(1~14)</t>
+          <t>黄昏/黎明过渡多少游戏小时(入夜前光照从1降到0、天亮后从0升到1;夜晚本身光照恒为0)</t>
         </is>
       </c>
     </row>
@@ -9414,15 +9414,15 @@
       <c r="A562" t="inlineStr"/>
       <c r="B562" t="inlineStr">
         <is>
-          <t>env.light.night_tint_r</t>
+          <t>env.calendar.days</t>
         </is>
       </c>
       <c r="C562" t="n">
-        <v>0.55</v>
+        <v>5</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>夜里主方向光的颜色(乘在场景原光色上)红分量</t>
+          <t>日历面板显示今天起几个游戏日(1~14)</t>
         </is>
       </c>
     </row>
@@ -9430,15 +9430,15 @@
       <c r="A563" t="inlineStr"/>
       <c r="B563" t="inlineStr">
         <is>
-          <t>env.light.night_tint_g</t>
+          <t>env.light.night_tint_r</t>
         </is>
       </c>
       <c r="C563" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>夜里主方向光颜色绿分量</t>
+          <t>夜里主方向光的颜色(乘在场景原光色上)红分量</t>
         </is>
       </c>
     </row>
@@ -9446,15 +9446,15 @@
       <c r="A564" t="inlineStr"/>
       <c r="B564" t="inlineStr">
         <is>
-          <t>env.light.night_tint_b</t>
+          <t>env.light.night_tint_g</t>
         </is>
       </c>
       <c r="C564" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>夜里主方向光颜色蓝分量</t>
+          <t>夜里主方向光颜色绿分量</t>
         </is>
       </c>
     </row>
@@ -9462,15 +9462,15 @@
       <c r="A565" t="inlineStr"/>
       <c r="B565" t="inlineStr">
         <is>
-          <t>env.light.apply_epsilon</t>
+          <t>env.light.night_tint_b</t>
         </is>
       </c>
       <c r="C565" t="n">
-        <v>0.003</v>
+        <v>1</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>画面亮度变化小于这个数时不写光照(每帧O(1),避免黄昏时每帧改灯)</t>
+          <t>夜里主方向光颜色蓝分量</t>
         </is>
       </c>
     </row>
@@ -9478,15 +9478,15 @@
       <c r="A566" t="inlineStr"/>
       <c r="B566" t="inlineStr">
         <is>
-          <t>env.silent.start_offset_hours</t>
+          <t>env.light.apply_epsilon</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>1.6</v>
+        <v>0.003</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>静默夜从入夜后第几个游戏小时开始(1.6 = 22:00;开始 + 持续必须落在夜里)</t>
+          <t>画面亮度变化小于这个数时不写光照(每帧O(1),避免黄昏时每帧改灯)</t>
         </is>
       </c>
     </row>
@@ -9494,15 +9494,15 @@
       <c r="A567" t="inlineStr"/>
       <c r="B567" t="inlineStr">
         <is>
-          <t>env.silent.duration_hours</t>
+          <t>env.silent.start_offset_hours</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>静默夜持续多少游戏小时(FG07 第10节:4 小时 = 1x 下约 3.3 分钟)</t>
+          <t>静默夜从入夜后第几个游戏小时开始(1.6 = 22:00;开始 + 持续必须落在夜里)</t>
         </is>
       </c>
     </row>
@@ -9510,15 +9510,15 @@
       <c r="A568" t="inlineStr"/>
       <c r="B568" t="inlineStr">
         <is>
-          <t>env.silent.warning_hours</t>
+          <t>env.silent.duration_hours</t>
         </is>
       </c>
       <c r="C568" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>开始前多少游戏小时预警(FG07 第10节:1.2 小时 = 1x 下约 60 秒)</t>
+          <t>静默夜持续多少游戏小时(FG07 第10节:4 小时 = 1x 下约 3.3 分钟)</t>
         </is>
       </c>
     </row>
@@ -9526,15 +9526,15 @@
       <c r="A569" t="inlineStr"/>
       <c r="B569" t="inlineStr">
         <is>
-          <t>env.silent.dim_ramp_hours</t>
+          <t>env.silent.warning_hours</t>
         </is>
       </c>
       <c r="C569" t="n">
-        <v>0.25</v>
+        <v>1.2</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>静默夜画面压暗的淡入 / 淡出游戏小时(纯表现)</t>
+          <t>开始前多少游戏小时预警(FG07 第10节:1.2 小时 = 1x 下约 60 秒)</t>
         </is>
       </c>
     </row>
@@ -9542,15 +9542,15 @@
       <c r="A570" t="inlineStr"/>
       <c r="B570" t="inlineStr">
         <is>
-          <t>env.silent.expedition_estimate_hours</t>
+          <t>env.silent.dim_ramp_hours</t>
         </is>
       </c>
       <c r="C570" t="n">
-        <v>12</v>
+        <v>0.25</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>远征准备时按多少游戏小时估计远征时长(跨过静默夜就提示;12 小时 = 1x 下 10 分钟)</t>
+          <t>静默夜画面压暗的淡入 / 淡出游戏小时(纯表现)</t>
         </is>
       </c>
     </row>
@@ -9558,15 +9558,15 @@
       <c r="A571" t="inlineStr"/>
       <c r="B571" t="inlineStr">
         <is>
-          <t>env.silent.debris_min</t>
+          <t>env.silent.expedition_estimate_hours</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>静默夜结束后家园出现几处风暴残骸(最少)</t>
+          <t>远征准备时按多少游戏小时估计远征时长(跨过静默夜就提示;12 小时 = 1x 下 10 分钟)</t>
         </is>
       </c>
     </row>
@@ -9574,15 +9574,15 @@
       <c r="A572" t="inlineStr"/>
       <c r="B572" t="inlineStr">
         <is>
-          <t>env.silent.debris_max</t>
+          <t>env.silent.debris_min</t>
         </is>
       </c>
       <c r="C572" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>风暴残骸最多几处</t>
+          <t>静默夜结束后家园出现几处风暴残骸(最少)</t>
         </is>
       </c>
     </row>
@@ -9590,15 +9590,15 @@
       <c r="A573" t="inlineStr"/>
       <c r="B573" t="inlineStr">
         <is>
-          <t>env.silent.debris_rare_chance</t>
+          <t>env.silent.debris_max</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>每次静默夜额外出现一处稀有残骸的概率(0~1)</t>
+          <t>风暴残骸最多几处</t>
         </is>
       </c>
     </row>
@@ -9606,15 +9606,15 @@
       <c r="A574" t="inlineStr"/>
       <c r="B574" t="inlineStr">
         <is>
-          <t>env.silent.debris_ring_min</t>
+          <t>env.silent.debris_rare_chance</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>10</v>
+        <v>0.25</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>风暴残骸离归还核心至少几格</t>
+          <t>每次静默夜额外出现一处稀有残骸的概率(0~1)</t>
         </is>
       </c>
     </row>
@@ -9622,15 +9622,15 @@
       <c r="A575" t="inlineStr"/>
       <c r="B575" t="inlineStr">
         <is>
-          <t>env.silent.debris_ring_max</t>
+          <t>env.silent.debris_ring_min</t>
         </is>
       </c>
       <c r="C575" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>风暴残骸离归还核心至多几格(按种子地形找空地,找不到就少放)</t>
+          <t>风暴残骸离归还核心至少几格</t>
         </is>
       </c>
     </row>
@@ -9638,15 +9638,15 @@
       <c r="A576" t="inlineStr"/>
       <c r="B576" t="inlineStr">
         <is>
-          <t>env.weather.duration_min_days</t>
+          <t>env.silent.debris_ring_max</t>
         </is>
       </c>
       <c r="C576" t="n">
-        <v>0.5</v>
+        <v>36</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>一段恶劣天气最短持续几个游戏日(FG07 第10节:0.5~1.5)</t>
+          <t>风暴残骸离归还核心至多几格(按种子地形找空地,找不到就少放)</t>
         </is>
       </c>
     </row>
@@ -9654,15 +9654,15 @@
       <c r="A577" t="inlineStr"/>
       <c r="B577" t="inlineStr">
         <is>
-          <t>env.weather.duration_max_days</t>
+          <t>env.weather.duration_min_days</t>
         </is>
       </c>
       <c r="C577" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>一段恶劣天气最长持续几个游戏日</t>
+          <t>一段恶劣天气最短持续几个游戏日(FG07 第10节:0.5~1.5)</t>
         </is>
       </c>
     </row>
@@ -9670,15 +9670,15 @@
       <c r="A578" t="inlineStr"/>
       <c r="B578" t="inlineStr">
         <is>
-          <t>env.weather.first_day</t>
+          <t>env.weather.duration_max_days</t>
         </is>
       </c>
       <c r="C578" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>第一段恶劣天气最早在第几个游戏日开始(开局先让玩家站稳;FG16 节奏表另见 FG-GAP)</t>
+          <t>一段恶劣天气最长持续几个游戏日</t>
         </is>
       </c>
     </row>
@@ -9686,15 +9686,15 @@
       <c r="A579" t="inlineStr"/>
       <c r="B579" t="inlineStr">
         <is>
-          <t>env.weather.warning_days</t>
+          <t>env.weather.first_day</t>
         </is>
       </c>
       <c r="C579" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>没有天气预报情报时,恶劣天气开始前多少游戏日预警(FGR-ENV-021:0.5 日)</t>
+          <t>第一段恶劣天气最早在第几个游戏日开始(开局先让玩家站稳;FG16 节奏表另见 FG-GAP)</t>
         </is>
       </c>
     </row>
@@ -9702,15 +9702,15 @@
       <c r="A580" t="inlineStr"/>
       <c r="B580" t="inlineStr">
         <is>
-          <t>env.weather.forecast_days</t>
+          <t>env.weather.warning_days</t>
         </is>
       </c>
       <c r="C580" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>有监听站 T2 的有效天气预报情报时,看得到未来几个游戏日的天气(FGR-ENV-021:3 日)</t>
+          <t>没有天气预报情报时,恶劣天气开始前多少游戏日预警(FGR-ENV-021:0.5 日)</t>
         </is>
       </c>
     </row>
@@ -9718,15 +9718,15 @@
       <c r="A581" t="inlineStr"/>
       <c r="B581" t="inlineStr">
         <is>
-          <t>env.weather.schedule_days</t>
+          <t>env.weather.forecast_days</t>
         </is>
       </c>
       <c r="C581" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>天气提前排定几个游戏日(必须 &gt; 预报天数,预报看得到的都已排定、写进存档)</t>
+          <t>有监听站 T2 的有效天气预报情报时,看得到未来几个游戏日的天气(FGR-ENV-021:3 日)</t>
         </is>
       </c>
     </row>
@@ -9734,15 +9734,15 @@
       <c r="A582" t="inlineStr"/>
       <c r="B582" t="inlineStr">
         <is>
-          <t>env.weather.acid_pct_per_hour</t>
+          <t>env.weather.schedule_days</t>
         </is>
       </c>
       <c r="C582" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>酸雨:露天建筑 / 传送带 / 炮塔每游戏小时损失最大耐久的百分之几(FG07 第10节:1%)</t>
+          <t>天气提前排定几个游戏日(必须 &gt; 预报天数,预报看得到的都已排定、写进存档)</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       <c r="A583" t="inlineStr"/>
       <c r="B583" t="inlineStr">
         <is>
-          <t>env.weather.damage_notify_hours</t>
+          <t>env.weather.acid_pct_per_hour</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>酸雨损伤的汇总通知最多每几个游戏小时一条(同一段酸雨内;摧毁另有通知)</t>
+          <t>酸雨:露天建筑 / 传送带 / 炮塔每游戏小时损失最大耐久的百分之几(FG07 第10节:1%)</t>
         </is>
       </c>
     </row>
@@ -9766,15 +9766,15 @@
       <c r="A584" t="inlineStr"/>
       <c r="B584" t="inlineStr">
         <is>
-          <t>env.weather.sand_detect_factor</t>
+          <t>env.weather.damage_notify_hours</t>
         </is>
       </c>
       <c r="C584" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>沙暴:露天炮塔探测(开火)距离乘这个数(FG07 第10节:-20%)</t>
+          <t>酸雨损伤的汇总通知最多每几个游戏小时一条(同一段酸雨内;摧毁另有通知)</t>
         </is>
       </c>
     </row>
@@ -9782,15 +9782,15 @@
       <c r="A585" t="inlineStr"/>
       <c r="B585" t="inlineStr">
         <is>
-          <t>env.weather.cold_dissipation_mult</t>
+          <t>env.weather.sand_detect_factor</t>
         </is>
       </c>
       <c r="C585" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>寒潮:家园里武器散热乘这个数(FG07 第10节:散热 +30%)</t>
+          <t>沙暴:露天炮塔探测(开火)距离乘这个数(FG07 第10节:-20%)</t>
         </is>
       </c>
     </row>
@@ -9798,15 +9798,15 @@
       <c r="A586" t="inlineStr"/>
       <c r="B586" t="inlineStr">
         <is>
-          <t>env.weather.sand_fog_density</t>
+          <t>env.weather.cold_dissipation_mult</t>
         </is>
       </c>
       <c r="C586" t="n">
-        <v>0.018</v>
+        <v>1.3</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>沙暴画面:指数雾浓度(纯表现;乘玩家的天气视觉效果强度)</t>
+          <t>寒潮:家园里武器散热乘这个数(FG07 第10节:散热 +30%)</t>
         </is>
       </c>
     </row>
@@ -9814,15 +9814,15 @@
       <c r="A587" t="inlineStr"/>
       <c r="B587" t="inlineStr">
         <is>
-          <t>env.weather.fx_ramp_hours</t>
+          <t>env.weather.sand_fog_density</t>
         </is>
       </c>
       <c r="C587" t="n">
-        <v>0.3</v>
+        <v>0.018</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>天气画面淡入 / 淡出的游戏小时(纯表现)</t>
+          <t>沙暴画面:指数雾浓度(纯表现;乘玩家的天气视觉效果强度)</t>
         </is>
       </c>
     </row>
@@ -9830,15 +9830,15 @@
       <c r="A588" t="inlineStr"/>
       <c r="B588" t="inlineStr">
         <is>
-          <t>env.weather.particles_max</t>
+          <t>env.weather.fx_ramp_hours</t>
         </is>
       </c>
       <c r="C588" t="n">
-        <v>600</v>
+        <v>0.3</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>雨 / 沙 / 雪粒子最多同时几颗(满强度;ART-PERF-BUDGET 占位,乘视觉效果强度)</t>
+          <t>天气画面淡入 / 淡出的游戏小时(纯表现)</t>
         </is>
       </c>
     </row>
@@ -9846,15 +9846,15 @@
       <c r="A589" t="inlineStr"/>
       <c r="B589" t="inlineStr">
         <is>
-          <t>env.roof.block_cells</t>
+          <t>env.weather.particles_max</t>
         </is>
       </c>
       <c r="C589" t="n">
-        <v>4</v>
+        <v>600</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>顶棚一块的边长(格;FGR-ENV-030:4×4)</t>
+          <t>雨 / 沙 / 雪粒子最多同时几颗(满强度;ART-PERF-BUDGET 占位,乘视觉效果强度)</t>
         </is>
       </c>
     </row>
@@ -9862,15 +9862,15 @@
       <c r="A590" t="inlineStr"/>
       <c r="B590" t="inlineStr">
         <is>
-          <t>env.roof.max_blocks_per_drag</t>
+          <t>env.roof.block_cells</t>
         </is>
       </c>
       <c r="C590" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>一次拖拽最多铺几块顶棚(超出给原因,不静默截断)</t>
+          <t>顶棚一块的边长(格;FGR-ENV-030:4×4)</t>
         </is>
       </c>
     </row>
@@ -9878,15 +9878,15 @@
       <c r="A591" t="inlineStr"/>
       <c r="B591" t="inlineStr">
         <is>
-          <t>env.roof.build_seconds_per_block</t>
+          <t>env.roof.max_blocks_per_drag</t>
         </is>
       </c>
       <c r="C591" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>机器施工一块顶棚要几游戏秒</t>
+          <t>一次拖拽最多铺几块顶棚(超出给原因,不静默截断)</t>
         </is>
       </c>
     </row>
@@ -9894,15 +9894,15 @@
       <c r="A592" t="inlineStr"/>
       <c r="B592" t="inlineStr">
         <is>
-          <t>purify.hours_per_level</t>
+          <t>env.roof.build_seconds_per_block</t>
         </is>
       </c>
       <c r="C592" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>净化速度:每格每 N 个游戏小时降 1 级(FG07 第 10 节初值 N = 2;按持续有电有冷却液的游戏时间累计,暂停 / 倍速同比例)</t>
+          <t>机器施工一块顶棚要几游戏秒</t>
         </is>
       </c>
     </row>
@@ -9910,15 +9910,15 @@
       <c r="A593" t="inlineStr"/>
       <c r="B593" t="inlineStr">
         <is>
-          <t>purify.coolant_mult_t2</t>
+          <t>purify.hours_per_level</t>
         </is>
       </c>
       <c r="C593" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>净化塔 T2 的冷却液用量 = T1(fg.TbProducer.fluidLpm)× 本值</t>
+          <t>净化速度:每格每 N 个游戏小时降 1 级(FG07 第 10 节初值 N = 2;按持续有电有冷却液的游戏时间累计,暂停 / 倍速同比例)</t>
         </is>
       </c>
     </row>
@@ -9926,15 +9926,15 @@
       <c r="A594" t="inlineStr"/>
       <c r="B594" t="inlineStr">
         <is>
-          <t>purify.coolant_mult_t3</t>
+          <t>purify.coolant_mult_t2</t>
         </is>
       </c>
       <c r="C594" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>净化塔 T3 的冷却液用量 = T1 × 本值</t>
+          <t>净化塔 T2 的冷却液用量 = T1(fg.TbProducer.fluidLpm)× 本值</t>
         </is>
       </c>
     </row>
@@ -9942,15 +9942,15 @@
       <c r="A595" t="inlineStr"/>
       <c r="B595" t="inlineStr">
         <is>
-          <t>purify.rich_ore.radius</t>
+          <t>purify.coolant_mult_t3</t>
         </is>
       </c>
       <c r="C595" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>归还 20,000 格的奖励“稀土富矿”:揭示(探索)的圆半径,也是富矿的范围(格;范围内压在稀土矿脉上的提取钻产出加倍)</t>
+          <t>净化塔 T3 的冷却液用量 = T1 × 本值</t>
         </is>
       </c>
     </row>
@@ -9958,15 +9958,15 @@
       <c r="A596" t="inlineStr"/>
       <c r="B596" t="inlineStr">
         <is>
-          <t>purify.rich_ore.yield_mult</t>
+          <t>purify.rich_ore.radius</t>
         </is>
       </c>
       <c r="C596" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>稀土富矿范围内的提取钻每份产出 × 本值(整数)</t>
+          <t>归还 20,000 格的奖励“稀土富矿”:揭示(探索)的圆半径,也是富矿的范围(格;范围内压在稀土矿脉上的提取钻产出加倍)</t>
         </is>
       </c>
     </row>
@@ -9974,15 +9974,15 @@
       <c r="A597" t="inlineStr"/>
       <c r="B597" t="inlineStr">
         <is>
-          <t>purify.rich_ore.search_radius</t>
+          <t>purify.rich_ore.yield_mult</t>
         </is>
       </c>
       <c r="C597" t="n">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>找稀土富矿的最远距离(格,从归还核心算;先按世界规划层的稀土矿带找,找不到再按种子粗采样)</t>
+          <t>稀土富矿范围内的提取钻每份产出 × 本值(整数)</t>
         </is>
       </c>
     </row>
@@ -9990,15 +9990,15 @@
       <c r="A598" t="inlineStr"/>
       <c r="B598" t="inlineStr">
         <is>
-          <t>purify.rich_ore.search_step</t>
+          <t>purify.rich_ore.search_radius</t>
         </is>
       </c>
       <c r="C598" t="n">
-        <v>6</v>
+        <v>400</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>粗采样的步长(格;只在规划层没有稀土矿带时用)</t>
+          <t>找稀土富矿的最远距离(格,从归还核心算;先按世界规划层的稀土矿带找,找不到再按种子粗采样)</t>
         </is>
       </c>
     </row>
@@ -10006,15 +10006,15 @@
       <c r="A599" t="inlineStr"/>
       <c r="B599" t="inlineStr">
         <is>
-          <t>explore.trail_gap_max</t>
+          <t>purify.rich_ore.search_step</t>
         </is>
       </c>
       <c r="C599" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>机器两次被检查之间走过的距离超过这么多格就当作“瞬移”(出厂 / 读档 / 跳转),不沿路补探索(格)</t>
+          <t>粗采样的步长(格;只在规划层没有稀土矿带时用)</t>
         </is>
       </c>
     </row>
@@ -10022,15 +10022,15 @@
       <c r="A600" t="inlineStr"/>
       <c r="B600" t="inlineStr">
         <is>
-          <t>explore.trail_step</t>
+          <t>explore.trail_gap_max</t>
         </is>
       </c>
       <c r="C600" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>沿机器走过的路补探索的采样间距(格;不大于机器探索半径的一半,保证路上不留缝)</t>
+          <t>机器两次被检查之间走过的距离超过这么多格就当作“瞬移”(出厂 / 读档 / 跳转),不沿路补探索(格)</t>
         </is>
       </c>
     </row>
@@ -10038,15 +10038,15 @@
       <c r="A601" t="inlineStr"/>
       <c r="B601" t="inlineStr">
         <is>
-          <t>relic.pick_radius</t>
+          <t>explore.trail_step</t>
         </is>
       </c>
       <c r="C601" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>右键 / 悬停离遗迹点多近算点中它(格,欧氏距离)</t>
+          <t>沿机器走过的路补探索的采样间距(格;不大于机器探索半径的一半,保证路上不留缝)</t>
         </is>
       </c>
     </row>
@@ -10054,15 +10054,15 @@
       <c r="A602" t="inlineStr"/>
       <c r="B602" t="inlineStr">
         <is>
-          <t>relic.notify_max</t>
+          <t>relic.pick_radius</t>
         </is>
       </c>
       <c r="C602" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>一次揭开的一大片里最多逐个发几条“发现遗迹点”通知(其余合成一条“又发现 N 个”)</t>
+          <t>右键 / 悬停离遗迹点多近算点中它(格,欧氏距离)</t>
         </is>
       </c>
     </row>
@@ -10070,15 +10070,15 @@
       <c r="A603" t="inlineStr"/>
       <c r="B603" t="inlineStr">
         <is>
-          <t>exp.check.severe_health_pct</t>
+          <t>relic.notify_max</t>
         </is>
       </c>
       <c r="C603" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>机器生命低于最大值的这个比例=重伤提醒(可以派,后果写明;0~1)</t>
+          <t>一次揭开的一大片里最多逐个发几条“发现遗迹点”通知(其余合成一条“又发现 N 个”)</t>
         </is>
       </c>
     </row>
@@ -10086,15 +10086,15 @@
       <c r="A604" t="inlineStr"/>
       <c r="B604" t="inlineStr">
         <is>
-          <t>exp.check.warn_health_pct</t>
+          <t>exp.check.severe_health_pct</t>
         </is>
       </c>
       <c r="C604" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>机器生命低于最大值的这个比例=伤势偏重提醒(0~1,应不低于重伤线)</t>
+          <t>机器生命低于最大值的这个比例=重伤提醒(可以派,后果写明;0~1)</t>
         </is>
       </c>
     </row>
@@ -10102,15 +10102,15 @@
       <c r="A605" t="inlineStr"/>
       <c r="B605" t="inlineStr">
         <is>
-          <t>exp.team.color_count</t>
+          <t>exp.check.warn_health_pct</t>
         </is>
       </c>
       <c r="C605" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>远征队可选颜色种数(颜色表见界面,1~8)</t>
+          <t>机器生命低于最大值的这个比例=伤势偏重提醒(0~1,应不低于重伤线)</t>
         </is>
       </c>
     </row>
@@ -10118,15 +10118,255 @@
       <c r="A606" t="inlineStr"/>
       <c r="B606" t="inlineStr">
         <is>
+          <t>exp.team.color_count</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>8</v>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>远征队可选颜色种数(颜色表见界面,1~8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr"/>
+      <c r="B607" t="inlineStr">
+        <is>
           <t>squad.group_double_tap_seconds</t>
         </is>
       </c>
-      <c r="C606" t="n">
+      <c r="C607" t="n">
         <v>0.35</v>
       </c>
-      <c r="D606" t="inlineStr">
+      <c r="D607" t="inlineStr">
         <is>
           <t>连按两次同一编组键的最长间隔(真实秒;镜头飞到编组,FG13 第5节)</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr"/>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>expedition.march.speed.wheel</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>6</v>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>行军速度:搬运轮式底盘(格/秒,FG08 初值);远征队速度取最慢的那台</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr"/>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>expedition.march.speed.hover</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>5</v>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>行军速度:维修悬浮底盘(格/秒,FG08 初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr"/>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>expedition.march.speed.track</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>行军速度:战斗履带底盘(格/秒,FG08 初值;系统占位机按此计)</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr"/>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>expedition.march.arrive_radius</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>10</v>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>全部存活成员走到目的地锚点这么近(格)就算到达,进入远征地点</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr"/>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>expedition.march.home_radius</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>24</v>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>返程的成员全部走到归还核心这么近(格)就算回到家园</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr"/>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>expedition.march.engage_radius</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>12</v>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>成员这么近(格)有敌对单位=交战中(远征队状态)</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr"/>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>expedition.encounter.radius_cells</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>40</v>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>行军途中敌方据点/巡逻/突袭队伍进入队伍这么近(格)就提示一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr"/>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>expedition.march.arrival_retry_seconds</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>15</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>到达失败(地点不开放/存档失败/载入出错已回滚)后,队伍照最后的“前进”隔这么久(游戏秒)自动重试进入</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr"/>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>expedition.anchor.max_attempts</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>8</v>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>锚点可达性校验的最多试探次数(每次换一个由种子决定的候选点)</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr"/>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>expedition.anchor.jitter_deg</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>35</v>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>锚点候选方向:从领地中心朝归还核心的方向左右各偏这么多度以内(由种子决定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr"/>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>expedition.anchor.radial_min</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>锚点候选离领地中心的最小距离(领地半径的倍数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr"/>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>expedition.anchor.radial_max</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>锚点候选离领地中心的最大距离(领地半径的倍数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr"/>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>expedition.anchor.fallback_distance.city</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>300</v>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>没有规划层的旧原型世界:破碎都市锚点离核心的距离(格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr"/>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>expedition.anchor.fallback_distance.foundry</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>600</v>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>没有规划层的旧原型世界:铸造前哨锚点离核心的距离(格)</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D621"/>
+  <dimension ref="A1:D636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10370,6 +10370,246 @@
         </is>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" t="inlineStr"/>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>territory.banner_seconds</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>4</v>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>进入 / 离开领地时屏幕上方名称提示停留多久(真实秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr"/>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>territory.belt_warn_cells</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>40</v>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>镜头 / 接入的机器离外圈危害带这么近(格)时提示“接近危害带”</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr"/>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>territory.presence_refresh_seconds</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>1</v>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>远征队“进入领地”提示的检查周期(游戏秒;与行军提示同一节拍)</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr"/>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>interior.pick_radius</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>5</v>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>左键点在离入口这么近(格)的地方算点中入口(打开进入面板)</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr"/>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>interior.exit_radius</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>6</v>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>室内:机器离出口这么近(格)才能离开</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr"/>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>interior.transition_seconds</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>进出室内的画面过渡(真实秒;过渡期间世界照常运行)</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr"/>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>interior.spawn_spacing</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>进出室内时机器在入口 / 出口旁排开的间距(格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr"/>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>anchor.reach_max_attempts</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>3</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>锚点可达性校验:一条寻路没交回结果时最多再发几次(之后记为失败并写日志)</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr"/>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>outpost.bucket_cells</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>128</v>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>据点空间索引的桶边长(格;地图 / 星球标记 / 休眠判定按桶粗筛)</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr"/>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>outer.reveal_margin_cells</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>96</v>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>外延区:揭开一片区域时,圆外再多登记这么多格内的零散前哨与缓存(按需生成,FGR-GEN-040)</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr"/>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>outer.cache_scrap_base</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>80</v>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>外延区资源缓存的废料基数</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr"/>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>outer.cache_scrap_per_1000</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>40</v>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>外延区资源缓存每离核心 1000 格多给多少废料(越远奖励越高)</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr"/>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>outer.cache_seconds</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>14</v>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>外延区资源缓存的打开工期(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr"/>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>scatter.cache_scrap</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>50</v>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>领地之间(零散)资源缓存的废料</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr"/>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>signal.coverage.site_root_mode</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>1</v>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>远征地点内部覆盖的根:1=远征接入点(恒连通,沿用 FG1-SIG-07);2=星球上的锚点必须在与核心连通的覆盖里(DEBT-FG8EXP02-02,待用户定是否切到 2)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D636"/>
+  <dimension ref="A1:D653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10610,6 +10610,278 @@
         </is>
       </c>
     </row>
+    <row r="637">
+      <c r="A637" t="inlineStr"/>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>territory.control.sync_seconds</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>1</v>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>领地控制度 / 状态 / 增援 / 精英残部 / 骚扰的检查周期(游戏秒;只看步序号,与观察无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr"/>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>territory.control.reclaim_below</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>20</v>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>平定中的领地控制度降到这个值以下(不含)时变为已收复(FGR-EXP-022 初值 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr"/>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>territory.reinforce.interval_days</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>3</v>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>首领被击败前,阵营每几个游戏日增援一次(FGR-EXP-022 初值 3;被摧毁的据点有可能重建)</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr"/>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>territory.reinforce.rebuild_chance</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>每次增援时,每个被摧毁的领地据点重建的概率(按世界种子 + 领地 + 第几次增援 + 据点确定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr"/>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>territory.reinforce.rebuild_max</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>1</v>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>每次增援每个领地最多重建几个据点</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr"/>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>territory.reinforce.rebuild_garrison_ratio</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>重建的据点驻军 = 上限 × 这个比例(至少 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr"/>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>territory.reinforce.block_radius_cells</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>80</v>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>据点这么近(格)内有己方建筑或机器时不重建(不在玩家眼前凭空出现)</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr"/>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>territory.elite.interval_days</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>7</v>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>已收复的领地里精英残部每几个游戏日刷新一次(FGR-EXP-022 初值 7;上一批没被击溃时不叠加)</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr"/>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>territory.harass.interval_hours</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>6</v>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>在敌控 / 平定中的领地里有己方建筑时,每几个游戏小时从最近的据点派一支骚扰部队</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr"/>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>territory.harass.units</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>3</v>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>骚扰部队台数(不超过据点驻军 - 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr"/>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>territory.engage.radius_cells</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>18</v>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>己方机器走到据点 / 巡逻这么近(格)时,驻军 / 巡逻就地展开迎战</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr"/>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>territory.engage.scout_nest_mode</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>1</v>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>家园区侦察巢是否也迎战:1=不迎战(初值,M1～M7 已验收的家园区节奏不变);2=与领地据点同一套迎战(由 FG9-BAL-01 第一幕平衡决定,DEBT-FG8EXP03-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr"/>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>territory.engage.regroup_seconds</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>20</v>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>迎战中附近没有己方机器满这么久(游戏秒),幸存者收拢回据点 / 巡逻(人数按幸存者)</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr"/>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>territory.engage.max_seconds</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>180</v>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>迎战僵持上限(游戏秒):到点收拢,之后这么久内不再展开(不在原地反复展开)</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr"/>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>territory.loot.scrap_per_tier</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>20</v>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>摧毁一个据点掉在原地的废料 = 等级 × 这个值(开搬运单)</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr"/>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>outpost.patrol_view_catchup</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>12</v>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>星球上巡逻标记追上逻辑位置的最快速度(格/真实秒;刚醒来拿到路线时不跳位,DEBT-FG8GEN02-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr"/>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>outpost.patrol_view_snap</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>120</v>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>巡逻标记与逻辑位置相差这么远(格)时直接放过去(读档 / 镜头跳到别处)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D653"/>
+  <dimension ref="A1:D670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6326,15 +6326,15 @@
       <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
-          <t>raid.min_interval_days</t>
+          <t>drop.range_cells</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>两次普通突袭(按抵达时刻)之间至少间隔几个游戏日(FGR-DEF-020;剧情 / 静默夜 / 巨构阶段除外;难度频率倍率除它)</t>
+          <t>投送距离(格,投送站到落点 / 回收点的直线距离;FG08 初值 T1 3000)</t>
         </is>
       </c>
     </row>
@@ -6342,15 +6342,15 @@
       <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
-          <t>raid.min_warning_hours</t>
+          <t>drop.speed_cells</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>1.5</v>
+        <v>60</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>最短预警(游戏小时,FGR-DEF-024;路程不够时推迟出发,部队在出发地集结;乘难度预警倍率)</t>
+          <t>投送舱飞行速度(格/游戏秒,直线飞,不受地形阻挡;FG08 初值)</t>
         </is>
       </c>
     </row>
@@ -6358,15 +6358,15 @@
       <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
-          <t>raid.intel_lead_days</t>
+          <t>drop.landing_seconds</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>有监听站时最早提前几个游戏日预报计划中的突袭(FGR-DEF-024)</t>
+          <t>每程着陆耗时(游戏秒;FG08 初值“加 5 秒着陆”)</t>
         </is>
       </c>
     </row>
@@ -6374,15 +6374,15 @@
       <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
-          <t>raid.plan_lead_days</t>
+          <t>drop.fuel_per_1000</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0.5</v>
+        <v>30</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>普通触发到部队出发(发预警)之间的筹备时间(游戏日;监听站在这段时间里可以破译出发前预报)</t>
+          <t>每舱每 1000 格消耗燃油(升;按往返距离付,发射时一次扣清;FG08 初值)</t>
         </is>
       </c>
     </row>
@@ -6390,15 +6390,15 @@
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
-          <t>raid.story_plan_lead_days</t>
+          <t>drop.cooldown_seconds</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>0.25</v>
+        <v>60</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>剧情 / 静默夜 / 巨构触发到部队出发的筹备时间(游戏日)</t>
+          <t>投送舱回到站里后的冷却(游戏秒;FG08 初值)</t>
         </is>
       </c>
     </row>
@@ -6406,15 +6406,15 @@
       <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
-          <t>raid.route_latency_seconds</t>
+          <t>drop.cargo_units</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>排定突袭的长路线走后台寻路通道,固定这么多游戏秒后采纳(DEBT-FG0ARCH06-09:冷的长路线要几百毫秒,不让采纳步硬等;延迟固定 → 结果确定)</t>
+          <t>每个投送舱载几个单位的货物(不装机器时;FG08 初值)</t>
         </is>
       </c>
     </row>
@@ -6422,15 +6422,15 @@
       <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
-          <t>raid.first_raid_min_days</t>
+          <t>drop.load_radius</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>开局宽限:第几个游戏日之前不会有暴露 / 骚扰触发的突袭抵达(FG16 节奏 2:00 第一次突袭;剧情突袭不受限)</t>
+          <t>投送站中心多少格内的机器能装舱(本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6438,15 +6438,15 @@
       <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
-          <t>raid.first_raid_scale</t>
+          <t>drop.recall_radius</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>第一次突袭固定 1 级,预算再乘这个系数(FG06 第 4 节“规模很小”)</t>
+          <t>回收点多少格内的机器 / 地上货物会被接走(本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6454,15 +6454,15 @@
       <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
-          <t>raid.act1_coef</t>
+          <t>drop.landing.flat_radius</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>幕系数:第一幕(FG16 第 5 节)</t>
+          <t>着陆要多大的平地:落点周围这么多格(含)都是可走地面、没有建筑(本 Story 补的初值,7×7)</t>
         </is>
       </c>
     </row>
@@ -6470,15 +6470,15 @@
       <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
-          <t>raid.act2_coef</t>
+          <t>drop.landing.hazard_center_ratio</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>幕系数:第二幕</t>
+          <t>危害带 / 危害区“中心”:离危害区中心不到半径的这个比例(危害带按带宽中线)就不能着陆(本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6486,15 +6486,15 @@
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
-          <t>raid.act3_coef</t>
+          <t>drop.landing.outpost_clear_cells</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>2.4</v>
+        <v>16</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>幕系数:第三幕</t>
+          <t>敌方据点多少格内不能着陆(落点被据点占着;本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6502,15 +6502,15 @@
       <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
-          <t>raid.interval_bonus_per_day</t>
+          <t>drop.antiair.radius_foundry</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>0.1</v>
+        <v>70</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>间隔系数:距上次突袭超过最短间隔后,每多 1 个游戏日预算 + 本值</t>
+          <t>铸造据点的对空高炮防空覆盖半径(格;1 级,本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6518,15 +6518,15 @@
       <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
-          <t>raid.interval_bonus_max</t>
+          <t>drop.antiair.radius_white_tide</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>0.5</v>
+        <v>55</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>间隔系数的加成上限</t>
+          <t>白潮据点的护卫无人机防空覆盖半径(格;1 级,本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6534,15 +6534,15 @@
       <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
-          <t>raid.level4_period_days</t>
+          <t>drop.antiair.radius_per_tier</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>暴露超过 90 后每隔几个游戏日发生一次 4 级突袭</t>
+          <t>据点每高 1 级,防空覆盖半径加多少格(本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6550,15 +6550,15 @@
       <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
-          <t>raid.threshold_rearm</t>
+          <t>drop.station.fuel_tank_liters</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>暴露降到阈值以下多少之后,再次越过这个阈值才会再次触发</t>
+          <t>投送站油箱(升;从管线进来的燃油存在这里;本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6566,15 +6566,15 @@
       <c r="A384" t="inlineStr"/>
       <c r="B384" t="inlineStr">
         <is>
-          <t>raid.harass_min_interval_days</t>
+          <t>drop.station.fuel_lpm</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>3</v>
+        <v>240</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>低强度骚扰的频率上限:两次骚扰至少间隔几个游戏日</t>
+          <t>投送站从管线进油的最大速度(升/分钟;本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6582,15 +6582,15 @@
       <c r="A385" t="inlineStr"/>
       <c r="B385" t="inlineStr">
         <is>
-          <t>raid.harass_quiet_days</t>
+          <t>drop.sync_seconds</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>距上一次任何突袭抵达至少几个游戏日才会来骚扰</t>
+          <t>投送站对账间隔(游戏秒:站点记录、燃油接点、自动补满、返程改降;按步序号定时做,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -6598,15 +6598,15 @@
       <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
-          <t>raid.max_units</t>
+          <t>raid.min_interval_days</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>一波突袭的单位数上限(FG15 同时存在的敌人 200;超出的预算换成精英)</t>
+          <t>两次普通突袭(按抵达时刻)之间至少间隔几个游戏日(FGR-DEF-020;剧情 / 静默夜 / 巨构阶段除外;难度频率倍率除它)</t>
         </is>
       </c>
     </row>
@@ -6614,15 +6614,15 @@
       <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
-          <t>raid.postgame_base</t>
+          <t>raid.min_warning_hours</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1200</v>
+        <v>1.5</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>后日谈第 n 次清洗的预算基数(FG16 第 5 节)</t>
+          <t>最短预警(游戏小时,FGR-DEF-024;路程不够时推迟出发,部队在出发地集结;乘难度预警倍率)</t>
         </is>
       </c>
     </row>
@@ -6630,15 +6630,15 @@
       <c r="A388" t="inlineStr"/>
       <c r="B388" t="inlineStr">
         <is>
-          <t>raid.postgame_growth</t>
+          <t>raid.intel_lead_days</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>后日谈每次清洗的预算增长倍率</t>
+          <t>有监听站时最早提前几个游戏日预报计划中的突袭(FGR-DEF-024)</t>
         </is>
       </c>
     </row>
@@ -6646,15 +6646,15 @@
       <c r="A389" t="inlineStr"/>
       <c r="B389" t="inlineStr">
         <is>
-          <t>raid.merge_window_seconds</t>
+          <t>raid.plan_lead_days</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1200</v>
+        <v>0.5</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>剧情 / 静默夜 / 巨构突袭与普通突袭抵达时间相差不超过这么多游戏秒视为重叠,合并为一波</t>
+          <t>普通触发到部队出发(发预警)之间的筹备时间(游戏日;监听站在这段时间里可以破译出发前预报)</t>
         </is>
       </c>
     </row>
@@ -6662,15 +6662,15 @@
       <c r="A390" t="inlineStr"/>
       <c r="B390" t="inlineStr">
         <is>
-          <t>raid.destroyed_outpost_interval_bonus</t>
+          <t>raid.story_plan_lead_days</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>某个方向(8 方位)每摧毁一个据点,从那个方向出发的突袭最短间隔 ×(1 + 本值)</t>
+          <t>剧情 / 静默夜 / 巨构触发到部队出发的筹备时间(游戏日)</t>
         </is>
       </c>
     </row>
@@ -6678,15 +6678,15 @@
       <c r="A391" t="inlineStr"/>
       <c r="B391" t="inlineStr">
         <is>
-          <t>raid.origin_max_distance</t>
+          <t>raid.route_latency_seconds</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1600</v>
+        <v>5</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>据点离目标超过这么多格就不算合适的出发地(改从迷雾外来袭)</t>
+          <t>排定突袭的长路线走后台寻路通道,固定这么多游戏秒后采纳(DEBT-FG0ARCH06-09:冷的长路线要几百毫秒,不让采纳步硬等;延迟固定 → 结果确定)</t>
         </is>
       </c>
     </row>
@@ -6694,15 +6694,15 @@
       <c r="A392" t="inlineStr"/>
       <c r="B392" t="inlineStr">
         <is>
-          <t>raid.target_home_weight</t>
+          <t>raid.first_raid_min_days</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>选突袭目标时家园的权重(前哨站权重 = 座数 / 10 × 领地临近系数)</t>
+          <t>开局宽限:第几个游戏日之前不会有暴露 / 骚扰触发的突袭抵达(FG16 节奏 2:00 第一次突袭;剧情突袭不受限)</t>
         </is>
       </c>
     </row>
@@ -6710,15 +6710,15 @@
       <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
-          <t>raid.target_outpost_min_buildings</t>
+          <t>raid.first_raid_scale</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>前哨站至少几座建筑才会被当成突袭目标</t>
+          <t>第一次突袭固定 1 级,预算再乘这个系数(FG06 第 4 节“规模很小”)</t>
         </is>
       </c>
     </row>
@@ -6726,15 +6726,15 @@
       <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
-          <t>raid.target_proximity_cells</t>
+          <t>raid.act1_coef</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>前哨站领地临近系数 = 1 + 本值 / (本值 + 到阵营领地边缘的距离)</t>
+          <t>幕系数:第一幕(FG16 第 5 节)</t>
         </is>
       </c>
     </row>
@@ -6742,15 +6742,15 @@
       <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
-          <t>raid.time_limit_hours</t>
+          <t>raid.act2_coef</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>到达后的时间上限(游戏小时,FGR-DEF-032);攻城行为(FG6-DEF-05)之前部队在外围停留这么久后沿原路撤回出发地</t>
+          <t>幕系数:第二幕</t>
         </is>
       </c>
     </row>
@@ -6758,15 +6758,15 @@
       <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr">
         <is>
-          <t>raid.history_max</t>
+          <t>raid.act3_coef</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>32</v>
+        <v>2.4</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>突袭历史最多保留几条</t>
+          <t>幕系数:第三幕</t>
         </is>
       </c>
     </row>
@@ -6774,15 +6774,15 @@
       <c r="A397" t="inlineStr"/>
       <c r="B397" t="inlineStr">
         <is>
-          <t>raid.warning_rows_max</t>
+          <t>raid.interval_bonus_per_day</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>6</v>
+        <v>0.1</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>预警条最多列几波(更多的写“还有 n 波”)</t>
+          <t>间隔系数:距上次突袭超过最短间隔后,每多 1 个游戏日预算 + 本值</t>
         </is>
       </c>
     </row>
@@ -6790,15 +6790,15 @@
       <c r="A398" t="inlineStr"/>
       <c r="B398" t="inlineStr">
         <is>
-          <t>siege.theater_radius_cells</t>
+          <t>raid.interval_bonus_max</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>140</v>
+        <v>0.5</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>攻城剧场:突袭目标点周围这么远(格)内的己方建筑算进流场范围</t>
+          <t>间隔系数的加成上限</t>
         </is>
       </c>
     </row>
@@ -6806,15 +6806,15 @@
       <c r="A399" t="inlineStr"/>
       <c r="B399" t="inlineStr">
         <is>
-          <t>siege.theater_margin_cells</t>
+          <t>raid.level4_period_days</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>攻城剧场:建筑外接矩形(含集结点)向外放宽的格数</t>
+          <t>暴露超过 90 后每隔几个游戏日发生一次 4 级突袭</t>
         </is>
       </c>
     </row>
@@ -6822,15 +6822,15 @@
       <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
-          <t>siege.theater_max_cells</t>
+          <t>raid.threshold_rearm</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>288</v>
+        <v>10</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>攻城剧场:流场矩形的最大边长(格);超出时以目标点为中心截取(流场内存与全量计算耗时的上限)</t>
+          <t>暴露降到阈值以下多少之后,再次越过这个阈值才会再次触发</t>
         </is>
       </c>
     </row>
@@ -6838,15 +6838,15 @@
       <c r="A401" t="inlineStr"/>
       <c r="B401" t="inlineStr">
         <is>
-          <t>siege.retarget_seconds</t>
+          <t>raid.harass_min_interval_days</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>突袭单位重新选目标 / 重新看破墙目标的间隔(游戏秒)</t>
+          <t>低强度骚扰的频率上限:两次骚扰至少间隔几个游戏日</t>
         </is>
       </c>
     </row>
@@ -6854,15 +6854,15 @@
       <c r="A402" t="inlineStr"/>
       <c r="B402" t="inlineStr">
         <is>
-          <t>siege.breach_base_cost</t>
+          <t>raid.harass_quiet_days</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>破墙流场:穿过一格建筑的基础代价(10 = 走 1 米);越大越倾向绕路而不是破墙</t>
+          <t>距上一次任何突袭抵达至少几个游戏日才会来骚扰</t>
         </is>
       </c>
     </row>
@@ -6870,15 +6870,15 @@
       <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
-          <t>siege.breach_hp_band</t>
+          <t>raid.max_units</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>破墙流场:耐久每多这么多算一档(耐久掉档时流场增量更新)</t>
+          <t>一波突袭的单位数上限(FG15 同时存在的敌人 200;超出的预算换成精英)</t>
         </is>
       </c>
     </row>
@@ -6886,15 +6886,15 @@
       <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
-          <t>siege.breach_cost_per_band</t>
+          <t>raid.postgame_base</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>30</v>
+        <v>1200</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>破墙流场:每档耐久加的代价(10 = 走 1 米);越大越倾向挑最薄弱的那段</t>
+          <t>后日谈第 n 次清洗的预算基数(FG16 第 5 节)</t>
         </is>
       </c>
     </row>
@@ -6902,15 +6902,15 @@
       <c r="A405" t="inlineStr"/>
       <c r="B405" t="inlineStr">
         <is>
-          <t>siege.loss_retreat_ratio</t>
+          <t>raid.postgame_growth</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>0.7</v>
+        <v>1.15</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>FGR-DEF-032:损失超过这个比例全队撤退(初值 70%)</t>
+          <t>后日谈每次清洗的预算增长倍率</t>
         </is>
       </c>
     </row>
@@ -6918,15 +6918,15 @@
       <c r="A406" t="inlineStr"/>
       <c r="B406" t="inlineStr">
         <is>
-          <t>siege.exit_radius_cells</t>
+          <t>raid.merge_window_seconds</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>2.5</v>
+        <v>1200</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>撤退:走到集结点这么近(格)就离开家园、并回行进队伍</t>
+          <t>剧情 / 静默夜 / 巨构突袭与普通突袭抵达时间相差不超过这么多游戏秒视为重叠,合并为一波</t>
         </is>
       </c>
     </row>
@@ -6934,15 +6934,15 @@
       <c r="A407" t="inlineStr"/>
       <c r="B407" t="inlineStr">
         <is>
-          <t>siege.retreat_max_seconds</t>
+          <t>raid.destroyed_outpost_interval_bonus</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>180</v>
+        <v>0.5</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>撤退兜底(B11):下撤退令后这么久(游戏秒)还走不回集结点的(路被堵死时会先拆墙;连墙都拆不出去,例如被地形困住)就地离场,队伍照常原路返回</t>
+          <t>某个方向(8 方位)每摧毁一个据点,从那个方向出发的突袭最短间隔 ×(1 + 本值)</t>
         </is>
       </c>
     </row>
@@ -6950,15 +6950,15 @@
       <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr">
         <is>
-          <t>siege.hp_scale</t>
+          <t>raid.origin_max_distance</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>1</v>
+        <v>1600</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>突袭单位耐久 = fg.TbMechEnemy.maxHp × 本值</t>
+          <t>据点离目标超过这么多格就不算合适的出发地(改从迷雾外来袭)</t>
         </is>
       </c>
     </row>
@@ -6966,15 +6966,15 @@
       <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
-          <t>siege.elite_hp_scale</t>
+          <t>raid.target_home_weight</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>精英突袭单位的耐久倍率</t>
+          <t>选突袭目标时家园的权重(前哨站权重 = 座数 / 10 × 领地临近系数)</t>
         </is>
       </c>
     </row>
@@ -6982,15 +6982,15 @@
       <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
-          <t>siege.elite_damage_scale</t>
+          <t>raid.target_outpost_min_buildings</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>精英突袭单位的伤害倍率</t>
+          <t>前哨站至少几座建筑才会被当成突袭目标</t>
         </is>
       </c>
     </row>
@@ -6998,15 +6998,15 @@
       <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
-          <t>siege.spawn_spacing</t>
+          <t>raid.target_proximity_cells</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>1.6</v>
+        <v>400</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>到达展开:单位之间的间距(米;按确定性的螺旋排布)</t>
+          <t>前哨站领地临近系数 = 1 + 本值 / (本值 + 到阵营领地边缘的距离)</t>
         </is>
       </c>
     </row>
@@ -7014,15 +7014,15 @@
       <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
-          <t>siege.collateral_ratio</t>
+          <t>raid.time_limit_hours</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>溅射:敌人每打中一次建筑,周围传送带 / 管线 / 施工虚影受到这一发伤害 × 本值</t>
+          <t>到达后的时间上限(游戏小时,FGR-DEF-032);攻城行为(FG6-DEF-05)之前部队在外围停留这么久后沿原路撤回出发地</t>
         </is>
       </c>
     </row>
@@ -7030,15 +7030,15 @@
       <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
-          <t>siege.collateral_radius_cells</t>
+          <t>raid.history_max</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>1.5</v>
+        <v>32</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>溅射:命中点周围多远(格)内的传送带 / 管线 / 施工虚影受波及</t>
+          <t>突袭历史最多保留几条</t>
         </is>
       </c>
     </row>
@@ -7046,15 +7046,15 @@
       <c r="A414" t="inlineStr"/>
       <c r="B414" t="inlineStr">
         <is>
-          <t>siege.collateral_drain_per_step</t>
+          <t>raid.warning_rows_max</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>溅射:热更层每步最多结算几个命中格(其余留到下一步,不丢、进存档)</t>
+          <t>预警条最多列几波(更多的写“还有 n 波”)</t>
         </is>
       </c>
     </row>
@@ -7062,15 +7062,15 @@
       <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
-          <t>siege.site_hp_fraction</t>
+          <t>siege.theater_radius_cells</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>0.35</v>
+        <v>140</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>施工中的虚影被溅射打掉的耐久 = 建筑最大耐久 × 本值(打满即“施工中被摧毁”)</t>
+          <t>攻城剧场:突袭目标点周围这么远(格)内的己方建筑算进流场范围</t>
         </is>
       </c>
     </row>
@@ -7078,15 +7078,15 @@
       <c r="A416" t="inlineStr"/>
       <c r="B416" t="inlineStr">
         <is>
-          <t>siege.sync_seconds</t>
+          <t>siege.theater_margin_cells</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>0.5</v>
+        <v>24</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>攻城对账间隔(游戏秒):建筑结构单位的耐久双向对账、撤退条件、溅射以外的检查</t>
+          <t>攻城剧场:建筑外接矩形(含集结点)向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -7094,15 +7094,15 @@
       <c r="A417" t="inlineStr"/>
       <c r="B417" t="inlineStr">
         <is>
-          <t>siege.breach_notify_seconds</t>
+          <t>siege.theater_max_cells</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>“敌人正在拆某段墙”通知的冷却(游戏秒;同一座只报一次,换目标才再报)</t>
+          <t>攻城剧场:流场矩形的最大边长(格);超出时以目标点为中心截取(流场内存与全量计算耗时的上限)</t>
         </is>
       </c>
     </row>
@@ -7110,15 +7110,15 @@
       <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>siege.guard_radius_cells</t>
+          <t>siege.retarget_seconds</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>18</v>
+        <v>0.5</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>驻防机器的守点交战半径(格):敌人进入驻防点这么近就去打,打完回驻防点</t>
+          <t>突袭单位重新选目标 / 重新看破墙目标的间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -7126,15 +7126,15 @@
       <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
-          <t>siege.intercept_radius_cells</t>
+          <t>siege.breach_base_cost</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>拦截:己方机器离行进中的突袭部队这么近(格)时,部队就地展开成战斗单位</t>
+          <t>破墙流场:穿过一格建筑的基础代价(10 = 走 1 米);越大越倾向绕路而不是破墙</t>
         </is>
       </c>
     </row>
@@ -7142,15 +7142,15 @@
       <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr">
         <is>
-          <t>siege.regroup_seconds</t>
+          <t>siege.breach_hp_band</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>拦截:附近没有己方机器满这么久(游戏秒)后,幸存者重新收拢成行进队伍继续走</t>
+          <t>破墙流场:耐久每多这么多算一档(耐久掉档时流场增量更新)</t>
         </is>
       </c>
     </row>
@@ -7158,15 +7158,15 @@
       <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
-          <t>siege.intercept_min_target_cells</t>
+          <t>siege.breach_cost_per_band</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>拦截:离目标(家园核心 / 前哨站)不到这么远(格)的行进队伍不拦截,照常到达展开攻城(同一场仗用流场打)</t>
+          <t>破墙流场:每档耐久加的代价(10 = 走 1 米);越大越倾向挑最薄弱的那段</t>
         </is>
       </c>
     </row>
@@ -7174,15 +7174,15 @@
       <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr">
         <is>
-          <t>siege.intercept_max_seconds</t>
+          <t>siege.loss_retreat_ratio</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>90</v>
+        <v>0.7</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>拦截:就地交战最多这么久(游戏秒),互相够不着的僵持到点后幸存者收拢继续走</t>
+          <t>FGR-DEF-032:损失超过这个比例全队撤退(初值 70%)</t>
         </is>
       </c>
     </row>
@@ -7190,15 +7190,15 @@
       <c r="A423" t="inlineStr"/>
       <c r="B423" t="inlineStr">
         <is>
-          <t>siege.overlay_refresh_seconds</t>
+          <t>siege.exit_radius_cells</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>突袭路径叠加层重画间隔(真实秒;纯表现)</t>
+          <t>撤退:走到集结点这么近(格)就离开家园、并回行进队伍</t>
         </is>
       </c>
     </row>
@@ -7206,15 +7206,15 @@
       <c r="A424" t="inlineStr"/>
       <c r="B424" t="inlineStr">
         <is>
-          <t>siege.perf.units</t>
+          <t>siege.retreat_max_seconds</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>性能验收:同时攻城的突袭单位数(FG06 第 7 节 200)</t>
+          <t>撤退兜底(B11):下撤退令后这么久(游戏秒)还走不回集结点的(路被堵死时会先拆墙;连墙都拆不出去,例如被地形困住)就地离场,队伍照常原路返回</t>
         </is>
       </c>
     </row>
@@ -7222,15 +7222,15 @@
       <c r="A425" t="inlineStr"/>
       <c r="B425" t="inlineStr">
         <is>
-          <t>siege.perf.field_update_ms</t>
+          <t>siege.hp_scale</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>性能验收:屏障变化时流场增量更新单次耗时上限(毫秒,FG06 第 7 节)</t>
+          <t>突袭单位耐久 = fg.TbMechEnemy.maxHp × 本值</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       <c r="A426" t="inlineStr"/>
       <c r="B426" t="inlineStr">
         <is>
-          <t>siege.perf.step_ms</t>
+          <t>siege.elite_hp_scale</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>性能验收:200 单位攻城时内核单步平均耗时上限(毫秒;120 帧预算 8.33 ms 的四分之一)</t>
+          <t>精英突袭单位的耐久倍率</t>
         </is>
       </c>
     </row>
@@ -7254,15 +7254,15 @@
       <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr">
         <is>
-          <t>logistics.pipe.hp_t1</t>
+          <t>siege.elite_damage_scale</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>60</v>
+        <v>1.5</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>管线 T1 一格的最大耐久(管线 / 泵 / 阀门 / 地下管线口按等级)</t>
+          <t>精英突袭单位的伤害倍率</t>
         </is>
       </c>
     </row>
@@ -7270,15 +7270,15 @@
       <c r="A428" t="inlineStr"/>
       <c r="B428" t="inlineStr">
         <is>
-          <t>logistics.pipe.hp_t2</t>
+          <t>siege.spawn_spacing</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>100</v>
+        <v>1.6</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>管线 T2 一格的最大耐久</t>
+          <t>到达展开:单位之间的间距(米;按确定性的螺旋排布)</t>
         </is>
       </c>
     </row>
@@ -7286,15 +7286,15 @@
       <c r="A429" t="inlineStr"/>
       <c r="B429" t="inlineStr">
         <is>
-          <t>logistics.pipe.hp_tank</t>
+          <t>siege.collateral_ratio</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>160</v>
+        <v>0.5</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>储罐一格的最大耐久</t>
+          <t>溅射:敌人每打中一次建筑,周围传送带 / 管线 / 施工虚影受到这一发伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -7302,15 +7302,15 @@
       <c r="A430" t="inlineStr"/>
       <c r="B430" t="inlineStr">
         <is>
-          <t>logistics.pipe.repair_kits</t>
+          <t>siege.collateral_radius_cells</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>维修无人机修满一格管线要的维修件(与传送带同口径)</t>
+          <t>溅射:命中点周围多远(格)内的传送带 / 管线 / 施工虚影受波及</t>
         </is>
       </c>
     </row>
@@ -7318,15 +7318,15 @@
       <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
-          <t>raid.auto_pause_first_raids</t>
+          <t>siege.collateral_drain_per_step</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>FGR-DEF-042:突袭到达时自动暂停的默认值只对本存档前几次突袭(波)开启;玩家在通知设置里改过的按玩家的</t>
+          <t>溅射:热更层每步最多结算几个命中格(其余留到下一步,不丢、进存档)</t>
         </is>
       </c>
     </row>
@@ -7334,15 +7334,15 @@
       <c r="A432" t="inlineStr"/>
       <c r="B432" t="inlineStr">
         <is>
-          <t>raid.spectate.default_speed</t>
+          <t>siege.site_hp_fraction</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>2</v>
+        <v>0.35</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>观战:点“观战”时切到的速度(2 或 3;复用统一时钟的倍速档)</t>
+          <t>施工中的虚影被溅射打掉的耐久 = 建筑最大耐久 × 本值(打满即“施工中被摧毁”)</t>
         </is>
       </c>
     </row>
@@ -7350,15 +7350,15 @@
       <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr">
         <is>
-          <t>raid.spectate.follow_seconds</t>
+          <t>siege.sync_seconds</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>观战:镜头每隔这么久(真实秒)重新看一次战斗重心</t>
+          <t>攻城对账间隔(游戏秒):建筑结构单位的耐久双向对账、撤退条件、溅射以外的检查</t>
         </is>
       </c>
     </row>
@@ -7366,15 +7366,15 @@
       <c r="A434" t="inlineStr"/>
       <c r="B434" t="inlineStr">
         <is>
-          <t>raid.spectate.follow_min_cells</t>
+          <t>siege.breach_notify_seconds</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>观战:战斗重心离镜头焦点超过这么远(格)才飞过去(免得镜头一直抖)</t>
+          <t>“敌人正在拆某段墙”通知的冷却(游戏秒;同一座只报一次,换目标才再报)</t>
         </is>
       </c>
     </row>
@@ -7382,15 +7382,15 @@
       <c r="A435" t="inlineStr"/>
       <c r="B435" t="inlineStr">
         <is>
-          <t>raid.spectate.manual_cells</t>
+          <t>siege.guard_radius_cells</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>观战:玩家自己把镜头移开超过这么远(格)就暂停跟随(点“跟随战斗”恢复)</t>
+          <t>驻防机器的守点交战半径(格):敌人进入驻防点这么近就去打,打完回驻防点</t>
         </is>
       </c>
     </row>
@@ -7398,15 +7398,15 @@
       <c r="A436" t="inlineStr"/>
       <c r="B436" t="inlineStr">
         <is>
-          <t>raid.music.volume</t>
+          <t>siege.intercept_radius_cells</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>0.6</v>
+        <v>16</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>预警 / 突袭音乐的音量(乘在音乐音量设置上;占位音乐,美术批次替换)</t>
+          <t>拦截:己方机器离行进中的突袭部队这么近(格)时,部队就地展开成战斗单位</t>
         </is>
       </c>
     </row>
@@ -7414,15 +7414,15 @@
       <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr">
         <is>
-          <t>raid.hud.refresh_seconds</t>
+          <t>siege.regroup_seconds</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>0.25</v>
+        <v>8</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>突袭 HUD 刷新间隔(真实秒;键没变不重建)</t>
+          <t>拦截:附近没有己方机器满这么久(游戏秒)后,幸存者重新收拢成行进队伍继续走</t>
         </is>
       </c>
     </row>
@@ -7430,15 +7430,15 @@
       <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr">
         <is>
-          <t>raid.hud.perf_ms</t>
+          <t>siege.intercept_min_target_cells</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>0.2</v>
+        <v>60</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>性能验收:突袭 HUD 一次数据刷新(各波剩余敌人 / 文字)的耗时上限(毫秒)</t>
+          <t>拦截:离目标(家园核心 / 前哨站)不到这么远(格)的行进队伍不拦截,照常到达展开攻城(同一场仗用流场打)</t>
         </is>
       </c>
     </row>
@@ -7446,15 +7446,15 @@
       <c r="A439" t="inlineStr"/>
       <c r="B439" t="inlineStr">
         <is>
-          <t>defov.margin_cells</t>
+          <t>siege.intercept_max_seconds</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>防御总览:热力图范围 = 家园己方建筑外接矩形向外放宽的格数</t>
+          <t>拦截:就地交战最多这么久(游戏秒),互相够不着的僵持到点后幸存者收拢继续走</t>
         </is>
       </c>
     </row>
@@ -7462,15 +7462,15 @@
       <c r="A440" t="inlineStr"/>
       <c r="B440" t="inlineStr">
         <is>
-          <t>defov.max_cells</t>
+          <t>siege.overlay_refresh_seconds</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>256</v>
+        <v>0.5</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>防御总览:热力图最大边长(格;超出时以归还核心为中心截取)</t>
+          <t>突袭路径叠加层重画间隔(真实秒;纯表现)</t>
         </is>
       </c>
     </row>
@@ -7478,15 +7478,15 @@
       <c r="A441" t="inlineStr"/>
       <c r="B441" t="inlineStr">
         <is>
-          <t>defov.weak_min_cells</t>
+          <t>siege.perf.units</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>防御总览:连续这么多格(沿路线 / 外围)没有火力覆盖才算一处薄弱点</t>
+          <t>性能验收:同时攻城的突袭单位数(FG06 第 7 节 200)</t>
         </is>
       </c>
     </row>
@@ -7494,15 +7494,15 @@
       <c r="A442" t="inlineStr"/>
       <c r="B442" t="inlineStr">
         <is>
-          <t>defov.weak_max</t>
+          <t>siege.perf.field_update_ms</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>防御总览:最多列出几处薄弱点(按离核心由近到远)</t>
+          <t>性能验收:屏障变化时流场增量更新单次耗时上限(毫秒,FG06 第 7 节)</t>
         </is>
       </c>
     </row>
@@ -7510,15 +7510,15 @@
       <c r="A443" t="inlineStr"/>
       <c r="B443" t="inlineStr">
         <is>
-          <t>defov.ring_extra_cells</t>
+          <t>siege.perf.step_ms</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>防御总览:没有预测路线时,外围检查圈 = 建筑外接矩形半对角线 + 这么多格</t>
+          <t>性能验收:200 单位攻城时内核单步平均耗时上限(毫秒;120 帧预算 8.33 ms 的四分之一)</t>
         </is>
       </c>
     </row>
@@ -7526,15 +7526,15 @@
       <c r="A444" t="inlineStr"/>
       <c r="B444" t="inlineStr">
         <is>
-          <t>defov.ring_samples</t>
+          <t>logistics.pipe.hp_t1</t>
         </is>
       </c>
       <c r="C444" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>防御总览:外围检查圈的采样点数</t>
+          <t>管线 T1 一格的最大耐久(管线 / 泵 / 阀门 / 地下管线口按等级)</t>
         </is>
       </c>
     </row>
@@ -7542,15 +7542,15 @@
       <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr">
         <is>
-          <t>defov.refresh_seconds</t>
+          <t>logistics.pipe.hp_t2</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>防御总览:面板开着时每隔这么久(真实秒)检查一次要不要重算覆盖(炮塔 / 建筑 / 突袭计划变了才重算)</t>
+          <t>管线 T2 一格的最大耐久</t>
         </is>
       </c>
     </row>
@@ -7558,15 +7558,15 @@
       <c r="A446" t="inlineStr"/>
       <c r="B446" t="inlineStr">
         <is>
-          <t>defov.perf_ms</t>
+          <t>logistics.pipe.hp_tank</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>性能验收:100 座炮塔时重算一次覆盖 + 薄弱点的耗时上限(毫秒;只在面板打开 / 防线变化时)</t>
+          <t>储罐一格的最大耐久</t>
         </is>
       </c>
     </row>
@@ -7574,15 +7574,15 @@
       <c r="A447" t="inlineStr"/>
       <c r="B447" t="inlineStr">
         <is>
-          <t>roster.patrol_max_points</t>
+          <t>logistics.pipe.repair_kits</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>6</v>
+        <v>0.25</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>驻防巡逻(FGR-DEF-043):一台机器的巡逻路线最多几个巡逻点(不含驻防点)</t>
+          <t>维修无人机修满一格管线要的维修件(与传送带同口径)</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       <c r="A448" t="inlineStr"/>
       <c r="B448" t="inlineStr">
         <is>
-          <t>roster.patrol_arrive_cells</t>
+          <t>raid.auto_pause_first_raids</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>驻防巡逻:走到巡逻点这么近(格)就去下一个点</t>
+          <t>FGR-DEF-042:突袭到达时自动暂停的默认值只对本存档前几次突袭(波)开启;玩家在通知设置里改过的按玩家的</t>
         </is>
       </c>
     </row>
@@ -7606,15 +7606,15 @@
       <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr">
         <is>
-          <t>roster.patrol_arrive_slack</t>
+          <t>raid.spectate.default_speed</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>驻防巡逻:判定“站稳在这一点”时在 roster.patrol_arrive_cells 之外再放宽的格数(机器与别的单位互相推挤时也能换点)</t>
+          <t>观战:点“观战”时切到的速度(2 或 3;复用统一时钟的倍速档)</t>
         </is>
       </c>
     </row>
@@ -7622,15 +7622,15 @@
       <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
-          <t>roster.patrol_retry_seconds</t>
+          <t>raid.spectate.follow_seconds</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>驻防巡逻:到不了的巡逻点先跳过,过这么久(游戏秒)再试一次(墙拆了 / 路通了能自动恢复;通知只发一次,直到走到过它)</t>
+          <t>观战:镜头每隔这么久(真实秒)重新看一次战斗重心</t>
         </is>
       </c>
     </row>
@@ -7638,15 +7638,15 @@
       <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
-          <t>raid.away.refresh_seconds</t>
+          <t>raid.spectate.follow_min_cells</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:远征 HUD 弹窗 / 倒计时的刷新间隔(真实秒;文字没变不重写)</t>
+          <t>观战:战斗重心离镜头焦点超过这么远(格)才飞过去(免得镜头一直抖)</t>
         </is>
       </c>
     </row>
@@ -7654,15 +7654,15 @@
       <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
-          <t>raid.away.home_refresh_seconds</t>
+          <t>raid.spectate.manual_cells</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:家园状态小窗(核心耐久 / 关键建筑 / 剩余敌人)重新汇总的间隔(真实秒;只在小窗显示时汇总)</t>
+          <t>观战:玩家自己把镜头移开超过这么远(格)就暂停跟随(点“跟随战斗”恢复)</t>
         </is>
       </c>
     </row>
@@ -7670,15 +7670,15 @@
       <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
-          <t>raid.away.perf_ms</t>
+          <t>raid.music.volume</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>性能验收:家园状态小窗汇总一次(全部建筑的类别与耐久 + 剩余敌人)的耗时上限(毫秒)</t>
+          <t>预警 / 突袭音乐的音量(乘在音乐音量设置上;占位音乐,美术批次替换)</t>
         </is>
       </c>
     </row>
@@ -7686,15 +7686,15 @@
       <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
-          <t>raid.away.decision_keep</t>
+          <t>raid.hud.refresh_seconds</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>8</v>
+        <v>0.25</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:存档里保留最近几波的选择(跳回家园 / 留在远征队;读档后同一波不再弹出)</t>
+          <t>突袭 HUD 刷新间隔(真实秒;键没变不重建)</t>
         </is>
       </c>
     </row>
@@ -7702,15 +7702,15 @@
       <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
-          <t>raid.away.status_seconds</t>
+          <t>raid.hud.perf_ms</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>6</v>
+        <v>0.2</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:小窗里选择 / 被拒提示的显示时长(真实秒)</t>
+          <t>性能验收:突袭 HUD 一次数据刷新(各波剩余敌人 / 文字)的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -7718,15 +7718,15 @@
       <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
-          <t>raid.away.core_low_ratio</t>
+          <t>defov.margin_cells</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>0.3</v>
+        <v>24</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:归还核心耐久条变红的耐久比例</t>
+          <t>防御总览:热力图范围 = 家园己方建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -7734,15 +7734,15 @@
       <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
-          <t>raid.away.march_focus_cells</t>
+          <t>defov.max_cells</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>FG8-EXP-02:远征队在星球上行军(还没进地点)时,镜头焦点离归还核心超过这么远(格)也算玩家在远征(远征决策条照常弹出;初值=归还核心覆盖半径)</t>
+          <t>防御总览:热力图最大边长(格;超出时以归还核心为中心截取)</t>
         </is>
       </c>
     </row>
@@ -7750,15 +7750,15 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>raid.away.intact_ratio</t>
+          <t>defov.weak_min_cells</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>0.999</v>
+        <v>4</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:关键建筑算“完好”的耐久比例(浮点误差内的满耐久)</t>
+          <t>防御总览:连续这么多格(沿路线 / 外围)没有火力覆盖才算一处薄弱点</t>
         </is>
       </c>
     </row>
@@ -7766,15 +7766,15 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>logistics.leak.breach_hp_ratio</t>
+          <t>defov.weak_max</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>击穿:管线件耐久掉到最大耐久 × 本值及以下(或被摧毁)就开始泄漏;维修回到本值以上算修好</t>
+          <t>防御总览:最多列出几处薄弱点(按离核心由近到远)</t>
         </is>
       </c>
     </row>
@@ -7782,15 +7782,15 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>logistics.leak.base_radius</t>
+          <t>defov.ring_extra_cells</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>液洼刚出现时的半径(米,× fg.TbFluidLeak.radiusScale)</t>
+          <t>防御总览:没有预测路线时,外围检查圈 = 建筑外接矩形半对角线 + 这么多格</t>
         </is>
       </c>
     </row>
@@ -7798,15 +7798,15 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>logistics.leak.max_radius</t>
+          <t>defov.ring_samples</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>2.6</v>
+        <v>96</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>液洼一直漏下去最大能扩到的半径(米,× radiusScale)</t>
+          <t>防御总览:外围检查圈的采样点数</t>
         </is>
       </c>
     </row>
@@ -7814,15 +7814,15 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>logistics.leak.grow_seconds</t>
+          <t>defov.refresh_seconds</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>液洼从刚出现扩到最大半径要的游戏秒(一直在漏时)</t>
+          <t>防御总览:面板开着时每隔这么久(真实秒)检查一次要不要重算覆盖(炮塔 / 建筑 / 突袭计划变了才重算)</t>
         </is>
       </c>
     </row>
@@ -7830,15 +7830,15 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>logistics.leak.fade_seconds</t>
+          <t>defov.perf_ms</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>修好管线(或冲洗 / 拆掉 / 破口两侧没有同种流体)后,液洼从当前半径缩小到消失要的游戏秒</t>
+          <t>性能验收:100 座炮塔时重算一次覆盖 + 薄弱点的耗时上限(毫秒;只在面板打开 / 防线变化时)</t>
         </is>
       </c>
     </row>
@@ -7846,15 +7846,15 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>logistics.leak.react_seconds</t>
+          <t>roster.patrol_max_points</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>液洼整片反应成残留区域(燃油遇火 = 燃烧区)后至少持续的游戏秒(与反应自己的残留时长取大)</t>
+          <t>驻防巡逻(FGR-DEF-043):一台机器的巡逻路线最多几个巡逻点(不含驻防点)</t>
         </is>
       </c>
     </row>
@@ -7862,15 +7862,15 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>logistics.leak.fire_dps</t>
+          <t>roster.patrol_arrive_cells</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>反应成的残留区域带持续伤害(燃烧)时,每游戏秒烧掉范围里管线 / 传送带 / 建筑的耐久(连锁烧毁产线)</t>
+          <t>驻防巡逻:走到巡逻点这么近(格)就去下一个点</t>
         </is>
       </c>
     </row>
@@ -7878,15 +7878,15 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>logistics.leak.fire_tick_seconds</t>
+          <t>roster.patrol_arrive_slack</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>火烧设施的结算间隔(游戏秒;每摊燃烧区按编号错开,每次扣 fire_dps × 本值;摊得开、每次对账只处理一部分燃烧区)</t>
+          <t>驻防巡逻:判定“站稳在这一点”时在 roster.patrol_arrive_cells 之外再放宽的格数(机器与别的单位互相推挤时也能换点)</t>
         </is>
       </c>
     </row>
@@ -7894,15 +7894,15 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>logistics.leak.sync_seconds</t>
+          <t>roster.patrol_retry_seconds</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>液洼对账间隔(游戏秒):击穿是否还在、半径扩散 / 消退、火烧坏范围里的设施;只看步序号,与观察无关</t>
+          <t>驻防巡逻:到不了的巡逻点先跳过,过这么久(游戏秒)再试一次(墙拆了 / 路通了能自动恢复;通知只发一次,直到走到过它)</t>
         </is>
       </c>
     </row>
@@ -7910,15 +7910,15 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>logistics.leak.max_puddles</t>
+          <t>raid.away.refresh_seconds</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>48</v>
+        <v>0.25</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>家园同时存在的液洼上限(超出的破口不再新增液洼并计数;一格管线最多一摊)</t>
+          <t>远征中家园遇袭:远征 HUD 弹窗 / 倒计时的刷新间隔(真实秒;文字没变不重写)</t>
         </is>
       </c>
     </row>
@@ -7926,15 +7926,15 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
-          <t>logistics.leak.warn_margin_cells</t>
+          <t>raid.away.home_refresh_seconds</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>泄漏起火告警:燃烧区半径外再放宽这么多格内有己方管线 / 传送带 / 建筑就发告警</t>
+          <t>远征中家园遇袭:家园状态小窗(核心耐久 / 关键建筑 / 剩余敌人)重新汇总的间隔(真实秒;只在小窗显示时汇总)</t>
         </is>
       </c>
     </row>
@@ -7942,15 +7942,15 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>logistics.leak.perf.puddles</t>
+          <t>raid.away.perf_ms</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>48</v>
+        <v>0.5</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>性能验收:同时存在的液洼数(= 上限)</t>
+          <t>性能验收:家园状态小窗汇总一次(全部建筑的类别与耐久 + 剩余敌人)的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -7958,15 +7958,15 @@
       <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
-          <t>logistics.leak.perf.sync_ms</t>
+          <t>raid.away.decision_keep</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>性能验收:48 摊液洼(含一半在燃烧)时热更层一次对账的耗时上限(毫秒)</t>
+          <t>远征中家园遇袭:存档里保留最近几波的选择(跳回家园 / 留在远征队;读档后同一波不再弹出)</t>
         </is>
       </c>
     </row>
@@ -7974,15 +7974,15 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>raid.result.wreck_per_unit</t>
+          <t>raid.away.status_seconds</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台普通攻城敌人留下几份敌方残骸(FGR-DEF-051)</t>
+          <t>远征中家园遇袭:小窗里选择 / 被拒提示的显示时长(真实秒)</t>
         </is>
       </c>
     </row>
@@ -7990,15 +7990,15 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>raid.result.wreck_per_elite</t>
+          <t>raid.away.core_low_ratio</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台精英留下几份敌方残骸</t>
+          <t>远征中家园遇袭:归还核心耐久条变红的耐久比例</t>
         </is>
       </c>
     </row>
@@ -8006,15 +8006,15 @@
       <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
-          <t>raid.result.wreck_merge_cells</t>
+          <t>raid.away.march_focus_cells</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>突袭结算:离同一波已有残骸堆多少格以内的新残骸并进那一堆(少生成地面物与搬运单)</t>
+          <t>FG8-EXP-02:远征队在星球上行军(还没进地点)时,镜头焦点离归还核心超过这么远(格)也算玩家在远征(远征决策条照常弹出;初值=归还核心覆盖半径)</t>
         </is>
       </c>
     </row>
@@ -8022,15 +8022,15 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>raid.result.wreck_pile_max</t>
+          <t>raid.away.intact_ratio</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>5</v>
+        <v>0.999</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>突袭结算:一堆残骸至多几份(一台机器一趟搬完)</t>
+          <t>远征中家园遇袭:关键建筑算“完好”的耐久比例(浮点误差内的满耐久)</t>
         </is>
       </c>
     </row>
@@ -8038,15 +8038,15 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>raid.result.piles_max</t>
+          <t>logistics.leak.breach_hp_ratio</t>
         </is>
       </c>
       <c r="C476" t="n">
-        <v>48</v>
+        <v>0.5</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>突袭结算:一次突袭至多记住几堆残骸(超出的照样落地,只是不再合并)</t>
+          <t>击穿:管线件耐久掉到最大耐久 × 本值及以下(或被摧毁)就开始泄漏;维修回到本值以上算修好</t>
         </is>
       </c>
     </row>
@@ -8054,15 +8054,15 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>raid.result.drop_module_chance</t>
+          <t>logistics.leak.base_radius</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>0.03</v>
+        <v>1.2</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台敌人掉落未解析模块的概率(FGR-DEF-051“少数情况”;低于远征,远征掉落表在 FG8-LOOT-01)</t>
+          <t>液洼刚出现时的半径(米,× fg.TbFluidLeak.radiusScale)</t>
         </is>
       </c>
     </row>
@@ -8070,15 +8070,15 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>raid.result.drop_firmware_chance</t>
+          <t>logistics.leak.max_radius</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>0.015</v>
+        <v>2.6</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台敌人掉落敌方加密固件的概率(同上)</t>
+          <t>液洼一直漏下去最大能扩到的半径(米,× radiusScale)</t>
         </is>
       </c>
     </row>
@@ -8086,15 +8086,15 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>raid.result.drop_elite_mult</t>
+          <t>logistics.leak.grow_seconds</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>突袭结算:精英的掉落概率倍率</t>
+          <t>液洼从刚出现扩到最大半径要的游戏秒(一直在漏时)</t>
         </is>
       </c>
     </row>
@@ -8102,15 +8102,15 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>raid.result.timeline_max</t>
+          <t>logistics.leak.fade_seconds</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>突袭结算:过程时间线每次至多几条(超出的计数)</t>
+          <t>修好管线(或冲洗 / 拆掉 / 破口两侧没有同种流体)后,液洼从当前半径缩小到消失要的游戏秒</t>
         </is>
       </c>
     </row>
@@ -8118,15 +8118,15 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>raid.result.losses_max</t>
+          <t>logistics.leak.react_seconds</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>突袭结算:损失明细每次至多几条(合计照常累加)</t>
+          <t>液洼整片反应成残留区域(燃油遇火 = 燃烧区)后至少持续的游戏秒(与反应自己的残留时长取大)</t>
         </is>
       </c>
     </row>
@@ -8134,15 +8134,15 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>raid.result.contrib_max</t>
+          <t>logistics.leak.fire_dps</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>突袭结算:贡献记录每次至多几个击毁者(更多的并进“其它”)</t>
+          <t>反应成的残留区域带持续伤害(燃烧)时,每游戏秒烧掉范围里管线 / 传送带 / 建筑的耐久(连锁烧毁产线)</t>
         </is>
       </c>
     </row>
@@ -8150,15 +8150,15 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>raid.result.contrib_top</t>
+          <t>logistics.leak.fire_tick_seconds</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>突袭结算 / 离家报告:贡献排行显示前几名</t>
+          <t>火烧设施的结算间隔(游戏秒;每摊燃烧区按编号错开,每次扣 fire_dps × 本值;摊得开、每次对账只处理一部分燃烧区)</t>
         </is>
       </c>
     </row>
@@ -8166,15 +8166,15 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>raid.result.route_seconds</t>
+          <t>logistics.leak.sync_seconds</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>残骸去向:每隔几游戏秒检查一次仓库里的残骸要不要送去解析台 / 回收站</t>
+          <t>液洼对账间隔(游戏秒):击穿是否还在、半径扩散 / 消退、火烧坏范围里的设施;只看步序号,与观察无关</t>
         </is>
       </c>
     </row>
@@ -8182,15 +8182,15 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>raid.result.route_batch</t>
+          <t>logistics.leak.max_puddles</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>残骸去向:一张送货单至多几份残骸</t>
+          <t>家园同时存在的液洼上限(超出的破口不再新增液洼并计数;一格管线最多一摊)</t>
         </is>
       </c>
     </row>
@@ -8198,15 +8198,15 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>raid.result.autosave_on_warning</t>
+          <t>logistics.leak.warn_margin_cells</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>突袭预警发出时自动存档(1=开;同一波只存一次;核心被摧毁后不再存)</t>
+          <t>泄漏起火告警:燃烧区半径外再放宽这么多格内有己方管线 / 传送带 / 建筑就发告警</t>
         </is>
       </c>
     </row>
@@ -8214,15 +8214,15 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>raid.result.panel_refresh_seconds</t>
+          <t>logistics.leak.perf.puddles</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>突袭历史面板:进行中的突袭每隔几真实秒重读一次</t>
+          <t>性能验收:同时存在的液洼数(= 上限)</t>
         </is>
       </c>
     </row>
@@ -8230,15 +8230,15 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>raid.result.perf_ms</t>
+          <t>logistics.leak.perf.sync_ms</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>性能验收:热更层处理一次击毁事件(残骸 / 掉落 / 贡献 / 结算记账)的平均耗时上限(毫秒)</t>
+          <t>性能验收:48 摊液洼(含一半在燃烧)时热更层一次对账的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -8246,15 +8246,15 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>difficulty.custom_min</t>
+          <t>raid.result.wreck_per_unit</t>
         </is>
       </c>
       <c r="C489" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>自定义难度:三个滑条(突袭频率 / 规模 / 预警时间倍率)的下限</t>
+          <t>突袭结算:每击毁一台普通攻城敌人留下几份敌方残骸(FGR-DEF-051)</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>difficulty.custom_max</t>
+          <t>raid.result.wreck_per_elite</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>自定义难度:三个滑条的上限</t>
+          <t>突袭结算:每击毁一台精英留下几份敌方残骸</t>
         </is>
       </c>
     </row>
@@ -8278,15 +8278,15 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>difficulty.custom_step</t>
+          <t>raid.result.wreck_merge_cells</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>自定义难度:滑条步长(存档里的值按它取整,同一设置同一字节)</t>
+          <t>突袭结算:离同一波已有残骸堆多少格以内的新残骸并进那一堆(少生成地面物与搬运单)</t>
         </is>
       </c>
     </row>
@@ -8294,15 +8294,15 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>difficulty.history_max</t>
+          <t>raid.result.wreck_pile_max</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>难度修改记录最多保留几条(更早的只留计数;开局难度与“是否离开过开局难度”永久保留)</t>
+          <t>突袭结算:一堆残骸至多几份(一台机器一趟搬完)</t>
         </is>
       </c>
     </row>
@@ -8310,15 +8310,15 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>raid.result.piles_max</t>
         </is>
       </c>
       <c r="C493" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>突袭结算:一次突袭至多记住几堆残骸(超出的照样落地,只是不再合并)</t>
         </is>
       </c>
     </row>
@@ -8326,15 +8326,15 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>raid.result.drop_module_chance</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>突袭结算:每击毁一台敌人掉落未解析模块的概率(FGR-DEF-051“少数情况”;低于远征,远征掉落表在 FG8-LOOT-01)</t>
         </is>
       </c>
     </row>
@@ -8342,15 +8342,15 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>raid.result.drop_firmware_chance</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>4</v>
+        <v>0.015</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>突袭结算:每击毁一台敌人掉落敌方加密固件的概率(同上)</t>
         </is>
       </c>
     </row>
@@ -8358,15 +8358,15 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>raid.result.drop_elite_mult</t>
         </is>
       </c>
       <c r="C496" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>突袭结算:精英的掉落概率倍率</t>
         </is>
       </c>
     </row>
@@ -8374,15 +8374,15 @@
       <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>raid.result.timeline_max</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>突袭结算:过程时间线每次至多几条(超出的计数)</t>
         </is>
       </c>
     </row>
@@ -8390,15 +8390,15 @@
       <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>raid.result.losses_max</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>突袭结算:损失明细每次至多几条(合计照常累加)</t>
         </is>
       </c>
     </row>
@@ -8406,15 +8406,15 @@
       <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>raid.result.contrib_max</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>突袭结算:贡献记录每次至多几个击毁者(更多的并进“其它”)</t>
         </is>
       </c>
     </row>
@@ -8422,15 +8422,15 @@
       <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>raid.result.contrib_top</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>突袭结算 / 离家报告:贡献排行显示前几名</t>
         </is>
       </c>
     </row>
@@ -8438,15 +8438,15 @@
       <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>raid.result.route_seconds</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>残骸去向:每隔几游戏秒检查一次仓库里的残骸要不要送去解析台 / 回收站</t>
         </is>
       </c>
     </row>
@@ -8454,15 +8454,15 @@
       <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>raid.result.route_batch</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>残骸去向:一张送货单至多几份残骸</t>
         </is>
       </c>
     </row>
@@ -8470,15 +8470,15 @@
       <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>raid.result.autosave_on_warning</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>突袭预警发出时自动存档(1=开;同一波只存一次;核心被摧毁后不再存)</t>
         </is>
       </c>
     </row>
@@ -8486,15 +8486,15 @@
       <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>raid.result.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>突袭历史面板:进行中的突袭每隔几真实秒重读一次</t>
         </is>
       </c>
     </row>
@@ -8502,15 +8502,15 @@
       <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>raid.result.perf_ms</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>500</v>
+        <v>0.05</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>性能验收:热更层处理一次击毁事件(残骸 / 掉落 / 贡献 / 结算记账)的平均耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -8518,15 +8518,15 @@
       <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>difficulty.custom_min</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>60</v>
+        <v>0.5</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>自定义难度:三个滑条(突袭频率 / 规模 / 预警时间倍率)的下限</t>
         </is>
       </c>
     </row>
@@ -8534,15 +8534,15 @@
       <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>difficulty.custom_max</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>自定义难度:三个滑条的上限</t>
         </is>
       </c>
     </row>
@@ -8550,15 +8550,15 @@
       <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>difficulty.custom_step</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>60</v>
+        <v>0.1</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>自定义难度:滑条步长(存档里的值按它取整,同一设置同一字节)</t>
         </is>
       </c>
     </row>
@@ -8566,15 +8566,15 @@
       <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>difficulty.history_max</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>难度修改记录最多保留几条(更早的只留计数;开局难度与“是否离开过开局难度”永久保留)</t>
         </is>
       </c>
     </row>
@@ -8582,15 +8582,15 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -8614,15 +8614,15 @@
       <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -8630,15 +8630,15 @@
       <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>0.02</v>
+        <v>10</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -8646,15 +8646,15 @@
       <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -8662,15 +8662,15 @@
       <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -8678,15 +8678,15 @@
       <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -8694,15 +8694,15 @@
       <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -8710,15 +8710,15 @@
       <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -8726,15 +8726,15 @@
       <c r="A519" t="inlineStr"/>
       <c r="B519" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -8742,15 +8742,15 @@
       <c r="A520" t="inlineStr"/>
       <c r="B520" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -8758,15 +8758,15 @@
       <c r="A521" t="inlineStr"/>
       <c r="B521" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -8774,15 +8774,15 @@
       <c r="A522" t="inlineStr"/>
       <c r="B522" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -8790,15 +8790,15 @@
       <c r="A523" t="inlineStr"/>
       <c r="B523" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -8806,15 +8806,15 @@
       <c r="A524" t="inlineStr"/>
       <c r="B524" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -8822,15 +8822,15 @@
       <c r="A525" t="inlineStr"/>
       <c r="B525" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -8838,15 +8838,15 @@
       <c r="A526" t="inlineStr"/>
       <c r="B526" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -8854,15 +8854,15 @@
       <c r="A527" t="inlineStr"/>
       <c r="B527" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -8870,15 +8870,15 @@
       <c r="A528" t="inlineStr"/>
       <c r="B528" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>1200</v>
+        <v>2</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -8886,15 +8886,15 @@
       <c r="A529" t="inlineStr"/>
       <c r="B529" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -8902,15 +8902,15 @@
       <c r="A530" t="inlineStr"/>
       <c r="B530" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>120</v>
+        <v>0.02</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -8918,15 +8918,15 @@
       <c r="A531" t="inlineStr"/>
       <c r="B531" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -8934,15 +8934,15 @@
       <c r="A532" t="inlineStr"/>
       <c r="B532" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -8950,15 +8950,15 @@
       <c r="A533" t="inlineStr"/>
       <c r="B533" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -8966,15 +8966,15 @@
       <c r="A534" t="inlineStr"/>
       <c r="B534" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -8982,15 +8982,15 @@
       <c r="A535" t="inlineStr"/>
       <c r="B535" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>0.5</v>
+        <v>200</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -8998,15 +8998,15 @@
       <c r="A536" t="inlineStr"/>
       <c r="B536" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -9014,15 +9014,15 @@
       <c r="A537" t="inlineStr"/>
       <c r="B537" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -9030,15 +9030,15 @@
       <c r="A538" t="inlineStr"/>
       <c r="B538" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>0.05</v>
+        <v>40</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -9046,15 +9046,15 @@
       <c r="A539" t="inlineStr"/>
       <c r="B539" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -9062,15 +9062,15 @@
       <c r="A540" t="inlineStr"/>
       <c r="B540" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -9078,15 +9078,15 @@
       <c r="A541" t="inlineStr"/>
       <c r="B541" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>100000</v>
+        <v>30</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -9094,15 +9094,15 @@
       <c r="A542" t="inlineStr"/>
       <c r="B542" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -9110,15 +9110,15 @@
       <c r="A543" t="inlineStr"/>
       <c r="B543" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -9126,15 +9126,15 @@
       <c r="A544" t="inlineStr"/>
       <c r="B544" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -9142,15 +9142,15 @@
       <c r="A545" t="inlineStr"/>
       <c r="B545" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>60</v>
+        <v>1200</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -9158,15 +9158,15 @@
       <c r="A546" t="inlineStr"/>
       <c r="B546" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -9174,15 +9174,15 @@
       <c r="A547" t="inlineStr"/>
       <c r="B547" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -9190,15 +9190,15 @@
       <c r="A548" t="inlineStr"/>
       <c r="B548" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C548" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -9206,15 +9206,15 @@
       <c r="A549" t="inlineStr"/>
       <c r="B549" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -9222,15 +9222,15 @@
       <c r="A550" t="inlineStr"/>
       <c r="B550" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C550" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -9238,15 +9238,15 @@
       <c r="A551" t="inlineStr"/>
       <c r="B551" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C551" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -9254,15 +9254,15 @@
       <c r="A552" t="inlineStr"/>
       <c r="B552" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C552" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -9270,15 +9270,15 @@
       <c r="A553" t="inlineStr"/>
       <c r="B553" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C553" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -9286,15 +9286,15 @@
       <c r="A554" t="inlineStr"/>
       <c r="B554" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C554" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -9302,15 +9302,15 @@
       <c r="A555" t="inlineStr"/>
       <c r="B555" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C555" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -9318,15 +9318,15 @@
       <c r="A556" t="inlineStr"/>
       <c r="B556" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C556" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       <c r="A557" t="inlineStr"/>
       <c r="B557" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -9350,15 +9350,15 @@
       <c r="A558" t="inlineStr"/>
       <c r="B558" t="inlineStr">
         <is>
-          <t>eco.softlock.unreachable_seconds</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C558" t="n">
-        <v>20</v>
+        <v>100000</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -9366,15 +9366,15 @@
       <c r="A559" t="inlineStr"/>
       <c r="B559" t="inlineStr">
         <is>
-          <t>env.daynight.night_start_hour</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C559" t="n">
-        <v>20.4</v>
+        <v>3</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>入夜时刻(游戏小时,0~24);初值20:24,夜晚以午夜为中心</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -9382,15 +9382,15 @@
       <c r="A560" t="inlineStr"/>
       <c r="B560" t="inlineStr">
         <is>
-          <t>env.daynight.night_hours</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C560" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>夜晚持续多少游戏小时;7.2=1x下6分钟(FG07 第10节:白天14分钟,夜晚6分钟)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -9398,15 +9398,15 @@
       <c r="A561" t="inlineStr"/>
       <c r="B561" t="inlineStr">
         <is>
-          <t>env.daynight.twilight_hours</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C561" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>黄昏/黎明过渡多少游戏小时(入夜前光照从1降到0、天亮后从0升到1;夜晚本身光照恒为0)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -9414,15 +9414,15 @@
       <c r="A562" t="inlineStr"/>
       <c r="B562" t="inlineStr">
         <is>
-          <t>env.calendar.days</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C562" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>日历面板显示今天起几个游戏日(1~14)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -9430,15 +9430,15 @@
       <c r="A563" t="inlineStr"/>
       <c r="B563" t="inlineStr">
         <is>
-          <t>env.light.night_tint_r</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C563" t="n">
-        <v>0.55</v>
+        <v>40</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>夜里主方向光的颜色(乘在场景原光色上)红分量</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -9446,15 +9446,15 @@
       <c r="A564" t="inlineStr"/>
       <c r="B564" t="inlineStr">
         <is>
-          <t>env.light.night_tint_g</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C564" t="n">
-        <v>0.65</v>
+        <v>20</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>夜里主方向光颜色绿分量</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -9462,15 +9462,15 @@
       <c r="A565" t="inlineStr"/>
       <c r="B565" t="inlineStr">
         <is>
-          <t>env.light.night_tint_b</t>
+          <t>away.machines_max</t>
         </is>
       </c>
       <c r="C565" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>夜里主方向光颜色蓝分量</t>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -9478,15 +9478,15 @@
       <c r="A566" t="inlineStr"/>
       <c r="B566" t="inlineStr">
         <is>
-          <t>env.light.apply_epsilon</t>
+          <t>alarm.jam_seconds</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>0.003</v>
+        <v>60</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>画面亮度变化小于这个数时不写光照(每帧O(1),避免黄昏时每帧改灯)</t>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
         </is>
       </c>
     </row>
@@ -9494,15 +9494,15 @@
       <c r="A567" t="inlineStr"/>
       <c r="B567" t="inlineStr">
         <is>
-          <t>env.silent.start_offset_hours</t>
+          <t>alarm.machine_wounded_fraction</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>静默夜从入夜后第几个游戏小时开始(1.6 = 22:00;开始 + 持续必须落在夜里)</t>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
         </is>
       </c>
     </row>
@@ -9510,15 +9510,15 @@
       <c r="A568" t="inlineStr"/>
       <c r="B568" t="inlineStr">
         <is>
-          <t>env.silent.duration_hours</t>
+          <t>eco.softlock.check_seconds</t>
         </is>
       </c>
       <c r="C568" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>静默夜持续多少游戏小时(FG07 第10节:4 小时 = 1x 下约 3.3 分钟)</t>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
         </is>
       </c>
     </row>
@@ -9526,15 +9526,15 @@
       <c r="A569" t="inlineStr"/>
       <c r="B569" t="inlineStr">
         <is>
-          <t>env.silent.warning_hours</t>
+          <t>eco.softlock.print_min_machines</t>
         </is>
       </c>
       <c r="C569" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>开始前多少游戏小时预警(FG07 第10节:1.2 小时 = 1x 下约 60 秒)</t>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
         </is>
       </c>
     </row>
@@ -9542,15 +9542,15 @@
       <c r="A570" t="inlineStr"/>
       <c r="B570" t="inlineStr">
         <is>
-          <t>env.silent.dim_ramp_hours</t>
+          <t>eco.softlock.print_health</t>
         </is>
       </c>
       <c r="C570" t="n">
-        <v>0.25</v>
+        <v>100</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>静默夜画面压暗的淡入 / 淡出游戏小时(纯表现)</t>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
         </is>
       </c>
     </row>
@@ -9558,15 +9558,15 @@
       <c r="A571" t="inlineStr"/>
       <c r="B571" t="inlineStr">
         <is>
-          <t>env.silent.expedition_estimate_hours</t>
+          <t>eco.softlock.core_scrap_per_minute</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>远征准备时按多少游戏小时估计远征时长(跨过静默夜就提示;12 小时 = 1x 下 10 分钟)</t>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
         </is>
       </c>
     </row>
@@ -9574,15 +9574,15 @@
       <c r="A572" t="inlineStr"/>
       <c r="B572" t="inlineStr">
         <is>
-          <t>env.silent.debris_min</t>
+          <t>eco.softlock.loop_check_seconds</t>
         </is>
       </c>
       <c r="C572" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>静默夜结束后家园出现几处风暴残骸(最少)</t>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
         </is>
       </c>
     </row>
@@ -9590,15 +9590,15 @@
       <c r="A573" t="inlineStr"/>
       <c r="B573" t="inlineStr">
         <is>
-          <t>env.silent.debris_max</t>
+          <t>eco.softlock.loop_stall_seconds</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>风暴残骸最多几处</t>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
         </is>
       </c>
     </row>
@@ -9606,15 +9606,15 @@
       <c r="A574" t="inlineStr"/>
       <c r="B574" t="inlineStr">
         <is>
-          <t>env.silent.debris_rare_chance</t>
+          <t>eco.softlock.reach_check_seconds</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>0.25</v>
+        <v>10</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>每次静默夜额外出现一处稀有残骸的概率(0~1)</t>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
         </is>
       </c>
     </row>
@@ -9622,15 +9622,15 @@
       <c r="A575" t="inlineStr"/>
       <c r="B575" t="inlineStr">
         <is>
-          <t>env.silent.debris_ring_min</t>
+          <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
       <c r="C575" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>风暴残骸离归还核心至少几格</t>
+          <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>
       </c>
     </row>
@@ -9638,15 +9638,15 @@
       <c r="A576" t="inlineStr"/>
       <c r="B576" t="inlineStr">
         <is>
-          <t>env.silent.debris_ring_max</t>
+          <t>env.daynight.night_start_hour</t>
         </is>
       </c>
       <c r="C576" t="n">
-        <v>36</v>
+        <v>20.4</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>风暴残骸离归还核心至多几格(按种子地形找空地,找不到就少放)</t>
+          <t>入夜时刻(游戏小时,0~24);初值20:24,夜晚以午夜为中心</t>
         </is>
       </c>
     </row>
@@ -9654,15 +9654,15 @@
       <c r="A577" t="inlineStr"/>
       <c r="B577" t="inlineStr">
         <is>
-          <t>env.weather.duration_min_days</t>
+          <t>env.daynight.night_hours</t>
         </is>
       </c>
       <c r="C577" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>一段恶劣天气最短持续几个游戏日(FG07 第10节:0.5~1.5)</t>
+          <t>夜晚持续多少游戏小时;7.2=1x下6分钟(FG07 第10节:白天14分钟,夜晚6分钟)</t>
         </is>
       </c>
     </row>
@@ -9670,15 +9670,15 @@
       <c r="A578" t="inlineStr"/>
       <c r="B578" t="inlineStr">
         <is>
-          <t>env.weather.duration_max_days</t>
+          <t>env.daynight.twilight_hours</t>
         </is>
       </c>
       <c r="C578" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>一段恶劣天气最长持续几个游戏日</t>
+          <t>黄昏/黎明过渡多少游戏小时(入夜前光照从1降到0、天亮后从0升到1;夜晚本身光照恒为0)</t>
         </is>
       </c>
     </row>
@@ -9686,15 +9686,15 @@
       <c r="A579" t="inlineStr"/>
       <c r="B579" t="inlineStr">
         <is>
-          <t>env.weather.first_day</t>
+          <t>env.calendar.days</t>
         </is>
       </c>
       <c r="C579" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>第一段恶劣天气最早在第几个游戏日开始(开局先让玩家站稳;FG16 节奏表另见 FG-GAP)</t>
+          <t>日历面板显示今天起几个游戏日(1~14)</t>
         </is>
       </c>
     </row>
@@ -9702,15 +9702,15 @@
       <c r="A580" t="inlineStr"/>
       <c r="B580" t="inlineStr">
         <is>
-          <t>env.weather.warning_days</t>
+          <t>env.light.night_tint_r</t>
         </is>
       </c>
       <c r="C580" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>没有天气预报情报时,恶劣天气开始前多少游戏日预警(FGR-ENV-021:0.5 日)</t>
+          <t>夜里主方向光的颜色(乘在场景原光色上)红分量</t>
         </is>
       </c>
     </row>
@@ -9718,15 +9718,15 @@
       <c r="A581" t="inlineStr"/>
       <c r="B581" t="inlineStr">
         <is>
-          <t>env.weather.forecast_days</t>
+          <t>env.light.night_tint_g</t>
         </is>
       </c>
       <c r="C581" t="n">
-        <v>3</v>
+        <v>0.65</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>有监听站 T2 的有效天气预报情报时,看得到未来几个游戏日的天气(FGR-ENV-021:3 日)</t>
+          <t>夜里主方向光颜色绿分量</t>
         </is>
       </c>
     </row>
@@ -9734,15 +9734,15 @@
       <c r="A582" t="inlineStr"/>
       <c r="B582" t="inlineStr">
         <is>
-          <t>env.weather.schedule_days</t>
+          <t>env.light.night_tint_b</t>
         </is>
       </c>
       <c r="C582" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>天气提前排定几个游戏日(必须 &gt; 预报天数,预报看得到的都已排定、写进存档)</t>
+          <t>夜里主方向光颜色蓝分量</t>
         </is>
       </c>
     </row>
@@ -9750,15 +9750,15 @@
       <c r="A583" t="inlineStr"/>
       <c r="B583" t="inlineStr">
         <is>
-          <t>env.weather.acid_pct_per_hour</t>
+          <t>env.light.apply_epsilon</t>
         </is>
       </c>
       <c r="C583" t="n">
-        <v>1</v>
+        <v>0.003</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>酸雨:露天建筑 / 传送带 / 炮塔每游戏小时损失最大耐久的百分之几(FG07 第10节:1%)</t>
+          <t>画面亮度变化小于这个数时不写光照(每帧O(1),避免黄昏时每帧改灯)</t>
         </is>
       </c>
     </row>
@@ -9766,15 +9766,15 @@
       <c r="A584" t="inlineStr"/>
       <c r="B584" t="inlineStr">
         <is>
-          <t>env.weather.damage_notify_hours</t>
+          <t>env.silent.start_offset_hours</t>
         </is>
       </c>
       <c r="C584" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>酸雨损伤的汇总通知最多每几个游戏小时一条(同一段酸雨内;摧毁另有通知)</t>
+          <t>静默夜从入夜后第几个游戏小时开始(1.6 = 22:00;开始 + 持续必须落在夜里)</t>
         </is>
       </c>
     </row>
@@ -9782,15 +9782,15 @@
       <c r="A585" t="inlineStr"/>
       <c r="B585" t="inlineStr">
         <is>
-          <t>env.weather.sand_detect_factor</t>
+          <t>env.silent.duration_hours</t>
         </is>
       </c>
       <c r="C585" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>沙暴:露天炮塔探测(开火)距离乘这个数(FG07 第10节:-20%)</t>
+          <t>静默夜持续多少游戏小时(FG07 第10节:4 小时 = 1x 下约 3.3 分钟)</t>
         </is>
       </c>
     </row>
@@ -9798,15 +9798,15 @@
       <c r="A586" t="inlineStr"/>
       <c r="B586" t="inlineStr">
         <is>
-          <t>env.weather.cold_dissipation_mult</t>
+          <t>env.silent.warning_hours</t>
         </is>
       </c>
       <c r="C586" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>寒潮:家园里武器散热乘这个数(FG07 第10节:散热 +30%)</t>
+          <t>开始前多少游戏小时预警(FG07 第10节:1.2 小时 = 1x 下约 60 秒)</t>
         </is>
       </c>
     </row>
@@ -9814,15 +9814,15 @@
       <c r="A587" t="inlineStr"/>
       <c r="B587" t="inlineStr">
         <is>
-          <t>env.weather.sand_fog_density</t>
+          <t>env.silent.dim_ramp_hours</t>
         </is>
       </c>
       <c r="C587" t="n">
-        <v>0.018</v>
+        <v>0.25</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>沙暴画面:指数雾浓度(纯表现;乘玩家的天气视觉效果强度)</t>
+          <t>静默夜画面压暗的淡入 / 淡出游戏小时(纯表现)</t>
         </is>
       </c>
     </row>
@@ -9830,15 +9830,15 @@
       <c r="A588" t="inlineStr"/>
       <c r="B588" t="inlineStr">
         <is>
-          <t>env.weather.fx_ramp_hours</t>
+          <t>env.silent.expedition_estimate_hours</t>
         </is>
       </c>
       <c r="C588" t="n">
-        <v>0.3</v>
+        <v>12</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>天气画面淡入 / 淡出的游戏小时(纯表现)</t>
+          <t>远征准备时按多少游戏小时估计远征时长(跨过静默夜就提示;12 小时 = 1x 下 10 分钟)</t>
         </is>
       </c>
     </row>
@@ -9846,15 +9846,15 @@
       <c r="A589" t="inlineStr"/>
       <c r="B589" t="inlineStr">
         <is>
-          <t>env.weather.particles_max</t>
+          <t>env.silent.debris_min</t>
         </is>
       </c>
       <c r="C589" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>雨 / 沙 / 雪粒子最多同时几颗(满强度;ART-PERF-BUDGET 占位,乘视觉效果强度)</t>
+          <t>静默夜结束后家园出现几处风暴残骸(最少)</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       <c r="A590" t="inlineStr"/>
       <c r="B590" t="inlineStr">
         <is>
-          <t>env.roof.block_cells</t>
+          <t>env.silent.debris_max</t>
         </is>
       </c>
       <c r="C590" t="n">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>顶棚一块的边长(格;FGR-ENV-030:4×4)</t>
+          <t>风暴残骸最多几处</t>
         </is>
       </c>
     </row>
@@ -9878,15 +9878,15 @@
       <c r="A591" t="inlineStr"/>
       <c r="B591" t="inlineStr">
         <is>
-          <t>env.roof.max_blocks_per_drag</t>
+          <t>env.silent.debris_rare_chance</t>
         </is>
       </c>
       <c r="C591" t="n">
-        <v>64</v>
+        <v>0.25</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>一次拖拽最多铺几块顶棚(超出给原因,不静默截断)</t>
+          <t>每次静默夜额外出现一处稀有残骸的概率(0~1)</t>
         </is>
       </c>
     </row>
@@ -9894,15 +9894,15 @@
       <c r="A592" t="inlineStr"/>
       <c r="B592" t="inlineStr">
         <is>
-          <t>env.roof.build_seconds_per_block</t>
+          <t>env.silent.debris_ring_min</t>
         </is>
       </c>
       <c r="C592" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>机器施工一块顶棚要几游戏秒</t>
+          <t>风暴残骸离归还核心至少几格</t>
         </is>
       </c>
     </row>
@@ -9910,15 +9910,15 @@
       <c r="A593" t="inlineStr"/>
       <c r="B593" t="inlineStr">
         <is>
-          <t>purify.hours_per_level</t>
+          <t>env.silent.debris_ring_max</t>
         </is>
       </c>
       <c r="C593" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>净化速度:每格每 N 个游戏小时降 1 级(FG07 第 10 节初值 N = 2;按持续有电有冷却液的游戏时间累计,暂停 / 倍速同比例)</t>
+          <t>风暴残骸离归还核心至多几格(按种子地形找空地,找不到就少放)</t>
         </is>
       </c>
     </row>
@@ -9926,15 +9926,15 @@
       <c r="A594" t="inlineStr"/>
       <c r="B594" t="inlineStr">
         <is>
-          <t>purify.coolant_mult_t2</t>
+          <t>env.weather.duration_min_days</t>
         </is>
       </c>
       <c r="C594" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>净化塔 T2 的冷却液用量 = T1(fg.TbProducer.fluidLpm)× 本值</t>
+          <t>一段恶劣天气最短持续几个游戏日(FG07 第10节:0.5~1.5)</t>
         </is>
       </c>
     </row>
@@ -9942,15 +9942,15 @@
       <c r="A595" t="inlineStr"/>
       <c r="B595" t="inlineStr">
         <is>
-          <t>purify.coolant_mult_t3</t>
+          <t>env.weather.duration_max_days</t>
         </is>
       </c>
       <c r="C595" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>净化塔 T3 的冷却液用量 = T1 × 本值</t>
+          <t>一段恶劣天气最长持续几个游戏日</t>
         </is>
       </c>
     </row>
@@ -9958,15 +9958,15 @@
       <c r="A596" t="inlineStr"/>
       <c r="B596" t="inlineStr">
         <is>
-          <t>purify.rich_ore.radius</t>
+          <t>env.weather.first_day</t>
         </is>
       </c>
       <c r="C596" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>归还 20,000 格的奖励“稀土富矿”:揭示(探索)的圆半径,也是富矿的范围(格;范围内压在稀土矿脉上的提取钻产出加倍)</t>
+          <t>第一段恶劣天气最早在第几个游戏日开始(开局先让玩家站稳;FG16 节奏表另见 FG-GAP)</t>
         </is>
       </c>
     </row>
@@ -9974,15 +9974,15 @@
       <c r="A597" t="inlineStr"/>
       <c r="B597" t="inlineStr">
         <is>
-          <t>purify.rich_ore.yield_mult</t>
+          <t>env.weather.warning_days</t>
         </is>
       </c>
       <c r="C597" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>稀土富矿范围内的提取钻每份产出 × 本值(整数)</t>
+          <t>没有天气预报情报时,恶劣天气开始前多少游戏日预警(FGR-ENV-021:0.5 日)</t>
         </is>
       </c>
     </row>
@@ -9990,15 +9990,15 @@
       <c r="A598" t="inlineStr"/>
       <c r="B598" t="inlineStr">
         <is>
-          <t>purify.rich_ore.search_radius</t>
+          <t>env.weather.forecast_days</t>
         </is>
       </c>
       <c r="C598" t="n">
-        <v>400</v>
+        <v>3</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>找稀土富矿的最远距离(格,从归还核心算;先按世界规划层的稀土矿带找,找不到再按种子粗采样)</t>
+          <t>有监听站 T2 的有效天气预报情报时,看得到未来几个游戏日的天气(FGR-ENV-021:3 日)</t>
         </is>
       </c>
     </row>
@@ -10006,15 +10006,15 @@
       <c r="A599" t="inlineStr"/>
       <c r="B599" t="inlineStr">
         <is>
-          <t>purify.rich_ore.search_step</t>
+          <t>env.weather.schedule_days</t>
         </is>
       </c>
       <c r="C599" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>粗采样的步长(格;只在规划层没有稀土矿带时用)</t>
+          <t>天气提前排定几个游戏日(必须 &gt; 预报天数,预报看得到的都已排定、写进存档)</t>
         </is>
       </c>
     </row>
@@ -10022,15 +10022,15 @@
       <c r="A600" t="inlineStr"/>
       <c r="B600" t="inlineStr">
         <is>
-          <t>explore.trail_gap_max</t>
+          <t>env.weather.acid_pct_per_hour</t>
         </is>
       </c>
       <c r="C600" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>机器两次被检查之间走过的距离超过这么多格就当作“瞬移”(出厂 / 读档 / 跳转),不沿路补探索(格)</t>
+          <t>酸雨:露天建筑 / 传送带 / 炮塔每游戏小时损失最大耐久的百分之几(FG07 第10节:1%)</t>
         </is>
       </c>
     </row>
@@ -10038,15 +10038,15 @@
       <c r="A601" t="inlineStr"/>
       <c r="B601" t="inlineStr">
         <is>
-          <t>explore.trail_step</t>
+          <t>env.weather.damage_notify_hours</t>
         </is>
       </c>
       <c r="C601" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>沿机器走过的路补探索的采样间距(格;不大于机器探索半径的一半,保证路上不留缝)</t>
+          <t>酸雨损伤的汇总通知最多每几个游戏小时一条(同一段酸雨内;摧毁另有通知)</t>
         </is>
       </c>
     </row>
@@ -10054,15 +10054,15 @@
       <c r="A602" t="inlineStr"/>
       <c r="B602" t="inlineStr">
         <is>
-          <t>relic.pick_radius</t>
+          <t>env.weather.sand_detect_factor</t>
         </is>
       </c>
       <c r="C602" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>右键 / 悬停离遗迹点多近算点中它(格,欧氏距离)</t>
+          <t>沙暴:露天炮塔探测(开火)距离乘这个数(FG07 第10节:-20%)</t>
         </is>
       </c>
     </row>
@@ -10070,15 +10070,15 @@
       <c r="A603" t="inlineStr"/>
       <c r="B603" t="inlineStr">
         <is>
-          <t>relic.notify_max</t>
+          <t>env.weather.cold_dissipation_mult</t>
         </is>
       </c>
       <c r="C603" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>一次揭开的一大片里最多逐个发几条“发现遗迹点”通知(其余合成一条“又发现 N 个”)</t>
+          <t>寒潮:家园里武器散热乘这个数(FG07 第10节:散热 +30%)</t>
         </is>
       </c>
     </row>
@@ -10086,15 +10086,15 @@
       <c r="A604" t="inlineStr"/>
       <c r="B604" t="inlineStr">
         <is>
-          <t>exp.check.severe_health_pct</t>
+          <t>env.weather.sand_fog_density</t>
         </is>
       </c>
       <c r="C604" t="n">
-        <v>0.25</v>
+        <v>0.018</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>机器生命低于最大值的这个比例=重伤提醒(可以派,后果写明;0~1)</t>
+          <t>沙暴画面:指数雾浓度(纯表现;乘玩家的天气视觉效果强度)</t>
         </is>
       </c>
     </row>
@@ -10102,15 +10102,15 @@
       <c r="A605" t="inlineStr"/>
       <c r="B605" t="inlineStr">
         <is>
-          <t>exp.check.warn_health_pct</t>
+          <t>env.weather.fx_ramp_hours</t>
         </is>
       </c>
       <c r="C605" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>机器生命低于最大值的这个比例=伤势偏重提醒(0~1,应不低于重伤线)</t>
+          <t>天气画面淡入 / 淡出的游戏小时(纯表现)</t>
         </is>
       </c>
     </row>
@@ -10118,15 +10118,15 @@
       <c r="A606" t="inlineStr"/>
       <c r="B606" t="inlineStr">
         <is>
-          <t>exp.team.color_count</t>
+          <t>env.weather.particles_max</t>
         </is>
       </c>
       <c r="C606" t="n">
-        <v>8</v>
+        <v>600</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>远征队可选颜色种数(颜色表见界面,1~8)</t>
+          <t>雨 / 沙 / 雪粒子最多同时几颗(满强度;ART-PERF-BUDGET 占位,乘视觉效果强度)</t>
         </is>
       </c>
     </row>
@@ -10134,15 +10134,15 @@
       <c r="A607" t="inlineStr"/>
       <c r="B607" t="inlineStr">
         <is>
-          <t>squad.group_double_tap_seconds</t>
+          <t>env.roof.block_cells</t>
         </is>
       </c>
       <c r="C607" t="n">
-        <v>0.35</v>
+        <v>4</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>连按两次同一编组键的最长间隔(真实秒;镜头飞到编组,FG13 第5节)</t>
+          <t>顶棚一块的边长(格;FGR-ENV-030:4×4)</t>
         </is>
       </c>
     </row>
@@ -10150,15 +10150,15 @@
       <c r="A608" t="inlineStr"/>
       <c r="B608" t="inlineStr">
         <is>
-          <t>expedition.march.speed.wheel</t>
+          <t>env.roof.max_blocks_per_drag</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>行军速度:搬运轮式底盘(格/秒,FG08 初值);远征队速度取最慢的那台</t>
+          <t>一次拖拽最多铺几块顶棚(超出给原因,不静默截断)</t>
         </is>
       </c>
     </row>
@@ -10166,15 +10166,15 @@
       <c r="A609" t="inlineStr"/>
       <c r="B609" t="inlineStr">
         <is>
-          <t>expedition.march.speed.hover</t>
+          <t>env.roof.build_seconds_per_block</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>行军速度:维修悬浮底盘(格/秒,FG08 初值)</t>
+          <t>机器施工一块顶棚要几游戏秒</t>
         </is>
       </c>
     </row>
@@ -10182,15 +10182,15 @@
       <c r="A610" t="inlineStr"/>
       <c r="B610" t="inlineStr">
         <is>
-          <t>expedition.march.speed.track</t>
+          <t>purify.hours_per_level</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>行军速度:战斗履带底盘(格/秒,FG08 初值;系统占位机按此计)</t>
+          <t>净化速度:每格每 N 个游戏小时降 1 级(FG07 第 10 节初值 N = 2;按持续有电有冷却液的游戏时间累计,暂停 / 倍速同比例)</t>
         </is>
       </c>
     </row>
@@ -10198,15 +10198,15 @@
       <c r="A611" t="inlineStr"/>
       <c r="B611" t="inlineStr">
         <is>
-          <t>expedition.march.arrive_radius</t>
+          <t>purify.coolant_mult_t2</t>
         </is>
       </c>
       <c r="C611" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>全部存活成员走到目的地锚点这么近(格)就算到达,进入远征地点</t>
+          <t>净化塔 T2 的冷却液用量 = T1(fg.TbProducer.fluidLpm)× 本值</t>
         </is>
       </c>
     </row>
@@ -10214,15 +10214,15 @@
       <c r="A612" t="inlineStr"/>
       <c r="B612" t="inlineStr">
         <is>
-          <t>expedition.march.home_radius</t>
+          <t>purify.coolant_mult_t3</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>返程的成员全部走到归还核心这么近(格)就算回到家园</t>
+          <t>净化塔 T3 的冷却液用量 = T1 × 本值</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10230,7 @@
       <c r="A613" t="inlineStr"/>
       <c r="B613" t="inlineStr">
         <is>
-          <t>expedition.march.engage_radius</t>
+          <t>purify.rich_ore.radius</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>成员这么近(格)有敌对单位=交战中(远征队状态)</t>
+          <t>归还 20,000 格的奖励“稀土富矿”:揭示(探索)的圆半径,也是富矿的范围(格;范围内压在稀土矿脉上的提取钻产出加倍)</t>
         </is>
       </c>
     </row>
@@ -10246,15 +10246,15 @@
       <c r="A614" t="inlineStr"/>
       <c r="B614" t="inlineStr">
         <is>
-          <t>expedition.encounter.radius_cells</t>
+          <t>purify.rich_ore.yield_mult</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>行军途中敌方据点/巡逻/突袭队伍进入队伍这么近(格)就提示一次</t>
+          <t>稀土富矿范围内的提取钻每份产出 × 本值(整数)</t>
         </is>
       </c>
     </row>
@@ -10262,15 +10262,15 @@
       <c r="A615" t="inlineStr"/>
       <c r="B615" t="inlineStr">
         <is>
-          <t>expedition.march.arrival_retry_seconds</t>
+          <t>purify.rich_ore.search_radius</t>
         </is>
       </c>
       <c r="C615" t="n">
-        <v>15</v>
+        <v>400</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>到达失败(地点不开放/存档失败/载入出错已回滚)后,队伍照最后的“前进”隔这么久(游戏秒)自动重试进入</t>
+          <t>找稀土富矿的最远距离(格,从归还核心算;先按世界规划层的稀土矿带找,找不到再按种子粗采样)</t>
         </is>
       </c>
     </row>
@@ -10278,15 +10278,15 @@
       <c r="A616" t="inlineStr"/>
       <c r="B616" t="inlineStr">
         <is>
-          <t>expedition.anchor.max_attempts</t>
+          <t>purify.rich_ore.search_step</t>
         </is>
       </c>
       <c r="C616" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>锚点可达性校验的最多试探次数(每次换一个由种子决定的候选点)</t>
+          <t>粗采样的步长(格;只在规划层没有稀土矿带时用)</t>
         </is>
       </c>
     </row>
@@ -10294,15 +10294,15 @@
       <c r="A617" t="inlineStr"/>
       <c r="B617" t="inlineStr">
         <is>
-          <t>expedition.anchor.jitter_deg</t>
+          <t>explore.trail_gap_max</t>
         </is>
       </c>
       <c r="C617" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>锚点候选方向:从领地中心朝归还核心的方向左右各偏这么多度以内(由种子决定)</t>
+          <t>机器两次被检查之间走过的距离超过这么多格就当作“瞬移”(出厂 / 读档 / 跳转),不沿路补探索(格)</t>
         </is>
       </c>
     </row>
@@ -10310,15 +10310,15 @@
       <c r="A618" t="inlineStr"/>
       <c r="B618" t="inlineStr">
         <is>
-          <t>expedition.anchor.radial_min</t>
+          <t>explore.trail_step</t>
         </is>
       </c>
       <c r="C618" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>锚点候选离领地中心的最小距离(领地半径的倍数)</t>
+          <t>沿机器走过的路补探索的采样间距(格;不大于机器探索半径的一半,保证路上不留缝)</t>
         </is>
       </c>
     </row>
@@ -10326,15 +10326,15 @@
       <c r="A619" t="inlineStr"/>
       <c r="B619" t="inlineStr">
         <is>
-          <t>expedition.anchor.radial_max</t>
+          <t>relic.pick_radius</t>
         </is>
       </c>
       <c r="C619" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>锚点候选离领地中心的最大距离(领地半径的倍数)</t>
+          <t>右键 / 悬停离遗迹点多近算点中它(格,欧氏距离)</t>
         </is>
       </c>
     </row>
@@ -10342,15 +10342,15 @@
       <c r="A620" t="inlineStr"/>
       <c r="B620" t="inlineStr">
         <is>
-          <t>expedition.anchor.fallback_distance.city</t>
+          <t>relic.notify_max</t>
         </is>
       </c>
       <c r="C620" t="n">
-        <v>300</v>
+        <v>6</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>没有规划层的旧原型世界:破碎都市锚点离核心的距离(格)</t>
+          <t>一次揭开的一大片里最多逐个发几条“发现遗迹点”通知(其余合成一条“又发现 N 个”)</t>
         </is>
       </c>
     </row>
@@ -10358,15 +10358,15 @@
       <c r="A621" t="inlineStr"/>
       <c r="B621" t="inlineStr">
         <is>
-          <t>expedition.anchor.fallback_distance.foundry</t>
+          <t>exp.check.severe_health_pct</t>
         </is>
       </c>
       <c r="C621" t="n">
-        <v>600</v>
+        <v>0.25</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>没有规划层的旧原型世界:铸造前哨锚点离核心的距离(格)</t>
+          <t>机器生命低于最大值的这个比例=重伤提醒(可以派,后果写明;0~1)</t>
         </is>
       </c>
     </row>
@@ -10374,15 +10374,15 @@
       <c r="A622" t="inlineStr"/>
       <c r="B622" t="inlineStr">
         <is>
-          <t>territory.banner_seconds</t>
+          <t>exp.check.warn_health_pct</t>
         </is>
       </c>
       <c r="C622" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>进入 / 离开领地时屏幕上方名称提示停留多久(真实秒)</t>
+          <t>机器生命低于最大值的这个比例=伤势偏重提醒(0~1,应不低于重伤线)</t>
         </is>
       </c>
     </row>
@@ -10390,15 +10390,15 @@
       <c r="A623" t="inlineStr"/>
       <c r="B623" t="inlineStr">
         <is>
-          <t>territory.belt_warn_cells</t>
+          <t>exp.team.color_count</t>
         </is>
       </c>
       <c r="C623" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>镜头 / 接入的机器离外圈危害带这么近(格)时提示“接近危害带”</t>
+          <t>远征队可选颜色种数(颜色表见界面,1~8)</t>
         </is>
       </c>
     </row>
@@ -10406,15 +10406,15 @@
       <c r="A624" t="inlineStr"/>
       <c r="B624" t="inlineStr">
         <is>
-          <t>territory.presence_refresh_seconds</t>
+          <t>squad.group_double_tap_seconds</t>
         </is>
       </c>
       <c r="C624" t="n">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>远征队“进入领地”提示的检查周期(游戏秒;与行军提示同一节拍)</t>
+          <t>连按两次同一编组键的最长间隔(真实秒;镜头飞到编组,FG13 第5节)</t>
         </is>
       </c>
     </row>
@@ -10422,15 +10422,15 @@
       <c r="A625" t="inlineStr"/>
       <c r="B625" t="inlineStr">
         <is>
-          <t>interior.pick_radius</t>
+          <t>expedition.march.speed.wheel</t>
         </is>
       </c>
       <c r="C625" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>左键点在离入口这么近(格)的地方算点中入口(打开进入面板)</t>
+          <t>行军速度:搬运轮式底盘(格/秒,FG08 初值);远征队速度取最慢的那台</t>
         </is>
       </c>
     </row>
@@ -10438,15 +10438,15 @@
       <c r="A626" t="inlineStr"/>
       <c r="B626" t="inlineStr">
         <is>
-          <t>interior.exit_radius</t>
+          <t>expedition.march.speed.hover</t>
         </is>
       </c>
       <c r="C626" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>室内:机器离出口这么近(格)才能离开</t>
+          <t>行军速度:维修悬浮底盘(格/秒,FG08 初值)</t>
         </is>
       </c>
     </row>
@@ -10454,15 +10454,15 @@
       <c r="A627" t="inlineStr"/>
       <c r="B627" t="inlineStr">
         <is>
-          <t>interior.transition_seconds</t>
+          <t>expedition.march.speed.track</t>
         </is>
       </c>
       <c r="C627" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>进出室内的画面过渡(真实秒;过渡期间世界照常运行)</t>
+          <t>行军速度:战斗履带底盘(格/秒,FG08 初值;系统占位机按此计)</t>
         </is>
       </c>
     </row>
@@ -10470,15 +10470,15 @@
       <c r="A628" t="inlineStr"/>
       <c r="B628" t="inlineStr">
         <is>
-          <t>interior.spawn_spacing</t>
+          <t>expedition.march.arrive_radius</t>
         </is>
       </c>
       <c r="C628" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>进出室内时机器在入口 / 出口旁排开的间距(格)</t>
+          <t>全部存活成员走到目的地锚点这么近(格)就算到达,进入远征地点</t>
         </is>
       </c>
     </row>
@@ -10486,15 +10486,15 @@
       <c r="A629" t="inlineStr"/>
       <c r="B629" t="inlineStr">
         <is>
-          <t>anchor.reach_max_attempts</t>
+          <t>expedition.march.home_radius</t>
         </is>
       </c>
       <c r="C629" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>锚点可达性校验:一条寻路没交回结果时最多再发几次(之后记为失败并写日志)</t>
+          <t>返程的成员全部走到归还核心这么近(格)就算回到家园</t>
         </is>
       </c>
     </row>
@@ -10502,15 +10502,15 @@
       <c r="A630" t="inlineStr"/>
       <c r="B630" t="inlineStr">
         <is>
-          <t>outpost.bucket_cells</t>
+          <t>expedition.march.engage_radius</t>
         </is>
       </c>
       <c r="C630" t="n">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>据点空间索引的桶边长(格;地图 / 星球标记 / 休眠判定按桶粗筛)</t>
+          <t>成员这么近(格)有敌对单位=交战中(远征队状态)</t>
         </is>
       </c>
     </row>
@@ -10518,15 +10518,15 @@
       <c r="A631" t="inlineStr"/>
       <c r="B631" t="inlineStr">
         <is>
-          <t>outer.reveal_margin_cells</t>
+          <t>expedition.encounter.radius_cells</t>
         </is>
       </c>
       <c r="C631" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>外延区:揭开一片区域时,圆外再多登记这么多格内的零散前哨与缓存(按需生成,FGR-GEN-040)</t>
+          <t>行军途中敌方据点/巡逻/突袭队伍进入队伍这么近(格)就提示一次</t>
         </is>
       </c>
     </row>
@@ -10534,15 +10534,15 @@
       <c r="A632" t="inlineStr"/>
       <c r="B632" t="inlineStr">
         <is>
-          <t>outer.cache_scrap_base</t>
+          <t>expedition.march.arrival_retry_seconds</t>
         </is>
       </c>
       <c r="C632" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>外延区资源缓存的废料基数</t>
+          <t>到达失败(地点不开放/存档失败/载入出错已回滚)后,队伍照最后的“前进”隔这么久(游戏秒)自动重试进入</t>
         </is>
       </c>
     </row>
@@ -10550,15 +10550,15 @@
       <c r="A633" t="inlineStr"/>
       <c r="B633" t="inlineStr">
         <is>
-          <t>outer.cache_scrap_per_1000</t>
+          <t>expedition.anchor.max_attempts</t>
         </is>
       </c>
       <c r="C633" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>外延区资源缓存每离核心 1000 格多给多少废料(越远奖励越高)</t>
+          <t>锚点可达性校验的最多试探次数(每次换一个由种子决定的候选点)</t>
         </is>
       </c>
     </row>
@@ -10566,15 +10566,15 @@
       <c r="A634" t="inlineStr"/>
       <c r="B634" t="inlineStr">
         <is>
-          <t>outer.cache_seconds</t>
+          <t>expedition.anchor.jitter_deg</t>
         </is>
       </c>
       <c r="C634" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>外延区资源缓存的打开工期(游戏秒)</t>
+          <t>锚点候选方向:从领地中心朝归还核心的方向左右各偏这么多度以内(由种子决定)</t>
         </is>
       </c>
     </row>
@@ -10582,15 +10582,15 @@
       <c r="A635" t="inlineStr"/>
       <c r="B635" t="inlineStr">
         <is>
-          <t>scatter.cache_scrap</t>
+          <t>expedition.anchor.radial_min</t>
         </is>
       </c>
       <c r="C635" t="n">
-        <v>50</v>
+        <v>0.7</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>领地之间(零散)资源缓存的废料</t>
+          <t>锚点候选离领地中心的最小距离(领地半径的倍数)</t>
         </is>
       </c>
     </row>
@@ -10598,15 +10598,15 @@
       <c r="A636" t="inlineStr"/>
       <c r="B636" t="inlineStr">
         <is>
-          <t>signal.coverage.site_root_mode</t>
+          <t>expedition.anchor.radial_max</t>
         </is>
       </c>
       <c r="C636" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>远征地点内部覆盖的根:1=远征接入点(恒连通,沿用 FG1-SIG-07);2=星球上的锚点必须在与核心连通的覆盖里(DEBT-FG8EXP02-02,待用户定是否切到 2)</t>
+          <t>锚点候选离领地中心的最大距离(领地半径的倍数)</t>
         </is>
       </c>
     </row>
@@ -10614,15 +10614,15 @@
       <c r="A637" t="inlineStr"/>
       <c r="B637" t="inlineStr">
         <is>
-          <t>territory.control.sync_seconds</t>
+          <t>expedition.anchor.fallback_distance.city</t>
         </is>
       </c>
       <c r="C637" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>领地控制度 / 状态 / 增援 / 精英残部 / 骚扰的检查周期(游戏秒;只看步序号,与观察无关)</t>
+          <t>没有规划层的旧原型世界:破碎都市锚点离核心的距离(格)</t>
         </is>
       </c>
     </row>
@@ -10630,15 +10630,15 @@
       <c r="A638" t="inlineStr"/>
       <c r="B638" t="inlineStr">
         <is>
-          <t>territory.control.reclaim_below</t>
+          <t>expedition.anchor.fallback_distance.foundry</t>
         </is>
       </c>
       <c r="C638" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>平定中的领地控制度降到这个值以下(不含)时变为已收复(FGR-EXP-022 初值 20)</t>
+          <t>没有规划层的旧原型世界:铸造前哨锚点离核心的距离(格)</t>
         </is>
       </c>
     </row>
@@ -10646,15 +10646,15 @@
       <c r="A639" t="inlineStr"/>
       <c r="B639" t="inlineStr">
         <is>
-          <t>territory.reinforce.interval_days</t>
+          <t>territory.banner_seconds</t>
         </is>
       </c>
       <c r="C639" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>首领被击败前,阵营每几个游戏日增援一次(FGR-EXP-022 初值 3;被摧毁的据点有可能重建)</t>
+          <t>进入 / 离开领地时屏幕上方名称提示停留多久(真实秒)</t>
         </is>
       </c>
     </row>
@@ -10662,15 +10662,15 @@
       <c r="A640" t="inlineStr"/>
       <c r="B640" t="inlineStr">
         <is>
-          <t>territory.reinforce.rebuild_chance</t>
+          <t>territory.belt_warn_cells</t>
         </is>
       </c>
       <c r="C640" t="n">
-        <v>0.5</v>
+        <v>40</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>每次增援时,每个被摧毁的领地据点重建的概率(按世界种子 + 领地 + 第几次增援 + 据点确定)</t>
+          <t>镜头 / 接入的机器离外圈危害带这么近(格)时提示“接近危害带”</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10678,7 @@
       <c r="A641" t="inlineStr"/>
       <c r="B641" t="inlineStr">
         <is>
-          <t>territory.reinforce.rebuild_max</t>
+          <t>territory.presence_refresh_seconds</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>每次增援每个领地最多重建几个据点</t>
+          <t>远征队“进入领地”提示的检查周期(游戏秒;与行军提示同一节拍)</t>
         </is>
       </c>
     </row>
@@ -10694,15 +10694,15 @@
       <c r="A642" t="inlineStr"/>
       <c r="B642" t="inlineStr">
         <is>
-          <t>territory.reinforce.rebuild_garrison_ratio</t>
+          <t>interior.pick_radius</t>
         </is>
       </c>
       <c r="C642" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>重建的据点驻军 = 上限 × 这个比例(至少 1)</t>
+          <t>左键点在离入口这么近(格)的地方算点中入口(打开进入面板)</t>
         </is>
       </c>
     </row>
@@ -10710,15 +10710,15 @@
       <c r="A643" t="inlineStr"/>
       <c r="B643" t="inlineStr">
         <is>
-          <t>territory.reinforce.block_radius_cells</t>
+          <t>interior.exit_radius</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>据点这么近(格)内有己方建筑或机器时不重建(不在玩家眼前凭空出现)</t>
+          <t>室内:机器离出口这么近(格)才能离开</t>
         </is>
       </c>
     </row>
@@ -10726,15 +10726,15 @@
       <c r="A644" t="inlineStr"/>
       <c r="B644" t="inlineStr">
         <is>
-          <t>territory.elite.interval_days</t>
+          <t>interior.transition_seconds</t>
         </is>
       </c>
       <c r="C644" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>已收复的领地里精英残部每几个游戏日刷新一次(FGR-EXP-022 初值 7;上一批没被击溃时不叠加)</t>
+          <t>进出室内的画面过渡(真实秒;过渡期间世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -10742,15 +10742,15 @@
       <c r="A645" t="inlineStr"/>
       <c r="B645" t="inlineStr">
         <is>
-          <t>territory.harass.interval_hours</t>
+          <t>interior.spawn_spacing</t>
         </is>
       </c>
       <c r="C645" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>在敌控 / 平定中的领地里有己方建筑时,每几个游戏小时从最近的据点派一支骚扰部队</t>
+          <t>进出室内时机器在入口 / 出口旁排开的间距(格)</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       <c r="A646" t="inlineStr"/>
       <c r="B646" t="inlineStr">
         <is>
-          <t>territory.harass.units</t>
+          <t>anchor.reach_max_attempts</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>骚扰部队台数(不超过据点驻军 - 1)</t>
+          <t>锚点可达性校验:一条寻路没交回结果时最多再发几次(之后记为失败并写日志)</t>
         </is>
       </c>
     </row>
@@ -10774,15 +10774,15 @@
       <c r="A647" t="inlineStr"/>
       <c r="B647" t="inlineStr">
         <is>
-          <t>territory.engage.radius_cells</t>
+          <t>outpost.bucket_cells</t>
         </is>
       </c>
       <c r="C647" t="n">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>己方机器走到据点 / 巡逻这么近(格)时,驻军 / 巡逻就地展开迎战</t>
+          <t>据点空间索引的桶边长(格;地图 / 星球标记 / 休眠判定按桶粗筛)</t>
         </is>
       </c>
     </row>
@@ -10790,15 +10790,15 @@
       <c r="A648" t="inlineStr"/>
       <c r="B648" t="inlineStr">
         <is>
-          <t>territory.engage.scout_nest_mode</t>
+          <t>outer.reveal_margin_cells</t>
         </is>
       </c>
       <c r="C648" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>家园区侦察巢是否也迎战:1=不迎战(初值,M1～M7 已验收的家园区节奏不变);2=与领地据点同一套迎战(由 FG9-BAL-01 第一幕平衡决定,DEBT-FG8EXP03-07)</t>
+          <t>外延区:揭开一片区域时,圆外再多登记这么多格内的零散前哨与缓存(按需生成,FGR-GEN-040)</t>
         </is>
       </c>
     </row>
@@ -10806,15 +10806,15 @@
       <c r="A649" t="inlineStr"/>
       <c r="B649" t="inlineStr">
         <is>
-          <t>territory.engage.regroup_seconds</t>
+          <t>outer.cache_scrap_base</t>
         </is>
       </c>
       <c r="C649" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>迎战中附近没有己方机器满这么久(游戏秒),幸存者收拢回据点 / 巡逻(人数按幸存者)</t>
+          <t>外延区资源缓存的废料基数</t>
         </is>
       </c>
     </row>
@@ -10822,15 +10822,15 @@
       <c r="A650" t="inlineStr"/>
       <c r="B650" t="inlineStr">
         <is>
-          <t>territory.engage.max_seconds</t>
+          <t>outer.cache_scrap_per_1000</t>
         </is>
       </c>
       <c r="C650" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>迎战僵持上限(游戏秒):到点收拢,之后这么久内不再展开(不在原地反复展开)</t>
+          <t>外延区资源缓存每离核心 1000 格多给多少废料(越远奖励越高)</t>
         </is>
       </c>
     </row>
@@ -10838,15 +10838,15 @@
       <c r="A651" t="inlineStr"/>
       <c r="B651" t="inlineStr">
         <is>
-          <t>territory.loot.scrap_per_tier</t>
+          <t>outer.cache_seconds</t>
         </is>
       </c>
       <c r="C651" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>摧毁一个据点掉在原地的废料 = 等级 × 这个值(开搬运单)</t>
+          <t>外延区资源缓存的打开工期(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -10854,15 +10854,15 @@
       <c r="A652" t="inlineStr"/>
       <c r="B652" t="inlineStr">
         <is>
-          <t>outpost.patrol_view_catchup</t>
+          <t>scatter.cache_scrap</t>
         </is>
       </c>
       <c r="C652" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>星球上巡逻标记追上逻辑位置的最快速度(格/真实秒;刚醒来拿到路线时不跳位,DEBT-FG8GEN02-07)</t>
+          <t>领地之间(零散)资源缓存的废料</t>
         </is>
       </c>
     </row>
@@ -10870,13 +10870,285 @@
       <c r="A653" t="inlineStr"/>
       <c r="B653" t="inlineStr">
         <is>
+          <t>signal.coverage.site_root_mode</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>1</v>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>远征地点内部覆盖的根:1=远征接入点(恒连通,沿用 FG1-SIG-07);2=星球上的锚点必须在与核心连通的覆盖里(DEBT-FG8EXP02-02,待用户定是否切到 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr"/>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>territory.control.sync_seconds</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>1</v>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>领地控制度 / 状态 / 增援 / 精英残部 / 骚扰的检查周期(游戏秒;只看步序号,与观察无关)</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr"/>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>territory.control.reclaim_below</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>20</v>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>平定中的领地控制度降到这个值以下(不含)时变为已收复(FGR-EXP-022 初值 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr"/>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>territory.reinforce.interval_days</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>3</v>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>首领被击败前,阵营每几个游戏日增援一次(FGR-EXP-022 初值 3;被摧毁的据点有可能重建)</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr"/>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>territory.reinforce.rebuild_chance</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>每次增援时,每个被摧毁的领地据点重建的概率(按世界种子 + 领地 + 第几次增援 + 据点确定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr"/>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>territory.reinforce.rebuild_max</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>1</v>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>每次增援每个领地最多重建几个据点</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr"/>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>territory.reinforce.rebuild_garrison_ratio</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>重建的据点驻军 = 上限 × 这个比例(至少 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr"/>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>territory.reinforce.block_radius_cells</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>80</v>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>据点这么近(格)内有己方建筑或机器时不重建(不在玩家眼前凭空出现)</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr"/>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>territory.elite.interval_days</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>7</v>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>已收复的领地里精英残部每几个游戏日刷新一次(FGR-EXP-022 初值 7;上一批没被击溃时不叠加)</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr"/>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>territory.harass.interval_hours</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>6</v>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>在敌控 / 平定中的领地里有己方建筑时,每几个游戏小时从最近的据点派一支骚扰部队</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr"/>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>territory.harass.units</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>3</v>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>骚扰部队台数(不超过据点驻军 - 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr"/>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>territory.engage.radius_cells</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>18</v>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>己方机器走到据点 / 巡逻这么近(格)时,驻军 / 巡逻就地展开迎战</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr"/>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>territory.engage.scout_nest_mode</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>1</v>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>家园区侦察巢是否也迎战:1=不迎战(初值,M1～M7 已验收的家园区节奏不变);2=与领地据点同一套迎战(由 FG9-BAL-01 第一幕平衡决定,DEBT-FG8EXP03-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr"/>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>territory.engage.regroup_seconds</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>20</v>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>迎战中附近没有己方机器满这么久(游戏秒),幸存者收拢回据点 / 巡逻(人数按幸存者)</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr"/>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>territory.engage.max_seconds</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>180</v>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>迎战僵持上限(游戏秒):到点收拢,之后这么久内不再展开(不在原地反复展开)</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr"/>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>territory.loot.scrap_per_tier</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>20</v>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>摧毁一个据点掉在原地的废料 = 等级 × 这个值(开搬运单)</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr"/>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>outpost.patrol_view_catchup</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>12</v>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>星球上巡逻标记追上逻辑位置的最快速度(格/真实秒;刚醒来拿到路线时不跳位,DEBT-FG8GEN02-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr"/>
+      <c r="B670" t="inlineStr">
+        <is>
           <t>outpost.patrol_view_snap</t>
         </is>
       </c>
-      <c r="C653" t="n">
+      <c r="C670" t="n">
         <v>120</v>
       </c>
-      <c r="D653" t="inlineStr">
+      <c r="D670" t="inlineStr">
         <is>
           <t>巡逻标记与逻辑位置相差这么远(格)时直接放过去(读档 / 镜头跳到别处)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D670"/>
+  <dimension ref="A1:D676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6598,7 +6598,7 @@
       <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
-          <t>raid.min_interval_days</t>
+          <t>outpost.sync_seconds</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>两次普通突袭(按抵达时刻)之间至少间隔几个游戏日(FGR-DEF-020;剧情 / 静默夜 / 巨构阶段除外;难度频率倍率除它)</t>
+          <t>前哨站对账间隔(游戏秒:认领 / 新开 / 合并 / 删除记录、全毁通知;按步序号定时做,与观察无关;本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6614,15 +6614,15 @@
       <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
-          <t>raid.min_warning_hours</t>
+          <t>outpost.min_buildings</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>最短预警(游戏小时,FGR-DEF-024;路程不够时推迟出发,部队在出发地集结;乘难度预警倍率)</t>
+          <t>至少几座建筑(含虚影)的建筑群才算前哨站(1 = 一座信号中继塔也算;本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6630,15 +6630,15 @@
       <c r="A388" t="inlineStr"/>
       <c r="B388" t="inlineStr">
         <is>
-          <t>raid.intel_lead_days</t>
+          <t>outpost.station_radius</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>有监听站时最早提前几个游戏日预报计划中的突袭(FGR-DEF-024)</t>
+          <t>前哨劳动的机器没活干时,离驻点超过这么多格(且不在自己的前哨站里)就走回去(本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6646,15 +6646,15 @@
       <c r="A389" t="inlineStr"/>
       <c r="B389" t="inlineStr">
         <is>
-          <t>raid.plan_lead_days</t>
+          <t>outpost.pack_radius</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>0.5</v>
+        <v>24</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>普通触发到部队出发(发预警)之间的筹备时间(游戏日;监听站在这段时间里可以破译出发前预报)</t>
+          <t>施工包着陆后,落点这么多格内还缺这种材料的施工现场直接收下(本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6662,15 +6662,15 @@
       <c r="A390" t="inlineStr"/>
       <c r="B390" t="inlineStr">
         <is>
-          <t>raid.story_plan_lead_days</t>
+          <t>outpost.rematch_buckets</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>剧情 / 静默夜 / 巨构触发到部队出发的筹备时间(游戏日)</t>
+          <t>建筑群锚点被拆后,按上次位置就近重新认领时最多几个聚合格远(聚合格边长 map.own_cluster_cells;本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6678,15 +6678,15 @@
       <c r="A391" t="inlineStr"/>
       <c r="B391" t="inlineStr">
         <is>
-          <t>raid.route_latency_seconds</t>
+          <t>outpost.overview_refresh_seconds</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>排定突袭的长路线走后台寻路通道,固定这么多游戏秒后采纳(DEBT-FG0ARCH06-09:冷的长路线要几百毫秒,不让采纳步硬等;延迟固定 → 结果确定)</t>
+          <t>前哨站总览打开时的刷新间隔(真实秒;本 Story 补的初值)</t>
         </is>
       </c>
     </row>
@@ -6694,15 +6694,15 @@
       <c r="A392" t="inlineStr"/>
       <c r="B392" t="inlineStr">
         <is>
-          <t>raid.first_raid_min_days</t>
+          <t>raid.min_interval_days</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>开局宽限:第几个游戏日之前不会有暴露 / 骚扰触发的突袭抵达(FG16 节奏 2:00 第一次突袭;剧情突袭不受限)</t>
+          <t>两次普通突袭(按抵达时刻)之间至少间隔几个游戏日(FGR-DEF-020;剧情 / 静默夜 / 巨构阶段除外;难度频率倍率除它)</t>
         </is>
       </c>
     </row>
@@ -6710,15 +6710,15 @@
       <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
-          <t>raid.first_raid_scale</t>
+          <t>raid.min_warning_hours</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>第一次突袭固定 1 级,预算再乘这个系数(FG06 第 4 节“规模很小”)</t>
+          <t>最短预警(游戏小时,FGR-DEF-024;路程不够时推迟出发,部队在出发地集结;乘难度预警倍率)</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
-          <t>raid.act1_coef</t>
+          <t>raid.intel_lead_days</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>幕系数:第一幕(FG16 第 5 节)</t>
+          <t>有监听站时最早提前几个游戏日预报计划中的突袭(FGR-DEF-024)</t>
         </is>
       </c>
     </row>
@@ -6742,15 +6742,15 @@
       <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
-          <t>raid.act2_coef</t>
+          <t>raid.plan_lead_days</t>
         </is>
       </c>
       <c r="C395" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>幕系数:第二幕</t>
+          <t>普通触发到部队出发(发预警)之间的筹备时间(游戏日;监听站在这段时间里可以破译出发前预报)</t>
         </is>
       </c>
     </row>
@@ -6758,15 +6758,15 @@
       <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr">
         <is>
-          <t>raid.act3_coef</t>
+          <t>raid.story_plan_lead_days</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2.4</v>
+        <v>0.25</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>幕系数:第三幕</t>
+          <t>剧情 / 静默夜 / 巨构触发到部队出发的筹备时间(游戏日)</t>
         </is>
       </c>
     </row>
@@ -6774,15 +6774,15 @@
       <c r="A397" t="inlineStr"/>
       <c r="B397" t="inlineStr">
         <is>
-          <t>raid.interval_bonus_per_day</t>
+          <t>raid.route_latency_seconds</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>间隔系数:距上次突袭超过最短间隔后,每多 1 个游戏日预算 + 本值</t>
+          <t>排定突袭的长路线走后台寻路通道,固定这么多游戏秒后采纳(DEBT-FG0ARCH06-09:冷的长路线要几百毫秒,不让采纳步硬等;延迟固定 → 结果确定)</t>
         </is>
       </c>
     </row>
@@ -6790,15 +6790,15 @@
       <c r="A398" t="inlineStr"/>
       <c r="B398" t="inlineStr">
         <is>
-          <t>raid.interval_bonus_max</t>
+          <t>raid.first_raid_min_days</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>间隔系数的加成上限</t>
+          <t>开局宽限:第几个游戏日之前不会有暴露 / 骚扰触发的突袭抵达(FG16 节奏 2:00 第一次突袭;剧情突袭不受限)</t>
         </is>
       </c>
     </row>
@@ -6806,15 +6806,15 @@
       <c r="A399" t="inlineStr"/>
       <c r="B399" t="inlineStr">
         <is>
-          <t>raid.level4_period_days</t>
+          <t>raid.first_raid_scale</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>暴露超过 90 后每隔几个游戏日发生一次 4 级突袭</t>
+          <t>第一次突袭固定 1 级,预算再乘这个系数(FG06 第 4 节“规模很小”)</t>
         </is>
       </c>
     </row>
@@ -6822,15 +6822,15 @@
       <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
-          <t>raid.threshold_rearm</t>
+          <t>raid.act1_coef</t>
         </is>
       </c>
       <c r="C400" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>暴露降到阈值以下多少之后,再次越过这个阈值才会再次触发</t>
+          <t>幕系数:第一幕(FG16 第 5 节)</t>
         </is>
       </c>
     </row>
@@ -6838,15 +6838,15 @@
       <c r="A401" t="inlineStr"/>
       <c r="B401" t="inlineStr">
         <is>
-          <t>raid.harass_min_interval_days</t>
+          <t>raid.act2_coef</t>
         </is>
       </c>
       <c r="C401" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>低强度骚扰的频率上限:两次骚扰至少间隔几个游戏日</t>
+          <t>幕系数:第二幕</t>
         </is>
       </c>
     </row>
@@ -6854,15 +6854,15 @@
       <c r="A402" t="inlineStr"/>
       <c r="B402" t="inlineStr">
         <is>
-          <t>raid.harass_quiet_days</t>
+          <t>raid.act3_coef</t>
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>距上一次任何突袭抵达至少几个游戏日才会来骚扰</t>
+          <t>幕系数:第三幕</t>
         </is>
       </c>
     </row>
@@ -6870,15 +6870,15 @@
       <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
-          <t>raid.max_units</t>
+          <t>raid.interval_bonus_per_day</t>
         </is>
       </c>
       <c r="C403" t="n">
-        <v>200</v>
+        <v>0.1</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>一波突袭的单位数上限(FG15 同时存在的敌人 200;超出的预算换成精英)</t>
+          <t>间隔系数:距上次突袭超过最短间隔后,每多 1 个游戏日预算 + 本值</t>
         </is>
       </c>
     </row>
@@ -6886,15 +6886,15 @@
       <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
-          <t>raid.postgame_base</t>
+          <t>raid.interval_bonus_max</t>
         </is>
       </c>
       <c r="C404" t="n">
-        <v>1200</v>
+        <v>0.5</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>后日谈第 n 次清洗的预算基数(FG16 第 5 节)</t>
+          <t>间隔系数的加成上限</t>
         </is>
       </c>
     </row>
@@ -6902,15 +6902,15 @@
       <c r="A405" t="inlineStr"/>
       <c r="B405" t="inlineStr">
         <is>
-          <t>raid.postgame_growth</t>
+          <t>raid.level4_period_days</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>后日谈每次清洗的预算增长倍率</t>
+          <t>暴露超过 90 后每隔几个游戏日发生一次 4 级突袭</t>
         </is>
       </c>
     </row>
@@ -6918,15 +6918,15 @@
       <c r="A406" t="inlineStr"/>
       <c r="B406" t="inlineStr">
         <is>
-          <t>raid.merge_window_seconds</t>
+          <t>raid.threshold_rearm</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>1200</v>
+        <v>10</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>剧情 / 静默夜 / 巨构突袭与普通突袭抵达时间相差不超过这么多游戏秒视为重叠,合并为一波</t>
+          <t>暴露降到阈值以下多少之后,再次越过这个阈值才会再次触发</t>
         </is>
       </c>
     </row>
@@ -6934,15 +6934,15 @@
       <c r="A407" t="inlineStr"/>
       <c r="B407" t="inlineStr">
         <is>
-          <t>raid.destroyed_outpost_interval_bonus</t>
+          <t>raid.harass_min_interval_days</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>某个方向(8 方位)每摧毁一个据点,从那个方向出发的突袭最短间隔 ×(1 + 本值)</t>
+          <t>低强度骚扰的频率上限:两次骚扰至少间隔几个游戏日</t>
         </is>
       </c>
     </row>
@@ -6950,15 +6950,15 @@
       <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr">
         <is>
-          <t>raid.origin_max_distance</t>
+          <t>raid.harass_quiet_days</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>1600</v>
+        <v>2</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>据点离目标超过这么多格就不算合适的出发地(改从迷雾外来袭)</t>
+          <t>距上一次任何突袭抵达至少几个游戏日才会来骚扰</t>
         </is>
       </c>
     </row>
@@ -6966,15 +6966,15 @@
       <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
-          <t>raid.target_home_weight</t>
+          <t>raid.max_units</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>选突袭目标时家园的权重(前哨站权重 = 座数 / 10 × 领地临近系数)</t>
+          <t>一波突袭的单位数上限(FG15 同时存在的敌人 200;超出的预算换成精英)</t>
         </is>
       </c>
     </row>
@@ -6982,15 +6982,15 @@
       <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
-          <t>raid.target_outpost_min_buildings</t>
+          <t>raid.postgame_base</t>
         </is>
       </c>
       <c r="C410" t="n">
-        <v>3</v>
+        <v>1200</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>前哨站至少几座建筑才会被当成突袭目标</t>
+          <t>后日谈第 n 次清洗的预算基数(FG16 第 5 节)</t>
         </is>
       </c>
     </row>
@@ -6998,15 +6998,15 @@
       <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
-          <t>raid.target_proximity_cells</t>
+          <t>raid.postgame_growth</t>
         </is>
       </c>
       <c r="C411" t="n">
-        <v>400</v>
+        <v>1.15</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>前哨站领地临近系数 = 1 + 本值 / (本值 + 到阵营领地边缘的距离)</t>
+          <t>后日谈每次清洗的预算增长倍率</t>
         </is>
       </c>
     </row>
@@ -7014,15 +7014,15 @@
       <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
-          <t>raid.time_limit_hours</t>
+          <t>raid.merge_window_seconds</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>到达后的时间上限(游戏小时,FGR-DEF-032);攻城行为(FG6-DEF-05)之前部队在外围停留这么久后沿原路撤回出发地</t>
+          <t>剧情 / 静默夜 / 巨构突袭与普通突袭抵达时间相差不超过这么多游戏秒视为重叠,合并为一波</t>
         </is>
       </c>
     </row>
@@ -7030,15 +7030,15 @@
       <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
-          <t>raid.history_max</t>
+          <t>raid.destroyed_outpost_interval_bonus</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>32</v>
+        <v>0.5</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>突袭历史最多保留几条</t>
+          <t>某个方向(8 方位)每摧毁一个据点,从那个方向出发的突袭最短间隔 ×(1 + 本值)</t>
         </is>
       </c>
     </row>
@@ -7046,15 +7046,15 @@
       <c r="A414" t="inlineStr"/>
       <c r="B414" t="inlineStr">
         <is>
-          <t>raid.warning_rows_max</t>
+          <t>raid.origin_max_distance</t>
         </is>
       </c>
       <c r="C414" t="n">
-        <v>6</v>
+        <v>1600</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>预警条最多列几波(更多的写“还有 n 波”)</t>
+          <t>据点离目标超过这么多格就不算合适的出发地(改从迷雾外来袭)</t>
         </is>
       </c>
     </row>
@@ -7062,15 +7062,15 @@
       <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
-          <t>siege.theater_radius_cells</t>
+          <t>raid.target_home_weight</t>
         </is>
       </c>
       <c r="C415" t="n">
-        <v>140</v>
+        <v>4</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>攻城剧场:突袭目标点周围这么远(格)内的己方建筑算进流场范围</t>
+          <t>选突袭目标时家园的权重(前哨站权重 = 座数 / 10 × 领地临近系数)</t>
         </is>
       </c>
     </row>
@@ -7078,15 +7078,15 @@
       <c r="A416" t="inlineStr"/>
       <c r="B416" t="inlineStr">
         <is>
-          <t>siege.theater_margin_cells</t>
+          <t>raid.target_outpost_min_buildings</t>
         </is>
       </c>
       <c r="C416" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>攻城剧场:建筑外接矩形(含集结点)向外放宽的格数</t>
+          <t>前哨站至少几座建筑才会被当成突袭目标</t>
         </is>
       </c>
     </row>
@@ -7094,15 +7094,15 @@
       <c r="A417" t="inlineStr"/>
       <c r="B417" t="inlineStr">
         <is>
-          <t>siege.theater_max_cells</t>
+          <t>raid.target_proximity_cells</t>
         </is>
       </c>
       <c r="C417" t="n">
-        <v>288</v>
+        <v>400</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>攻城剧场:流场矩形的最大边长(格);超出时以目标点为中心截取(流场内存与全量计算耗时的上限)</t>
+          <t>前哨站领地临近系数 = 1 + 本值 / (本值 + 到阵营领地边缘的距离)</t>
         </is>
       </c>
     </row>
@@ -7110,15 +7110,15 @@
       <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>siege.retarget_seconds</t>
+          <t>raid.time_limit_hours</t>
         </is>
       </c>
       <c r="C418" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>突袭单位重新选目标 / 重新看破墙目标的间隔(游戏秒)</t>
+          <t>到达后的时间上限(游戏小时,FGR-DEF-032);攻城行为(FG6-DEF-05)之前部队在外围停留这么久后沿原路撤回出发地</t>
         </is>
       </c>
     </row>
@@ -7126,15 +7126,15 @@
       <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
-          <t>siege.breach_base_cost</t>
+          <t>raid.history_max</t>
         </is>
       </c>
       <c r="C419" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>破墙流场:穿过一格建筑的基础代价(10 = 走 1 米);越大越倾向绕路而不是破墙</t>
+          <t>突袭历史最多保留几条</t>
         </is>
       </c>
     </row>
@@ -7142,15 +7142,15 @@
       <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr">
         <is>
-          <t>siege.breach_hp_band</t>
+          <t>raid.warning_rows_max</t>
         </is>
       </c>
       <c r="C420" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>破墙流场:耐久每多这么多算一档(耐久掉档时流场增量更新)</t>
+          <t>预警条最多列几波(更多的写“还有 n 波”)</t>
         </is>
       </c>
     </row>
@@ -7158,15 +7158,15 @@
       <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
-          <t>siege.breach_cost_per_band</t>
+          <t>siege.theater_radius_cells</t>
         </is>
       </c>
       <c r="C421" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>破墙流场:每档耐久加的代价(10 = 走 1 米);越大越倾向挑最薄弱的那段</t>
+          <t>攻城剧场:突袭目标点周围这么远(格)内的己方建筑算进流场范围</t>
         </is>
       </c>
     </row>
@@ -7174,15 +7174,15 @@
       <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr">
         <is>
-          <t>siege.loss_retreat_ratio</t>
+          <t>siege.theater_margin_cells</t>
         </is>
       </c>
       <c r="C422" t="n">
-        <v>0.7</v>
+        <v>24</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>FGR-DEF-032:损失超过这个比例全队撤退(初值 70%)</t>
+          <t>攻城剧场:建筑外接矩形(含集结点)向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -7190,15 +7190,15 @@
       <c r="A423" t="inlineStr"/>
       <c r="B423" t="inlineStr">
         <is>
-          <t>siege.exit_radius_cells</t>
+          <t>siege.theater_max_cells</t>
         </is>
       </c>
       <c r="C423" t="n">
-        <v>2.5</v>
+        <v>288</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>撤退:走到集结点这么近(格)就离开家园、并回行进队伍</t>
+          <t>攻城剧场:流场矩形的最大边长(格);超出时以目标点为中心截取(流场内存与全量计算耗时的上限)</t>
         </is>
       </c>
     </row>
@@ -7206,15 +7206,15 @@
       <c r="A424" t="inlineStr"/>
       <c r="B424" t="inlineStr">
         <is>
-          <t>siege.retreat_max_seconds</t>
+          <t>siege.retarget_seconds</t>
         </is>
       </c>
       <c r="C424" t="n">
-        <v>180</v>
+        <v>0.5</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>撤退兜底(B11):下撤退令后这么久(游戏秒)还走不回集结点的(路被堵死时会先拆墙;连墙都拆不出去,例如被地形困住)就地离场,队伍照常原路返回</t>
+          <t>突袭单位重新选目标 / 重新看破墙目标的间隔(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -7222,15 +7222,15 @@
       <c r="A425" t="inlineStr"/>
       <c r="B425" t="inlineStr">
         <is>
-          <t>siege.hp_scale</t>
+          <t>siege.breach_base_cost</t>
         </is>
       </c>
       <c r="C425" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>突袭单位耐久 = fg.TbMechEnemy.maxHp × 本值</t>
+          <t>破墙流场:穿过一格建筑的基础代价(10 = 走 1 米);越大越倾向绕路而不是破墙</t>
         </is>
       </c>
     </row>
@@ -7238,15 +7238,15 @@
       <c r="A426" t="inlineStr"/>
       <c r="B426" t="inlineStr">
         <is>
-          <t>siege.elite_hp_scale</t>
+          <t>siege.breach_hp_band</t>
         </is>
       </c>
       <c r="C426" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>精英突袭单位的耐久倍率</t>
+          <t>破墙流场:耐久每多这么多算一档(耐久掉档时流场增量更新)</t>
         </is>
       </c>
     </row>
@@ -7254,15 +7254,15 @@
       <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr">
         <is>
-          <t>siege.elite_damage_scale</t>
+          <t>siege.breach_cost_per_band</t>
         </is>
       </c>
       <c r="C427" t="n">
-        <v>1.5</v>
+        <v>30</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>精英突袭单位的伤害倍率</t>
+          <t>破墙流场:每档耐久加的代价(10 = 走 1 米);越大越倾向挑最薄弱的那段</t>
         </is>
       </c>
     </row>
@@ -7270,15 +7270,15 @@
       <c r="A428" t="inlineStr"/>
       <c r="B428" t="inlineStr">
         <is>
-          <t>siege.spawn_spacing</t>
+          <t>siege.loss_retreat_ratio</t>
         </is>
       </c>
       <c r="C428" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>到达展开:单位之间的间距(米;按确定性的螺旋排布)</t>
+          <t>FGR-DEF-032:损失超过这个比例全队撤退(初值 70%)</t>
         </is>
       </c>
     </row>
@@ -7286,15 +7286,15 @@
       <c r="A429" t="inlineStr"/>
       <c r="B429" t="inlineStr">
         <is>
-          <t>siege.collateral_ratio</t>
+          <t>siege.exit_radius_cells</t>
         </is>
       </c>
       <c r="C429" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>溅射:敌人每打中一次建筑,周围传送带 / 管线 / 施工虚影受到这一发伤害 × 本值</t>
+          <t>撤退:走到集结点这么近(格)就离开家园、并回行进队伍</t>
         </is>
       </c>
     </row>
@@ -7302,15 +7302,15 @@
       <c r="A430" t="inlineStr"/>
       <c r="B430" t="inlineStr">
         <is>
-          <t>siege.collateral_radius_cells</t>
+          <t>siege.retreat_max_seconds</t>
         </is>
       </c>
       <c r="C430" t="n">
-        <v>1.5</v>
+        <v>180</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>溅射:命中点周围多远(格)内的传送带 / 管线 / 施工虚影受波及</t>
+          <t>撤退兜底(B11):下撤退令后这么久(游戏秒)还走不回集结点的(路被堵死时会先拆墙;连墙都拆不出去,例如被地形困住)就地离场,队伍照常原路返回</t>
         </is>
       </c>
     </row>
@@ -7318,15 +7318,15 @@
       <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
-          <t>siege.collateral_drain_per_step</t>
+          <t>siege.hp_scale</t>
         </is>
       </c>
       <c r="C431" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>溅射:热更层每步最多结算几个命中格(其余留到下一步,不丢、进存档)</t>
+          <t>突袭单位耐久 = fg.TbMechEnemy.maxHp × 本值</t>
         </is>
       </c>
     </row>
@@ -7334,15 +7334,15 @@
       <c r="A432" t="inlineStr"/>
       <c r="B432" t="inlineStr">
         <is>
-          <t>siege.site_hp_fraction</t>
+          <t>siege.elite_hp_scale</t>
         </is>
       </c>
       <c r="C432" t="n">
-        <v>0.35</v>
+        <v>2</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>施工中的虚影被溅射打掉的耐久 = 建筑最大耐久 × 本值(打满即“施工中被摧毁”)</t>
+          <t>精英突袭单位的耐久倍率</t>
         </is>
       </c>
     </row>
@@ -7350,15 +7350,15 @@
       <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr">
         <is>
-          <t>siege.sync_seconds</t>
+          <t>siege.elite_damage_scale</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>攻城对账间隔(游戏秒):建筑结构单位的耐久双向对账、撤退条件、溅射以外的检查</t>
+          <t>精英突袭单位的伤害倍率</t>
         </is>
       </c>
     </row>
@@ -7366,15 +7366,15 @@
       <c r="A434" t="inlineStr"/>
       <c r="B434" t="inlineStr">
         <is>
-          <t>siege.breach_notify_seconds</t>
+          <t>siege.spawn_spacing</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>20</v>
+        <v>1.6</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>“敌人正在拆某段墙”通知的冷却(游戏秒;同一座只报一次,换目标才再报)</t>
+          <t>到达展开:单位之间的间距(米;按确定性的螺旋排布)</t>
         </is>
       </c>
     </row>
@@ -7382,15 +7382,15 @@
       <c r="A435" t="inlineStr"/>
       <c r="B435" t="inlineStr">
         <is>
-          <t>siege.guard_radius_cells</t>
+          <t>siege.collateral_ratio</t>
         </is>
       </c>
       <c r="C435" t="n">
-        <v>18</v>
+        <v>0.5</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>驻防机器的守点交战半径(格):敌人进入驻防点这么近就去打,打完回驻防点</t>
+          <t>溅射:敌人每打中一次建筑,周围传送带 / 管线 / 施工虚影受到这一发伤害 × 本值</t>
         </is>
       </c>
     </row>
@@ -7398,15 +7398,15 @@
       <c r="A436" t="inlineStr"/>
       <c r="B436" t="inlineStr">
         <is>
-          <t>siege.intercept_radius_cells</t>
+          <t>siege.collateral_radius_cells</t>
         </is>
       </c>
       <c r="C436" t="n">
-        <v>16</v>
+        <v>1.5</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>拦截:己方机器离行进中的突袭部队这么近(格)时,部队就地展开成战斗单位</t>
+          <t>溅射:命中点周围多远(格)内的传送带 / 管线 / 施工虚影受波及</t>
         </is>
       </c>
     </row>
@@ -7414,15 +7414,15 @@
       <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr">
         <is>
-          <t>siege.regroup_seconds</t>
+          <t>siege.collateral_drain_per_step</t>
         </is>
       </c>
       <c r="C437" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>拦截:附近没有己方机器满这么久(游戏秒)后,幸存者重新收拢成行进队伍继续走</t>
+          <t>溅射:热更层每步最多结算几个命中格(其余留到下一步,不丢、进存档)</t>
         </is>
       </c>
     </row>
@@ -7430,15 +7430,15 @@
       <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr">
         <is>
-          <t>siege.intercept_min_target_cells</t>
+          <t>siege.site_hp_fraction</t>
         </is>
       </c>
       <c r="C438" t="n">
-        <v>60</v>
+        <v>0.35</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>拦截:离目标(家园核心 / 前哨站)不到这么远(格)的行进队伍不拦截,照常到达展开攻城(同一场仗用流场打)</t>
+          <t>施工中的虚影被溅射打掉的耐久 = 建筑最大耐久 × 本值(打满即“施工中被摧毁”)</t>
         </is>
       </c>
     </row>
@@ -7446,15 +7446,15 @@
       <c r="A439" t="inlineStr"/>
       <c r="B439" t="inlineStr">
         <is>
-          <t>siege.intercept_max_seconds</t>
+          <t>siege.sync_seconds</t>
         </is>
       </c>
       <c r="C439" t="n">
-        <v>90</v>
+        <v>0.5</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>拦截:就地交战最多这么久(游戏秒),互相够不着的僵持到点后幸存者收拢继续走</t>
+          <t>攻城对账间隔(游戏秒):建筑结构单位的耐久双向对账、撤退条件、溅射以外的检查</t>
         </is>
       </c>
     </row>
@@ -7462,15 +7462,15 @@
       <c r="A440" t="inlineStr"/>
       <c r="B440" t="inlineStr">
         <is>
-          <t>siege.overlay_refresh_seconds</t>
+          <t>siege.breach_notify_seconds</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>突袭路径叠加层重画间隔(真实秒;纯表现)</t>
+          <t>“敌人正在拆某段墙”通知的冷却(游戏秒;同一座只报一次,换目标才再报)</t>
         </is>
       </c>
     </row>
@@ -7478,15 +7478,15 @@
       <c r="A441" t="inlineStr"/>
       <c r="B441" t="inlineStr">
         <is>
-          <t>siege.perf.units</t>
+          <t>siege.guard_radius_cells</t>
         </is>
       </c>
       <c r="C441" t="n">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>性能验收:同时攻城的突袭单位数(FG06 第 7 节 200)</t>
+          <t>驻防机器的守点交战半径(格):敌人进入驻防点这么近就去打,打完回驻防点</t>
         </is>
       </c>
     </row>
@@ -7494,15 +7494,15 @@
       <c r="A442" t="inlineStr"/>
       <c r="B442" t="inlineStr">
         <is>
-          <t>siege.perf.field_update_ms</t>
+          <t>siege.intercept_radius_cells</t>
         </is>
       </c>
       <c r="C442" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>性能验收:屏障变化时流场增量更新单次耗时上限(毫秒,FG06 第 7 节)</t>
+          <t>拦截:己方机器离行进中的突袭部队这么近(格)时,部队就地展开成战斗单位</t>
         </is>
       </c>
     </row>
@@ -7510,15 +7510,15 @@
       <c r="A443" t="inlineStr"/>
       <c r="B443" t="inlineStr">
         <is>
-          <t>siege.perf.step_ms</t>
+          <t>siege.regroup_seconds</t>
         </is>
       </c>
       <c r="C443" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>性能验收:200 单位攻城时内核单步平均耗时上限(毫秒;120 帧预算 8.33 ms 的四分之一)</t>
+          <t>拦截:附近没有己方机器满这么久(游戏秒)后,幸存者重新收拢成行进队伍继续走</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       <c r="A444" t="inlineStr"/>
       <c r="B444" t="inlineStr">
         <is>
-          <t>logistics.pipe.hp_t1</t>
+          <t>siege.intercept_min_target_cells</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>管线 T1 一格的最大耐久(管线 / 泵 / 阀门 / 地下管线口按等级)</t>
+          <t>拦截:离目标(家园核心 / 前哨站)不到这么远(格)的行进队伍不拦截,照常到达展开攻城(同一场仗用流场打)</t>
         </is>
       </c>
     </row>
@@ -7542,15 +7542,15 @@
       <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr">
         <is>
-          <t>logistics.pipe.hp_t2</t>
+          <t>siege.intercept_max_seconds</t>
         </is>
       </c>
       <c r="C445" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>管线 T2 一格的最大耐久</t>
+          <t>拦截:就地交战最多这么久(游戏秒),互相够不着的僵持到点后幸存者收拢继续走</t>
         </is>
       </c>
     </row>
@@ -7558,15 +7558,15 @@
       <c r="A446" t="inlineStr"/>
       <c r="B446" t="inlineStr">
         <is>
-          <t>logistics.pipe.hp_tank</t>
+          <t>siege.overlay_refresh_seconds</t>
         </is>
       </c>
       <c r="C446" t="n">
-        <v>160</v>
+        <v>0.5</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>储罐一格的最大耐久</t>
+          <t>突袭路径叠加层重画间隔(真实秒;纯表现)</t>
         </is>
       </c>
     </row>
@@ -7574,15 +7574,15 @@
       <c r="A447" t="inlineStr"/>
       <c r="B447" t="inlineStr">
         <is>
-          <t>logistics.pipe.repair_kits</t>
+          <t>siege.perf.units</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>0.25</v>
+        <v>200</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>维修无人机修满一格管线要的维修件(与传送带同口径)</t>
+          <t>性能验收:同时攻城的突袭单位数(FG06 第 7 节 200)</t>
         </is>
       </c>
     </row>
@@ -7590,15 +7590,15 @@
       <c r="A448" t="inlineStr"/>
       <c r="B448" t="inlineStr">
         <is>
-          <t>raid.auto_pause_first_raids</t>
+          <t>siege.perf.field_update_ms</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>FGR-DEF-042:突袭到达时自动暂停的默认值只对本存档前几次突袭(波)开启;玩家在通知设置里改过的按玩家的</t>
+          <t>性能验收:屏障变化时流场增量更新单次耗时上限(毫秒,FG06 第 7 节)</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr">
         <is>
-          <t>raid.spectate.default_speed</t>
+          <t>siege.perf.step_ms</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>观战:点“观战”时切到的速度(2 或 3;复用统一时钟的倍速档)</t>
+          <t>性能验收:200 单位攻城时内核单步平均耗时上限(毫秒;120 帧预算 8.33 ms 的四分之一)</t>
         </is>
       </c>
     </row>
@@ -7622,15 +7622,15 @@
       <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
-          <t>raid.spectate.follow_seconds</t>
+          <t>logistics.pipe.hp_t1</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>观战:镜头每隔这么久(真实秒)重新看一次战斗重心</t>
+          <t>管线 T1 一格的最大耐久(管线 / 泵 / 阀门 / 地下管线口按等级)</t>
         </is>
       </c>
     </row>
@@ -7638,15 +7638,15 @@
       <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
-          <t>raid.spectate.follow_min_cells</t>
+          <t>logistics.pipe.hp_t2</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>观战:战斗重心离镜头焦点超过这么远(格)才飞过去(免得镜头一直抖)</t>
+          <t>管线 T2 一格的最大耐久</t>
         </is>
       </c>
     </row>
@@ -7654,15 +7654,15 @@
       <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
-          <t>raid.spectate.manual_cells</t>
+          <t>logistics.pipe.hp_tank</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>观战:玩家自己把镜头移开超过这么远(格)就暂停跟随(点“跟随战斗”恢复)</t>
+          <t>储罐一格的最大耐久</t>
         </is>
       </c>
     </row>
@@ -7670,15 +7670,15 @@
       <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
-          <t>raid.music.volume</t>
+          <t>logistics.pipe.repair_kits</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>预警 / 突袭音乐的音量(乘在音乐音量设置上;占位音乐,美术批次替换)</t>
+          <t>维修无人机修满一格管线要的维修件(与传送带同口径)</t>
         </is>
       </c>
     </row>
@@ -7686,15 +7686,15 @@
       <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
-          <t>raid.hud.refresh_seconds</t>
+          <t>raid.auto_pause_first_raids</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>突袭 HUD 刷新间隔(真实秒;键没变不重建)</t>
+          <t>FGR-DEF-042:突袭到达时自动暂停的默认值只对本存档前几次突袭(波)开启;玩家在通知设置里改过的按玩家的</t>
         </is>
       </c>
     </row>
@@ -7702,15 +7702,15 @@
       <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
-          <t>raid.hud.perf_ms</t>
+          <t>raid.spectate.default_speed</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>性能验收:突袭 HUD 一次数据刷新(各波剩余敌人 / 文字)的耗时上限(毫秒)</t>
+          <t>观战:点“观战”时切到的速度(2 或 3;复用统一时钟的倍速档)</t>
         </is>
       </c>
     </row>
@@ -7718,15 +7718,15 @@
       <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
-          <t>defov.margin_cells</t>
+          <t>raid.spectate.follow_seconds</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>防御总览:热力图范围 = 家园己方建筑外接矩形向外放宽的格数</t>
+          <t>观战:镜头每隔这么久(真实秒)重新看一次战斗重心</t>
         </is>
       </c>
     </row>
@@ -7734,15 +7734,15 @@
       <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
-          <t>defov.max_cells</t>
+          <t>raid.spectate.follow_min_cells</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>256</v>
+        <v>6</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>防御总览:热力图最大边长(格;超出时以归还核心为中心截取)</t>
+          <t>观战:战斗重心离镜头焦点超过这么远(格)才飞过去(免得镜头一直抖)</t>
         </is>
       </c>
     </row>
@@ -7750,15 +7750,15 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>defov.weak_min_cells</t>
+          <t>raid.spectate.manual_cells</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>防御总览:连续这么多格(沿路线 / 外围)没有火力覆盖才算一处薄弱点</t>
+          <t>观战:玩家自己把镜头移开超过这么远(格)就暂停跟随(点“跟随战斗”恢复)</t>
         </is>
       </c>
     </row>
@@ -7766,15 +7766,15 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>defov.weak_max</t>
+          <t>raid.music.volume</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>12</v>
+        <v>0.6</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>防御总览:最多列出几处薄弱点(按离核心由近到远)</t>
+          <t>预警 / 突袭音乐的音量(乘在音乐音量设置上;占位音乐,美术批次替换)</t>
         </is>
       </c>
     </row>
@@ -7782,15 +7782,15 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>defov.ring_extra_cells</t>
+          <t>raid.hud.refresh_seconds</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>10</v>
+        <v>0.25</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>防御总览:没有预测路线时,外围检查圈 = 建筑外接矩形半对角线 + 这么多格</t>
+          <t>突袭 HUD 刷新间隔(真实秒;键没变不重建)</t>
         </is>
       </c>
     </row>
@@ -7798,15 +7798,15 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>defov.ring_samples</t>
+          <t>raid.hud.perf_ms</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>96</v>
+        <v>0.2</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>防御总览:外围检查圈的采样点数</t>
+          <t>性能验收:突袭 HUD 一次数据刷新(各波剩余敌人 / 文字)的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -7814,15 +7814,15 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>defov.refresh_seconds</t>
+          <t>defov.margin_cells</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>防御总览:面板开着时每隔这么久(真实秒)检查一次要不要重算覆盖(炮塔 / 建筑 / 突袭计划变了才重算)</t>
+          <t>防御总览:热力图范围 = 家园己方建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -7830,15 +7830,15 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>defov.perf_ms</t>
+          <t>defov.max_cells</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>8</v>
+        <v>256</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>性能验收:100 座炮塔时重算一次覆盖 + 薄弱点的耗时上限(毫秒;只在面板打开 / 防线变化时)</t>
+          <t>防御总览:热力图最大边长(格;超出时以归还核心为中心截取)</t>
         </is>
       </c>
     </row>
@@ -7846,15 +7846,15 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>roster.patrol_max_points</t>
+          <t>defov.weak_min_cells</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>驻防巡逻(FGR-DEF-043):一台机器的巡逻路线最多几个巡逻点(不含驻防点)</t>
+          <t>防御总览:连续这么多格(沿路线 / 外围)没有火力覆盖才算一处薄弱点</t>
         </is>
       </c>
     </row>
@@ -7862,15 +7862,15 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>roster.patrol_arrive_cells</t>
+          <t>defov.weak_max</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>驻防巡逻:走到巡逻点这么近(格)就去下一个点</t>
+          <t>防御总览:最多列出几处薄弱点(按离核心由近到远)</t>
         </is>
       </c>
     </row>
@@ -7878,15 +7878,15 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>roster.patrol_arrive_slack</t>
+          <t>defov.ring_extra_cells</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>驻防巡逻:判定“站稳在这一点”时在 roster.patrol_arrive_cells 之外再放宽的格数(机器与别的单位互相推挤时也能换点)</t>
+          <t>防御总览:没有预测路线时,外围检查圈 = 建筑外接矩形半对角线 + 这么多格</t>
         </is>
       </c>
     </row>
@@ -7894,15 +7894,15 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>roster.patrol_retry_seconds</t>
+          <t>defov.ring_samples</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>驻防巡逻:到不了的巡逻点先跳过,过这么久(游戏秒)再试一次(墙拆了 / 路通了能自动恢复;通知只发一次,直到走到过它)</t>
+          <t>防御总览:外围检查圈的采样点数</t>
         </is>
       </c>
     </row>
@@ -7910,15 +7910,15 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>raid.away.refresh_seconds</t>
+          <t>defov.refresh_seconds</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:远征 HUD 弹窗 / 倒计时的刷新间隔(真实秒;文字没变不重写)</t>
+          <t>防御总览:面板开着时每隔这么久(真实秒)检查一次要不要重算覆盖(炮塔 / 建筑 / 突袭计划变了才重算)</t>
         </is>
       </c>
     </row>
@@ -7926,15 +7926,15 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
-          <t>raid.away.home_refresh_seconds</t>
+          <t>defov.perf_ms</t>
         </is>
       </c>
       <c r="C469" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:家园状态小窗(核心耐久 / 关键建筑 / 剩余敌人)重新汇总的间隔(真实秒;只在小窗显示时汇总)</t>
+          <t>性能验收:100 座炮塔时重算一次覆盖 + 薄弱点的耗时上限(毫秒;只在面板打开 / 防线变化时)</t>
         </is>
       </c>
     </row>
@@ -7942,15 +7942,15 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
-          <t>raid.away.perf_ms</t>
+          <t>roster.patrol_max_points</t>
         </is>
       </c>
       <c r="C470" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>性能验收:家园状态小窗汇总一次(全部建筑的类别与耐久 + 剩余敌人)的耗时上限(毫秒)</t>
+          <t>驻防巡逻(FGR-DEF-043):一台机器的巡逻路线最多几个巡逻点(不含驻防点)</t>
         </is>
       </c>
     </row>
@@ -7958,15 +7958,15 @@
       <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
-          <t>raid.away.decision_keep</t>
+          <t>roster.patrol_arrive_cells</t>
         </is>
       </c>
       <c r="C471" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:存档里保留最近几波的选择(跳回家园 / 留在远征队;读档后同一波不再弹出)</t>
+          <t>驻防巡逻:走到巡逻点这么近(格)就去下一个点</t>
         </is>
       </c>
     </row>
@@ -7974,15 +7974,15 @@
       <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
-          <t>raid.away.status_seconds</t>
+          <t>roster.patrol_arrive_slack</t>
         </is>
       </c>
       <c r="C472" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:小窗里选择 / 被拒提示的显示时长(真实秒)</t>
+          <t>驻防巡逻:判定“站稳在这一点”时在 roster.patrol_arrive_cells 之外再放宽的格数(机器与别的单位互相推挤时也能换点)</t>
         </is>
       </c>
     </row>
@@ -7990,15 +7990,15 @@
       <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
-          <t>raid.away.core_low_ratio</t>
+          <t>roster.patrol_retry_seconds</t>
         </is>
       </c>
       <c r="C473" t="n">
-        <v>0.3</v>
+        <v>60</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:归还核心耐久条变红的耐久比例</t>
+          <t>驻防巡逻:到不了的巡逻点先跳过,过这么久(游戏秒)再试一次(墙拆了 / 路通了能自动恢复;通知只发一次,直到走到过它)</t>
         </is>
       </c>
     </row>
@@ -8006,15 +8006,15 @@
       <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
-          <t>raid.away.march_focus_cells</t>
+          <t>raid.away.refresh_seconds</t>
         </is>
       </c>
       <c r="C474" t="n">
-        <v>150</v>
+        <v>0.25</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>FG8-EXP-02:远征队在星球上行军(还没进地点)时,镜头焦点离归还核心超过这么远(格)也算玩家在远征(远征决策条照常弹出;初值=归还核心覆盖半径)</t>
+          <t>远征中家园遇袭:远征 HUD 弹窗 / 倒计时的刷新间隔(真实秒;文字没变不重写)</t>
         </is>
       </c>
     </row>
@@ -8022,15 +8022,15 @@
       <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
-          <t>raid.away.intact_ratio</t>
+          <t>raid.away.home_refresh_seconds</t>
         </is>
       </c>
       <c r="C475" t="n">
-        <v>0.999</v>
+        <v>0.5</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>远征中家园遇袭:关键建筑算“完好”的耐久比例(浮点误差内的满耐久)</t>
+          <t>远征中家园遇袭:家园状态小窗(核心耐久 / 关键建筑 / 剩余敌人)重新汇总的间隔(真实秒;只在小窗显示时汇总)</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
-          <t>logistics.leak.breach_hp_ratio</t>
+          <t>raid.away.perf_ms</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>击穿:管线件耐久掉到最大耐久 × 本值及以下(或被摧毁)就开始泄漏;维修回到本值以上算修好</t>
+          <t>性能验收:家园状态小窗汇总一次(全部建筑的类别与耐久 + 剩余敌人)的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -8054,15 +8054,15 @@
       <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
-          <t>logistics.leak.base_radius</t>
+          <t>raid.away.decision_keep</t>
         </is>
       </c>
       <c r="C477" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>液洼刚出现时的半径(米,× fg.TbFluidLeak.radiusScale)</t>
+          <t>远征中家园遇袭:存档里保留最近几波的选择(跳回家园 / 留在远征队;读档后同一波不再弹出)</t>
         </is>
       </c>
     </row>
@@ -8070,15 +8070,15 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
-          <t>logistics.leak.max_radius</t>
+          <t>raid.away.status_seconds</t>
         </is>
       </c>
       <c r="C478" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>液洼一直漏下去最大能扩到的半径(米,× radiusScale)</t>
+          <t>远征中家园遇袭:小窗里选择 / 被拒提示的显示时长(真实秒)</t>
         </is>
       </c>
     </row>
@@ -8086,15 +8086,15 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
-          <t>logistics.leak.grow_seconds</t>
+          <t>raid.away.core_low_ratio</t>
         </is>
       </c>
       <c r="C479" t="n">
-        <v>20</v>
+        <v>0.3</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>液洼从刚出现扩到最大半径要的游戏秒(一直在漏时)</t>
+          <t>远征中家园遇袭:归还核心耐久条变红的耐久比例</t>
         </is>
       </c>
     </row>
@@ -8102,15 +8102,15 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
-          <t>logistics.leak.fade_seconds</t>
+          <t>raid.away.march_focus_cells</t>
         </is>
       </c>
       <c r="C480" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>修好管线(或冲洗 / 拆掉 / 破口两侧没有同种流体)后,液洼从当前半径缩小到消失要的游戏秒</t>
+          <t>FG8-EXP-02:远征队在星球上行军(还没进地点)时,镜头焦点离归还核心超过这么远(格)也算玩家在远征(远征决策条照常弹出;初值=归还核心覆盖半径)</t>
         </is>
       </c>
     </row>
@@ -8118,15 +8118,15 @@
       <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
-          <t>logistics.leak.react_seconds</t>
+          <t>raid.away.intact_ratio</t>
         </is>
       </c>
       <c r="C481" t="n">
-        <v>12</v>
+        <v>0.999</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>液洼整片反应成残留区域(燃油遇火 = 燃烧区)后至少持续的游戏秒(与反应自己的残留时长取大)</t>
+          <t>远征中家园遇袭:关键建筑算“完好”的耐久比例(浮点误差内的满耐久)</t>
         </is>
       </c>
     </row>
@@ -8134,15 +8134,15 @@
       <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
-          <t>logistics.leak.fire_dps</t>
+          <t>logistics.leak.breach_hp_ratio</t>
         </is>
       </c>
       <c r="C482" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>反应成的残留区域带持续伤害(燃烧)时,每游戏秒烧掉范围里管线 / 传送带 / 建筑的耐久(连锁烧毁产线)</t>
+          <t>击穿:管线件耐久掉到最大耐久 × 本值及以下(或被摧毁)就开始泄漏;维修回到本值以上算修好</t>
         </is>
       </c>
     </row>
@@ -8150,15 +8150,15 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr">
         <is>
-          <t>logistics.leak.fire_tick_seconds</t>
+          <t>logistics.leak.base_radius</t>
         </is>
       </c>
       <c r="C483" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>火烧设施的结算间隔(游戏秒;每摊燃烧区按编号错开,每次扣 fire_dps × 本值;摊得开、每次对账只处理一部分燃烧区)</t>
+          <t>液洼刚出现时的半径(米,× fg.TbFluidLeak.radiusScale)</t>
         </is>
       </c>
     </row>
@@ -8166,15 +8166,15 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr">
         <is>
-          <t>logistics.leak.sync_seconds</t>
+          <t>logistics.leak.max_radius</t>
         </is>
       </c>
       <c r="C484" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>液洼对账间隔(游戏秒):击穿是否还在、半径扩散 / 消退、火烧坏范围里的设施;只看步序号,与观察无关</t>
+          <t>液洼一直漏下去最大能扩到的半径(米,× radiusScale)</t>
         </is>
       </c>
     </row>
@@ -8182,15 +8182,15 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr">
         <is>
-          <t>logistics.leak.max_puddles</t>
+          <t>logistics.leak.grow_seconds</t>
         </is>
       </c>
       <c r="C485" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>家园同时存在的液洼上限(超出的破口不再新增液洼并计数;一格管线最多一摊)</t>
+          <t>液洼从刚出现扩到最大半径要的游戏秒(一直在漏时)</t>
         </is>
       </c>
     </row>
@@ -8198,15 +8198,15 @@
       <c r="A486" t="inlineStr"/>
       <c r="B486" t="inlineStr">
         <is>
-          <t>logistics.leak.warn_margin_cells</t>
+          <t>logistics.leak.fade_seconds</t>
         </is>
       </c>
       <c r="C486" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>泄漏起火告警:燃烧区半径外再放宽这么多格内有己方管线 / 传送带 / 建筑就发告警</t>
+          <t>修好管线(或冲洗 / 拆掉 / 破口两侧没有同种流体)后,液洼从当前半径缩小到消失要的游戏秒</t>
         </is>
       </c>
     </row>
@@ -8214,15 +8214,15 @@
       <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr">
         <is>
-          <t>logistics.leak.perf.puddles</t>
+          <t>logistics.leak.react_seconds</t>
         </is>
       </c>
       <c r="C487" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>性能验收:同时存在的液洼数(= 上限)</t>
+          <t>液洼整片反应成残留区域(燃油遇火 = 燃烧区)后至少持续的游戏秒(与反应自己的残留时长取大)</t>
         </is>
       </c>
     </row>
@@ -8230,15 +8230,15 @@
       <c r="A488" t="inlineStr"/>
       <c r="B488" t="inlineStr">
         <is>
-          <t>logistics.leak.perf.sync_ms</t>
+          <t>logistics.leak.fire_dps</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>性能验收:48 摊液洼(含一半在燃烧)时热更层一次对账的耗时上限(毫秒)</t>
+          <t>反应成的残留区域带持续伤害(燃烧)时,每游戏秒烧掉范围里管线 / 传送带 / 建筑的耐久(连锁烧毁产线)</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       <c r="A489" t="inlineStr"/>
       <c r="B489" t="inlineStr">
         <is>
-          <t>raid.result.wreck_per_unit</t>
+          <t>logistics.leak.fire_tick_seconds</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台普通攻城敌人留下几份敌方残骸(FGR-DEF-051)</t>
+          <t>火烧设施的结算间隔(游戏秒;每摊燃烧区按编号错开,每次扣 fire_dps × 本值;摊得开、每次对账只处理一部分燃烧区)</t>
         </is>
       </c>
     </row>
@@ -8262,15 +8262,15 @@
       <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr">
         <is>
-          <t>raid.result.wreck_per_elite</t>
+          <t>logistics.leak.sync_seconds</t>
         </is>
       </c>
       <c r="C490" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台精英留下几份敌方残骸</t>
+          <t>液洼对账间隔(游戏秒):击穿是否还在、半径扩散 / 消退、火烧坏范围里的设施;只看步序号,与观察无关</t>
         </is>
       </c>
     </row>
@@ -8278,15 +8278,15 @@
       <c r="A491" t="inlineStr"/>
       <c r="B491" t="inlineStr">
         <is>
-          <t>raid.result.wreck_merge_cells</t>
+          <t>logistics.leak.max_puddles</t>
         </is>
       </c>
       <c r="C491" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>突袭结算:离同一波已有残骸堆多少格以内的新残骸并进那一堆(少生成地面物与搬运单)</t>
+          <t>家园同时存在的液洼上限(超出的破口不再新增液洼并计数;一格管线最多一摊)</t>
         </is>
       </c>
     </row>
@@ -8294,15 +8294,15 @@
       <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr">
         <is>
-          <t>raid.result.wreck_pile_max</t>
+          <t>logistics.leak.warn_margin_cells</t>
         </is>
       </c>
       <c r="C492" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>突袭结算:一堆残骸至多几份(一台机器一趟搬完)</t>
+          <t>泄漏起火告警:燃烧区半径外再放宽这么多格内有己方管线 / 传送带 / 建筑就发告警</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr">
         <is>
-          <t>raid.result.piles_max</t>
+          <t>logistics.leak.perf.puddles</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>突袭结算:一次突袭至多记住几堆残骸(超出的照样落地,只是不再合并)</t>
+          <t>性能验收:同时存在的液洼数(= 上限)</t>
         </is>
       </c>
     </row>
@@ -8326,15 +8326,15 @@
       <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr">
         <is>
-          <t>raid.result.drop_module_chance</t>
+          <t>logistics.leak.perf.sync_ms</t>
         </is>
       </c>
       <c r="C494" t="n">
-        <v>0.03</v>
+        <v>0.5</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台敌人掉落未解析模块的概率(FGR-DEF-051“少数情况”;低于远征,远征掉落表在 FG8-LOOT-01)</t>
+          <t>性能验收:48 摊液洼(含一半在燃烧)时热更层一次对账的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -8342,15 +8342,15 @@
       <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr">
         <is>
-          <t>raid.result.drop_firmware_chance</t>
+          <t>raid.result.wreck_per_unit</t>
         </is>
       </c>
       <c r="C495" t="n">
-        <v>0.015</v>
+        <v>1</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>突袭结算:每击毁一台敌人掉落敌方加密固件的概率(同上)</t>
+          <t>突袭结算:每击毁一台普通攻城敌人留下几份敌方残骸(FGR-DEF-051)</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr">
         <is>
-          <t>raid.result.drop_elite_mult</t>
+          <t>raid.result.wreck_per_elite</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>突袭结算:精英的掉落概率倍率</t>
+          <t>突袭结算:每击毁一台精英留下几份敌方残骸</t>
         </is>
       </c>
     </row>
@@ -8374,15 +8374,15 @@
       <c r="A497" t="inlineStr"/>
       <c r="B497" t="inlineStr">
         <is>
-          <t>raid.result.timeline_max</t>
+          <t>raid.result.wreck_merge_cells</t>
         </is>
       </c>
       <c r="C497" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>突袭结算:过程时间线每次至多几条(超出的计数)</t>
+          <t>突袭结算:离同一波已有残骸堆多少格以内的新残骸并进那一堆(少生成地面物与搬运单)</t>
         </is>
       </c>
     </row>
@@ -8390,15 +8390,15 @@
       <c r="A498" t="inlineStr"/>
       <c r="B498" t="inlineStr">
         <is>
-          <t>raid.result.losses_max</t>
+          <t>raid.result.wreck_pile_max</t>
         </is>
       </c>
       <c r="C498" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>突袭结算:损失明细每次至多几条(合计照常累加)</t>
+          <t>突袭结算:一堆残骸至多几份(一台机器一趟搬完)</t>
         </is>
       </c>
     </row>
@@ -8406,15 +8406,15 @@
       <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr">
         <is>
-          <t>raid.result.contrib_max</t>
+          <t>raid.result.piles_max</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>突袭结算:贡献记录每次至多几个击毁者(更多的并进“其它”)</t>
+          <t>突袭结算:一次突袭至多记住几堆残骸(超出的照样落地,只是不再合并)</t>
         </is>
       </c>
     </row>
@@ -8422,15 +8422,15 @@
       <c r="A500" t="inlineStr"/>
       <c r="B500" t="inlineStr">
         <is>
-          <t>raid.result.contrib_top</t>
+          <t>raid.result.drop_module_chance</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>3</v>
+        <v>0.03</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>突袭结算 / 离家报告:贡献排行显示前几名</t>
+          <t>突袭结算:每击毁一台敌人掉落未解析模块的概率(FGR-DEF-051“少数情况”;低于远征,远征掉落表在 FG8-LOOT-01)</t>
         </is>
       </c>
     </row>
@@ -8438,15 +8438,15 @@
       <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr">
         <is>
-          <t>raid.result.route_seconds</t>
+          <t>raid.result.drop_firmware_chance</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>10</v>
+        <v>0.015</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>残骸去向:每隔几游戏秒检查一次仓库里的残骸要不要送去解析台 / 回收站</t>
+          <t>突袭结算:每击毁一台敌人掉落敌方加密固件的概率(同上)</t>
         </is>
       </c>
     </row>
@@ -8454,15 +8454,15 @@
       <c r="A502" t="inlineStr"/>
       <c r="B502" t="inlineStr">
         <is>
-          <t>raid.result.route_batch</t>
+          <t>raid.result.drop_elite_mult</t>
         </is>
       </c>
       <c r="C502" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>残骸去向:一张送货单至多几份残骸</t>
+          <t>突袭结算:精英的掉落概率倍率</t>
         </is>
       </c>
     </row>
@@ -8470,15 +8470,15 @@
       <c r="A503" t="inlineStr"/>
       <c r="B503" t="inlineStr">
         <is>
-          <t>raid.result.autosave_on_warning</t>
+          <t>raid.result.timeline_max</t>
         </is>
       </c>
       <c r="C503" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>突袭预警发出时自动存档(1=开;同一波只存一次;核心被摧毁后不再存)</t>
+          <t>突袭结算:过程时间线每次至多几条(超出的计数)</t>
         </is>
       </c>
     </row>
@@ -8486,15 +8486,15 @@
       <c r="A504" t="inlineStr"/>
       <c r="B504" t="inlineStr">
         <is>
-          <t>raid.result.panel_refresh_seconds</t>
+          <t>raid.result.losses_max</t>
         </is>
       </c>
       <c r="C504" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>突袭历史面板:进行中的突袭每隔几真实秒重读一次</t>
+          <t>突袭结算:损失明细每次至多几条(合计照常累加)</t>
         </is>
       </c>
     </row>
@@ -8502,15 +8502,15 @@
       <c r="A505" t="inlineStr"/>
       <c r="B505" t="inlineStr">
         <is>
-          <t>raid.result.perf_ms</t>
+          <t>raid.result.contrib_max</t>
         </is>
       </c>
       <c r="C505" t="n">
-        <v>0.05</v>
+        <v>24</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>性能验收:热更层处理一次击毁事件(残骸 / 掉落 / 贡献 / 结算记账)的平均耗时上限(毫秒)</t>
+          <t>突袭结算:贡献记录每次至多几个击毁者(更多的并进“其它”)</t>
         </is>
       </c>
     </row>
@@ -8518,15 +8518,15 @@
       <c r="A506" t="inlineStr"/>
       <c r="B506" t="inlineStr">
         <is>
-          <t>difficulty.custom_min</t>
+          <t>raid.result.contrib_top</t>
         </is>
       </c>
       <c r="C506" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>自定义难度:三个滑条(突袭频率 / 规模 / 预警时间倍率)的下限</t>
+          <t>突袭结算 / 离家报告:贡献排行显示前几名</t>
         </is>
       </c>
     </row>
@@ -8534,15 +8534,15 @@
       <c r="A507" t="inlineStr"/>
       <c r="B507" t="inlineStr">
         <is>
-          <t>difficulty.custom_max</t>
+          <t>raid.result.route_seconds</t>
         </is>
       </c>
       <c r="C507" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>自定义难度:三个滑条的上限</t>
+          <t>残骸去向:每隔几游戏秒检查一次仓库里的残骸要不要送去解析台 / 回收站</t>
         </is>
       </c>
     </row>
@@ -8550,15 +8550,15 @@
       <c r="A508" t="inlineStr"/>
       <c r="B508" t="inlineStr">
         <is>
-          <t>difficulty.custom_step</t>
+          <t>raid.result.route_batch</t>
         </is>
       </c>
       <c r="C508" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>自定义难度:滑条步长(存档里的值按它取整,同一设置同一字节)</t>
+          <t>残骸去向:一张送货单至多几份残骸</t>
         </is>
       </c>
     </row>
@@ -8566,15 +8566,15 @@
       <c r="A509" t="inlineStr"/>
       <c r="B509" t="inlineStr">
         <is>
-          <t>difficulty.history_max</t>
+          <t>raid.result.autosave_on_warning</t>
         </is>
       </c>
       <c r="C509" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>难度修改记录最多保留几条(更早的只留计数;开局难度与“是否离开过开局难度”永久保留)</t>
+          <t>突袭预警发出时自动存档(1=开;同一波只存一次;核心被摧毁后不再存)</t>
         </is>
       </c>
     </row>
@@ -8582,15 +8582,15 @@
       <c r="A510" t="inlineStr"/>
       <c r="B510" t="inlineStr">
         <is>
-          <t>building.name.max_chars</t>
+          <t>raid.result.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C510" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
+          <t>突袭历史面板:进行中的突袭每隔几真实秒重读一次</t>
         </is>
       </c>
     </row>
@@ -8598,15 +8598,15 @@
       <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr">
         <is>
-          <t>building.repair.min_seconds</t>
+          <t>raid.result.perf_ms</t>
         </is>
       </c>
       <c r="C511" t="n">
-        <v>2</v>
+        <v>0.05</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>一次维修工期的下限(秒)</t>
+          <t>性能验收:热更层处理一次击毁事件(残骸 / 掉落 / 贡献 / 结算记账)的平均耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -8614,15 +8614,15 @@
       <c r="A512" t="inlineStr"/>
       <c r="B512" t="inlineStr">
         <is>
-          <t>building.jump.max_links</t>
+          <t>difficulty.custom_min</t>
         </is>
       </c>
       <c r="C512" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
+          <t>自定义难度:三个滑条(突袭频率 / 规模 / 预警时间倍率)的下限</t>
         </is>
       </c>
     </row>
@@ -8630,15 +8630,15 @@
       <c r="A513" t="inlineStr"/>
       <c r="B513" t="inlineStr">
         <is>
-          <t>building.stats.window_minutes</t>
+          <t>difficulty.custom_max</t>
         </is>
       </c>
       <c r="C513" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
+          <t>自定义难度:三个滑条的上限</t>
         </is>
       </c>
     </row>
@@ -8646,15 +8646,15 @@
       <c r="A514" t="inlineStr"/>
       <c r="B514" t="inlineStr">
         <is>
-          <t>building.stats.bucket_seconds</t>
+          <t>difficulty.custom_step</t>
         </is>
       </c>
       <c r="C514" t="n">
-        <v>60</v>
+        <v>0.1</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
+          <t>自定义难度:滑条步长(存档里的值按它取整,同一设置同一字节)</t>
         </is>
       </c>
     </row>
@@ -8662,15 +8662,15 @@
       <c r="A515" t="inlineStr"/>
       <c r="B515" t="inlineStr">
         <is>
-          <t>building.batch.confirm</t>
+          <t>difficulty.history_max</t>
         </is>
       </c>
       <c r="C515" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
+          <t>难度修改记录最多保留几条(更早的只留计数;开局难度与“是否离开过开局难度”永久保留)</t>
         </is>
       </c>
     </row>
@@ -8678,15 +8678,15 @@
       <c r="A516" t="inlineStr"/>
       <c r="B516" t="inlineStr">
         <is>
-          <t>ui.build.result_seconds</t>
+          <t>building.name.max_chars</t>
         </is>
       </c>
       <c r="C516" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
+          <t>建筑自定义名字最多几个字符(FGR-ECO-011 改名;英文通常更长,界面按这个长度留宽)</t>
         </is>
       </c>
     </row>
@@ -8694,15 +8694,15 @@
       <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr">
         <is>
-          <t>logistics.port.keep.1</t>
+          <t>building.repair.min_seconds</t>
         </is>
       </c>
       <c r="C517" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
+          <t>一次维修工期的下限(秒)</t>
         </is>
       </c>
     </row>
@@ -8710,15 +8710,15 @@
       <c r="A518" t="inlineStr"/>
       <c r="B518" t="inlineStr">
         <is>
-          <t>logistics.port.keep.2</t>
+          <t>building.jump.max_links</t>
         </is>
       </c>
       <c r="C518" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>预设 2</t>
+          <t>面板里上游 / 下游各列几座建筑(界面固定 4 个槽位,超过 4 按 4)</t>
         </is>
       </c>
     </row>
@@ -8726,15 +8726,15 @@
       <c r="A519" t="inlineStr"/>
       <c r="B519" t="inlineStr">
         <is>
-          <t>logistics.port.keep.3</t>
+          <t>building.stats.window_minutes</t>
         </is>
       </c>
       <c r="C519" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>预设 3</t>
+          <t>面板效率与产出统计的时间窗口(游戏分钟,FGR-ECO-011“最近 10 分钟”)</t>
         </is>
       </c>
     </row>
@@ -8742,15 +8742,15 @@
       <c r="A520" t="inlineStr"/>
       <c r="B520" t="inlineStr">
         <is>
-          <t>logistics.port.keep.4</t>
+          <t>building.stats.bucket_seconds</t>
         </is>
       </c>
       <c r="C520" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>预设 4</t>
+          <t>统计按多少游戏秒一桶聚合(窗口 = 桶数 × 桶长;按完成事件累加,不每帧遍历)</t>
         </is>
       </c>
     </row>
@@ -8758,15 +8758,15 @@
       <c r="A521" t="inlineStr"/>
       <c r="B521" t="inlineStr">
         <is>
-          <t>logistics.port.keep.5</t>
+          <t>building.batch.confirm</t>
         </is>
       </c>
       <c r="C521" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>预设 5</t>
+          <t>批量启用 / 禁用 / 改优先级:改动超过这么多座先确认(B04;1 = 只改本座以外的都确认)</t>
         </is>
       </c>
     </row>
@@ -8774,15 +8774,15 @@
       <c r="A522" t="inlineStr"/>
       <c r="B522" t="inlineStr">
         <is>
-          <t>logistics.port.keep.6</t>
+          <t>ui.build.result_seconds</t>
         </is>
       </c>
       <c r="C522" t="n">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>预设 6</t>
+          <t>建造模式状态行:操作结果在鼠标指向别的东西后还留多久(真实秒,FG-GAP-091)</t>
         </is>
       </c>
     </row>
@@ -8790,15 +8790,15 @@
       <c r="A523" t="inlineStr"/>
       <c r="B523" t="inlineStr">
         <is>
-          <t>rules.check_seconds</t>
+          <t>logistics.port.keep.1</t>
         </is>
       </c>
       <c r="C523" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
+          <t>仓库输出口“保留 N 件”下拉的预设 1(FG-GAP-093)</t>
         </is>
       </c>
     </row>
@@ -8806,15 +8806,15 @@
       <c r="A524" t="inlineStr"/>
       <c r="B524" t="inlineStr">
         <is>
-          <t>rules.log_max</t>
+          <t>logistics.port.keep.2</t>
         </is>
       </c>
       <c r="C524" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
+          <t>预设 2</t>
         </is>
       </c>
     </row>
@@ -8822,15 +8822,15 @@
       <c r="A525" t="inlineStr"/>
       <c r="B525" t="inlineStr">
         <is>
-          <t>rules.max_count</t>
+          <t>logistics.port.keep.3</t>
         </is>
       </c>
       <c r="C525" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
+          <t>预设 3</t>
         </is>
       </c>
     </row>
@@ -8838,15 +8838,15 @@
       <c r="A526" t="inlineStr"/>
       <c r="B526" t="inlineStr">
         <is>
-          <t>rules.supply.batch_default</t>
+          <t>logistics.port.keep.4</t>
         </is>
       </c>
       <c r="C526" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>阈值补给每次送几件的默认值</t>
+          <t>预设 4</t>
         </is>
       </c>
     </row>
@@ -8854,15 +8854,15 @@
       <c r="A527" t="inlineStr"/>
       <c r="B527" t="inlineStr">
         <is>
-          <t>rules.supply.batch_max</t>
+          <t>logistics.port.keep.5</t>
         </is>
       </c>
       <c r="C527" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>阈值补给每次最多送几件</t>
+          <t>预设 5</t>
         </is>
       </c>
     </row>
@@ -8870,15 +8870,15 @@
       <c r="A528" t="inlineStr"/>
       <c r="B528" t="inlineStr">
         <is>
-          <t>rules.supply.unload_seconds</t>
+          <t>logistics.port.keep.6</t>
         </is>
       </c>
       <c r="C528" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>机器把补给放进建筑要多久(游戏秒)</t>
+          <t>预设 6</t>
         </is>
       </c>
     </row>
@@ -8886,15 +8886,15 @@
       <c r="A529" t="inlineStr"/>
       <c r="B529" t="inlineStr">
         <is>
-          <t>rules.repair_bay.slots</t>
+          <t>rules.check_seconds</t>
         </is>
       </c>
       <c r="C529" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>一座维修台同时修几台机器</t>
+          <t>常驻规则按固定频率检查的间隔(游戏秒;FG04 第 7 节“初值:每游戏分钟一次”,不每帧运行)</t>
         </is>
       </c>
     </row>
@@ -8902,15 +8902,15 @@
       <c r="A530" t="inlineStr"/>
       <c r="B530" t="inlineStr">
         <is>
-          <t>rules.repair_bay.heal_fraction_per_second</t>
+          <t>rules.log_max</t>
         </is>
       </c>
       <c r="C530" t="n">
-        <v>0.02</v>
+        <v>100</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
+          <t>触发日志只保留最近多少条(FG04 第 6 节“日志只保留最近 100 条”)</t>
         </is>
       </c>
     </row>
@@ -8918,15 +8918,15 @@
       <c r="A531" t="inlineStr"/>
       <c r="B531" t="inlineStr">
         <is>
-          <t>rules.war.repair_priority</t>
+          <t>rules.max_count</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
+          <t>最多多少条规则(B12:超大数量时界面仍可用)</t>
         </is>
       </c>
     </row>
@@ -8934,15 +8934,15 @@
       <c r="A532" t="inlineStr"/>
       <c r="B532" t="inlineStr">
         <is>
-          <t>roster.name_max_length</t>
+          <t>rules.supply.batch_default</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
+          <t>阈值补给每次送几件的默认值</t>
         </is>
       </c>
     </row>
@@ -8950,15 +8950,15 @@
       <c r="A533" t="inlineStr"/>
       <c r="B533" t="inlineStr">
         <is>
-          <t>roster.labor_refresh_seconds</t>
+          <t>rules.supply.batch_max</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
+          <t>阈值补给每次最多送几件</t>
         </is>
       </c>
     </row>
@@ -8966,15 +8966,15 @@
       <c r="A534" t="inlineStr"/>
       <c r="B534" t="inlineStr">
         <is>
-          <t>roster.batch_max</t>
+          <t>rules.supply.unload_seconds</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
+          <t>机器把补给放进建筑要多久(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -8982,15 +8982,15 @@
       <c r="A535" t="inlineStr"/>
       <c r="B535" t="inlineStr">
         <is>
-          <t>work.history_keep</t>
+          <t>rules.repair_bay.slots</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>一座维修台同时修几台机器</t>
         </is>
       </c>
     </row>
@@ -8998,15 +8998,15 @@
       <c r="A536" t="inlineStr"/>
       <c r="B536" t="inlineStr">
         <is>
-          <t>ledger.history_keep</t>
+          <t>rules.repair_bay.heal_fraction_per_second</t>
         </is>
       </c>
       <c r="C536" t="n">
-        <v>600</v>
+        <v>0.02</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
+          <t>维修台每游戏秒修复机器最大耐久的比例(0.02 = 50 秒修满)</t>
         </is>
       </c>
     </row>
@@ -9014,15 +9014,15 @@
       <c r="A537" t="inlineStr"/>
       <c r="B537" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_001</t>
+          <t>rules.war.repair_priority</t>
         </is>
       </c>
       <c r="C537" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
+          <t>战时预案把维修工作单提到的优先级(= 施工优先级“最高”)</t>
         </is>
       </c>
     </row>
@@ -9030,15 +9030,15 @@
       <c r="A538" t="inlineStr"/>
       <c r="B538" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_002</t>
+          <t>roster.name_max_length</t>
         </is>
       </c>
       <c r="C538" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>ERC-002 每趟取料上限</t>
+          <t>机器名字最多多少个字(按字符计,中英文都算 1 个;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -9046,15 +9046,15 @@
       <c r="A539" t="inlineStr"/>
       <c r="B539" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.erc_003</t>
+          <t>roster.labor_refresh_seconds</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>ERC-003 战斗履带每趟取料上限</t>
+          <t>顶栏劳动力与名册列表最多每多少真实秒重算一次(O(机器数 + 工单数),不每帧算)</t>
         </is>
       </c>
     </row>
@@ -9062,15 +9062,15 @@
       <c r="A540" t="inlineStr"/>
       <c r="B540" t="inlineStr">
         <is>
-          <t>build.carry_per_trip.chassis_hover</t>
+          <t>roster.batch_max</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>维修悬浮每趟取料上限</t>
+          <t>名册一次批量改岗位最多多少台(超过的不改并说明)</t>
         </is>
       </c>
     </row>
@@ -9078,15 +9078,15 @@
       <c r="A541" t="inlineStr"/>
       <c r="B541" t="inlineStr">
         <is>
-          <t>eco.stats.buckets</t>
+          <t>work.history_keep</t>
         </is>
       </c>
       <c r="C541" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
+          <t>已结束的工单(完成 / 取消 / 失败)最多保留多少张(更早的在派工评估时清掉;规则与岗位还在引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -9094,15 +9094,15 @@
       <c r="A542" t="inlineStr"/>
       <c r="B542" t="inlineStr">
         <is>
-          <t>eco.stats.tier0.bucket_seconds</t>
+          <t>ledger.history_keep</t>
         </is>
       </c>
       <c r="C542" t="n">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
+          <t>已结束的资源事务(已结算 / 取消 / 失败)最多保留多少条(更早的在派工评估时清掉;在办工单引用的不清;DEBT-FG3LOG02-09)</t>
         </is>
       </c>
     </row>
@@ -9110,15 +9110,15 @@
       <c r="A543" t="inlineStr"/>
       <c r="B543" t="inlineStr">
         <is>
-          <t>eco.stats.tier1.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_001</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
+          <t>ERC-001 搬运轮式每趟取料上限(缺这一行时用 build.carry_per_trip)</t>
         </is>
       </c>
     </row>
@@ -9126,15 +9126,15 @@
       <c r="A544" t="inlineStr"/>
       <c r="B544" t="inlineStr">
         <is>
-          <t>eco.stats.tier2.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_002</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
+          <t>ERC-002 每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -9142,15 +9142,15 @@
       <c r="A545" t="inlineStr"/>
       <c r="B545" t="inlineStr">
         <is>
-          <t>eco.stats.tier3.bucket_seconds</t>
+          <t>build.carry_per_trip.erc_003</t>
         </is>
       </c>
       <c r="C545" t="n">
-        <v>1200</v>
+        <v>40</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
+          <t>ERC-003 战斗履带每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -9158,15 +9158,15 @@
       <c r="A546" t="inlineStr"/>
       <c r="B546" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_minutes</t>
+          <t>build.carry_per_trip.chassis_hover</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
+          <t>维修悬浮每趟取料上限</t>
         </is>
       </c>
     </row>
@@ -9174,15 +9174,15 @@
       <c r="A547" t="inlineStr"/>
       <c r="B547" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_probe_seconds</t>
+          <t>eco.stats.buckets</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
+          <t>每个时间窗口的桶数(窗口 = 桶长 × 桶数;也是速率曲线的点数)</t>
         </is>
       </c>
     </row>
@@ -9190,15 +9190,15 @@
       <c r="A548" t="inlineStr"/>
       <c r="B548" t="inlineStr">
         <is>
-          <t>eco.stats.deficit_check_seconds</t>
+          <t>eco.stats.tier0.bucket_seconds</t>
         </is>
       </c>
       <c r="C548" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
+          <t>1 分钟窗口每桶多少游戏秒(2 × 30 = 60)</t>
         </is>
       </c>
     </row>
@@ -9206,15 +9206,15 @@
       <c r="A549" t="inlineStr"/>
       <c r="B549" t="inlineStr">
         <is>
-          <t>eco.stats.panel_refresh_seconds</t>
+          <t>eco.stats.tier1.bucket_seconds</t>
         </is>
       </c>
       <c r="C549" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
+          <t>10 分钟窗口每桶多少游戏秒(20 × 30 = 600)</t>
         </is>
       </c>
     </row>
@@ -9222,15 +9222,15 @@
       <c r="A550" t="inlineStr"/>
       <c r="B550" t="inlineStr">
         <is>
-          <t>eco.stats.bottleneck_top</t>
+          <t>eco.stats.tier2.bucket_seconds</t>
         </is>
       </c>
       <c r="C550" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>瓶颈页最多列几种物品</t>
+          <t>1 小时窗口每桶多少游戏秒(120 × 30 = 3600)</t>
         </is>
       </c>
     </row>
@@ -9238,15 +9238,15 @@
       <c r="A551" t="inlineStr"/>
       <c r="B551" t="inlineStr">
         <is>
-          <t>eco.topbar.max_pins</t>
+          <t>eco.stats.tier3.bucket_seconds</t>
         </is>
       </c>
       <c r="C551" t="n">
-        <v>8</v>
+        <v>1200</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
+          <t>10 小时窗口每桶多少游戏秒(1200 × 30 = 36000)</t>
         </is>
       </c>
     </row>
@@ -9254,15 +9254,15 @@
       <c r="A552" t="inlineStr"/>
       <c r="B552" t="inlineStr">
         <is>
-          <t>eco.topbar.refresh_seconds</t>
+          <t>eco.stats.deficit_minutes</t>
         </is>
       </c>
       <c r="C552" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
+          <t>持续赤字:某物品消耗大于产出超过多少游戏分钟发警告(FGR-ECO-050 初值 10)</t>
         </is>
       </c>
     </row>
@@ -9270,15 +9270,15 @@
       <c r="A553" t="inlineStr"/>
       <c r="B553" t="inlineStr">
         <is>
-          <t>eco.topbar.rate_window</t>
+          <t>eco.stats.deficit_probe_seconds</t>
         </is>
       </c>
       <c r="C553" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
+          <t>判断“消耗大于产出”看最近多少游戏秒的收支(短于它的配方周期抖动不算赤字)</t>
         </is>
       </c>
     </row>
@@ -9286,15 +9286,15 @@
       <c r="A554" t="inlineStr"/>
       <c r="B554" t="inlineStr">
         <is>
-          <t>eco.topbar.max_subnets</t>
+          <t>eco.stats.deficit_check_seconds</t>
         </is>
       </c>
       <c r="C554" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
+          <t>每多少游戏秒检查一次持续赤字(按世界步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -9302,15 +9302,15 @@
       <c r="A555" t="inlineStr"/>
       <c r="B555" t="inlineStr">
         <is>
-          <t>eco.topbar.target_tolerance</t>
+          <t>eco.stats.panel_refresh_seconds</t>
         </is>
       </c>
       <c r="C555" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
+          <t>统计面板打开时每多少真实秒重读一次(速率随时间变化;关着时不读)</t>
         </is>
       </c>
     </row>
@@ -9318,15 +9318,15 @@
       <c r="A556" t="inlineStr"/>
       <c r="B556" t="inlineStr">
         <is>
-          <t>eco.planner.max_depth</t>
+          <t>eco.stats.bottleneck_top</t>
         </is>
       </c>
       <c r="C556" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
+          <t>瓶颈页最多列几种物品</t>
         </is>
       </c>
     </row>
@@ -9334,15 +9334,15 @@
       <c r="A557" t="inlineStr"/>
       <c r="B557" t="inlineStr">
         <is>
-          <t>eco.planner.default_rate</t>
+          <t>eco.topbar.max_pins</t>
         </is>
       </c>
       <c r="C557" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>规划助手默认目标产量(每游戏分钟)</t>
+          <t>资源顶栏最多固定几种物品(超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -9350,15 +9350,15 @@
       <c r="A558" t="inlineStr"/>
       <c r="B558" t="inlineStr">
         <is>
-          <t>eco.planner.max_rate</t>
+          <t>eco.topbar.refresh_seconds</t>
         </is>
       </c>
       <c r="C558" t="n">
-        <v>100000</v>
+        <v>0.5</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
+          <t>资源顶栏每多少真实秒刷新一次读数(固定 / 语言变化立刻刷新)</t>
         </is>
       </c>
     </row>
@@ -9366,15 +9366,15 @@
       <c r="A559" t="inlineStr"/>
       <c r="B559" t="inlineStr">
         <is>
-          <t>away.reports_keep</t>
+          <t>eco.topbar.rate_window</t>
         </is>
       </c>
       <c r="C559" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
+          <t>顶栏速率用哪个时间窗口(0 = 1 分钟、1 = 10 分钟、2 = 1 小时、3 = 10 小时;初值 10 分钟,配方周期长时 1 分钟会跳动)</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       <c r="A560" t="inlineStr"/>
       <c r="B560" t="inlineStr">
         <is>
-          <t>away.bottleneck_top</t>
+          <t>eco.topbar.max_subnets</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
+          <t>顶栏最多单独显示几个电网(其余合成“+N 个电网”)</t>
         </is>
       </c>
     </row>
@@ -9398,15 +9398,15 @@
       <c r="A561" t="inlineStr"/>
       <c r="B561" t="inlineStr">
         <is>
-          <t>away.items_max</t>
+          <t>eco.topbar.target_tolerance</t>
         </is>
       </c>
       <c r="C561" t="n">
-        <v>12</v>
+        <v>0.05</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
+          <t>顶栏“达标”的容差(产量 ≥ 目标 × (1 - 容差);与 FGT-ECO-008 的 5% 一致)</t>
         </is>
       </c>
     </row>
@@ -9414,15 +9414,15 @@
       <c r="A562" t="inlineStr"/>
       <c r="B562" t="inlineStr">
         <is>
-          <t>away.entries_max</t>
+          <t>eco.planner.max_depth</t>
         </is>
       </c>
       <c r="C562" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
+          <t>规划助手沿配方往上游最多展开几层(循环或更深的当作原料并写明)</t>
         </is>
       </c>
     </row>
@@ -9430,15 +9430,15 @@
       <c r="A563" t="inlineStr"/>
       <c r="B563" t="inlineStr">
         <is>
-          <t>away.rules_max</t>
+          <t>eco.planner.default_rate</t>
         </is>
       </c>
       <c r="C563" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
+          <t>规划助手默认目标产量(每游戏分钟)</t>
         </is>
       </c>
     </row>
@@ -9446,15 +9446,15 @@
       <c r="A564" t="inlineStr"/>
       <c r="B564" t="inlineStr">
         <is>
-          <t>away.outages_max</t>
+          <t>eco.planner.max_rate</t>
         </is>
       </c>
       <c r="C564" t="n">
-        <v>20</v>
+        <v>100000</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>离家报告最多记几段停电(超出的只计数)</t>
+          <t>规划助手目标产量上限(每游戏分钟;超过拒绝并说明)</t>
         </is>
       </c>
     </row>
@@ -9462,15 +9462,15 @@
       <c r="A565" t="inlineStr"/>
       <c r="B565" t="inlineStr">
         <is>
-          <t>away.machines_max</t>
+          <t>away.reports_keep</t>
         </is>
       </c>
       <c r="C565" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
+          <t>离家报告保留最近几份(FGR-ECO-060“随时可以查看最近 3 份报告”;更早的丢掉)</t>
         </is>
       </c>
     </row>
@@ -9478,15 +9478,15 @@
       <c r="A566" t="inlineStr"/>
       <c r="B566" t="inlineStr">
         <is>
-          <t>alarm.jam_seconds</t>
+          <t>away.bottleneck_top</t>
         </is>
       </c>
       <c r="C566" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
+          <t>离家报告列出前几个瓶颈(FGR-ECO-060“前三个瓶颈”;按离家期间缺料时长)</t>
         </is>
       </c>
     </row>
@@ -9494,15 +9494,15 @@
       <c r="A567" t="inlineStr"/>
       <c r="B567" t="inlineStr">
         <is>
-          <t>alarm.machine_wounded_fraction</t>
+          <t>away.items_max</t>
         </is>
       </c>
       <c r="C567" t="n">
-        <v>0.3</v>
+        <v>12</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
+          <t>离家报告生产段最多逐行列几种物品(按净产量绝对值排序;其余合成“另有 N 种”一行)</t>
         </is>
       </c>
     </row>
@@ -9510,15 +9510,15 @@
       <c r="A568" t="inlineStr"/>
       <c r="B568" t="inlineStr">
         <is>
-          <t>eco.softlock.check_seconds</t>
+          <t>away.entries_max</t>
         </is>
       </c>
       <c r="C568" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
+          <t>离家报告最多记多少条事件(突袭 / 天气 / 事件 / 研究 / 建筑受损 / 电力事件…;超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -9526,15 +9526,15 @@
       <c r="A569" t="inlineStr"/>
       <c r="B569" t="inlineStr">
         <is>
-          <t>eco.softlock.print_min_machines</t>
+          <t>away.rules_max</t>
         </is>
       </c>
       <c r="C569" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
+          <t>离家报告最多记多少条常驻规则动作(超出的只计数;FG-GAP-098)</t>
         </is>
       </c>
     </row>
@@ -9542,15 +9542,15 @@
       <c r="A570" t="inlineStr"/>
       <c r="B570" t="inlineStr">
         <is>
-          <t>eco.softlock.print_health</t>
+          <t>away.outages_max</t>
         </is>
       </c>
       <c r="C570" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
+          <t>离家报告最多记几段停电(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -9558,15 +9558,15 @@
       <c r="A571" t="inlineStr"/>
       <c r="B571" t="inlineStr">
         <is>
-          <t>eco.softlock.core_scrap_per_minute</t>
+          <t>away.machines_max</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
+          <t>离家报告最多记几台机器的伤势 / 阵亡(超出的只计数)</t>
         </is>
       </c>
     </row>
@@ -9574,15 +9574,15 @@
       <c r="A572" t="inlineStr"/>
       <c r="B572" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_check_seconds</t>
+          <t>alarm.jam_seconds</t>
         </is>
       </c>
       <c r="C572" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
+          <t>生产建筑缺料 / 输出堵塞持续多少游戏秒算“持续缺料 / 输出持续堵塞”(发一次警告,进告警的“工厂堵塞”级)</t>
         </is>
       </c>
     </row>
@@ -9590,15 +9590,15 @@
       <c r="A573" t="inlineStr"/>
       <c r="B573" t="inlineStr">
         <is>
-          <t>eco.softlock.loop_stall_seconds</t>
+          <t>alarm.machine_wounded_fraction</t>
         </is>
       </c>
       <c r="C573" t="n">
-        <v>120</v>
+        <v>0.3</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
+          <t>机器耐久降到上限的多少以下算“重伤”(发一次警告,进告警的“机器重伤”级;与撤离时的重伤经历同一阈值)</t>
         </is>
       </c>
     </row>
@@ -9606,15 +9606,15 @@
       <c r="A574" t="inlineStr"/>
       <c r="B574" t="inlineStr">
         <is>
-          <t>eco.softlock.reach_check_seconds</t>
+          <t>eco.softlock.check_seconds</t>
         </is>
       </c>
       <c r="C574" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
+          <t>应急打印 / 核心产废料的检查间隔(游戏秒;按世界步序号,与观察无关;只数机器、只在废料为0时看回收站)</t>
         </is>
       </c>
     </row>
@@ -9622,15 +9622,15 @@
       <c r="A575" t="inlineStr"/>
       <c r="B575" t="inlineStr">
         <is>
-          <t>eco.softlock.unreachable_seconds</t>
+          <t>eco.softlock.print_min_machines</t>
         </is>
       </c>
       <c r="C575" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
+          <t>家园机器少于这么多台时归还核心每个游戏日免费打印一台搬运机(FGR-ECO-070 初值 2)</t>
         </is>
       </c>
     </row>
@@ -9638,15 +9638,15 @@
       <c r="A576" t="inlineStr"/>
       <c r="B576" t="inlineStr">
         <is>
-          <t>env.daynight.night_start_hour</t>
+          <t>eco.softlock.print_health</t>
         </is>
       </c>
       <c r="C576" t="n">
-        <v>20.4</v>
+        <v>100</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>入夜时刻(游戏小时,0~24);初值20:24,夜晚以午夜为中心</t>
+          <t>应急打印的搬运机出厂耐久(与装配站造的同型机器一致)</t>
         </is>
       </c>
     </row>
@@ -9654,15 +9654,15 @@
       <c r="A577" t="inlineStr"/>
       <c r="B577" t="inlineStr">
         <is>
-          <t>env.daynight.night_hours</t>
+          <t>eco.softlock.core_scrap_per_minute</t>
         </is>
       </c>
       <c r="C577" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>夜晚持续多少游戏小时;7.2=1x下6分钟(FG07 第10节:白天14分钟,夜晚6分钟)</t>
+          <t>废料为0且没有能工作的回收站时归还核心每分钟产出的废料(FGR-ECO-070 初值 1);产到够造一座回收站为止</t>
         </is>
       </c>
     </row>
@@ -9670,15 +9670,15 @@
       <c r="A578" t="inlineStr"/>
       <c r="B578" t="inlineStr">
         <is>
-          <t>env.daynight.twilight_hours</t>
+          <t>eco.softlock.loop_check_seconds</t>
         </is>
       </c>
       <c r="C578" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>黄昏/黎明过渡多少游戏小时(入夜前光照从1降到0、天亮后从0升到1;夜晚本身光照恒为0)</t>
+          <t>传送带闭环死锁检查间隔(游戏秒;只看有环的网络,O(网络数))</t>
         </is>
       </c>
     </row>
@@ -9686,15 +9686,15 @@
       <c r="A579" t="inlineStr"/>
       <c r="B579" t="inlineStr">
         <is>
-          <t>env.calendar.days</t>
+          <t>eco.softlock.loop_stall_seconds</t>
         </is>
       </c>
       <c r="C579" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>日历面板显示今天起几个游戏日(1~14)</t>
+          <t>传送带闭环里的物品连续这么久既不减少也没有被取走就警告(FGR-ECO-072)</t>
         </is>
       </c>
     </row>
@@ -9702,15 +9702,15 @@
       <c r="A580" t="inlineStr"/>
       <c r="B580" t="inlineStr">
         <is>
-          <t>env.light.night_tint_r</t>
+          <t>eco.softlock.reach_check_seconds</t>
         </is>
       </c>
       <c r="C580" t="n">
-        <v>0.55</v>
+        <v>10</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>夜里主方向光的颜色(乘在场景原光色上)红分量</t>
+          <t>施工 / 维修目标可达性检查间隔(游戏秒;只在有施工 / 维修工单时做,从归还核心与家园机器出发的一次泛洪,Burst)</t>
         </is>
       </c>
     </row>
@@ -9718,15 +9718,15 @@
       <c r="A581" t="inlineStr"/>
       <c r="B581" t="inlineStr">
         <is>
-          <t>env.light.night_tint_g</t>
+          <t>eco.softlock.unreachable_seconds</t>
         </is>
       </c>
       <c r="C581" t="n">
-        <v>0.65</v>
+        <v>20</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>夜里主方向光颜色绿分量</t>
+          <t>施工 / 维修目标连续这么久机器到不了就警告(躲开放置过程中的瞬时围堵,FGR-ECO-072)</t>
         </is>
       </c>
     </row>
@@ -9734,15 +9734,15 @@
       <c r="A582" t="inlineStr"/>
       <c r="B582" t="inlineStr">
         <is>
-          <t>env.light.night_tint_b</t>
+          <t>env.daynight.night_start_hour</t>
         </is>
       </c>
       <c r="C582" t="n">
-        <v>1</v>
+        <v>20.4</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>夜里主方向光颜色蓝分量</t>
+          <t>入夜时刻(游戏小时,0~24);初值20:24,夜晚以午夜为中心</t>
         </is>
       </c>
     </row>
@@ -9750,15 +9750,15 @@
       <c r="A583" t="inlineStr"/>
       <c r="B583" t="inlineStr">
         <is>
-          <t>env.light.apply_epsilon</t>
+          <t>env.daynight.night_hours</t>
         </is>
       </c>
       <c r="C583" t="n">
-        <v>0.003</v>
+        <v>7.2</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>画面亮度变化小于这个数时不写光照(每帧O(1),避免黄昏时每帧改灯)</t>
+          <t>夜晚持续多少游戏小时;7.2=1x下6分钟(FG07 第10节:白天14分钟,夜晚6分钟)</t>
         </is>
       </c>
     </row>
@@ -9766,15 +9766,15 @@
       <c r="A584" t="inlineStr"/>
       <c r="B584" t="inlineStr">
         <is>
-          <t>env.silent.start_offset_hours</t>
+          <t>env.daynight.twilight_hours</t>
         </is>
       </c>
       <c r="C584" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>静默夜从入夜后第几个游戏小时开始(1.6 = 22:00;开始 + 持续必须落在夜里)</t>
+          <t>黄昏/黎明过渡多少游戏小时(入夜前光照从1降到0、天亮后从0升到1;夜晚本身光照恒为0)</t>
         </is>
       </c>
     </row>
@@ -9782,15 +9782,15 @@
       <c r="A585" t="inlineStr"/>
       <c r="B585" t="inlineStr">
         <is>
-          <t>env.silent.duration_hours</t>
+          <t>env.calendar.days</t>
         </is>
       </c>
       <c r="C585" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>静默夜持续多少游戏小时(FG07 第10节:4 小时 = 1x 下约 3.3 分钟)</t>
+          <t>日历面板显示今天起几个游戏日(1~14)</t>
         </is>
       </c>
     </row>
@@ -9798,15 +9798,15 @@
       <c r="A586" t="inlineStr"/>
       <c r="B586" t="inlineStr">
         <is>
-          <t>env.silent.warning_hours</t>
+          <t>env.light.night_tint_r</t>
         </is>
       </c>
       <c r="C586" t="n">
-        <v>1.2</v>
+        <v>0.55</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>开始前多少游戏小时预警(FG07 第10节:1.2 小时 = 1x 下约 60 秒)</t>
+          <t>夜里主方向光的颜色(乘在场景原光色上)红分量</t>
         </is>
       </c>
     </row>
@@ -9814,15 +9814,15 @@
       <c r="A587" t="inlineStr"/>
       <c r="B587" t="inlineStr">
         <is>
-          <t>env.silent.dim_ramp_hours</t>
+          <t>env.light.night_tint_g</t>
         </is>
       </c>
       <c r="C587" t="n">
-        <v>0.25</v>
+        <v>0.65</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>静默夜画面压暗的淡入 / 淡出游戏小时(纯表现)</t>
+          <t>夜里主方向光颜色绿分量</t>
         </is>
       </c>
     </row>
@@ -9830,15 +9830,15 @@
       <c r="A588" t="inlineStr"/>
       <c r="B588" t="inlineStr">
         <is>
-          <t>env.silent.expedition_estimate_hours</t>
+          <t>env.light.night_tint_b</t>
         </is>
       </c>
       <c r="C588" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>远征准备时按多少游戏小时估计远征时长(跨过静默夜就提示;12 小时 = 1x 下 10 分钟)</t>
+          <t>夜里主方向光颜色蓝分量</t>
         </is>
       </c>
     </row>
@@ -9846,15 +9846,15 @@
       <c r="A589" t="inlineStr"/>
       <c r="B589" t="inlineStr">
         <is>
-          <t>env.silent.debris_min</t>
+          <t>env.light.apply_epsilon</t>
         </is>
       </c>
       <c r="C589" t="n">
-        <v>2</v>
+        <v>0.003</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>静默夜结束后家园出现几处风暴残骸(最少)</t>
+          <t>画面亮度变化小于这个数时不写光照(每帧O(1),避免黄昏时每帧改灯)</t>
         </is>
       </c>
     </row>
@@ -9862,15 +9862,15 @@
       <c r="A590" t="inlineStr"/>
       <c r="B590" t="inlineStr">
         <is>
-          <t>env.silent.debris_max</t>
+          <t>env.silent.start_offset_hours</t>
         </is>
       </c>
       <c r="C590" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>风暴残骸最多几处</t>
+          <t>静默夜从入夜后第几个游戏小时开始(1.6 = 22:00;开始 + 持续必须落在夜里)</t>
         </is>
       </c>
     </row>
@@ -9878,15 +9878,15 @@
       <c r="A591" t="inlineStr"/>
       <c r="B591" t="inlineStr">
         <is>
-          <t>env.silent.debris_rare_chance</t>
+          <t>env.silent.duration_hours</t>
         </is>
       </c>
       <c r="C591" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>每次静默夜额外出现一处稀有残骸的概率(0~1)</t>
+          <t>静默夜持续多少游戏小时(FG07 第10节:4 小时 = 1x 下约 3.3 分钟)</t>
         </is>
       </c>
     </row>
@@ -9894,15 +9894,15 @@
       <c r="A592" t="inlineStr"/>
       <c r="B592" t="inlineStr">
         <is>
-          <t>env.silent.debris_ring_min</t>
+          <t>env.silent.warning_hours</t>
         </is>
       </c>
       <c r="C592" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>风暴残骸离归还核心至少几格</t>
+          <t>开始前多少游戏小时预警(FG07 第10节:1.2 小时 = 1x 下约 60 秒)</t>
         </is>
       </c>
     </row>
@@ -9910,15 +9910,15 @@
       <c r="A593" t="inlineStr"/>
       <c r="B593" t="inlineStr">
         <is>
-          <t>env.silent.debris_ring_max</t>
+          <t>env.silent.dim_ramp_hours</t>
         </is>
       </c>
       <c r="C593" t="n">
-        <v>36</v>
+        <v>0.25</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>风暴残骸离归还核心至多几格(按种子地形找空地,找不到就少放)</t>
+          <t>静默夜画面压暗的淡入 / 淡出游戏小时(纯表现)</t>
         </is>
       </c>
     </row>
@@ -9926,15 +9926,15 @@
       <c r="A594" t="inlineStr"/>
       <c r="B594" t="inlineStr">
         <is>
-          <t>env.weather.duration_min_days</t>
+          <t>env.silent.expedition_estimate_hours</t>
         </is>
       </c>
       <c r="C594" t="n">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>一段恶劣天气最短持续几个游戏日(FG07 第10节:0.5~1.5)</t>
+          <t>远征准备时按多少游戏小时估计远征时长(跨过静默夜就提示;12 小时 = 1x 下 10 分钟)</t>
         </is>
       </c>
     </row>
@@ -9942,15 +9942,15 @@
       <c r="A595" t="inlineStr"/>
       <c r="B595" t="inlineStr">
         <is>
-          <t>env.weather.duration_max_days</t>
+          <t>env.silent.debris_min</t>
         </is>
       </c>
       <c r="C595" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>一段恶劣天气最长持续几个游戏日</t>
+          <t>静默夜结束后家园出现几处风暴残骸(最少)</t>
         </is>
       </c>
     </row>
@@ -9958,15 +9958,15 @@
       <c r="A596" t="inlineStr"/>
       <c r="B596" t="inlineStr">
         <is>
-          <t>env.weather.first_day</t>
+          <t>env.silent.debris_max</t>
         </is>
       </c>
       <c r="C596" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>第一段恶劣天气最早在第几个游戏日开始(开局先让玩家站稳;FG16 节奏表另见 FG-GAP)</t>
+          <t>风暴残骸最多几处</t>
         </is>
       </c>
     </row>
@@ -9974,15 +9974,15 @@
       <c r="A597" t="inlineStr"/>
       <c r="B597" t="inlineStr">
         <is>
-          <t>env.weather.warning_days</t>
+          <t>env.silent.debris_rare_chance</t>
         </is>
       </c>
       <c r="C597" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>没有天气预报情报时,恶劣天气开始前多少游戏日预警(FGR-ENV-021:0.5 日)</t>
+          <t>每次静默夜额外出现一处稀有残骸的概率(0~1)</t>
         </is>
       </c>
     </row>
@@ -9990,15 +9990,15 @@
       <c r="A598" t="inlineStr"/>
       <c r="B598" t="inlineStr">
         <is>
-          <t>env.weather.forecast_days</t>
+          <t>env.silent.debris_ring_min</t>
         </is>
       </c>
       <c r="C598" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>有监听站 T2 的有效天气预报情报时,看得到未来几个游戏日的天气(FGR-ENV-021:3 日)</t>
+          <t>风暴残骸离归还核心至少几格</t>
         </is>
       </c>
     </row>
@@ -10006,15 +10006,15 @@
       <c r="A599" t="inlineStr"/>
       <c r="B599" t="inlineStr">
         <is>
-          <t>env.weather.schedule_days</t>
+          <t>env.silent.debris_ring_max</t>
         </is>
       </c>
       <c r="C599" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>天气提前排定几个游戏日(必须 &gt; 预报天数,预报看得到的都已排定、写进存档)</t>
+          <t>风暴残骸离归还核心至多几格(按种子地形找空地,找不到就少放)</t>
         </is>
       </c>
     </row>
@@ -10022,15 +10022,15 @@
       <c r="A600" t="inlineStr"/>
       <c r="B600" t="inlineStr">
         <is>
-          <t>env.weather.acid_pct_per_hour</t>
+          <t>env.weather.duration_min_days</t>
         </is>
       </c>
       <c r="C600" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>酸雨:露天建筑 / 传送带 / 炮塔每游戏小时损失最大耐久的百分之几(FG07 第10节:1%)</t>
+          <t>一段恶劣天气最短持续几个游戏日(FG07 第10节:0.5~1.5)</t>
         </is>
       </c>
     </row>
@@ -10038,15 +10038,15 @@
       <c r="A601" t="inlineStr"/>
       <c r="B601" t="inlineStr">
         <is>
-          <t>env.weather.damage_notify_hours</t>
+          <t>env.weather.duration_max_days</t>
         </is>
       </c>
       <c r="C601" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>酸雨损伤的汇总通知最多每几个游戏小时一条(同一段酸雨内;摧毁另有通知)</t>
+          <t>一段恶劣天气最长持续几个游戏日</t>
         </is>
       </c>
     </row>
@@ -10054,15 +10054,15 @@
       <c r="A602" t="inlineStr"/>
       <c r="B602" t="inlineStr">
         <is>
-          <t>env.weather.sand_detect_factor</t>
+          <t>env.weather.first_day</t>
         </is>
       </c>
       <c r="C602" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>沙暴:露天炮塔探测(开火)距离乘这个数(FG07 第10节:-20%)</t>
+          <t>第一段恶劣天气最早在第几个游戏日开始(开局先让玩家站稳;FG16 节奏表另见 FG-GAP)</t>
         </is>
       </c>
     </row>
@@ -10070,15 +10070,15 @@
       <c r="A603" t="inlineStr"/>
       <c r="B603" t="inlineStr">
         <is>
-          <t>env.weather.cold_dissipation_mult</t>
+          <t>env.weather.warning_days</t>
         </is>
       </c>
       <c r="C603" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>寒潮:家园里武器散热乘这个数(FG07 第10节:散热 +30%)</t>
+          <t>没有天气预报情报时,恶劣天气开始前多少游戏日预警(FGR-ENV-021:0.5 日)</t>
         </is>
       </c>
     </row>
@@ -10086,15 +10086,15 @@
       <c r="A604" t="inlineStr"/>
       <c r="B604" t="inlineStr">
         <is>
-          <t>env.weather.sand_fog_density</t>
+          <t>env.weather.forecast_days</t>
         </is>
       </c>
       <c r="C604" t="n">
-        <v>0.018</v>
+        <v>3</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>沙暴画面:指数雾浓度(纯表现;乘玩家的天气视觉效果强度)</t>
+          <t>有监听站 T2 的有效天气预报情报时,看得到未来几个游戏日的天气(FGR-ENV-021:3 日)</t>
         </is>
       </c>
     </row>
@@ -10102,15 +10102,15 @@
       <c r="A605" t="inlineStr"/>
       <c r="B605" t="inlineStr">
         <is>
-          <t>env.weather.fx_ramp_hours</t>
+          <t>env.weather.schedule_days</t>
         </is>
       </c>
       <c r="C605" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>天气画面淡入 / 淡出的游戏小时(纯表现)</t>
+          <t>天气提前排定几个游戏日(必须 &gt; 预报天数,预报看得到的都已排定、写进存档)</t>
         </is>
       </c>
     </row>
@@ -10118,15 +10118,15 @@
       <c r="A606" t="inlineStr"/>
       <c r="B606" t="inlineStr">
         <is>
-          <t>env.weather.particles_max</t>
+          <t>env.weather.acid_pct_per_hour</t>
         </is>
       </c>
       <c r="C606" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>雨 / 沙 / 雪粒子最多同时几颗(满强度;ART-PERF-BUDGET 占位,乘视觉效果强度)</t>
+          <t>酸雨:露天建筑 / 传送带 / 炮塔每游戏小时损失最大耐久的百分之几(FG07 第10节:1%)</t>
         </is>
       </c>
     </row>
@@ -10134,15 +10134,15 @@
       <c r="A607" t="inlineStr"/>
       <c r="B607" t="inlineStr">
         <is>
-          <t>env.roof.block_cells</t>
+          <t>env.weather.damage_notify_hours</t>
         </is>
       </c>
       <c r="C607" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>顶棚一块的边长(格;FGR-ENV-030:4×4)</t>
+          <t>酸雨损伤的汇总通知最多每几个游戏小时一条(同一段酸雨内;摧毁另有通知)</t>
         </is>
       </c>
     </row>
@@ -10150,15 +10150,15 @@
       <c r="A608" t="inlineStr"/>
       <c r="B608" t="inlineStr">
         <is>
-          <t>env.roof.max_blocks_per_drag</t>
+          <t>env.weather.sand_detect_factor</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>64</v>
+        <v>0.8</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>一次拖拽最多铺几块顶棚(超出给原因,不静默截断)</t>
+          <t>沙暴:露天炮塔探测(开火)距离乘这个数(FG07 第10节:-20%)</t>
         </is>
       </c>
     </row>
@@ -10166,15 +10166,15 @@
       <c r="A609" t="inlineStr"/>
       <c r="B609" t="inlineStr">
         <is>
-          <t>env.roof.build_seconds_per_block</t>
+          <t>env.weather.cold_dissipation_mult</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>机器施工一块顶棚要几游戏秒</t>
+          <t>寒潮:家园里武器散热乘这个数(FG07 第10节:散热 +30%)</t>
         </is>
       </c>
     </row>
@@ -10182,15 +10182,15 @@
       <c r="A610" t="inlineStr"/>
       <c r="B610" t="inlineStr">
         <is>
-          <t>purify.hours_per_level</t>
+          <t>env.weather.sand_fog_density</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>2</v>
+        <v>0.018</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>净化速度:每格每 N 个游戏小时降 1 级(FG07 第 10 节初值 N = 2;按持续有电有冷却液的游戏时间累计,暂停 / 倍速同比例)</t>
+          <t>沙暴画面:指数雾浓度(纯表现;乘玩家的天气视觉效果强度)</t>
         </is>
       </c>
     </row>
@@ -10198,15 +10198,15 @@
       <c r="A611" t="inlineStr"/>
       <c r="B611" t="inlineStr">
         <is>
-          <t>purify.coolant_mult_t2</t>
+          <t>env.weather.fx_ramp_hours</t>
         </is>
       </c>
       <c r="C611" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>净化塔 T2 的冷却液用量 = T1(fg.TbProducer.fluidLpm)× 本值</t>
+          <t>天气画面淡入 / 淡出的游戏小时(纯表现)</t>
         </is>
       </c>
     </row>
@@ -10214,15 +10214,15 @@
       <c r="A612" t="inlineStr"/>
       <c r="B612" t="inlineStr">
         <is>
-          <t>purify.coolant_mult_t3</t>
+          <t>env.weather.particles_max</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>净化塔 T3 的冷却液用量 = T1 × 本值</t>
+          <t>雨 / 沙 / 雪粒子最多同时几颗(满强度;ART-PERF-BUDGET 占位,乘视觉效果强度)</t>
         </is>
       </c>
     </row>
@@ -10230,15 +10230,15 @@
       <c r="A613" t="inlineStr"/>
       <c r="B613" t="inlineStr">
         <is>
-          <t>purify.rich_ore.radius</t>
+          <t>env.roof.block_cells</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>归还 20,000 格的奖励“稀土富矿”:揭示(探索)的圆半径,也是富矿的范围(格;范围内压在稀土矿脉上的提取钻产出加倍)</t>
+          <t>顶棚一块的边长(格;FGR-ENV-030:4×4)</t>
         </is>
       </c>
     </row>
@@ -10246,15 +10246,15 @@
       <c r="A614" t="inlineStr"/>
       <c r="B614" t="inlineStr">
         <is>
-          <t>purify.rich_ore.yield_mult</t>
+          <t>env.roof.max_blocks_per_drag</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>稀土富矿范围内的提取钻每份产出 × 本值(整数)</t>
+          <t>一次拖拽最多铺几块顶棚(超出给原因,不静默截断)</t>
         </is>
       </c>
     </row>
@@ -10262,15 +10262,15 @@
       <c r="A615" t="inlineStr"/>
       <c r="B615" t="inlineStr">
         <is>
-          <t>purify.rich_ore.search_radius</t>
+          <t>env.roof.build_seconds_per_block</t>
         </is>
       </c>
       <c r="C615" t="n">
-        <v>400</v>
+        <v>3</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>找稀土富矿的最远距离(格,从归还核心算;先按世界规划层的稀土矿带找,找不到再按种子粗采样)</t>
+          <t>机器施工一块顶棚要几游戏秒</t>
         </is>
       </c>
     </row>
@@ -10278,15 +10278,15 @@
       <c r="A616" t="inlineStr"/>
       <c r="B616" t="inlineStr">
         <is>
-          <t>purify.rich_ore.search_step</t>
+          <t>purify.hours_per_level</t>
         </is>
       </c>
       <c r="C616" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>粗采样的步长(格;只在规划层没有稀土矿带时用)</t>
+          <t>净化速度:每格每 N 个游戏小时降 1 级(FG07 第 10 节初值 N = 2;按持续有电有冷却液的游戏时间累计,暂停 / 倍速同比例)</t>
         </is>
       </c>
     </row>
@@ -10294,15 +10294,15 @@
       <c r="A617" t="inlineStr"/>
       <c r="B617" t="inlineStr">
         <is>
-          <t>explore.trail_gap_max</t>
+          <t>purify.coolant_mult_t2</t>
         </is>
       </c>
       <c r="C617" t="n">
-        <v>64</v>
+        <v>1.5</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>机器两次被检查之间走过的距离超过这么多格就当作“瞬移”(出厂 / 读档 / 跳转),不沿路补探索(格)</t>
+          <t>净化塔 T2 的冷却液用量 = T1(fg.TbProducer.fluidLpm)× 本值</t>
         </is>
       </c>
     </row>
@@ -10310,15 +10310,15 @@
       <c r="A618" t="inlineStr"/>
       <c r="B618" t="inlineStr">
         <is>
-          <t>explore.trail_step</t>
+          <t>purify.coolant_mult_t3</t>
         </is>
       </c>
       <c r="C618" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>沿机器走过的路补探索的采样间距(格;不大于机器探索半径的一半,保证路上不留缝)</t>
+          <t>净化塔 T3 的冷却液用量 = T1 × 本值</t>
         </is>
       </c>
     </row>
@@ -10326,15 +10326,15 @@
       <c r="A619" t="inlineStr"/>
       <c r="B619" t="inlineStr">
         <is>
-          <t>relic.pick_radius</t>
+          <t>purify.rich_ore.radius</t>
         </is>
       </c>
       <c r="C619" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>右键 / 悬停离遗迹点多近算点中它(格,欧氏距离)</t>
+          <t>归还 20,000 格的奖励“稀土富矿”:揭示(探索)的圆半径,也是富矿的范围(格;范围内压在稀土矿脉上的提取钻产出加倍)</t>
         </is>
       </c>
     </row>
@@ -10342,15 +10342,15 @@
       <c r="A620" t="inlineStr"/>
       <c r="B620" t="inlineStr">
         <is>
-          <t>relic.notify_max</t>
+          <t>purify.rich_ore.yield_mult</t>
         </is>
       </c>
       <c r="C620" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>一次揭开的一大片里最多逐个发几条“发现遗迹点”通知(其余合成一条“又发现 N 个”)</t>
+          <t>稀土富矿范围内的提取钻每份产出 × 本值(整数)</t>
         </is>
       </c>
     </row>
@@ -10358,15 +10358,15 @@
       <c r="A621" t="inlineStr"/>
       <c r="B621" t="inlineStr">
         <is>
-          <t>exp.check.severe_health_pct</t>
+          <t>purify.rich_ore.search_radius</t>
         </is>
       </c>
       <c r="C621" t="n">
-        <v>0.25</v>
+        <v>400</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>机器生命低于最大值的这个比例=重伤提醒(可以派,后果写明;0~1)</t>
+          <t>找稀土富矿的最远距离(格,从归还核心算;先按世界规划层的稀土矿带找,找不到再按种子粗采样)</t>
         </is>
       </c>
     </row>
@@ -10374,15 +10374,15 @@
       <c r="A622" t="inlineStr"/>
       <c r="B622" t="inlineStr">
         <is>
-          <t>exp.check.warn_health_pct</t>
+          <t>purify.rich_ore.search_step</t>
         </is>
       </c>
       <c r="C622" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>机器生命低于最大值的这个比例=伤势偏重提醒(0~1,应不低于重伤线)</t>
+          <t>粗采样的步长(格;只在规划层没有稀土矿带时用)</t>
         </is>
       </c>
     </row>
@@ -10390,15 +10390,15 @@
       <c r="A623" t="inlineStr"/>
       <c r="B623" t="inlineStr">
         <is>
-          <t>exp.team.color_count</t>
+          <t>explore.trail_gap_max</t>
         </is>
       </c>
       <c r="C623" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>远征队可选颜色种数(颜色表见界面,1~8)</t>
+          <t>机器两次被检查之间走过的距离超过这么多格就当作“瞬移”(出厂 / 读档 / 跳转),不沿路补探索(格)</t>
         </is>
       </c>
     </row>
@@ -10406,15 +10406,15 @@
       <c r="A624" t="inlineStr"/>
       <c r="B624" t="inlineStr">
         <is>
-          <t>squad.group_double_tap_seconds</t>
+          <t>explore.trail_step</t>
         </is>
       </c>
       <c r="C624" t="n">
-        <v>0.35</v>
+        <v>6</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>连按两次同一编组键的最长间隔(真实秒;镜头飞到编组,FG13 第5节)</t>
+          <t>沿机器走过的路补探索的采样间距(格;不大于机器探索半径的一半,保证路上不留缝)</t>
         </is>
       </c>
     </row>
@@ -10422,15 +10422,15 @@
       <c r="A625" t="inlineStr"/>
       <c r="B625" t="inlineStr">
         <is>
-          <t>expedition.march.speed.wheel</t>
+          <t>relic.pick_radius</t>
         </is>
       </c>
       <c r="C625" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>行军速度:搬运轮式底盘(格/秒,FG08 初值);远征队速度取最慢的那台</t>
+          <t>右键 / 悬停离遗迹点多近算点中它(格,欧氏距离)</t>
         </is>
       </c>
     </row>
@@ -10438,15 +10438,15 @@
       <c r="A626" t="inlineStr"/>
       <c r="B626" t="inlineStr">
         <is>
-          <t>expedition.march.speed.hover</t>
+          <t>relic.notify_max</t>
         </is>
       </c>
       <c r="C626" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>行军速度:维修悬浮底盘(格/秒,FG08 初值)</t>
+          <t>一次揭开的一大片里最多逐个发几条“发现遗迹点”通知(其余合成一条“又发现 N 个”)</t>
         </is>
       </c>
     </row>
@@ -10454,15 +10454,15 @@
       <c r="A627" t="inlineStr"/>
       <c r="B627" t="inlineStr">
         <is>
-          <t>expedition.march.speed.track</t>
+          <t>exp.check.severe_health_pct</t>
         </is>
       </c>
       <c r="C627" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>行军速度:战斗履带底盘(格/秒,FG08 初值;系统占位机按此计)</t>
+          <t>机器生命低于最大值的这个比例=重伤提醒(可以派,后果写明;0~1)</t>
         </is>
       </c>
     </row>
@@ -10470,15 +10470,15 @@
       <c r="A628" t="inlineStr"/>
       <c r="B628" t="inlineStr">
         <is>
-          <t>expedition.march.arrive_radius</t>
+          <t>exp.check.warn_health_pct</t>
         </is>
       </c>
       <c r="C628" t="n">
-        <v>10</v>
+        <v>0.6</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>全部存活成员走到目的地锚点这么近(格)就算到达,进入远征地点</t>
+          <t>机器生命低于最大值的这个比例=伤势偏重提醒(0~1,应不低于重伤线)</t>
         </is>
       </c>
     </row>
@@ -10486,15 +10486,15 @@
       <c r="A629" t="inlineStr"/>
       <c r="B629" t="inlineStr">
         <is>
-          <t>expedition.march.home_radius</t>
+          <t>exp.team.color_count</t>
         </is>
       </c>
       <c r="C629" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>返程的成员全部走到归还核心这么近(格)就算回到家园</t>
+          <t>远征队可选颜色种数(颜色表见界面,1~8)</t>
         </is>
       </c>
     </row>
@@ -10502,15 +10502,15 @@
       <c r="A630" t="inlineStr"/>
       <c r="B630" t="inlineStr">
         <is>
-          <t>expedition.march.engage_radius</t>
+          <t>squad.group_double_tap_seconds</t>
         </is>
       </c>
       <c r="C630" t="n">
-        <v>12</v>
+        <v>0.35</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>成员这么近(格)有敌对单位=交战中(远征队状态)</t>
+          <t>连按两次同一编组键的最长间隔(真实秒;镜头飞到编组,FG13 第5节)</t>
         </is>
       </c>
     </row>
@@ -10518,15 +10518,15 @@
       <c r="A631" t="inlineStr"/>
       <c r="B631" t="inlineStr">
         <is>
-          <t>expedition.encounter.radius_cells</t>
+          <t>expedition.march.speed.wheel</t>
         </is>
       </c>
       <c r="C631" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>行军途中敌方据点/巡逻/突袭队伍进入队伍这么近(格)就提示一次</t>
+          <t>行军速度:搬运轮式底盘(格/秒,FG08 初值);远征队速度取最慢的那台</t>
         </is>
       </c>
     </row>
@@ -10534,15 +10534,15 @@
       <c r="A632" t="inlineStr"/>
       <c r="B632" t="inlineStr">
         <is>
-          <t>expedition.march.arrival_retry_seconds</t>
+          <t>expedition.march.speed.hover</t>
         </is>
       </c>
       <c r="C632" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>到达失败(地点不开放/存档失败/载入出错已回滚)后,队伍照最后的“前进”隔这么久(游戏秒)自动重试进入</t>
+          <t>行军速度:维修悬浮底盘(格/秒,FG08 初值)</t>
         </is>
       </c>
     </row>
@@ -10550,15 +10550,15 @@
       <c r="A633" t="inlineStr"/>
       <c r="B633" t="inlineStr">
         <is>
-          <t>expedition.anchor.max_attempts</t>
+          <t>expedition.march.speed.track</t>
         </is>
       </c>
       <c r="C633" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>锚点可达性校验的最多试探次数(每次换一个由种子决定的候选点)</t>
+          <t>行军速度:战斗履带底盘(格/秒,FG08 初值;系统占位机按此计)</t>
         </is>
       </c>
     </row>
@@ -10566,15 +10566,15 @@
       <c r="A634" t="inlineStr"/>
       <c r="B634" t="inlineStr">
         <is>
-          <t>expedition.anchor.jitter_deg</t>
+          <t>expedition.march.arrive_radius</t>
         </is>
       </c>
       <c r="C634" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>锚点候选方向:从领地中心朝归还核心的方向左右各偏这么多度以内(由种子决定)</t>
+          <t>全部存活成员走到目的地锚点这么近(格)就算到达,进入远征地点</t>
         </is>
       </c>
     </row>
@@ -10582,15 +10582,15 @@
       <c r="A635" t="inlineStr"/>
       <c r="B635" t="inlineStr">
         <is>
-          <t>expedition.anchor.radial_min</t>
+          <t>expedition.march.home_radius</t>
         </is>
       </c>
       <c r="C635" t="n">
-        <v>0.7</v>
+        <v>24</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>锚点候选离领地中心的最小距离(领地半径的倍数)</t>
+          <t>返程的成员全部走到归还核心这么近(格)就算回到家园</t>
         </is>
       </c>
     </row>
@@ -10598,15 +10598,15 @@
       <c r="A636" t="inlineStr"/>
       <c r="B636" t="inlineStr">
         <is>
-          <t>expedition.anchor.radial_max</t>
+          <t>expedition.march.engage_radius</t>
         </is>
       </c>
       <c r="C636" t="n">
-        <v>0.9</v>
+        <v>12</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>锚点候选离领地中心的最大距离(领地半径的倍数)</t>
+          <t>成员这么近(格)有敌对单位=交战中(远征队状态)</t>
         </is>
       </c>
     </row>
@@ -10614,15 +10614,15 @@
       <c r="A637" t="inlineStr"/>
       <c r="B637" t="inlineStr">
         <is>
-          <t>expedition.anchor.fallback_distance.city</t>
+          <t>expedition.encounter.radius_cells</t>
         </is>
       </c>
       <c r="C637" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>没有规划层的旧原型世界:破碎都市锚点离核心的距离(格)</t>
+          <t>行军途中敌方据点/巡逻/突袭队伍进入队伍这么近(格)就提示一次</t>
         </is>
       </c>
     </row>
@@ -10630,15 +10630,15 @@
       <c r="A638" t="inlineStr"/>
       <c r="B638" t="inlineStr">
         <is>
-          <t>expedition.anchor.fallback_distance.foundry</t>
+          <t>expedition.march.arrival_retry_seconds</t>
         </is>
       </c>
       <c r="C638" t="n">
-        <v>600</v>
+        <v>15</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>没有规划层的旧原型世界:铸造前哨锚点离核心的距离(格)</t>
+          <t>到达失败(地点不开放/存档失败/载入出错已回滚)后,队伍照最后的“前进”隔这么久(游戏秒)自动重试进入</t>
         </is>
       </c>
     </row>
@@ -10646,15 +10646,15 @@
       <c r="A639" t="inlineStr"/>
       <c r="B639" t="inlineStr">
         <is>
-          <t>territory.banner_seconds</t>
+          <t>expedition.anchor.max_attempts</t>
         </is>
       </c>
       <c r="C639" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>进入 / 离开领地时屏幕上方名称提示停留多久(真实秒)</t>
+          <t>锚点可达性校验的最多试探次数(每次换一个由种子决定的候选点)</t>
         </is>
       </c>
     </row>
@@ -10662,15 +10662,15 @@
       <c r="A640" t="inlineStr"/>
       <c r="B640" t="inlineStr">
         <is>
-          <t>territory.belt_warn_cells</t>
+          <t>expedition.anchor.jitter_deg</t>
         </is>
       </c>
       <c r="C640" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>镜头 / 接入的机器离外圈危害带这么近(格)时提示“接近危害带”</t>
+          <t>锚点候选方向:从领地中心朝归还核心的方向左右各偏这么多度以内(由种子决定)</t>
         </is>
       </c>
     </row>
@@ -10678,15 +10678,15 @@
       <c r="A641" t="inlineStr"/>
       <c r="B641" t="inlineStr">
         <is>
-          <t>territory.presence_refresh_seconds</t>
+          <t>expedition.anchor.radial_min</t>
         </is>
       </c>
       <c r="C641" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>远征队“进入领地”提示的检查周期(游戏秒;与行军提示同一节拍)</t>
+          <t>锚点候选离领地中心的最小距离(领地半径的倍数)</t>
         </is>
       </c>
     </row>
@@ -10694,15 +10694,15 @@
       <c r="A642" t="inlineStr"/>
       <c r="B642" t="inlineStr">
         <is>
-          <t>interior.pick_radius</t>
+          <t>expedition.anchor.radial_max</t>
         </is>
       </c>
       <c r="C642" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>左键点在离入口这么近(格)的地方算点中入口(打开进入面板)</t>
+          <t>锚点候选离领地中心的最大距离(领地半径的倍数)</t>
         </is>
       </c>
     </row>
@@ -10710,15 +10710,15 @@
       <c r="A643" t="inlineStr"/>
       <c r="B643" t="inlineStr">
         <is>
-          <t>interior.exit_radius</t>
+          <t>expedition.anchor.fallback_distance.city</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>室内:机器离出口这么近(格)才能离开</t>
+          <t>没有规划层的旧原型世界:破碎都市锚点离核心的距离(格)</t>
         </is>
       </c>
     </row>
@@ -10726,15 +10726,15 @@
       <c r="A644" t="inlineStr"/>
       <c r="B644" t="inlineStr">
         <is>
-          <t>interior.transition_seconds</t>
+          <t>expedition.anchor.fallback_distance.foundry</t>
         </is>
       </c>
       <c r="C644" t="n">
-        <v>0.6</v>
+        <v>600</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>进出室内的画面过渡(真实秒;过渡期间世界照常运行)</t>
+          <t>没有规划层的旧原型世界:铸造前哨锚点离核心的距离(格)</t>
         </is>
       </c>
     </row>
@@ -10742,15 +10742,15 @@
       <c r="A645" t="inlineStr"/>
       <c r="B645" t="inlineStr">
         <is>
-          <t>interior.spawn_spacing</t>
+          <t>territory.banner_seconds</t>
         </is>
       </c>
       <c r="C645" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>进出室内时机器在入口 / 出口旁排开的间距(格)</t>
+          <t>进入 / 离开领地时屏幕上方名称提示停留多久(真实秒)</t>
         </is>
       </c>
     </row>
@@ -10758,15 +10758,15 @@
       <c r="A646" t="inlineStr"/>
       <c r="B646" t="inlineStr">
         <is>
-          <t>anchor.reach_max_attempts</t>
+          <t>territory.belt_warn_cells</t>
         </is>
       </c>
       <c r="C646" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>锚点可达性校验:一条寻路没交回结果时最多再发几次(之后记为失败并写日志)</t>
+          <t>镜头 / 接入的机器离外圈危害带这么近(格)时提示“接近危害带”</t>
         </is>
       </c>
     </row>
@@ -10774,15 +10774,15 @@
       <c r="A647" t="inlineStr"/>
       <c r="B647" t="inlineStr">
         <is>
-          <t>outpost.bucket_cells</t>
+          <t>territory.presence_refresh_seconds</t>
         </is>
       </c>
       <c r="C647" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>据点空间索引的桶边长(格;地图 / 星球标记 / 休眠判定按桶粗筛)</t>
+          <t>远征队“进入领地”提示的检查周期(游戏秒;与行军提示同一节拍)</t>
         </is>
       </c>
     </row>
@@ -10790,15 +10790,15 @@
       <c r="A648" t="inlineStr"/>
       <c r="B648" t="inlineStr">
         <is>
-          <t>outer.reveal_margin_cells</t>
+          <t>interior.pick_radius</t>
         </is>
       </c>
       <c r="C648" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>外延区:揭开一片区域时,圆外再多登记这么多格内的零散前哨与缓存(按需生成,FGR-GEN-040)</t>
+          <t>左键点在离入口这么近(格)的地方算点中入口(打开进入面板)</t>
         </is>
       </c>
     </row>
@@ -10806,15 +10806,15 @@
       <c r="A649" t="inlineStr"/>
       <c r="B649" t="inlineStr">
         <is>
-          <t>outer.cache_scrap_base</t>
+          <t>interior.exit_radius</t>
         </is>
       </c>
       <c r="C649" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>外延区资源缓存的废料基数</t>
+          <t>室内:机器离出口这么近(格)才能离开</t>
         </is>
       </c>
     </row>
@@ -10822,15 +10822,15 @@
       <c r="A650" t="inlineStr"/>
       <c r="B650" t="inlineStr">
         <is>
-          <t>outer.cache_scrap_per_1000</t>
+          <t>interior.transition_seconds</t>
         </is>
       </c>
       <c r="C650" t="n">
-        <v>40</v>
+        <v>0.6</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>外延区资源缓存每离核心 1000 格多给多少废料(越远奖励越高)</t>
+          <t>进出室内的画面过渡(真实秒;过渡期间世界照常运行)</t>
         </is>
       </c>
     </row>
@@ -10838,15 +10838,15 @@
       <c r="A651" t="inlineStr"/>
       <c r="B651" t="inlineStr">
         <is>
-          <t>outer.cache_seconds</t>
+          <t>interior.spawn_spacing</t>
         </is>
       </c>
       <c r="C651" t="n">
-        <v>14</v>
+        <v>2.5</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>外延区资源缓存的打开工期(游戏秒)</t>
+          <t>进出室内时机器在入口 / 出口旁排开的间距(格)</t>
         </is>
       </c>
     </row>
@@ -10854,15 +10854,15 @@
       <c r="A652" t="inlineStr"/>
       <c r="B652" t="inlineStr">
         <is>
-          <t>scatter.cache_scrap</t>
+          <t>anchor.reach_max_attempts</t>
         </is>
       </c>
       <c r="C652" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>领地之间(零散)资源缓存的废料</t>
+          <t>锚点可达性校验:一条寻路没交回结果时最多再发几次(之后记为失败并写日志)</t>
         </is>
       </c>
     </row>
@@ -10870,15 +10870,15 @@
       <c r="A653" t="inlineStr"/>
       <c r="B653" t="inlineStr">
         <is>
-          <t>signal.coverage.site_root_mode</t>
+          <t>outpost.bucket_cells</t>
         </is>
       </c>
       <c r="C653" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>远征地点内部覆盖的根:1=远征接入点(恒连通,沿用 FG1-SIG-07);2=星球上的锚点必须在与核心连通的覆盖里(DEBT-FG8EXP02-02,待用户定是否切到 2)</t>
+          <t>据点空间索引的桶边长(格;地图 / 星球标记 / 休眠判定按桶粗筛)</t>
         </is>
       </c>
     </row>
@@ -10886,15 +10886,15 @@
       <c r="A654" t="inlineStr"/>
       <c r="B654" t="inlineStr">
         <is>
-          <t>territory.control.sync_seconds</t>
+          <t>outer.reveal_margin_cells</t>
         </is>
       </c>
       <c r="C654" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>领地控制度 / 状态 / 增援 / 精英残部 / 骚扰的检查周期(游戏秒;只看步序号,与观察无关)</t>
+          <t>外延区:揭开一片区域时,圆外再多登记这么多格内的零散前哨与缓存(按需生成,FGR-GEN-040)</t>
         </is>
       </c>
     </row>
@@ -10902,15 +10902,15 @@
       <c r="A655" t="inlineStr"/>
       <c r="B655" t="inlineStr">
         <is>
-          <t>territory.control.reclaim_below</t>
+          <t>outer.cache_scrap_base</t>
         </is>
       </c>
       <c r="C655" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>平定中的领地控制度降到这个值以下(不含)时变为已收复(FGR-EXP-022 初值 20)</t>
+          <t>外延区资源缓存的废料基数</t>
         </is>
       </c>
     </row>
@@ -10918,15 +10918,15 @@
       <c r="A656" t="inlineStr"/>
       <c r="B656" t="inlineStr">
         <is>
-          <t>territory.reinforce.interval_days</t>
+          <t>outer.cache_scrap_per_1000</t>
         </is>
       </c>
       <c r="C656" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>首领被击败前,阵营每几个游戏日增援一次(FGR-EXP-022 初值 3;被摧毁的据点有可能重建)</t>
+          <t>外延区资源缓存每离核心 1000 格多给多少废料(越远奖励越高)</t>
         </is>
       </c>
     </row>
@@ -10934,15 +10934,15 @@
       <c r="A657" t="inlineStr"/>
       <c r="B657" t="inlineStr">
         <is>
-          <t>territory.reinforce.rebuild_chance</t>
+          <t>outer.cache_seconds</t>
         </is>
       </c>
       <c r="C657" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>每次增援时,每个被摧毁的领地据点重建的概率(按世界种子 + 领地 + 第几次增援 + 据点确定)</t>
+          <t>外延区资源缓存的打开工期(游戏秒)</t>
         </is>
       </c>
     </row>
@@ -10950,15 +10950,15 @@
       <c r="A658" t="inlineStr"/>
       <c r="B658" t="inlineStr">
         <is>
-          <t>territory.reinforce.rebuild_max</t>
+          <t>scatter.cache_scrap</t>
         </is>
       </c>
       <c r="C658" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>每次增援每个领地最多重建几个据点</t>
+          <t>领地之间(零散)资源缓存的废料</t>
         </is>
       </c>
     </row>
@@ -10966,15 +10966,15 @@
       <c r="A659" t="inlineStr"/>
       <c r="B659" t="inlineStr">
         <is>
-          <t>territory.reinforce.rebuild_garrison_ratio</t>
+          <t>signal.coverage.site_root_mode</t>
         </is>
       </c>
       <c r="C659" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>重建的据点驻军 = 上限 × 这个比例(至少 1)</t>
+          <t>远征地点内部覆盖的根:1=远征接入点(恒连通,沿用 FG1-SIG-07);2=星球上的锚点必须在与核心连通的覆盖里(DEBT-FG8EXP02-02,待用户定是否切到 2)</t>
         </is>
       </c>
     </row>
@@ -10982,15 +10982,15 @@
       <c r="A660" t="inlineStr"/>
       <c r="B660" t="inlineStr">
         <is>
-          <t>territory.reinforce.block_radius_cells</t>
+          <t>territory.control.sync_seconds</t>
         </is>
       </c>
       <c r="C660" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>据点这么近(格)内有己方建筑或机器时不重建(不在玩家眼前凭空出现)</t>
+          <t>领地控制度 / 状态 / 增援 / 精英残部 / 骚扰的检查周期(游戏秒;只看步序号,与观察无关)</t>
         </is>
       </c>
     </row>
@@ -10998,15 +10998,15 @@
       <c r="A661" t="inlineStr"/>
       <c r="B661" t="inlineStr">
         <is>
-          <t>territory.elite.interval_days</t>
+          <t>territory.control.reclaim_below</t>
         </is>
       </c>
       <c r="C661" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>已收复的领地里精英残部每几个游戏日刷新一次(FGR-EXP-022 初值 7;上一批没被击溃时不叠加)</t>
+          <t>平定中的领地控制度降到这个值以下(不含)时变为已收复(FGR-EXP-022 初值 20)</t>
         </is>
       </c>
     </row>
@@ -11014,15 +11014,15 @@
       <c r="A662" t="inlineStr"/>
       <c r="B662" t="inlineStr">
         <is>
-          <t>territory.harass.interval_hours</t>
+          <t>territory.reinforce.interval_days</t>
         </is>
       </c>
       <c r="C662" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>在敌控 / 平定中的领地里有己方建筑时,每几个游戏小时从最近的据点派一支骚扰部队</t>
+          <t>首领被击败前,阵营每几个游戏日增援一次(FGR-EXP-022 初值 3;被摧毁的据点有可能重建)</t>
         </is>
       </c>
     </row>
@@ -11030,15 +11030,15 @@
       <c r="A663" t="inlineStr"/>
       <c r="B663" t="inlineStr">
         <is>
-          <t>territory.harass.units</t>
+          <t>territory.reinforce.rebuild_chance</t>
         </is>
       </c>
       <c r="C663" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>骚扰部队台数(不超过据点驻军 - 1)</t>
+          <t>每次增援时,每个被摧毁的领地据点重建的概率(按世界种子 + 领地 + 第几次增援 + 据点确定)</t>
         </is>
       </c>
     </row>
@@ -11046,15 +11046,15 @@
       <c r="A664" t="inlineStr"/>
       <c r="B664" t="inlineStr">
         <is>
-          <t>territory.engage.radius_cells</t>
+          <t>territory.reinforce.rebuild_max</t>
         </is>
       </c>
       <c r="C664" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>己方机器走到据点 / 巡逻这么近(格)时,驻军 / 巡逻就地展开迎战</t>
+          <t>每次增援每个领地最多重建几个据点</t>
         </is>
       </c>
     </row>
@@ -11062,15 +11062,15 @@
       <c r="A665" t="inlineStr"/>
       <c r="B665" t="inlineStr">
         <is>
-          <t>territory.engage.scout_nest_mode</t>
+          <t>territory.reinforce.rebuild_garrison_ratio</t>
         </is>
       </c>
       <c r="C665" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>家园区侦察巢是否也迎战:1=不迎战(初值,M1～M7 已验收的家园区节奏不变);2=与领地据点同一套迎战(由 FG9-BAL-01 第一幕平衡决定,DEBT-FG8EXP03-07)</t>
+          <t>重建的据点驻军 = 上限 × 这个比例(至少 1)</t>
         </is>
       </c>
     </row>
@@ -11078,15 +11078,15 @@
       <c r="A666" t="inlineStr"/>
       <c r="B666" t="inlineStr">
         <is>
-          <t>territory.engage.regroup_seconds</t>
+          <t>territory.reinforce.block_radius_cells</t>
         </is>
       </c>
       <c r="C666" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>迎战中附近没有己方机器满这么久(游戏秒),幸存者收拢回据点 / 巡逻(人数按幸存者)</t>
+          <t>据点这么近(格)内有己方建筑或机器时不重建(不在玩家眼前凭空出现)</t>
         </is>
       </c>
     </row>
@@ -11094,15 +11094,15 @@
       <c r="A667" t="inlineStr"/>
       <c r="B667" t="inlineStr">
         <is>
-          <t>territory.engage.max_seconds</t>
+          <t>territory.elite.interval_days</t>
         </is>
       </c>
       <c r="C667" t="n">
-        <v>180</v>
+        <v>7</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>迎战僵持上限(游戏秒):到点收拢,之后这么久内不再展开(不在原地反复展开)</t>
+          <t>已收复的领地里精英残部每几个游戏日刷新一次(FGR-EXP-022 初值 7;上一批没被击溃时不叠加)</t>
         </is>
       </c>
     </row>
@@ -11110,15 +11110,15 @@
       <c r="A668" t="inlineStr"/>
       <c r="B668" t="inlineStr">
         <is>
-          <t>territory.loot.scrap_per_tier</t>
+          <t>territory.harass.interval_hours</t>
         </is>
       </c>
       <c r="C668" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>摧毁一个据点掉在原地的废料 = 等级 × 这个值(开搬运单)</t>
+          <t>在敌控 / 平定中的领地里有己方建筑时,每几个游戏小时从最近的据点派一支骚扰部队</t>
         </is>
       </c>
     </row>
@@ -11126,15 +11126,15 @@
       <c r="A669" t="inlineStr"/>
       <c r="B669" t="inlineStr">
         <is>
-          <t>outpost.patrol_view_catchup</t>
+          <t>territory.harass.units</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>星球上巡逻标记追上逻辑位置的最快速度(格/真实秒;刚醒来拿到路线时不跳位,DEBT-FG8GEN02-07)</t>
+          <t>骚扰部队台数(不超过据点驻军 - 1)</t>
         </is>
       </c>
     </row>
@@ -11142,13 +11142,109 @@
       <c r="A670" t="inlineStr"/>
       <c r="B670" t="inlineStr">
         <is>
+          <t>territory.engage.radius_cells</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>18</v>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>己方机器走到据点 / 巡逻这么近(格)时,驻军 / 巡逻就地展开迎战</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr"/>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>territory.engage.scout_nest_mode</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>1</v>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>家园区侦察巢是否也迎战:1=不迎战(初值,M1～M7 已验收的家园区节奏不变);2=与领地据点同一套迎战(由 FG9-BAL-01 第一幕平衡决定,DEBT-FG8EXP03-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr"/>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>territory.engage.regroup_seconds</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>20</v>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>迎战中附近没有己方机器满这么久(游戏秒),幸存者收拢回据点 / 巡逻(人数按幸存者)</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr"/>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>territory.engage.max_seconds</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>180</v>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>迎战僵持上限(游戏秒):到点收拢,之后这么久内不再展开(不在原地反复展开)</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr"/>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>territory.loot.scrap_per_tier</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>20</v>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>摧毁一个据点掉在原地的废料 = 等级 × 这个值(开搬运单)</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr"/>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>outpost.patrol_view_catchup</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>12</v>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>星球上巡逻标记追上逻辑位置的最快速度(格/真实秒;刚醒来拿到路线时不跳位,DEBT-FG8GEN02-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr"/>
+      <c r="B676" t="inlineStr">
+        <is>
           <t>outpost.patrol_view_snap</t>
         </is>
       </c>
-      <c r="C670" t="n">
+      <c r="C676" t="n">
         <v>120</v>
       </c>
-      <c r="D670" t="inlineStr">
+      <c r="D676" t="inlineStr">
         <is>
           <t>巡逻标记与逻辑位置相差这么远(格)时直接放过去(读档 / 镜头跳到别处)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D676"/>
+  <dimension ref="A1:D681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11250,6 +11250,86 @@
         </is>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" t="inlineStr"/>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>loot.merge_cells</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>3</v>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>野外掉落的材料落在这么近(格)内已有的同种材料堆上就合并(带身份的敌方物品一件一堆,不合并)</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr"/>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>loot.pile_max</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>40</v>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>一堆合并后最多多少件(超过另起一堆)</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr"/>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>loot.claw_bonus</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>致命一击来自主组件是拆解钳的机器时,废料与残骸多回收的比例(0.5=+50%,向上取整;DEBT-FG2VFX02-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr"/>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>loot.tags_max</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>512</v>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>地上带身份的敌方物品最多记多少条身份(超过时丢最早的身份,物品本身不丢,解析时按身份不明)</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr"/>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>loot.perf_ms</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>单次野外击毁掉落结算的耗时预算(毫秒;自检性能断言用)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D681"/>
+  <dimension ref="A1:D708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11330,6 +11330,438 @@
         </is>
       </c>
     </row>
+    <row r="682">
+      <c r="A682" t="inlineStr"/>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>loot.pick.weight.common</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>60</v>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>三选一每个候选位抽到“普通”的权重(FGR-LOOT-021 初值 60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr"/>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>loot.pick.weight.fine</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>30</v>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>抽到“精良”的权重(初值 30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr"/>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>loot.pick.weight.rare</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>9</v>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>抽到“稀有”的权重(初值 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr"/>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>loot.pick.weight.prototype</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>1</v>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>抽到“原型”的权重(初值 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr"/>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>loot.pick.pity</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>5</v>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>保底:连续这么多个数据包没有出现稀有及以上,下一个数据包必定有一个稀有位(FGR-LOOT-021 初值 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr"/>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>loot.pick.candidates</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>3</v>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>每个数据包的候选数(FGR-LOOT-020 三选一)</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr"/>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>loot.pick.tech.common</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>1</v>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>没选的“普通”候选转成的技术数据(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr"/>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>loot.pick.tech.fine</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>2</v>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>没选的“精良”候选转成的技术数据(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr"/>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>loot.pick.tech.rare</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>3</v>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>没选的“稀有”候选转成的技术数据(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr"/>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>loot.pick.tech.prototype</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>5</v>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>没选的“原型”候选转成的技术数据(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr"/>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>loot.pick.share_radius</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>30</v>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>精英被炮塔 / 不明来源击毁时,数据包交给这么近(格)内最近的己方机器;没有就留在原地</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr"/>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>loot.pick.claim_radius</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>6</v>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>地上的数据包:己方机器走到这么近(格)就捡起来</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr"/>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>loot.pick.depot_radius</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>24</v>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>携带机器离归还核心或运转中的仓库这么近(格)=在家园 / 带仓库的前哨站:可以随时分拣,选中的直接入库</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr"/>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>loot.pick.check_seconds</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>1</v>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>地上数据包的拾取 / 携带者对账间隔(游戏秒;只在有数据包时做)</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr"/>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>loot.pick.log_max</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>64</v>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>三选一的选择记录最多保留多少条(远征结算 FG8-EXP-05 读)</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr"/>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>loot.pick.perf_ms</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>单次生成数据包的耗时预算(毫秒;自检性能断言用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr"/>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>loot.cargo.cap.wheel</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>12</v>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>搬运轮式底盘的货舱容量(空间单位;FGR-LOOT-030“搬运轮式最大”,初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr"/>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>loot.cargo.cap.hover</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>6</v>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>维修悬浮底盘的货舱容量(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr"/>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>loot.cargo.cap.track</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>4</v>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>战斗履带底盘的货舱容量(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr"/>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>loot.cargo.cap.module</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>6</v>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>装了货舱结构模块的机器另加的容量(初值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr"/>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>loot.cargo.material_per_space</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>10</v>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>材料每这么多件占 1 格货舱(FGR-LOOT-030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr"/>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>loot.cargo.firmware</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>1</v>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>固件占用(FGR-LOOT-030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr"/>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>loot.cargo.component</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>3</v>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>组件(作战组件 / 结构模块 / 投送舱)占用(FGR-LOOT-030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr"/>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>loot.cargo.core</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>2</v>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>数据核心占用(FGR-LOOT-030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr"/>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>loot.cargo.module</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>3</v>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>未解析模块占用(FGR-LOOT-030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr"/>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>loot.cargo.legacy</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>2</v>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>人类遗产占用(FGR-LOOT-030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr"/>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>loot.cargo.blackbox</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>1</v>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>黑匣子占用(FGR-LOOT-030)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D708"/>
+  <dimension ref="A1:D717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11762,6 +11762,150 @@
         </is>
       </c>
     </row>
+    <row r="709">
+      <c r="A709" t="inlineStr"/>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>loot.cargo.check_seconds</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>1</v>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>货舱对账间隔(游戏秒):自动拾取、黑匣子带回家园即回收、快满 / 已满提示;只在有在外的远征队或携带中的黑匣子时做</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr"/>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>loot.cargo.pickup_radius</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>6</v>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>自动拾取:在外的远征队成员走到地上的货这么近(格)就装进货舱(放得下才装;家园 / 带仓库的前哨站附近不自动拾取)</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr"/>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>loot.cargo.transfer_radius</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>30</v>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>战略暂停中在机器之间转移货物:两台机器要在同一地点、这么近(格)以内</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr"/>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>loot.cargo.warn_ratio</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>货舱占用达到容量的这个比例时提示“快满了”(每台机器进入该状态时一次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr"/>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>loot.cargo.discard_clear_radius</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>12</v>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>玩家丢弃的货:附近(格)还有队员时不被自动拾取捡回去;队员都走开后恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr"/>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>loot.cargo.discard_max</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>64</v>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>最多记住多少件“刚丢弃、暂不自动拾取”的货</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr"/>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>loot.cargo.perf_ms</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>单次货舱对账(自动拾取等)的耗时预算(毫秒;自检性能断言用)</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr"/>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>expedition.cargo.suggest_first</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>16</v>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>出发检查单:第一次去某个远征地点时建议的货舱总容量(格;FG8-LOOT-03 起与货舱同一空间单位)</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr"/>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>expedition.cargo.suggest</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>12</v>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>出发检查单:之后的远征建议的货舱总容量(格)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D717"/>
+  <dimension ref="A1:D725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11906,6 +11906,134 @@
         </is>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" t="inlineStr"/>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>quest.check_seconds</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>1</v>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>任务判定(到达 / 停留 / 护送 / 时限)的检查周期(游戏秒;只看步序号,与观察无关;建筑 / 首领类每次目标重算都判定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr"/>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>quest.track_max</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>3</v>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>HUD 追踪栏最多同时追踪几个任务(FGR-QST-003 初值 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr"/>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>quest.reach_radius_cells</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>12</v>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>机器走到任务地点这么近(格)算到达(调查、护送的接车点)</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr"/>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>quest.hold_radius_cells</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>14</v>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>“夺回数据 / 取回蓝图”:机器在地点这么近(格)以内才累计停留时间(走开就暂停,不清零)</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr"/>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>quest.escort_health</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>160</v>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>护送货运车的耐久(搬运轮式底盘)</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr"/>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>quest.escort_spawn_offset</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>4</v>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>货运车出现在支线地点旁边这么远(格;找最近一格机器能站的)</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr"/>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>quest.outpost_radius_cells</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>80</v>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>“建立前哨”:离支线地点这么近(格)以内有己方前哨站(至少一座完好建筑)就算完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr"/>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>quest.perf_ms</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>一次任务检查(全部进行中的任务)的耗时预算(毫秒;自检性能断言用)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D725"/>
+  <dimension ref="A1:D733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12034,6 +12034,134 @@
         </is>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" t="inlineStr"/>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>heritage.place_attempts</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>24</v>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>给一件遗产找遗迹点时最多试几个方向(每个方向按种子取角度与距离)</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr"/>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>heritage.place_search</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>96</v>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>每个方向在目标点周围多大的方框里找生成器给出的遗迹点(半边长,格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr"/>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>heritage.pickup_seconds</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>6</v>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>遗迹已回收、遗产留在原地时,机器到场取走遗产要多少游戏秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr"/>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>heritage.reach_check_seconds</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>1</v>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>剧情遗产可达校验:世界步里每隔多少游戏秒看一次有没有要校验的(FGR-GEN-033)</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr"/>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>heritage.reach_latency_seconds</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>剧情遗产可达校验:后台寻路发出后固定多少游戏秒那一步采纳结果(不跨帧硬等,只看步序号)</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr"/>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>heritage.reach_near_cells</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>2</v>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>剧情遗产可达校验:部分路线的终点离遗迹点不超过多少格也算走得到(回收时机器站在旁边)</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr"/>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>heritage.reach_max_repicks</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>4</v>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>剧情遗产可达校验:遗迹点走不到时最多改挑几次,仍走不到就写错误日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr"/>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>relic.block_radius</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>1</v>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>未回收的遗迹点(或留着遗产的遗迹点)周围多少格不能放建筑(切比雪夫距离;保证机器走得到,FG-GAP-127)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D733"/>
+  <dimension ref="A1:D739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12162,6 +12162,102 @@
         </is>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" t="inlineStr"/>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>loot.expire.days</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>1</v>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>地上没被带走的普通战利品过这么久(游戏日)被敌方回收并消失(FG08 FGR-EXP-032 初值);关键材料/关键物/黑匣子/数据包永不消失;家园与带仓库的前哨站范围内不回收</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr"/>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>loot.expire.warn_hours</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>3</v>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>普通战利品被回收前这么久(游戏小时)提示一次“快要被回收”(每堆一次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr"/>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>expedition.leave.list_radius</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>60</v>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>星球上下“返回家园”前列出队伍附近地上还没捡的东西的半径(格,以队伍中心为圆心);阵亡处附近按它的 1/4 计入结算</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr"/>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>expedition.leave.list_max</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>6</v>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>撤离面板 / 远征结算里“留在原地的东西”最多列几条(其余写“还有 N 处”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr"/>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>expedition.leave.warn_lines</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>3</v>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>行军条“返回家园”二次确认里最多列几条地上还没捡的东西</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr"/>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>expedition.leave.confirm_seconds</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>8</v>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>行军条“返回家园”二次确认的有效时间(真实秒):第一次点只列清单,这段时间内再点一次才返回</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D739"/>
+  <dimension ref="A1:D753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12258,6 +12258,230 @@
         </is>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" t="inlineStr"/>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>boss.silent.relay_jump_seconds</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>14</v>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>阶段一·藏身:主脑每隔这么多游戏秒在中继节点之间转移一次(中继跳转)</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr"/>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>boss.silent.relay_warn_seconds</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>中继跳转:目标节点提前亮起的预警(游戏秒,≥0.8;FGR-FAC-008 ①)</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr"/>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>boss.silent.reveal_seconds</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>6</v>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>中继跳转途中目标节点被摧毁:跳转取消,主脑留在出发节点并现形这么久(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr"/>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>boss.silent.phase2_hp_fraction</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>阶段二·磁暴:主脑核心耐久降到这个比例以下进入全频静默预警</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr"/>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>boss.silent.silence_warn_seconds</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>5</v>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>阶段三·全频静默:开始前的情报预警倒计时(游戏秒,≥0.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr"/>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>boss.silent.silence_seconds</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>20</v>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>阶段三·全频静默:全场断链的时长(游戏秒;FG09 第 13 节初值 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr"/>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>boss.silent.exposed_damage_mult</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>撑过全频静默后主脑核心暴露:受到的伤害倍率</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr"/>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>boss.silent.retry_hint_seconds</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>8</v>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>首领战失败后“上次止步于第几阶段”通知的停留时间(真实秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr"/>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>hazard.emi_noise.coverage_mult</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>电磁噪声区内:信号覆盖源的有效半径 × 这个值(-30%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr"/>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>hazard.emi_noise.emitter_hp</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>120</v>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>噪声发射器的耐久(难度的敌人耐久倍率另乘)</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr"/>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>hazard.emi_noise.emitter_radius</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>噪声发射器的碰撞半径(格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr"/>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>silent.counter.core_fire_per_day</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>6</v>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>反制:上一个游戏日核心固件发动次数 ≥ 这个值时,静默的对策选“监听节点 + 寂听者”</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr"/>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>silent.counter.fuse_share</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>反制:存活机器里装引信与弹芯类固件的比例 ≥ 这个值时,对策选“磁暴棱柱”</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr"/>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>silent.counter.em_share</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>反制:存活机器里装电磁场控类固件的比例 ≥ 这个值时,对策选“干扰机”</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D753"/>
+  <dimension ref="A1:D764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12482,6 +12482,182 @@
         </is>
       </c>
     </row>
+    <row r="754">
+      <c r="A754" t="inlineStr"/>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>boss.foundry.phase3_hp_fraction</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>阶段二:主核心耐久降到这个比例时进入阶段三·对空形态(阶段二的伤害不会把它打到这条线以下)</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr"/>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>boss.foundry.antiair_seconds</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>15</v>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>阶段三·对空形态:所有炮口转向天空、核心暴露的时长(游戏秒;FG09 第 13 节初值 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr"/>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>boss.foundry.exposed_damage_mult</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>对空形态:核心暴露期间受到的伤害倍率(爆发窗口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr"/>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>boss.foundry.berserk_cooldown_mult</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>狂暴:主核心对地开火间隔 × 这个值(0.5 = 火力加倍)</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr"/>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>boss.foundry.arena_leave_seconds</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>20</v>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>场地边界(FGR-FAC-006):玩家的机器全部离开核心区超过这么久(游戏秒),主核心复位并恢复当前阶段耐久</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr"/>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>hazard.slag_heat.dissipation_mult</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>熔渣热区内:武器散热 × 这个值(-30%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr"/>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>foundry.counter.drone_share</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>反制:存活机器里主武器是无人机载体的比例 ≥ 这个值时,铸造的对策选“对空加强”(空爆炮台)</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr"/>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>foundry.counter.melee_share</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>反制:存活机器里主武器是格斗载体的比例 ≥ 这个值时,铸造的对策选“雷区”(布雷车)</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr"/>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>foundry.mine.life_seconds</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>90</v>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>一颗子母雷铺下后多久(游戏秒)没被触发就自行失效(雷区不会永远留在地上)</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr"/>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>foundry.mine.max_per_site</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>12</v>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>一个地点里同时存在的子母雷上限(各布雷车自己的上限另算;性能预算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr"/>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>drop.antiair.radius_battery</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>60</v>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>铸造前哨对空阵地(还有对空高炮存活)的防空覆盖半径(格)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D764"/>
+  <dimension ref="A1:D775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12658,6 +12658,182 @@
         </is>
       </c>
     </row>
+    <row r="765">
+      <c r="A765" t="inlineStr"/>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>pace.check_seconds</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>1</v>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>第一幕节奏台账的检查周期(游戏秒;只看步序号,暂停不走,倍速只是一帧多走几步)</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr"/>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>pace.deviation_warn</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>节奏统计:实际时刻偏离目标时刻超过这个比例时标黄(FGT-BAL-004 每个种子偏差 ≤ 25%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr"/>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>site.garrison.tries</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>48</v>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>每个驻军据点按子种子试探几次落点(要在窗口里、Demo 矩形外、可走的地形上、彼此不太近)</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr"/>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>site.garrison.ring_cells</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>驻军单位围着据点点位排开的间距(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr"/>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>site.garrison.scrap_per_tier</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>20</v>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>地点里一个驻军据点全灭时掉在原地的废料 = 等级 × 这个值(与星球据点同一口径 territory.loot.scrap_per_tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr"/>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>site.decoy.count</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>4</v>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>静默阵营的领地里按种子放的诱饵中继个数(地图上与真据点一样显示成未识别信号)</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr"/>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>site.decoy.radial_min</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>诱饵中继离领地中心的最小距离(领地半径的倍数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr"/>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>site.decoy.radial_max</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>诱饵中继离领地中心的最大距离(领地半径的倍数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr"/>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>site.contact.detect_cells</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>150</v>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>远征队成员这么近(格)内的静默信号(真据点 + 诱饵)被侦测到,出现在战略地图 / 小地图上(进存档,之后一直显示到被识破 / 摧毁)</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr"/>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>site.contact.check_seconds</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>2</v>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>信号侦测的检查周期(游戏秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr"/>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>env.silent.expedition_site_hours</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>2</v>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>派遣检查单估远征时长:往返路线(锚点路线 ÷ 行军速度)之外,在远征地点里停留多久(游戏小时;承接 DEBT-FG7ENV02-03)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D775"/>
+  <dimension ref="A1:D787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12834,6 +12834,198 @@
         </is>
       </c>
     </row>
+    <row r="776">
+      <c r="A776" t="inlineStr"/>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>hazard.acid_marsh.corrode_pct</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>酸沼:站在酸液里的地面单位每游戏秒损失最大耐久的比例(FG09 初值 2%;外圈酸沼带与领地里的酸沼同一规则,重叠只扣一次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr"/>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>hazard.acid_marsh.wet_mult</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>酸沼 / 酸液池 / 分裂液:单位湿润(身上挂湿润 / 站在冷却液或水的区域里)时的腐蚀倍率(冷却液冲淡)</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr"/>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>clarity.chill.slow_max</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>受寒满时的最大减速比例(受寒 0～1 线性:移动速度 × (1 − 本值 × 受寒))</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr"/>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>clarity.chill.decay_per_sec</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>受寒每游戏秒自然消退量(燃烧 +2 倍、积热过半 +1 倍)</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr"/>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>clarity.chill.freeze_seconds</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>受寒满 1 时冻结的游戏秒数(不能移动、不能开火;燃烧 / 高热解冻更快)</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr"/>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>clarity.chill.thaw_guard_seconds</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>解冻后这么久不再受寒(不会被永久冻住)</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr"/>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>clarity.pool.chill_tick_frac</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>液氮池:每个区域节拍给站在里面的单位加的受寒 = 喷淋命中受寒 × 本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr"/>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>clarity.pool.cap</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>192</v>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>一个战斗内核里喷淋池 + 油迹同时存在的上限(超出不生成并计数;性能预算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr"/>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>clarity.counter.fire_share</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>反制:玩家在用的固件里带燃烧标签的比例 ≥ 本值 → 澄净的对策选“液氮压制”(液氮泵车)</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr"/>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>clarity.counter.fuse_share</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>反制:引信类固件比例 ≥ 本值 → “蜂群饱和”(腐蚀蜂群)</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr"/>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>clarity.counter.em_share</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>反制:电磁类固件比例 ≥ 本值 → “绝缘涂层”(带 adapt_insulate 标签的单位当天挂不上电击类标签)</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr"/>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>clarity.counter.extra_units</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>2</v>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>反制:澄净据点 / 巡逻展开时在编成里追加几台对策单位(液氮泵车 / 腐蚀蜂群;绝缘涂层不加单位)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="C782" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D787"/>
+  <dimension ref="A1:D790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12870,15 +12870,15 @@
       <c r="A778" t="inlineStr"/>
       <c r="B778" t="inlineStr">
         <is>
-          <t>clarity.chill.slow_max</t>
+          <t>hazard.acid_marsh.coating_resist</t>
         </is>
       </c>
       <c r="C778" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>受寒满时的最大减速比例(受寒 0～1 线性:移动速度 × (1 − 本值 × 受寒))</t>
+          <t>防腐涂层:拿到蓝图后玩家机器的酸蚀抗性下限(0~1;酸沼 / 酸液池 / 分裂液的伤害 × (1 − 本值);炮塔与建筑不涂)</t>
         </is>
       </c>
     </row>
@@ -12886,15 +12886,15 @@
       <c r="A779" t="inlineStr"/>
       <c r="B779" t="inlineStr">
         <is>
-          <t>clarity.chill.decay_per_sec</t>
+          <t>hazard.acid_marsh.gate_confirm_seconds</t>
         </is>
       </c>
       <c r="C779" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>受寒每游戏秒自然消退量(燃烧 +2 倍、积热过半 +1 倍)</t>
+          <t>没有防腐涂层时命令机器走进酸沼:第一次拒绝并说明,这么多真实秒内再下一次 = 强行进入</t>
         </is>
       </c>
     </row>
@@ -12902,15 +12902,15 @@
       <c r="A780" t="inlineStr"/>
       <c r="B780" t="inlineStr">
         <is>
-          <t>clarity.chill.freeze_seconds</t>
+          <t>hazard.acid_marsh.pickup_margin</t>
         </is>
       </c>
       <c r="C780" t="n">
-        <v>2.5</v>
+        <v>16</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>受寒满 1 时冻结的游戏秒数(不能移动、不能开火;燃烧 / 高热解冻更快)</t>
+          <t>防腐涂层样品车的接取点:在酸沼带外缘再往家园方向这么多格(拿涂层之前不用先穿过酸沼)</t>
         </is>
       </c>
     </row>
@@ -12918,15 +12918,15 @@
       <c r="A781" t="inlineStr"/>
       <c r="B781" t="inlineStr">
         <is>
-          <t>clarity.chill.thaw_guard_seconds</t>
+          <t>clarity.chill.slow_max</t>
         </is>
       </c>
       <c r="C781" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>解冻后这么久不再受寒(不会被永久冻住)</t>
+          <t>受寒满时的最大减速比例(受寒 0～1 线性:移动速度 × (1 − 本值 × 受寒))</t>
         </is>
       </c>
     </row>
@@ -12934,15 +12934,15 @@
       <c r="A782" t="inlineStr"/>
       <c r="B782" t="inlineStr">
         <is>
-          <t>clarity.pool.chill_tick_frac</t>
+          <t>clarity.chill.decay_per_sec</t>
         </is>
       </c>
       <c r="C782" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>液氮池:每个区域节拍给站在里面的单位加的受寒 = 喷淋命中受寒 × 本值</t>
+          <t>受寒每游戏秒自然消退量(燃烧 +2 倍、积热过半 +1 倍)</t>
         </is>
       </c>
     </row>
@@ -12950,15 +12950,15 @@
       <c r="A783" t="inlineStr"/>
       <c r="B783" t="inlineStr">
         <is>
-          <t>clarity.pool.cap</t>
+          <t>clarity.chill.freeze_seconds</t>
         </is>
       </c>
       <c r="C783" t="n">
-        <v>192</v>
+        <v>2.5</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>一个战斗内核里喷淋池 + 油迹同时存在的上限(超出不生成并计数;性能预算)</t>
+          <t>受寒满 1 时冻结的游戏秒数(不能移动、不能开火;燃烧 / 高热解冻更快)</t>
         </is>
       </c>
     </row>
@@ -12966,15 +12966,15 @@
       <c r="A784" t="inlineStr"/>
       <c r="B784" t="inlineStr">
         <is>
-          <t>clarity.counter.fire_share</t>
+          <t>clarity.chill.thaw_guard_seconds</t>
         </is>
       </c>
       <c r="C784" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>反制:玩家在用的固件里带燃烧标签的比例 ≥ 本值 → 澄净的对策选“液氮压制”(液氮泵车)</t>
+          <t>解冻后这么久不再受寒(不会被永久冻住)</t>
         </is>
       </c>
     </row>
@@ -12982,15 +12982,15 @@
       <c r="A785" t="inlineStr"/>
       <c r="B785" t="inlineStr">
         <is>
-          <t>clarity.counter.fuse_share</t>
+          <t>clarity.pool.chill_tick_frac</t>
         </is>
       </c>
       <c r="C785" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>反制:引信类固件比例 ≥ 本值 → “蜂群饱和”(腐蚀蜂群)</t>
+          <t>液氮池:每个区域节拍给站在里面的单位加的受寒 = 喷淋命中受寒 × 本值</t>
         </is>
       </c>
     </row>
@@ -12998,15 +12998,15 @@
       <c r="A786" t="inlineStr"/>
       <c r="B786" t="inlineStr">
         <is>
-          <t>clarity.counter.em_share</t>
+          <t>clarity.pool.cap</t>
         </is>
       </c>
       <c r="C786" t="n">
-        <v>0.3</v>
+        <v>192</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>反制:电磁类固件比例 ≥ 本值 → “绝缘涂层”(带 adapt_insulate 标签的单位当天挂不上电击类标签)</t>
+          <t>一个战斗内核里喷淋池 + 油迹同时存在的上限(超出不生成并计数;性能预算)</t>
         </is>
       </c>
     </row>
@@ -13014,13 +13014,61 @@
       <c r="A787" t="inlineStr"/>
       <c r="B787" t="inlineStr">
         <is>
+          <t>clarity.counter.fire_share</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>反制:玩家在用的固件里带燃烧标签的比例 ≥ 本值 → 澄净的对策选“液氮压制”(液氮泵车)</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr"/>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>clarity.counter.fuse_share</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>反制:引信类固件比例 ≥ 本值 → “蜂群饱和”(腐蚀蜂群)</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr"/>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>clarity.counter.em_share</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>反制:电磁类固件比例 ≥ 本值 → “绝缘涂层”(带 adapt_insulate 标签的单位当天挂不上电击类标签)</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr"/>
+      <c r="B790" t="inlineStr">
+        <is>
           <t>clarity.counter.extra_units</t>
         </is>
       </c>
-      <c r="C787" t="n">
+      <c r="C790" t="n">
         <v>2</v>
       </c>
-      <c r="D787" t="inlineStr">
+      <c r="D790" t="inlineStr">
         <is>
           <t>反制:澄净据点 / 巡逻展开时在编成里追加几台对策单位(液氮泵车 / 腐蚀蜂群;绝缘涂层不加单位)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12918,15 +12918,15 @@
       <c r="A781" t="inlineStr"/>
       <c r="B781" t="inlineStr">
         <is>
-          <t>clarity.chill.slow_max</t>
+          <t>boss.clarity.arena_radius</t>
         </is>
       </c>
       <c r="C781" t="n">
-        <v>0.6</v>
+        <v>40</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>受寒满时的最大减速比例(受寒 0～1 线性:移动速度 × (1 − 本值 × 受寒))</t>
+          <t>洗礼塔场地半径(格,以湖心平台锚点为圆心):有己方机器进来就开战;全部离开超过 arena_leave_seconds 首领复位</t>
         </is>
       </c>
     </row>
@@ -12934,15 +12934,15 @@
       <c r="A782" t="inlineStr"/>
       <c r="B782" t="inlineStr">
         <is>
-          <t>clarity.chill.decay_per_sec</t>
+          <t>boss.clarity.arena_leave_seconds</t>
         </is>
       </c>
       <c r="C782" t="n">
-        <v>0.25</v>
+        <v>20</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>受寒每游戏秒自然消退量(燃烧 +2 倍、积热过半 +1 倍)</t>
+          <t>首领战中己方机器全部离开场地(或全灭)这么多游戏秒 → 洗礼塔复位到开战前(FGR-FAC-006 初值 20 秒)</t>
         </is>
       </c>
     </row>
@@ -12950,15 +12950,15 @@
       <c r="A783" t="inlineStr"/>
       <c r="B783" t="inlineStr">
         <is>
-          <t>clarity.chill.freeze_seconds</t>
+          <t>boss.clarity.pump_ring</t>
         </is>
       </c>
       <c r="C783" t="n">
-        <v>2.5</v>
+        <v>18</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>受寒满 1 时冻结的游戏秒数(不能移动、不能开火;燃烧 / 高热解冻更快)</t>
+          <t>4 座泵站离反应塔的距离(格)</t>
         </is>
       </c>
     </row>
@@ -12966,15 +12966,15 @@
       <c r="A784" t="inlineStr"/>
       <c r="B784" t="inlineStr">
         <is>
-          <t>clarity.chill.thaw_guard_seconds</t>
+          <t>boss.clarity.fill_seconds</t>
         </is>
       </c>
       <c r="C784" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>解冻后这么久不再受寒(不会被永久冻住)</t>
+          <t>灌注节拍:每隔这么多游戏秒,轮到的那座存活泵站往场地里灌一片它的流体</t>
         </is>
       </c>
     </row>
@@ -12982,15 +12982,15 @@
       <c r="A785" t="inlineStr"/>
       <c r="B785" t="inlineStr">
         <is>
-          <t>clarity.pool.chill_tick_frac</t>
+          <t>boss.clarity.fill_warn_seconds</t>
         </is>
       </c>
       <c r="C785" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>液氮池:每个区域节拍给站在里面的单位加的受寒 = 喷淋命中受寒 × 本值</t>
+          <t>灌注前的预警(游戏秒;落点先亮起,≥ 0.8)</t>
         </is>
       </c>
     </row>
@@ -12998,15 +12998,15 @@
       <c r="A786" t="inlineStr"/>
       <c r="B786" t="inlineStr">
         <is>
-          <t>clarity.pool.cap</t>
+          <t>boss.clarity.fill_radius</t>
         </is>
       </c>
       <c r="C786" t="n">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>一个战斗内核里喷淋池 + 油迹同时存在的上限(超出不生成并计数;性能预算)</t>
+          <t>一片流体的半径(格)</t>
         </is>
       </c>
     </row>
@@ -13014,15 +13014,15 @@
       <c r="A787" t="inlineStr"/>
       <c r="B787" t="inlineStr">
         <is>
-          <t>clarity.counter.fire_share</t>
+          <t>boss.clarity.fill_life_seconds</t>
         </is>
       </c>
       <c r="C787" t="n">
-        <v>0.3</v>
+        <v>40</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>反制:玩家在用的固件里带燃烧标签的比例 ≥ 本值 → 澄净的对策选“液氮压制”(液氮泵车)</t>
+          <t>一片流体存留多少游戏秒</t>
         </is>
       </c>
     </row>
@@ -13030,15 +13030,15 @@
       <c r="A788" t="inlineStr"/>
       <c r="B788" t="inlineStr">
         <is>
-          <t>clarity.counter.fuse_share</t>
+          <t>boss.clarity.fill_cap</t>
         </is>
       </c>
       <c r="C788" t="n">
-        <v>0.4</v>
+        <v>8</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>反制:引信类固件比例 ≥ 本值 → “蜂群饱和”(腐蚀蜂群)</t>
+          <t>场上同时最多几片流体(超出时最老的先干涸)</t>
         </is>
       </c>
     </row>
@@ -13046,15 +13046,15 @@
       <c r="A789" t="inlineStr"/>
       <c r="B789" t="inlineStr">
         <is>
-          <t>clarity.counter.em_share</t>
+          <t>boss.clarity.react_seconds</t>
         </is>
       </c>
       <c r="C789" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>反制:电磁类固件比例 ≥ 本值 → “绝缘涂层”(带 adapt_insulate 标签的单位当天挂不上电击类标签)</t>
+          <t>阶段二起:每隔这么多游戏秒,反应塔挑一片流体主动引发反应(油 / 酸 → 点燃,水 → 通电)</t>
         </is>
       </c>
     </row>
@@ -13062,13 +13062,333 @@
       <c r="A790" t="inlineStr"/>
       <c r="B790" t="inlineStr">
         <is>
+          <t>boss.clarity.react_warn_seconds</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>主动反应前的预警(游戏秒,≥ 0.8;那片流体闪烁 + 声音 + 字幕)</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr"/>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>boss.clarity.react_zone_seconds</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>2</v>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>引发反应时盖在流体上的火 / 电区域存留多少游戏秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr"/>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>boss.clarity.react_dps</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>8</v>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>引发反应的火 / 电区域每秒伤害(再加各自的状态与反应)</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr"/>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>boss.clarity.phase2_hp_fraction</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>反应塔耐久降到这一比例 → 阶段二·反应</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr"/>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>boss.clarity.phase3_hp_fraction</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>反应塔耐久降到这一比例 → 阶段三·泄压</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr"/>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>boss.clarity.vent_cycle_seconds</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>16</v>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>阶段三:一次泄压循环(封闭 + 预警 + 泄压)多少游戏秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr"/>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>boss.clarity.vent_seconds</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>6</v>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>阶段三:每次泄压(核心暴露)持续多少游戏秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr"/>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>boss.clarity.vent_warn_seconds</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>1</v>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>泄压前的预警(游戏秒,≥ 0.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr"/>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>boss.clarity.vent_damage_mult</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>2</v>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>泄压时核心暴露:受到的伤害倍率(此时可以被冻结)</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr"/>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>boss.clarity.sealed_damage_mult</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>阶段三封闭时:受到的伤害倍率(不能被冻结)</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr"/>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>boss.clarity.wave_count</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>4</v>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>阶段二开始时召来几台澄净单位(从澄净的突袭编成里按顺序取,不按 ID 写死)</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr"/>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>clarity.chill.slow_max</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>受寒满时的最大减速比例(受寒 0～1 线性:移动速度 × (1 − 本值 × 受寒))</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr"/>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>clarity.chill.decay_per_sec</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>受寒每游戏秒自然消退量(燃烧 +2 倍、积热过半 +1 倍)</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr"/>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>clarity.chill.freeze_seconds</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>受寒满 1 时冻结的游戏秒数(不能移动、不能开火;燃烧 / 高热解冻更快)</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr"/>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>clarity.chill.thaw_guard_seconds</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>解冻后这么久不再受寒(不会被永久冻住)</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr"/>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>clarity.pool.chill_tick_frac</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>液氮池:每个区域节拍给站在里面的单位加的受寒 = 喷淋命中受寒 × 本值</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr"/>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>clarity.pool.cap</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>192</v>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>一个战斗内核里喷淋池 + 油迹同时存在的上限(超出不生成并计数;性能预算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr"/>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>clarity.counter.fire_share</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>反制:玩家在用的固件里带燃烧标签的比例 ≥ 本值 → 澄净的对策选“液氮压制”(液氮泵车)</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr"/>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>clarity.counter.fuse_share</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>反制:引信类固件比例 ≥ 本值 → “蜂群饱和”(腐蚀蜂群)</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr"/>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>clarity.counter.em_share</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>反制:电磁类固件比例 ≥ 本值 → “绝缘涂层”(带 adapt_insulate 标签的单位当天挂不上电击类标签)</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr"/>
+      <c r="B810" t="inlineStr">
+        <is>
           <t>clarity.counter.extra_units</t>
         </is>
       </c>
-      <c r="C790" t="n">
+      <c r="C810" t="n">
         <v>2</v>
       </c>
-      <c r="D790" t="inlineStr">
+      <c r="D810" t="inlineStr">
         <is>
           <t>反制:澄净据点 / 巡逻展开时在编成里追加几台对策单位(液氮泵车 / 腐蚀蜂群;绝缘涂层不加单位)</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#HomeTuning-家园与格网调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D810"/>
+  <dimension ref="A1:D815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7574,15 +7574,15 @@
       <c r="A447" t="inlineStr"/>
       <c r="B447" t="inlineStr">
         <is>
-          <t>siege.perf.units</t>
+          <t>siege.clarity.other_shift_m</t>
         </is>
       </c>
       <c r="C447" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>性能验收:同时攻城的突袭单位数(FG06 第 7 节 200)</t>
+          <t>澄净突袭在场:净化塔对三种职能都是主目标(偏好 0),其它类别的偏好整体加这么多(米):净化塔比别的目标远不到这么多,就先去打净化塔</t>
         </is>
       </c>
     </row>
@@ -7590,15 +7590,15 @@
       <c r="A448" t="inlineStr"/>
       <c r="B448" t="inlineStr">
         <is>
-          <t>siege.perf.field_update_ms</t>
+          <t>siege.perf.units</t>
         </is>
       </c>
       <c r="C448" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>性能验收:屏障变化时流场增量更新单次耗时上限(毫秒,FG06 第 7 节)</t>
+          <t>性能验收:同时攻城的突袭单位数(FG06 第 7 节 200)</t>
         </is>
       </c>
     </row>
@@ -7606,15 +7606,15 @@
       <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr">
         <is>
-          <t>siege.perf.step_ms</t>
+          <t>siege.perf.field_update_ms</t>
         </is>
       </c>
       <c r="C449" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>性能验收:200 单位攻城时内核单步平均耗时上限(毫秒;120 帧预算 8.33 ms 的四分之一)</t>
+          <t>性能验收:屏障变化时流场增量更新单次耗时上限(毫秒,FG06 第 7 节)</t>
         </is>
       </c>
     </row>
@@ -7622,15 +7622,15 @@
       <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
-          <t>logistics.pipe.hp_t1</t>
+          <t>siege.perf.step_ms</t>
         </is>
       </c>
       <c r="C450" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>管线 T1 一格的最大耐久(管线 / 泵 / 阀门 / 地下管线口按等级)</t>
+          <t>性能验收:200 单位攻城时内核单步平均耗时上限(毫秒;120 帧预算 8.33 ms 的四分之一)</t>
         </is>
       </c>
     </row>
@@ -7638,15 +7638,15 @@
       <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
-          <t>logistics.pipe.hp_t2</t>
+          <t>logistics.pipe.hp_t1</t>
         </is>
       </c>
       <c r="C451" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>管线 T2 一格的最大耐久</t>
+          <t>管线 T1 一格的最大耐久(管线 / 泵 / 阀门 / 地下管线口按等级)</t>
         </is>
       </c>
     </row>
@@ -7654,15 +7654,15 @@
       <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
-          <t>logistics.pipe.hp_tank</t>
+          <t>logistics.pipe.hp_t2</t>
         </is>
       </c>
       <c r="C452" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>储罐一格的最大耐久</t>
+          <t>管线 T2 一格的最大耐久</t>
         </is>
       </c>
     </row>
@@ -7670,15 +7670,15 @@
       <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
-          <t>logistics.pipe.repair_kits</t>
+          <t>logistics.pipe.hp_tank</t>
         </is>
       </c>
       <c r="C453" t="n">
-        <v>0.25</v>
+        <v>160</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>维修无人机修满一格管线要的维修件(与传送带同口径)</t>
+          <t>储罐一格的最大耐久</t>
         </is>
       </c>
     </row>
@@ -7686,15 +7686,15 @@
       <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
-          <t>raid.auto_pause_first_raids</t>
+          <t>logistics.pipe.repair_kits</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>FGR-DEF-042:突袭到达时自动暂停的默认值只对本存档前几次突袭(波)开启;玩家在通知设置里改过的按玩家的</t>
+          <t>维修无人机修满一格管线要的维修件(与传送带同口径)</t>
         </is>
       </c>
     </row>
@@ -7702,15 +7702,15 @@
       <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
-          <t>raid.spectate.default_speed</t>
+          <t>raid.auto_pause_first_raids</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>观战:点“观战”时切到的速度(2 或 3;复用统一时钟的倍速档)</t>
+          <t>FGR-DEF-042:突袭到达时自动暂停的默认值只对本存档前几次突袭(波)开启;玩家在通知设置里改过的按玩家的</t>
         </is>
       </c>
     </row>
@@ -7718,15 +7718,15 @@
       <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
-          <t>raid.spectate.follow_seconds</t>
+          <t>raid.spectate.default_speed</t>
         </is>
       </c>
       <c r="C456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>观战:镜头每隔这么久(真实秒)重新看一次战斗重心</t>
+          <t>观战:点“观战”时切到的速度(2 或 3;复用统一时钟的倍速档)</t>
         </is>
       </c>
     </row>
@@ -7734,15 +7734,15 @@
       <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
-          <t>raid.spectate.follow_min_cells</t>
+          <t>raid.spectate.follow_seconds</t>
         </is>
       </c>
       <c r="C457" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>观战:战斗重心离镜头焦点超过这么远(格)才飞过去(免得镜头一直抖)</t>
+          <t>观战:镜头每隔这么久(真实秒)重新看一次战斗重心</t>
         </is>
       </c>
     </row>
@@ -7750,15 +7750,15 @@
       <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
-          <t>raid.spectate.manual_cells</t>
+          <t>raid.spectate.follow_min_cells</t>
         </is>
       </c>
       <c r="C458" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>观战:玩家自己把镜头移开超过这么远(格)就暂停跟随(点“跟随战斗”恢复)</t>
+          <t>观战:战斗重心离镜头焦点超过这么远(格)才飞过去(免得镜头一直抖)</t>
         </is>
       </c>
     </row>
@@ -7766,15 +7766,15 @@
       <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
-          <t>raid.music.volume</t>
+          <t>raid.spectate.manual_cells</t>
         </is>
       </c>
       <c r="C459" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>预警 / 突袭音乐的音量(乘在音乐音量设置上;占位音乐,美术批次替换)</t>
+          <t>观战:玩家自己把镜头移开超过这么远(格)就暂停跟随(点“跟随战斗”恢复)</t>
         </is>
       </c>
     </row>
@@ -7782,15 +7782,15 @@
       <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
-          <t>raid.hud.refresh_seconds</t>
+          <t>raid.music.volume</t>
         </is>
       </c>
       <c r="C460" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>突袭 HUD 刷新间隔(真实秒;键没变不重建)</t>
+          <t>预警 / 突袭音乐的音量(乘在音乐音量设置上;占位音乐,美术批次替换)</t>
         </is>
       </c>
     </row>
@@ -7798,15 +7798,15 @@
       <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
-          <t>raid.hud.perf_ms</t>
+          <t>raid.hud.refresh_seconds</t>
         </is>
       </c>
       <c r="C461" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>性能验收:突袭 HUD 一次数据刷新(各波剩余敌人 / 文字)的耗时上限(毫秒)</t>
+          <t>突袭 HUD 刷新间隔(真实秒;键没变不重建)</t>
         </is>
       </c>
     </row>
@@ -7814,15 +7814,15 @@
       <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
-          <t>defov.margin_cells</t>
+          <t>raid.hud.perf_ms</t>
         </is>
       </c>
       <c r="C462" t="n">
-        <v>24</v>
+        <v>0.2</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>防御总览:热力图范围 = 家园己方建筑外接矩形向外放宽的格数</t>
+          <t>性能验收:突袭 HUD 一次数据刷新(各波剩余敌人 / 文字)的耗时上限(毫秒)</t>
         </is>
       </c>
     </row>
@@ -7830,15 +7830,15 @@
       <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
-          <t>defov.max_cells</t>
+          <t>defov.margin_cells</t>
         </is>
       </c>
       <c r="C463" t="n">
-        <v>256</v>
+        <v>24</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>防御总览:热力图最大边长(格;超出时以归还核心为中心截取)</t>
+          <t>防御总览:热力图范围 = 家园己方建筑外接矩形向外放宽的格数</t>
         </is>
       </c>
     </row>
@@ -7846,15 +7846,15 @@
       <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
-          <t>defov.weak_min_cells</t>
+          <t>defov.max_cells</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>4</v>
+        <v>256</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>防御总览:连续这么多格(沿路线 / 外围)没有火力覆盖才算一处薄弱点</t>
+          <t>防御总览:热力图最大边长(格;超出时以归还核心为中心截取)</t>
         </is>
       </c>
     </row>
@@ -7862,15 +7862,15 @@
       <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
-          <t>defov.weak_max</t>
+          <t>defov.weak_min_cells</t>
         </is>
       </c>
       <c r="C465" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>防御总览:最多列出几处薄弱点(按离核心由近到远)</t>
+          <t>防御总览:连续这么多格(沿路线 / 外围)没有火力覆盖才算一处薄弱点</t>
         </is>
       </c>
     </row>
@@ -7878,15 +7878,15 @@
       <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
-          <t>defov.ring_extra_cells</t>
+          <t>defov.weak_max</t>
         </is>
       </c>
       <c r="C466" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>防御总览:没有预测路线时,外围检查圈 = 建筑外接矩形半对角线 + 这么多格</t>
+          <t>防御总览:最多列出几处薄弱点(按离核心由近到远)</t>
         </is>
       </c>
     </row>
@@ -7894,15 +7894,15 @@
       <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
-          <t>defov.ring_samples</t>
+          <t>defov.ring_extra_cells</t>
         </is>
       </c>
       <c r="C467" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>防御总览:外围检查圈的采样点数</t>
+          <t>防御总览:没有预测路线时,外围检查圈 = 建筑外接矩形半对角线 + 这么多格</t>
         </is>
       </c>
     </row>
@@ -7910,15 +7910,15 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
-          <t>defov.refresh_seconds</t>
+          <t>defov.ring_samples</t>
         </is>
       </c>
       <c r="C468" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>防御总览:面板开着时每隔这么久(真